--- a/基本設計書.xlsx
+++ b/基本設計書.xlsx
@@ -8,37 +8,40 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\7_Programing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{375CD5B2-994E-47E2-847F-361E8F5DD493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23AE07A2-4AB8-423E-8AE6-2F5622417071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7470" yWindow="0" windowWidth="11820" windowHeight="10170" tabRatio="774" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="774" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="IO関連図　原本・見本" sheetId="27" r:id="rId1"/>
-    <sheet name="画面レイアウト　原本・見本" sheetId="28" r:id="rId2"/>
-    <sheet name="表紙" sheetId="26" r:id="rId3"/>
-    <sheet name="IO関連図（アカウント検索・一覧）" sheetId="13" r:id="rId4"/>
-    <sheet name="IO関連図 (2)" sheetId="29" r:id="rId5"/>
-    <sheet name="画面レイアウト" sheetId="15" r:id="rId6"/>
+    <sheet name="IO関連図（アカウント検索・一覧） (2)" sheetId="31" r:id="rId1"/>
+    <sheet name="IO関連図　原本・見本" sheetId="27" r:id="rId2"/>
+    <sheet name="画面レイアウト　原本・見本" sheetId="28" r:id="rId3"/>
+    <sheet name="表紙" sheetId="26" r:id="rId4"/>
+    <sheet name="IO関連図（アカウント登録）" sheetId="30" r:id="rId5"/>
+    <sheet name="IO関連図（アカウント検索・一覧）" sheetId="13" r:id="rId6"/>
+    <sheet name="画面レイアウト" sheetId="15" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'IO関連図 (2)'!$A$1:$AG$42</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'IO関連図　原本・見本'!$A$1:$AG$42</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'IO関連図（アカウント検索・一覧）'!$A$1:$AG$42</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">画面レイアウト!$A$1:$AG$42</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'画面レイアウト　原本・見本'!$A$1:$AG$42</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">表紙!$A$1:$AF$43</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">'IO関連図 (2)'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'IO関連図　原本・見本'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'IO関連図（アカウント検索・一覧）'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">画面レイアウト!$1:$3</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'画面レイアウト　原本・見本'!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'IO関連図　原本・見本'!$A$1:$AG$42</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'IO関連図（アカウント検索・一覧）'!$A$1:$AG$42</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'IO関連図（アカウント検索・一覧） (2)'!$A$1:$AG$42</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'IO関連図（アカウント登録）'!$A$1:$AG$42</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">画面レイアウト!$A$1:$AG$42</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'画面レイアウト　原本・見本'!$A$1:$AG$42</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">表紙!$A$1:$AF$43</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'IO関連図　原本・見本'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'IO関連図（アカウント検索・一覧）'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'IO関連図（アカウント検索・一覧） (2)'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'IO関連図（アカウント登録）'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">画面レイアウト!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'画面レイアウト　原本・見本'!$1:$3</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="58">
   <si>
     <t>システム名</t>
     <rPh sb="4" eb="5">
@@ -440,6 +443,13 @@
     </rPh>
     <phoneticPr fontId="4"/>
   </si>
+  <si>
+    <t>アカウント登録</t>
+    <rPh sb="5" eb="7">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
 </sst>
 </file>
 
@@ -817,6 +827,74 @@
     </xf>
     <xf numFmtId="14" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="4" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="4" applyFill="1" applyBorder="1"/>
@@ -844,74 +922,6 @@
     <xf numFmtId="14" fontId="5" fillId="2" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -935,6 +945,849 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>31750</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="computr1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E132F841-67B3-42F7-876D-8EFA69801504}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noEditPoints="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1619250" y="2705100"/>
+          <a:ext cx="698500" cy="762000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst>
+            <a:gd name="T0" fmla="*/ 19535 w 21600"/>
+            <a:gd name="T1" fmla="*/ 0 h 21600"/>
+            <a:gd name="T2" fmla="*/ 10800 w 21600"/>
+            <a:gd name="T3" fmla="*/ 0 h 21600"/>
+            <a:gd name="T4" fmla="*/ 2065 w 21600"/>
+            <a:gd name="T5" fmla="*/ 0 h 21600"/>
+            <a:gd name="T6" fmla="*/ 0 w 21600"/>
+            <a:gd name="T7" fmla="*/ 15388 h 21600"/>
+            <a:gd name="T8" fmla="*/ 0 w 21600"/>
+            <a:gd name="T9" fmla="*/ 21600 h 21600"/>
+            <a:gd name="T10" fmla="*/ 10800 w 21600"/>
+            <a:gd name="T11" fmla="*/ 21600 h 21600"/>
+            <a:gd name="T12" fmla="*/ 21600 w 21600"/>
+            <a:gd name="T13" fmla="*/ 21600 h 21600"/>
+            <a:gd name="T14" fmla="*/ 21600 w 21600"/>
+            <a:gd name="T15" fmla="*/ 15388 h 21600"/>
+            <a:gd name="T16" fmla="*/ 19535 w 21600"/>
+            <a:gd name="T17" fmla="*/ 13553 h 21600"/>
+            <a:gd name="T18" fmla="*/ 2065 w 21600"/>
+            <a:gd name="T19" fmla="*/ 13553 h 21600"/>
+            <a:gd name="T20" fmla="*/ 2065 w 21600"/>
+            <a:gd name="T21" fmla="*/ 6776 h 21600"/>
+            <a:gd name="T22" fmla="*/ 19535 w 21600"/>
+            <a:gd name="T23" fmla="*/ 6776 h 21600"/>
+            <a:gd name="T24" fmla="*/ 0 w 21600"/>
+            <a:gd name="T25" fmla="*/ 18494 h 21600"/>
+            <a:gd name="T26" fmla="*/ 21600 w 21600"/>
+            <a:gd name="T27" fmla="*/ 18494 h 21600"/>
+            <a:gd name="T28" fmla="*/ 4923 w 21600"/>
+            <a:gd name="T29" fmla="*/ 2541 h 21600"/>
+            <a:gd name="T30" fmla="*/ 16756 w 21600"/>
+            <a:gd name="T31" fmla="*/ 11153 h 21600"/>
+          </a:gdLst>
+          <a:ahLst/>
+          <a:cxnLst>
+            <a:cxn ang="0">
+              <a:pos x="T0" y="T1"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="T2" y="T3"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="T4" y="T5"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="T6" y="T7"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="T8" y="T9"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="T10" y="T11"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="T12" y="T13"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="T14" y="T15"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="T16" y="T17"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="T18" y="T19"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="T20" y="T21"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="T22" y="T23"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="T24" y="T25"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="T26" y="T27"/>
+            </a:cxn>
+          </a:cxnLst>
+          <a:rect l="T28" t="T29" r="T30" b="T31"/>
+          <a:pathLst>
+            <a:path w="21600" h="21600" extrusionOk="0">
+              <a:moveTo>
+                <a:pt x="16994" y="15388"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="16994" y="13553"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="19535" y="13553"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="19535" y="10729"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="19535" y="6776"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="19535" y="0"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="10800" y="0"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="2065" y="0"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="2065" y="6776"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="2065" y="10729"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="2065" y="13553"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="4606" y="13553"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="4606" y="15388"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="0" y="15388"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="0" y="21600"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="10800" y="21600"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="21600" y="21600"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="21600" y="15388"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="16994" y="15388"/>
+              </a:lnTo>
+              <a:close/>
+            </a:path>
+            <a:path w="21600" h="21600" extrusionOk="0">
+              <a:moveTo>
+                <a:pt x="4606" y="15388"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="4606" y="13553"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="16994" y="13553"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="16994" y="15388"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="4606" y="15388"/>
+              </a:lnTo>
+            </a:path>
+            <a:path w="21600" h="21600" extrusionOk="0">
+              <a:moveTo>
+                <a:pt x="4606" y="11294"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="4606" y="2259"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="16994" y="2259"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="16994" y="11294"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="4606" y="11294"/>
+              </a:lnTo>
+              <a:moveTo>
+                <a:pt x="13976" y="17082"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="13976" y="16376"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="20171" y="16376"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="20171" y="17082"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="13976" y="17082"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFCC"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+        <a:effectLst/>
+        <a:extLst>
+          <a:ext uri="{AF507438-7753-43E0-B8FC-AC1667EBCBE1}">
+            <a14:hiddenEffects xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:effectLst>
+                <a:outerShdw dist="107763" dir="13500000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="808080"/>
+                </a:outerShdw>
+              </a:effectLst>
+            </a14:hiddenEffects>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>165652</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>55217</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>280227</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>138043</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="Rectangle 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{804D2E21-CBA4-4CAC-B081-72F8C2065C63}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3308902" y="2760317"/>
+          <a:ext cx="1829075" cy="717826"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="22860" rIns="36576" bIns="0" anchor="ctr" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1200"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:latin typeface="ＭＳ Ｐゴシック"/>
+            <a:ea typeface="ＭＳ Ｐゴシック"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>110435</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>64420</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>265965</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>46015</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="Rectangle 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F01455F9-EAC2-4CB9-979B-2F26A7AF1D4A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="2682185" y="705770"/>
+          <a:ext cx="3013030" cy="1410345"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="22860" rIns="0" bIns="0" anchor="t" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1300"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:latin typeface="ＭＳ Ｐゴシック"/>
+            <a:ea typeface="ＭＳ Ｐゴシック"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1200"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:latin typeface="ＭＳ Ｐゴシック"/>
+            <a:ea typeface="ＭＳ Ｐゴシック"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>184150</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>184150</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="Line 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{29C8587A-1CB2-4686-9B7F-637716C0FDFC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeShapeType="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4184650" y="2133600"/>
+          <a:ext cx="0" cy="565150"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd type="triangle" w="med" len="med"/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:noFill/>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>44450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>260350</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>44450</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="Line 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5A0D3340-58B1-47AE-8743-6C20CA3F5211}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeShapeType="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm flipH="1">
+          <a:off x="2400300" y="3067050"/>
+          <a:ext cx="717550" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd type="triangle" w="med" len="med"/>
+          <a:tailEnd/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:noFill/>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>28253</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>64421</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>136203</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>146326</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="Rectangle 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F57644DB-B6A8-48C9-8721-F568E83842C2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="6314753" y="2134521"/>
+          <a:ext cx="2965450" cy="1828155"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="22860" rIns="0" bIns="0" anchor="t" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1300"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:latin typeface="ＭＳ Ｐゴシック"/>
+            <a:ea typeface="ＭＳ Ｐゴシック"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1200"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:latin typeface="ＭＳ Ｐゴシック"/>
+            <a:ea typeface="ＭＳ Ｐゴシック"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>146050</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="Line 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B53B0DAD-C822-4F21-B5D1-B8B193A1A536}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeShapeType="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5448300" y="3060700"/>
+          <a:ext cx="698500" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd type="triangle" w="med" len="med"/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:noFill/>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="Line 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5590FD19-BE9E-4C12-87F8-F69CF95283B5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeShapeType="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4171950" y="3524250"/>
+          <a:ext cx="0" cy="349250"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd type="triangle" w="med" len="med"/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:noFill/>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>55217</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="AutoShape 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3063CF07-D486-407C-88DF-DAFE8BCD8DFF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4292600" y="3892550"/>
+          <a:ext cx="850900" cy="772767"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartMagneticDisk">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="22860" rIns="36576" bIns="0" anchor="t" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1200"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:latin typeface="ＭＳ Ｐゴシック"/>
+            <a:ea typeface="ＭＳ Ｐゴシック"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>165100</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>127000</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>73623</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="AutoShape 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{641A24A5-FF5A-483E-949F-E706BC1C2448}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3308350" y="3975100"/>
+          <a:ext cx="819150" cy="708623"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartDocument">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="22860" rIns="36576" bIns="0" anchor="t" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1200"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:latin typeface="ＭＳ Ｐゴシック"/>
+            <a:ea typeface="ＭＳ Ｐゴシック"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -2005,7 +2858,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -2214,7 +3067,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -2369,7 +3222,1375 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>31750</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="computr1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7AD36EB-D6F0-4988-BE1F-EDF75BC4F19F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noEditPoints="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1619250" y="2705100"/>
+          <a:ext cx="698500" cy="762000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst>
+            <a:gd name="T0" fmla="*/ 19535 w 21600"/>
+            <a:gd name="T1" fmla="*/ 0 h 21600"/>
+            <a:gd name="T2" fmla="*/ 10800 w 21600"/>
+            <a:gd name="T3" fmla="*/ 0 h 21600"/>
+            <a:gd name="T4" fmla="*/ 2065 w 21600"/>
+            <a:gd name="T5" fmla="*/ 0 h 21600"/>
+            <a:gd name="T6" fmla="*/ 0 w 21600"/>
+            <a:gd name="T7" fmla="*/ 15388 h 21600"/>
+            <a:gd name="T8" fmla="*/ 0 w 21600"/>
+            <a:gd name="T9" fmla="*/ 21600 h 21600"/>
+            <a:gd name="T10" fmla="*/ 10800 w 21600"/>
+            <a:gd name="T11" fmla="*/ 21600 h 21600"/>
+            <a:gd name="T12" fmla="*/ 21600 w 21600"/>
+            <a:gd name="T13" fmla="*/ 21600 h 21600"/>
+            <a:gd name="T14" fmla="*/ 21600 w 21600"/>
+            <a:gd name="T15" fmla="*/ 15388 h 21600"/>
+            <a:gd name="T16" fmla="*/ 19535 w 21600"/>
+            <a:gd name="T17" fmla="*/ 13553 h 21600"/>
+            <a:gd name="T18" fmla="*/ 2065 w 21600"/>
+            <a:gd name="T19" fmla="*/ 13553 h 21600"/>
+            <a:gd name="T20" fmla="*/ 2065 w 21600"/>
+            <a:gd name="T21" fmla="*/ 6776 h 21600"/>
+            <a:gd name="T22" fmla="*/ 19535 w 21600"/>
+            <a:gd name="T23" fmla="*/ 6776 h 21600"/>
+            <a:gd name="T24" fmla="*/ 0 w 21600"/>
+            <a:gd name="T25" fmla="*/ 18494 h 21600"/>
+            <a:gd name="T26" fmla="*/ 21600 w 21600"/>
+            <a:gd name="T27" fmla="*/ 18494 h 21600"/>
+            <a:gd name="T28" fmla="*/ 4923 w 21600"/>
+            <a:gd name="T29" fmla="*/ 2541 h 21600"/>
+            <a:gd name="T30" fmla="*/ 16756 w 21600"/>
+            <a:gd name="T31" fmla="*/ 11153 h 21600"/>
+          </a:gdLst>
+          <a:ahLst/>
+          <a:cxnLst>
+            <a:cxn ang="0">
+              <a:pos x="T0" y="T1"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="T2" y="T3"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="T4" y="T5"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="T6" y="T7"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="T8" y="T9"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="T10" y="T11"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="T12" y="T13"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="T14" y="T15"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="T16" y="T17"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="T18" y="T19"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="T20" y="T21"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="T22" y="T23"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="T24" y="T25"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="T26" y="T27"/>
+            </a:cxn>
+          </a:cxnLst>
+          <a:rect l="T28" t="T29" r="T30" b="T31"/>
+          <a:pathLst>
+            <a:path w="21600" h="21600" extrusionOk="0">
+              <a:moveTo>
+                <a:pt x="16994" y="15388"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="16994" y="13553"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="19535" y="13553"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="19535" y="10729"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="19535" y="6776"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="19535" y="0"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="10800" y="0"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="2065" y="0"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="2065" y="6776"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="2065" y="10729"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="2065" y="13553"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="4606" y="13553"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="4606" y="15388"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="0" y="15388"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="0" y="21600"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="10800" y="21600"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="21600" y="21600"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="21600" y="15388"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="16994" y="15388"/>
+              </a:lnTo>
+              <a:close/>
+            </a:path>
+            <a:path w="21600" h="21600" extrusionOk="0">
+              <a:moveTo>
+                <a:pt x="4606" y="15388"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="4606" y="13553"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="16994" y="13553"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="16994" y="15388"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="4606" y="15388"/>
+              </a:lnTo>
+            </a:path>
+            <a:path w="21600" h="21600" extrusionOk="0">
+              <a:moveTo>
+                <a:pt x="4606" y="11294"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="4606" y="2259"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="16994" y="2259"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="16994" y="11294"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="4606" y="11294"/>
+              </a:lnTo>
+              <a:moveTo>
+                <a:pt x="13976" y="17082"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="13976" y="16376"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="20171" y="16376"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="20171" y="17082"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="13976" y="17082"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFCC"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+        <a:effectLst/>
+        <a:extLst>
+          <a:ext uri="{AF507438-7753-43E0-B8FC-AC1667EBCBE1}">
+            <a14:hiddenEffects xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:effectLst>
+                <a:outerShdw dist="107763" dir="13500000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="808080"/>
+                </a:outerShdw>
+              </a:effectLst>
+            </a14:hiddenEffects>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>165652</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>55217</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>280227</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>138043</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="Rectangle 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D4B06E5-1252-452E-B5D6-2830C358FCBA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3308902" y="2760317"/>
+          <a:ext cx="1829075" cy="717826"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="22860" rIns="36576" bIns="0" anchor="ctr" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1200"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:latin typeface="ＭＳ Ｐゴシック"/>
+            <a:ea typeface="ＭＳ Ｐゴシック"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1200"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1600" b="1" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>アカウント登録</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="800" b="1" i="0" u="none" strike="noStrike" baseline="0">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:latin typeface="ＭＳ Ｐゴシック"/>
+            <a:ea typeface="ＭＳ Ｐゴシック"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>110435</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>101232</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>265965</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>101232</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="Rectangle 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FBF512D8-CF38-47A6-9AAE-007134324548}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="2678044" y="579783"/>
+          <a:ext cx="3008428" cy="1720942"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="22860" rIns="0" bIns="0" anchor="t" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1300"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>【</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>アカウント登録画面</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>】</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1300"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:latin typeface="ＭＳ Ｐゴシック"/>
+            <a:ea typeface="ＭＳ Ｐゴシック"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1300"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>・名前（性）、名前（名）、カナ（性）、カナ（名）</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:latin typeface="ＭＳ Ｐゴシック"/>
+            <a:ea typeface="ＭＳ Ｐゴシック"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1300"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>・メールアドレス</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:latin typeface="ＭＳ Ｐゴシック"/>
+            <a:ea typeface="ＭＳ Ｐゴシック"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1300"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>・パスワード</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:latin typeface="ＭＳ Ｐゴシック"/>
+            <a:ea typeface="ＭＳ Ｐゴシック"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1300"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>・性別</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:latin typeface="ＭＳ Ｐゴシック"/>
+            <a:ea typeface="ＭＳ Ｐゴシック"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1300"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>・郵便番号</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:latin typeface="ＭＳ Ｐゴシック"/>
+            <a:ea typeface="ＭＳ Ｐゴシック"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1300"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>・住所（都道府県、市区町村、番地）</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:latin typeface="ＭＳ Ｐゴシック"/>
+            <a:ea typeface="ＭＳ Ｐゴシック"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1300"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>・アカウント権限</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:latin typeface="ＭＳ Ｐゴシック"/>
+            <a:ea typeface="ＭＳ Ｐゴシック"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1300"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>→「確認する」ボタン</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1300"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:latin typeface="ＭＳ Ｐゴシック"/>
+            <a:ea typeface="ＭＳ Ｐゴシック"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1200"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:latin typeface="ＭＳ Ｐゴシック"/>
+            <a:ea typeface="ＭＳ Ｐゴシック"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>230164</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>18405</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>239275</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>115588</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="Line 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{56C5306A-9172-4A87-A942-FDAF0F46D2ED}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeShapeType="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm flipH="1">
+          <a:off x="4224222" y="2374347"/>
+          <a:ext cx="9111" cy="253632"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd type="triangle" w="med" len="med"/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:noFill/>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>44450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>260350</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>44450</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="Line 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D76E985D-89D3-4E7B-8E3F-DF2DED8CB4E9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeShapeType="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm flipH="1">
+          <a:off x="2400300" y="3067050"/>
+          <a:ext cx="717550" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd type="triangle" w="med" len="med"/>
+          <a:tailEnd/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:noFill/>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>28253</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>64421</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>136203</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>146326</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="Rectangle 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D8DF15A-1347-47D6-B3EB-1799F6D072F7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="6314753" y="2134521"/>
+          <a:ext cx="2965450" cy="1828155"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="22860" rIns="0" bIns="0" anchor="t" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1300"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>【</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>アカウント登録確認画面</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>】</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1300"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:latin typeface="ＭＳ Ｐゴシック"/>
+            <a:ea typeface="ＭＳ Ｐゴシック"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1300"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>・名前（性）、名前（名）、カナ（性）、カナ（名）</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1300"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>・メールアドレス</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1300"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>・パスワード</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1300"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>・性別</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1300"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>・郵便番号</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1300"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>・住所（都道府県、市区町村、番地）</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1300"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>・アカウント権限</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:latin typeface="ＭＳ Ｐゴシック"/>
+            <a:ea typeface="ＭＳ Ｐゴシック"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1300"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>・「前に戻る」ボタン、「登録する」ボタン</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1300"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:latin typeface="ＭＳ Ｐゴシック"/>
+            <a:ea typeface="ＭＳ Ｐゴシック"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1200"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:latin typeface="ＭＳ Ｐゴシック"/>
+            <a:ea typeface="ＭＳ Ｐゴシック"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>146050</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="Line 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{460AE28A-EA86-47B9-A362-FD38F2B80654}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeShapeType="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5448300" y="3060700"/>
+          <a:ext cx="698500" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd type="triangle" w="med" len="med"/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:noFill/>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>217464</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>34603</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>217464</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>66353</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="Line 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B5C78E9D-CDAE-4E8A-B39D-A092C221C38B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeShapeType="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4211522" y="3485690"/>
+          <a:ext cx="0" cy="344649"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd type="triangle" w="med" len="med"/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:noFill/>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>55217</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="AutoShape 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{54B5A63B-60D5-4BD3-8DDF-D45AFD21C6CC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4292600" y="3892550"/>
+          <a:ext cx="850900" cy="772767"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartMagneticDisk">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="22860" rIns="36576" bIns="0" anchor="t" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1200"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:latin typeface="ＭＳ Ｐゴシック"/>
+            <a:ea typeface="ＭＳ Ｐゴシック"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>165100</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>156448</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>127000</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>9202</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="AutoShape 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{90A18201-2FDB-4018-B475-CB41E3CE02C3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3303288" y="3920434"/>
+          <a:ext cx="817770" cy="791449"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartDocument">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="22860" rIns="36576" bIns="0" anchor="t" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1200"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:latin typeface="ＭＳ Ｐゴシック"/>
+            <a:ea typeface="ＭＳ Ｐゴシック"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1200"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>アカウント</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:latin typeface="ＭＳ Ｐゴシック"/>
+            <a:ea typeface="ＭＳ Ｐゴシック"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1200"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>登録確認画面</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:latin typeface="ＭＳ Ｐゴシック"/>
+            <a:ea typeface="ＭＳ Ｐゴシック"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -3664,7 +5885,57 @@
             </a:lnSpc>
             <a:defRPr sz="1000"/>
           </a:pPr>
-          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:latin typeface="ＭＳ Ｐゴシック"/>
+            <a:ea typeface="ＭＳ Ｐゴシック"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1200"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>アカウント</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:latin typeface="ＭＳ Ｐゴシック"/>
+            <a:ea typeface="ＭＳ Ｐゴシック"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1200"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>一覧</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
             <a:solidFill>
               <a:srgbClr val="000000"/>
             </a:solidFill>
@@ -3679,910 +5950,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>31750</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>127000</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="computr1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D834FA45-AD42-4C01-90CE-BC0DF55BC885}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noEditPoints="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1619250" y="2705100"/>
-          <a:ext cx="698500" cy="762000"/>
-        </a:xfrm>
-        <a:custGeom>
-          <a:avLst/>
-          <a:gdLst>
-            <a:gd name="T0" fmla="*/ 19535 w 21600"/>
-            <a:gd name="T1" fmla="*/ 0 h 21600"/>
-            <a:gd name="T2" fmla="*/ 10800 w 21600"/>
-            <a:gd name="T3" fmla="*/ 0 h 21600"/>
-            <a:gd name="T4" fmla="*/ 2065 w 21600"/>
-            <a:gd name="T5" fmla="*/ 0 h 21600"/>
-            <a:gd name="T6" fmla="*/ 0 w 21600"/>
-            <a:gd name="T7" fmla="*/ 15388 h 21600"/>
-            <a:gd name="T8" fmla="*/ 0 w 21600"/>
-            <a:gd name="T9" fmla="*/ 21600 h 21600"/>
-            <a:gd name="T10" fmla="*/ 10800 w 21600"/>
-            <a:gd name="T11" fmla="*/ 21600 h 21600"/>
-            <a:gd name="T12" fmla="*/ 21600 w 21600"/>
-            <a:gd name="T13" fmla="*/ 21600 h 21600"/>
-            <a:gd name="T14" fmla="*/ 21600 w 21600"/>
-            <a:gd name="T15" fmla="*/ 15388 h 21600"/>
-            <a:gd name="T16" fmla="*/ 19535 w 21600"/>
-            <a:gd name="T17" fmla="*/ 13553 h 21600"/>
-            <a:gd name="T18" fmla="*/ 2065 w 21600"/>
-            <a:gd name="T19" fmla="*/ 13553 h 21600"/>
-            <a:gd name="T20" fmla="*/ 2065 w 21600"/>
-            <a:gd name="T21" fmla="*/ 6776 h 21600"/>
-            <a:gd name="T22" fmla="*/ 19535 w 21600"/>
-            <a:gd name="T23" fmla="*/ 6776 h 21600"/>
-            <a:gd name="T24" fmla="*/ 0 w 21600"/>
-            <a:gd name="T25" fmla="*/ 18494 h 21600"/>
-            <a:gd name="T26" fmla="*/ 21600 w 21600"/>
-            <a:gd name="T27" fmla="*/ 18494 h 21600"/>
-            <a:gd name="T28" fmla="*/ 4923 w 21600"/>
-            <a:gd name="T29" fmla="*/ 2541 h 21600"/>
-            <a:gd name="T30" fmla="*/ 16756 w 21600"/>
-            <a:gd name="T31" fmla="*/ 11153 h 21600"/>
-          </a:gdLst>
-          <a:ahLst/>
-          <a:cxnLst>
-            <a:cxn ang="0">
-              <a:pos x="T0" y="T1"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="T2" y="T3"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="T4" y="T5"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="T6" y="T7"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="T8" y="T9"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="T10" y="T11"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="T12" y="T13"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="T14" y="T15"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="T16" y="T17"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="T18" y="T19"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="T20" y="T21"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="T22" y="T23"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="T24" y="T25"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="T26" y="T27"/>
-            </a:cxn>
-          </a:cxnLst>
-          <a:rect l="T28" t="T29" r="T30" b="T31"/>
-          <a:pathLst>
-            <a:path w="21600" h="21600" extrusionOk="0">
-              <a:moveTo>
-                <a:pt x="16994" y="15388"/>
-              </a:moveTo>
-              <a:lnTo>
-                <a:pt x="16994" y="13553"/>
-              </a:lnTo>
-              <a:lnTo>
-                <a:pt x="19535" y="13553"/>
-              </a:lnTo>
-              <a:lnTo>
-                <a:pt x="19535" y="10729"/>
-              </a:lnTo>
-              <a:lnTo>
-                <a:pt x="19535" y="6776"/>
-              </a:lnTo>
-              <a:lnTo>
-                <a:pt x="19535" y="0"/>
-              </a:lnTo>
-              <a:lnTo>
-                <a:pt x="10800" y="0"/>
-              </a:lnTo>
-              <a:lnTo>
-                <a:pt x="2065" y="0"/>
-              </a:lnTo>
-              <a:lnTo>
-                <a:pt x="2065" y="6776"/>
-              </a:lnTo>
-              <a:lnTo>
-                <a:pt x="2065" y="10729"/>
-              </a:lnTo>
-              <a:lnTo>
-                <a:pt x="2065" y="13553"/>
-              </a:lnTo>
-              <a:lnTo>
-                <a:pt x="4606" y="13553"/>
-              </a:lnTo>
-              <a:lnTo>
-                <a:pt x="4606" y="15388"/>
-              </a:lnTo>
-              <a:lnTo>
-                <a:pt x="0" y="15388"/>
-              </a:lnTo>
-              <a:lnTo>
-                <a:pt x="0" y="21600"/>
-              </a:lnTo>
-              <a:lnTo>
-                <a:pt x="10800" y="21600"/>
-              </a:lnTo>
-              <a:lnTo>
-                <a:pt x="21600" y="21600"/>
-              </a:lnTo>
-              <a:lnTo>
-                <a:pt x="21600" y="15388"/>
-              </a:lnTo>
-              <a:lnTo>
-                <a:pt x="16994" y="15388"/>
-              </a:lnTo>
-              <a:close/>
-            </a:path>
-            <a:path w="21600" h="21600" extrusionOk="0">
-              <a:moveTo>
-                <a:pt x="4606" y="15388"/>
-              </a:moveTo>
-              <a:lnTo>
-                <a:pt x="4606" y="13553"/>
-              </a:lnTo>
-              <a:lnTo>
-                <a:pt x="16994" y="13553"/>
-              </a:lnTo>
-              <a:lnTo>
-                <a:pt x="16994" y="15388"/>
-              </a:lnTo>
-              <a:lnTo>
-                <a:pt x="4606" y="15388"/>
-              </a:lnTo>
-            </a:path>
-            <a:path w="21600" h="21600" extrusionOk="0">
-              <a:moveTo>
-                <a:pt x="4606" y="11294"/>
-              </a:moveTo>
-              <a:lnTo>
-                <a:pt x="4606" y="2259"/>
-              </a:lnTo>
-              <a:lnTo>
-                <a:pt x="16994" y="2259"/>
-              </a:lnTo>
-              <a:lnTo>
-                <a:pt x="16994" y="11294"/>
-              </a:lnTo>
-              <a:lnTo>
-                <a:pt x="4606" y="11294"/>
-              </a:lnTo>
-              <a:moveTo>
-                <a:pt x="13976" y="17082"/>
-              </a:moveTo>
-              <a:lnTo>
-                <a:pt x="13976" y="16376"/>
-              </a:lnTo>
-              <a:lnTo>
-                <a:pt x="20171" y="16376"/>
-              </a:lnTo>
-              <a:lnTo>
-                <a:pt x="20171" y="17082"/>
-              </a:lnTo>
-              <a:lnTo>
-                <a:pt x="13976" y="17082"/>
-              </a:lnTo>
-            </a:path>
-          </a:pathLst>
-        </a:custGeom>
-        <a:solidFill>
-          <a:srgbClr val="FFFFCC"/>
-        </a:solidFill>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:miter lim="800000"/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-        <a:effectLst/>
-        <a:extLst>
-          <a:ext uri="{AF507438-7753-43E0-B8FC-AC1667EBCBE1}">
-            <a14:hiddenEffects xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:effectLst>
-                <a:outerShdw dist="107763" dir="13500000" algn="ctr" rotWithShape="0">
-                  <a:srgbClr val="808080"/>
-                </a:outerShdw>
-              </a:effectLst>
-            </a14:hiddenEffects>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>44450</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>44450</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>31750</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>88900</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="Rectangle 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A6ABBE42-0BA7-47A2-B8C9-A11E71721925}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3187700" y="2749550"/>
-          <a:ext cx="1987550" cy="679450"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-        </a:solidFill>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-          </a:solidFill>
-          <a:miter lim="800000"/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="22860" rIns="36576" bIns="0" anchor="t" upright="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr" rtl="0">
-            <a:lnSpc>
-              <a:spcPts val="1200"/>
-            </a:lnSpc>
-            <a:defRPr sz="1000"/>
-          </a:pPr>
-          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:latin typeface="ＭＳ Ｐゴシック"/>
-            <a:ea typeface="ＭＳ Ｐゴシック"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>196850</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>44450</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>63500</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>146050</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="Rectangle 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{347B3DDF-7D2A-40B4-8091-136169004070}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="2768600" y="844550"/>
-          <a:ext cx="3295650" cy="1212850"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-        </a:solidFill>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-          </a:solidFill>
-          <a:miter lim="800000"/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="22860" rIns="0" bIns="0" anchor="t" upright="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l" rtl="0">
-            <a:lnSpc>
-              <a:spcPts val="1300"/>
-            </a:lnSpc>
-            <a:defRPr sz="1000"/>
-          </a:pPr>
-          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:latin typeface="ＭＳ Ｐゴシック"/>
-            <a:ea typeface="ＭＳ Ｐゴシック"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l" rtl="0">
-            <a:lnSpc>
-              <a:spcPts val="1300"/>
-            </a:lnSpc>
-            <a:defRPr sz="1000"/>
-          </a:pPr>
-          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:latin typeface="ＭＳ Ｐゴシック"/>
-            <a:ea typeface="ＭＳ Ｐゴシック"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l" rtl="0">
-            <a:lnSpc>
-              <a:spcPts val="1300"/>
-            </a:lnSpc>
-            <a:defRPr sz="1000"/>
-          </a:pPr>
-          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:latin typeface="ＭＳ Ｐゴシック"/>
-            <a:ea typeface="ＭＳ Ｐゴシック"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l" rtl="0">
-            <a:lnSpc>
-              <a:spcPts val="1200"/>
-            </a:lnSpc>
-            <a:defRPr sz="1000"/>
-          </a:pPr>
-          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:latin typeface="ＭＳ Ｐゴシック"/>
-            <a:ea typeface="ＭＳ Ｐゴシック"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>184150</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>63500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>184150</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="Line 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E8650F5B-D7F3-4FE7-80DD-DA9B2D80F4D2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeShapeType="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4184650" y="2133600"/>
-          <a:ext cx="0" cy="565150"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-          </a:solidFill>
-          <a:round/>
-          <a:headEnd/>
-          <a:tailEnd type="triangle" w="med" len="med"/>
-        </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:noFill/>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>44450</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>260350</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>44450</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="Line 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E3164E14-FCF4-47EB-9AF8-F8D08229506D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeShapeType="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm flipH="1">
-          <a:off x="2400300" y="3067050"/>
-          <a:ext cx="717550" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-          </a:solidFill>
-          <a:round/>
-          <a:headEnd type="triangle" w="med" len="med"/>
-          <a:tailEnd/>
-        </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:noFill/>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>32</xdr:col>
-      <xdr:colOff>127000</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>63500</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="Rectangle 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{09F3CAA2-54A1-4002-9959-A57B6BC85FEF}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="6305550" y="2362200"/>
-          <a:ext cx="2965450" cy="1200150"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-        </a:solidFill>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-          </a:solidFill>
-          <a:miter lim="800000"/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="22860" rIns="0" bIns="0" anchor="t" upright="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l" rtl="0">
-            <a:lnSpc>
-              <a:spcPts val="1300"/>
-            </a:lnSpc>
-            <a:defRPr sz="1000"/>
-          </a:pPr>
-          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:latin typeface="ＭＳ Ｐゴシック"/>
-            <a:ea typeface="ＭＳ Ｐゴシック"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l" rtl="0">
-            <a:lnSpc>
-              <a:spcPts val="1300"/>
-            </a:lnSpc>
-            <a:defRPr sz="1000"/>
-          </a:pPr>
-          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:latin typeface="ＭＳ Ｐゴシック"/>
-            <a:ea typeface="ＭＳ Ｐゴシック"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l" rtl="0">
-            <a:lnSpc>
-              <a:spcPts val="1300"/>
-            </a:lnSpc>
-            <a:defRPr sz="1000"/>
-          </a:pPr>
-          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:latin typeface="ＭＳ Ｐゴシック"/>
-            <a:ea typeface="ＭＳ Ｐゴシック"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l" rtl="0">
-            <a:lnSpc>
-              <a:spcPts val="1200"/>
-            </a:lnSpc>
-            <a:defRPr sz="1000"/>
-          </a:pPr>
-          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:latin typeface="ＭＳ Ｐゴシック"/>
-            <a:ea typeface="ＭＳ Ｐゴシック"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>146050</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="8" name="Line 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D8C0352-A769-478D-BF8F-C02FBBFA0F9F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeShapeType="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="5448300" y="3060700"/>
-          <a:ext cx="698500" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-          </a:solidFill>
-          <a:round/>
-          <a:headEnd/>
-          <a:tailEnd type="triangle" w="med" len="med"/>
-        </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:noFill/>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>171450</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>171450</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="9" name="Line 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7EAD3F69-BDD1-467C-8CFC-E815C918D742}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeShapeType="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4171950" y="3524250"/>
-          <a:ext cx="0" cy="349250"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-          </a:solidFill>
-          <a:round/>
-          <a:headEnd/>
-          <a:tailEnd type="triangle" w="med" len="med"/>
-        </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:noFill/>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>6350</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>55217</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="10" name="AutoShape 10">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{147BE263-0A1E-4B88-B79C-D74B7866FAD0}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4292600" y="3892550"/>
-          <a:ext cx="850900" cy="772767"/>
-        </a:xfrm>
-        <a:prstGeom prst="flowChartMagneticDisk">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-        </a:solidFill>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-          </a:solidFill>
-          <a:round/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="22860" rIns="36576" bIns="0" anchor="t" upright="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr" rtl="0">
-            <a:lnSpc>
-              <a:spcPts val="1200"/>
-            </a:lnSpc>
-            <a:defRPr sz="1000"/>
-          </a:pPr>
-          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:latin typeface="ＭＳ Ｐゴシック"/>
-            <a:ea typeface="ＭＳ Ｐゴシック"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>165100</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>127000</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>73623</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="11" name="AutoShape 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47B32EF0-7B4A-42E5-860A-B01602D5AF92}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3308350" y="3975100"/>
-          <a:ext cx="819150" cy="708623"/>
-        </a:xfrm>
-        <a:prstGeom prst="flowChartDocument">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-        </a:solidFill>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-          </a:solidFill>
-          <a:miter lim="800000"/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="22860" rIns="36576" bIns="0" anchor="t" upright="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr" rtl="0">
-            <a:lnSpc>
-              <a:spcPts val="1200"/>
-            </a:lnSpc>
-            <a:defRPr sz="1000"/>
-          </a:pPr>
-          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:latin typeface="ＭＳ Ｐゴシック"/>
-            <a:ea typeface="ＭＳ Ｐゴシック"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -5087,10 +6455,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1625C5FC-8882-4352-9CF7-99B5F4D09A18}">
-  <sheetPr>
-    <tabColor rgb="FFFFC000"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41733A60-6337-421B-9083-D3195211E5A8}">
   <dimension ref="A1:FU42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
@@ -5102,127 +6467,121 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:177" ht="12.75" customHeight="1">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
-      <c r="L1" s="77"/>
-      <c r="M1" s="77"/>
-      <c r="N1" s="77"/>
-      <c r="O1" s="77"/>
-      <c r="P1" s="77"/>
-      <c r="Q1" s="77"/>
-      <c r="R1" s="77"/>
-      <c r="S1" s="77"/>
-      <c r="T1" s="77"/>
-      <c r="U1" s="77"/>
-      <c r="V1" s="77"/>
-      <c r="W1" s="77"/>
-      <c r="X1" s="77"/>
-      <c r="Y1" s="77"/>
-      <c r="Z1" s="77"/>
-      <c r="AA1" s="77"/>
-      <c r="AB1" s="77"/>
-      <c r="AC1" s="77"/>
-      <c r="AD1" s="77"/>
-      <c r="AE1" s="77"/>
-      <c r="AF1" s="77"/>
-      <c r="AG1" s="77"/>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
+      <c r="H1" s="58"/>
+      <c r="I1" s="58"/>
+      <c r="J1" s="58"/>
+      <c r="K1" s="58"/>
+      <c r="L1" s="58"/>
+      <c r="M1" s="58"/>
+      <c r="N1" s="58"/>
+      <c r="O1" s="58"/>
+      <c r="P1" s="58"/>
+      <c r="Q1" s="58"/>
+      <c r="R1" s="58"/>
+      <c r="S1" s="58"/>
+      <c r="T1" s="58"/>
+      <c r="U1" s="58"/>
+      <c r="V1" s="58"/>
+      <c r="W1" s="58"/>
+      <c r="X1" s="58"/>
+      <c r="Y1" s="58"/>
+      <c r="Z1" s="58"/>
+      <c r="AA1" s="58"/>
+      <c r="AB1" s="58"/>
+      <c r="AC1" s="58"/>
+      <c r="AD1" s="58"/>
+      <c r="AE1" s="58"/>
+      <c r="AF1" s="58"/>
+      <c r="AG1" s="58"/>
     </row>
     <row r="2" spans="1:177" ht="13" customHeight="1">
-      <c r="A2" s="78" t="s">
+      <c r="A2" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="78" t="s">
+      <c r="B2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="59" t="s">
         <v>48</v>
       </c>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
-      <c r="J2" s="79"/>
-      <c r="K2" s="79"/>
-      <c r="L2" s="79"/>
-      <c r="M2" s="79"/>
-      <c r="N2" s="79"/>
-      <c r="O2" s="79"/>
-      <c r="P2" s="79"/>
-      <c r="Q2" s="79"/>
-      <c r="R2" s="79"/>
-      <c r="S2" s="79"/>
-      <c r="T2" s="79"/>
-      <c r="U2" s="79"/>
-      <c r="V2" s="79"/>
-      <c r="W2" s="79"/>
-      <c r="X2" s="79"/>
-      <c r="Y2" s="79"/>
-      <c r="Z2" s="79"/>
-      <c r="AA2" s="79"/>
-      <c r="AB2" s="79"/>
-      <c r="AC2" s="80"/>
-      <c r="AD2" s="78" t="s">
+      <c r="H2" s="60"/>
+      <c r="I2" s="60"/>
+      <c r="J2" s="60"/>
+      <c r="K2" s="60"/>
+      <c r="L2" s="60"/>
+      <c r="M2" s="60"/>
+      <c r="N2" s="60"/>
+      <c r="O2" s="60"/>
+      <c r="P2" s="60"/>
+      <c r="Q2" s="60"/>
+      <c r="R2" s="60"/>
+      <c r="S2" s="60"/>
+      <c r="T2" s="60"/>
+      <c r="U2" s="60"/>
+      <c r="V2" s="60"/>
+      <c r="W2" s="60"/>
+      <c r="X2" s="60"/>
+      <c r="Y2" s="60"/>
+      <c r="Z2" s="60"/>
+      <c r="AA2" s="60"/>
+      <c r="AB2" s="60"/>
+      <c r="AC2" s="61"/>
+      <c r="AD2" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="AE2" s="80"/>
-      <c r="AF2" s="78" t="s">
+      <c r="AE2" s="61"/>
+      <c r="AF2" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="AG2" s="80"/>
+      <c r="AG2" s="61"/>
     </row>
     <row r="3" spans="1:177" s="3" customFormat="1" ht="12.75" customHeight="1">
-      <c r="A3" s="78" t="s">
-        <v>49</v>
+      <c r="A3" s="59" t="s">
+        <v>54</v>
       </c>
-      <c r="B3" s="79"/>
-      <c r="C3" s="79"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="79"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="78" t="s">
-        <v>51</v>
-      </c>
-      <c r="H3" s="79"/>
-      <c r="I3" s="79"/>
-      <c r="J3" s="79"/>
-      <c r="K3" s="79"/>
-      <c r="L3" s="79"/>
-      <c r="M3" s="79"/>
-      <c r="N3" s="79"/>
-      <c r="O3" s="79"/>
-      <c r="P3" s="79"/>
-      <c r="Q3" s="79"/>
-      <c r="R3" s="79"/>
-      <c r="S3" s="79"/>
-      <c r="T3" s="79"/>
-      <c r="U3" s="79"/>
-      <c r="V3" s="79"/>
-      <c r="W3" s="79"/>
-      <c r="X3" s="79"/>
-      <c r="Y3" s="79"/>
-      <c r="Z3" s="79"/>
-      <c r="AA3" s="79"/>
-      <c r="AB3" s="79"/>
-      <c r="AC3" s="80"/>
-      <c r="AD3" s="78" t="s">
-        <v>15</v>
-      </c>
-      <c r="AE3" s="80"/>
-      <c r="AF3" s="78" t="s">
-        <v>47</v>
-      </c>
-      <c r="AG3" s="80"/>
+      <c r="B3" s="60"/>
+      <c r="C3" s="60"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="60"/>
+      <c r="I3" s="60"/>
+      <c r="J3" s="60"/>
+      <c r="K3" s="60"/>
+      <c r="L3" s="60"/>
+      <c r="M3" s="60"/>
+      <c r="N3" s="60"/>
+      <c r="O3" s="60"/>
+      <c r="P3" s="60"/>
+      <c r="Q3" s="60"/>
+      <c r="R3" s="60"/>
+      <c r="S3" s="60"/>
+      <c r="T3" s="60"/>
+      <c r="U3" s="60"/>
+      <c r="V3" s="60"/>
+      <c r="W3" s="60"/>
+      <c r="X3" s="60"/>
+      <c r="Y3" s="60"/>
+      <c r="Z3" s="60"/>
+      <c r="AA3" s="60"/>
+      <c r="AB3" s="60"/>
+      <c r="AC3" s="61"/>
+      <c r="AD3" s="59"/>
+      <c r="AE3" s="61"/>
+      <c r="AF3" s="59"/>
+      <c r="AG3" s="61"/>
       <c r="AH3" s="2"/>
       <c r="AI3" s="5"/>
       <c r="AJ3" s="5"/>
@@ -6759,6 +8118,1678 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1625C5FC-8882-4352-9CF7-99B5F4D09A18}">
+  <sheetPr>
+    <tabColor rgb="FFFFC000"/>
+  </sheetPr>
+  <dimension ref="A1:FU42"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" customHeight="1"/>
+  <cols>
+    <col min="1" max="4" width="4.08984375" style="1" customWidth="1"/>
+    <col min="5" max="6" width="4.08984375" style="4" customWidth="1"/>
+    <col min="7" max="33" width="4.08984375" style="1" customWidth="1"/>
+    <col min="34" max="37" width="4" style="1" customWidth="1"/>
+    <col min="38" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:177" ht="12.75" customHeight="1">
+      <c r="A1" s="58" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
+      <c r="H1" s="58"/>
+      <c r="I1" s="58"/>
+      <c r="J1" s="58"/>
+      <c r="K1" s="58"/>
+      <c r="L1" s="58"/>
+      <c r="M1" s="58"/>
+      <c r="N1" s="58"/>
+      <c r="O1" s="58"/>
+      <c r="P1" s="58"/>
+      <c r="Q1" s="58"/>
+      <c r="R1" s="58"/>
+      <c r="S1" s="58"/>
+      <c r="T1" s="58"/>
+      <c r="U1" s="58"/>
+      <c r="V1" s="58"/>
+      <c r="W1" s="58"/>
+      <c r="X1" s="58"/>
+      <c r="Y1" s="58"/>
+      <c r="Z1" s="58"/>
+      <c r="AA1" s="58"/>
+      <c r="AB1" s="58"/>
+      <c r="AC1" s="58"/>
+      <c r="AD1" s="58"/>
+      <c r="AE1" s="58"/>
+      <c r="AF1" s="58"/>
+      <c r="AG1" s="58"/>
+    </row>
+    <row r="2" spans="1:177" ht="13" customHeight="1">
+      <c r="A2" s="59" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="59" t="s">
+        <v>48</v>
+      </c>
+      <c r="H2" s="60"/>
+      <c r="I2" s="60"/>
+      <c r="J2" s="60"/>
+      <c r="K2" s="60"/>
+      <c r="L2" s="60"/>
+      <c r="M2" s="60"/>
+      <c r="N2" s="60"/>
+      <c r="O2" s="60"/>
+      <c r="P2" s="60"/>
+      <c r="Q2" s="60"/>
+      <c r="R2" s="60"/>
+      <c r="S2" s="60"/>
+      <c r="T2" s="60"/>
+      <c r="U2" s="60"/>
+      <c r="V2" s="60"/>
+      <c r="W2" s="60"/>
+      <c r="X2" s="60"/>
+      <c r="Y2" s="60"/>
+      <c r="Z2" s="60"/>
+      <c r="AA2" s="60"/>
+      <c r="AB2" s="60"/>
+      <c r="AC2" s="61"/>
+      <c r="AD2" s="59" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE2" s="61"/>
+      <c r="AF2" s="59" t="s">
+        <v>2</v>
+      </c>
+      <c r="AG2" s="61"/>
+    </row>
+    <row r="3" spans="1:177" s="3" customFormat="1" ht="12.75" customHeight="1">
+      <c r="A3" s="59" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" s="60"/>
+      <c r="C3" s="60"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="59" t="s">
+        <v>51</v>
+      </c>
+      <c r="H3" s="60"/>
+      <c r="I3" s="60"/>
+      <c r="J3" s="60"/>
+      <c r="K3" s="60"/>
+      <c r="L3" s="60"/>
+      <c r="M3" s="60"/>
+      <c r="N3" s="60"/>
+      <c r="O3" s="60"/>
+      <c r="P3" s="60"/>
+      <c r="Q3" s="60"/>
+      <c r="R3" s="60"/>
+      <c r="S3" s="60"/>
+      <c r="T3" s="60"/>
+      <c r="U3" s="60"/>
+      <c r="V3" s="60"/>
+      <c r="W3" s="60"/>
+      <c r="X3" s="60"/>
+      <c r="Y3" s="60"/>
+      <c r="Z3" s="60"/>
+      <c r="AA3" s="60"/>
+      <c r="AB3" s="60"/>
+      <c r="AC3" s="61"/>
+      <c r="AD3" s="59" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE3" s="61"/>
+      <c r="AF3" s="59" t="s">
+        <v>47</v>
+      </c>
+      <c r="AG3" s="61"/>
+      <c r="AH3" s="2"/>
+      <c r="AI3" s="5"/>
+      <c r="AJ3" s="5"/>
+      <c r="AK3" s="5"/>
+      <c r="AL3" s="5"/>
+      <c r="AM3" s="5"/>
+      <c r="AN3" s="5"/>
+      <c r="AO3" s="5"/>
+      <c r="AP3" s="5"/>
+      <c r="AQ3" s="5"/>
+      <c r="AR3" s="5"/>
+      <c r="AS3" s="5"/>
+      <c r="AT3" s="5"/>
+      <c r="AU3" s="5"/>
+      <c r="AV3" s="5"/>
+      <c r="AW3" s="5"/>
+      <c r="AX3" s="5"/>
+      <c r="AY3" s="5"/>
+      <c r="AZ3" s="5"/>
+      <c r="BA3" s="5"/>
+      <c r="BB3" s="5"/>
+      <c r="BC3" s="5"/>
+      <c r="BD3" s="5"/>
+      <c r="BE3" s="5"/>
+      <c r="BF3" s="5"/>
+      <c r="BG3" s="5"/>
+      <c r="BH3" s="5"/>
+      <c r="BI3" s="5"/>
+      <c r="BJ3" s="5"/>
+      <c r="BK3" s="5"/>
+      <c r="BL3" s="5"/>
+      <c r="BM3" s="5"/>
+      <c r="BN3" s="5"/>
+      <c r="BO3" s="5"/>
+      <c r="BP3" s="5"/>
+      <c r="BQ3" s="5"/>
+      <c r="BR3" s="5"/>
+      <c r="BS3" s="5"/>
+      <c r="BT3" s="5"/>
+      <c r="BU3" s="5"/>
+      <c r="BV3" s="5"/>
+      <c r="BW3" s="5"/>
+      <c r="BX3" s="5"/>
+      <c r="BY3" s="5"/>
+      <c r="BZ3" s="5"/>
+      <c r="CA3" s="5"/>
+      <c r="CB3" s="5"/>
+      <c r="CC3" s="5"/>
+      <c r="CD3" s="5"/>
+      <c r="CE3" s="5"/>
+      <c r="CF3" s="5"/>
+      <c r="CG3" s="5"/>
+      <c r="CH3" s="5"/>
+      <c r="CI3" s="5"/>
+      <c r="CJ3" s="5"/>
+      <c r="CK3" s="5"/>
+      <c r="CL3" s="5"/>
+      <c r="CM3" s="5"/>
+      <c r="CN3" s="5"/>
+      <c r="CO3" s="5"/>
+      <c r="CP3" s="5"/>
+      <c r="CQ3" s="5"/>
+      <c r="CR3" s="5"/>
+      <c r="CS3" s="5"/>
+      <c r="CT3" s="5"/>
+      <c r="CU3" s="5"/>
+      <c r="CV3" s="5"/>
+      <c r="CW3" s="5"/>
+      <c r="CX3" s="5"/>
+      <c r="CY3" s="5"/>
+      <c r="CZ3" s="5"/>
+      <c r="DA3" s="5"/>
+      <c r="DB3" s="5"/>
+      <c r="DC3" s="5"/>
+      <c r="DD3" s="5"/>
+      <c r="DE3" s="5"/>
+      <c r="DF3" s="5"/>
+      <c r="DG3" s="5"/>
+      <c r="DH3" s="5"/>
+      <c r="DI3" s="5"/>
+      <c r="DJ3" s="5"/>
+      <c r="DK3" s="5"/>
+      <c r="DL3" s="5"/>
+      <c r="DM3" s="5"/>
+      <c r="DN3" s="5"/>
+      <c r="DO3" s="5"/>
+      <c r="DP3" s="5"/>
+      <c r="DQ3" s="5"/>
+      <c r="DR3" s="5"/>
+      <c r="DS3" s="5"/>
+      <c r="DT3" s="5"/>
+      <c r="DU3" s="5"/>
+      <c r="DV3" s="5"/>
+      <c r="DW3" s="5"/>
+      <c r="DX3" s="5"/>
+      <c r="DY3" s="5"/>
+      <c r="DZ3" s="5"/>
+      <c r="EA3" s="5"/>
+      <c r="EB3" s="5"/>
+      <c r="EC3" s="5"/>
+      <c r="ED3" s="5"/>
+      <c r="EE3" s="5"/>
+      <c r="EF3" s="5"/>
+      <c r="EG3" s="5"/>
+      <c r="EH3" s="5"/>
+      <c r="EI3" s="5"/>
+      <c r="EJ3" s="5"/>
+      <c r="EK3" s="5"/>
+      <c r="EL3" s="5"/>
+      <c r="EM3" s="5"/>
+      <c r="EN3" s="5"/>
+      <c r="EO3" s="5"/>
+      <c r="EP3" s="5"/>
+      <c r="EQ3" s="5"/>
+      <c r="ER3" s="5"/>
+      <c r="ES3" s="5"/>
+      <c r="ET3" s="5"/>
+      <c r="EU3" s="5"/>
+      <c r="EV3" s="5"/>
+      <c r="EW3" s="5"/>
+      <c r="EX3" s="5"/>
+      <c r="EY3" s="5"/>
+      <c r="EZ3" s="5"/>
+      <c r="FA3" s="5"/>
+      <c r="FB3" s="5"/>
+      <c r="FC3" s="5"/>
+      <c r="FD3" s="5"/>
+      <c r="FE3" s="5"/>
+      <c r="FF3" s="5"/>
+      <c r="FG3" s="5"/>
+      <c r="FH3" s="5"/>
+      <c r="FI3" s="5"/>
+      <c r="FJ3" s="5"/>
+      <c r="FK3" s="5"/>
+      <c r="FL3" s="5"/>
+      <c r="FM3" s="5"/>
+      <c r="FN3" s="5"/>
+      <c r="FO3" s="5"/>
+      <c r="FP3" s="5"/>
+      <c r="FQ3" s="5"/>
+      <c r="FR3" s="5"/>
+      <c r="FS3" s="5"/>
+      <c r="FT3" s="5"/>
+      <c r="FU3" s="5"/>
+    </row>
+    <row r="4" spans="1:177" ht="12.75" customHeight="1">
+      <c r="A4" s="32"/>
+      <c r="B4" s="33"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="33"/>
+      <c r="H4" s="33"/>
+      <c r="I4" s="33"/>
+      <c r="J4" s="33"/>
+      <c r="K4" s="33"/>
+      <c r="L4" s="33"/>
+      <c r="M4" s="33"/>
+      <c r="N4" s="33"/>
+      <c r="O4" s="33"/>
+      <c r="P4" s="33"/>
+      <c r="Q4" s="33"/>
+      <c r="R4" s="33"/>
+      <c r="S4" s="33"/>
+      <c r="T4" s="33"/>
+      <c r="U4" s="33"/>
+      <c r="V4" s="33"/>
+      <c r="W4" s="33"/>
+      <c r="X4" s="33"/>
+      <c r="Y4" s="33"/>
+      <c r="Z4" s="33"/>
+      <c r="AA4" s="33"/>
+      <c r="AB4" s="33"/>
+      <c r="AC4" s="33"/>
+      <c r="AD4" s="33"/>
+      <c r="AE4" s="33"/>
+      <c r="AF4" s="33"/>
+      <c r="AG4" s="34"/>
+    </row>
+    <row r="5" spans="1:177" ht="12.75" customHeight="1">
+      <c r="A5" s="16"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="35"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="13"/>
+      <c r="M5" s="13"/>
+      <c r="N5" s="13"/>
+      <c r="O5" s="13"/>
+      <c r="P5" s="13"/>
+      <c r="Q5" s="13"/>
+      <c r="R5" s="13"/>
+      <c r="S5" s="13"/>
+      <c r="T5" s="13"/>
+      <c r="U5" s="13"/>
+      <c r="V5" s="13"/>
+      <c r="W5" s="13"/>
+      <c r="X5" s="13"/>
+      <c r="Y5" s="13"/>
+      <c r="Z5" s="13"/>
+      <c r="AA5" s="13"/>
+      <c r="AB5" s="13"/>
+      <c r="AC5" s="13"/>
+      <c r="AD5" s="13"/>
+      <c r="AE5" s="13"/>
+      <c r="AF5" s="13"/>
+      <c r="AG5" s="18"/>
+    </row>
+    <row r="6" spans="1:177" ht="12.75" customHeight="1">
+      <c r="A6" s="16"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="35"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="13"/>
+      <c r="N6" s="13"/>
+      <c r="O6" s="13"/>
+      <c r="P6" s="36"/>
+      <c r="Q6" s="13"/>
+      <c r="R6" s="13"/>
+      <c r="S6" s="13"/>
+      <c r="T6" s="13"/>
+      <c r="U6" s="13"/>
+      <c r="V6" s="13"/>
+      <c r="W6" s="13"/>
+      <c r="X6" s="13"/>
+      <c r="Y6" s="13"/>
+      <c r="Z6" s="13"/>
+      <c r="AA6" s="13"/>
+      <c r="AB6" s="13"/>
+      <c r="AC6" s="13"/>
+      <c r="AD6" s="13"/>
+      <c r="AE6" s="13"/>
+      <c r="AF6" s="13"/>
+      <c r="AG6" s="18"/>
+    </row>
+    <row r="7" spans="1:177" ht="12.75" customHeight="1">
+      <c r="A7" s="16"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="13"/>
+      <c r="L7" s="13"/>
+      <c r="M7" s="13"/>
+      <c r="N7" s="13"/>
+      <c r="O7" s="13"/>
+      <c r="P7" s="36"/>
+      <c r="Q7" s="13"/>
+      <c r="R7" s="13"/>
+      <c r="S7" s="36"/>
+      <c r="T7" s="36"/>
+      <c r="U7" s="36"/>
+      <c r="V7" s="36"/>
+      <c r="W7" s="36"/>
+      <c r="X7" s="36"/>
+      <c r="Y7" s="36"/>
+      <c r="Z7" s="13"/>
+      <c r="AA7" s="13"/>
+      <c r="AB7" s="13"/>
+      <c r="AC7" s="13"/>
+      <c r="AD7" s="13"/>
+      <c r="AE7" s="13"/>
+      <c r="AF7" s="13"/>
+      <c r="AG7" s="18"/>
+    </row>
+    <row r="8" spans="1:177" ht="12.75" customHeight="1">
+      <c r="A8" s="16"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="13"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="13"/>
+      <c r="M8" s="13"/>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13"/>
+      <c r="P8" s="36"/>
+      <c r="Q8" s="13"/>
+      <c r="R8" s="13"/>
+      <c r="S8" s="13"/>
+      <c r="T8" s="36"/>
+      <c r="U8" s="36"/>
+      <c r="V8" s="36"/>
+      <c r="W8" s="36"/>
+      <c r="X8" s="36"/>
+      <c r="Y8" s="36"/>
+      <c r="Z8" s="13"/>
+      <c r="AA8" s="13"/>
+      <c r="AB8" s="13"/>
+      <c r="AC8" s="13"/>
+      <c r="AD8" s="13"/>
+      <c r="AE8" s="13"/>
+      <c r="AF8" s="13"/>
+      <c r="AG8" s="18"/>
+    </row>
+    <row r="9" spans="1:177" ht="12.75" customHeight="1">
+      <c r="A9" s="16"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="13"/>
+      <c r="P9" s="36"/>
+      <c r="Q9" s="13"/>
+      <c r="R9" s="13"/>
+      <c r="S9" s="13"/>
+      <c r="T9" s="36"/>
+      <c r="U9" s="36"/>
+      <c r="V9" s="36"/>
+      <c r="W9" s="36"/>
+      <c r="X9" s="36"/>
+      <c r="Y9" s="36"/>
+      <c r="Z9" s="13"/>
+      <c r="AA9" s="13"/>
+      <c r="AB9" s="13"/>
+      <c r="AC9" s="13"/>
+      <c r="AD9" s="13"/>
+      <c r="AE9" s="13"/>
+      <c r="AF9" s="13"/>
+      <c r="AG9" s="18"/>
+    </row>
+    <row r="10" spans="1:177" ht="12.75" customHeight="1">
+      <c r="A10" s="16"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="13"/>
+      <c r="L10" s="13"/>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13"/>
+      <c r="P10" s="36"/>
+      <c r="Q10" s="13"/>
+      <c r="R10" s="13"/>
+      <c r="S10" s="36"/>
+      <c r="T10" s="36"/>
+      <c r="U10" s="36"/>
+      <c r="V10" s="36"/>
+      <c r="W10" s="36"/>
+      <c r="X10" s="36"/>
+      <c r="Y10" s="36"/>
+      <c r="Z10" s="13"/>
+      <c r="AA10" s="13"/>
+      <c r="AB10" s="13"/>
+      <c r="AC10" s="13"/>
+      <c r="AD10" s="13"/>
+      <c r="AE10" s="13"/>
+      <c r="AF10" s="13"/>
+      <c r="AG10" s="18"/>
+    </row>
+    <row r="11" spans="1:177" ht="12.75" customHeight="1">
+      <c r="A11" s="16"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="13"/>
+      <c r="L11" s="13"/>
+      <c r="M11" s="13"/>
+      <c r="N11" s="13"/>
+      <c r="O11" s="13"/>
+      <c r="P11" s="36"/>
+      <c r="Q11" s="13"/>
+      <c r="R11" s="13"/>
+      <c r="S11" s="13"/>
+      <c r="T11" s="13"/>
+      <c r="U11" s="13"/>
+      <c r="V11" s="13"/>
+      <c r="W11" s="13"/>
+      <c r="X11" s="13"/>
+      <c r="Y11" s="13"/>
+      <c r="Z11" s="13"/>
+      <c r="AA11" s="13"/>
+      <c r="AB11" s="13"/>
+      <c r="AC11" s="13"/>
+      <c r="AD11" s="13"/>
+      <c r="AE11" s="13"/>
+      <c r="AF11" s="13"/>
+      <c r="AG11" s="18"/>
+    </row>
+    <row r="12" spans="1:177" ht="12.75" customHeight="1">
+      <c r="A12" s="16"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="13"/>
+      <c r="K12" s="13"/>
+      <c r="L12" s="13"/>
+      <c r="M12" s="13"/>
+      <c r="N12" s="13"/>
+      <c r="O12" s="13"/>
+      <c r="P12" s="36"/>
+      <c r="Q12" s="13"/>
+      <c r="R12" s="13"/>
+      <c r="S12" s="13"/>
+      <c r="T12" s="13"/>
+      <c r="U12" s="13"/>
+      <c r="V12" s="13"/>
+      <c r="W12" s="13"/>
+      <c r="X12" s="13"/>
+      <c r="Y12" s="13"/>
+      <c r="Z12" s="13"/>
+      <c r="AA12" s="13"/>
+      <c r="AB12" s="13"/>
+      <c r="AC12" s="13"/>
+      <c r="AD12" s="13"/>
+      <c r="AE12" s="13"/>
+      <c r="AF12" s="13"/>
+      <c r="AG12" s="18"/>
+    </row>
+    <row r="13" spans="1:177" ht="12.75" customHeight="1">
+      <c r="A13" s="16"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="13"/>
+      <c r="J13" s="13"/>
+      <c r="K13" s="13"/>
+      <c r="L13" s="13"/>
+      <c r="M13" s="13"/>
+      <c r="N13" s="13"/>
+      <c r="O13" s="13"/>
+      <c r="P13" s="36"/>
+      <c r="Q13" s="13"/>
+      <c r="R13" s="13"/>
+      <c r="S13" s="13"/>
+      <c r="T13" s="13"/>
+      <c r="U13" s="13"/>
+      <c r="V13" s="36"/>
+      <c r="W13" s="36"/>
+      <c r="X13" s="13"/>
+      <c r="Y13" s="13"/>
+      <c r="Z13" s="13"/>
+      <c r="AA13" s="13"/>
+      <c r="AB13" s="13"/>
+      <c r="AC13" s="13"/>
+      <c r="AD13" s="13"/>
+      <c r="AE13" s="13"/>
+      <c r="AF13" s="13"/>
+      <c r="AG13" s="18"/>
+    </row>
+    <row r="14" spans="1:177" ht="12.75" customHeight="1">
+      <c r="A14" s="16"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="13"/>
+      <c r="K14" s="13"/>
+      <c r="L14" s="13"/>
+      <c r="M14" s="13"/>
+      <c r="N14" s="13"/>
+      <c r="O14" s="13"/>
+      <c r="P14" s="36"/>
+      <c r="Q14" s="13"/>
+      <c r="R14" s="13"/>
+      <c r="S14" s="13"/>
+      <c r="T14" s="13"/>
+      <c r="U14" s="13"/>
+      <c r="V14" s="13"/>
+      <c r="W14" s="13"/>
+      <c r="X14" s="13"/>
+      <c r="Y14" s="13"/>
+      <c r="Z14" s="13"/>
+      <c r="AA14" s="13"/>
+      <c r="AB14" s="13"/>
+      <c r="AC14" s="13"/>
+      <c r="AD14" s="13"/>
+      <c r="AE14" s="13"/>
+      <c r="AF14" s="13"/>
+      <c r="AG14" s="18"/>
+    </row>
+    <row r="15" spans="1:177" ht="12.75" customHeight="1">
+      <c r="A15" s="16"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="13"/>
+      <c r="J15" s="13"/>
+      <c r="K15" s="13"/>
+      <c r="L15" s="13"/>
+      <c r="M15" s="13"/>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13"/>
+      <c r="P15" s="36"/>
+      <c r="Q15" s="13"/>
+      <c r="R15" s="13"/>
+      <c r="S15" s="13"/>
+      <c r="T15" s="13"/>
+      <c r="U15" s="13"/>
+      <c r="V15" s="13"/>
+      <c r="W15" s="13"/>
+      <c r="X15" s="13"/>
+      <c r="Y15" s="13"/>
+      <c r="Z15" s="13"/>
+      <c r="AA15" s="13"/>
+      <c r="AB15" s="13"/>
+      <c r="AC15" s="13"/>
+      <c r="AD15" s="13"/>
+      <c r="AE15" s="13"/>
+      <c r="AF15" s="13"/>
+      <c r="AG15" s="18"/>
+    </row>
+    <row r="16" spans="1:177" ht="12.75" customHeight="1">
+      <c r="A16" s="16"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="13"/>
+      <c r="I16" s="13"/>
+      <c r="J16" s="13"/>
+      <c r="K16" s="13"/>
+      <c r="L16" s="13"/>
+      <c r="M16" s="13"/>
+      <c r="N16" s="13"/>
+      <c r="O16" s="13"/>
+      <c r="P16" s="36"/>
+      <c r="Q16" s="13"/>
+      <c r="R16" s="13"/>
+      <c r="S16" s="36"/>
+      <c r="T16" s="13"/>
+      <c r="U16" s="13"/>
+      <c r="V16" s="13"/>
+      <c r="W16" s="13"/>
+      <c r="X16" s="13"/>
+      <c r="Y16" s="13"/>
+      <c r="Z16" s="13"/>
+      <c r="AA16" s="13"/>
+      <c r="AB16" s="13"/>
+      <c r="AC16" s="13"/>
+      <c r="AD16" s="13"/>
+      <c r="AE16" s="13"/>
+      <c r="AF16" s="13"/>
+      <c r="AG16" s="18"/>
+    </row>
+    <row r="17" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A17" s="16"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="13"/>
+      <c r="K17" s="13"/>
+      <c r="L17" s="13"/>
+      <c r="M17" s="13"/>
+      <c r="N17" s="13"/>
+      <c r="O17" s="13"/>
+      <c r="P17" s="36"/>
+      <c r="Q17" s="13"/>
+      <c r="R17" s="13"/>
+      <c r="S17" s="13"/>
+      <c r="T17" s="13"/>
+      <c r="U17" s="13"/>
+      <c r="V17" s="13"/>
+      <c r="W17" s="36"/>
+      <c r="X17" s="13"/>
+      <c r="Y17" s="13"/>
+      <c r="Z17" s="13"/>
+      <c r="AA17" s="13"/>
+      <c r="AB17" s="13"/>
+      <c r="AC17" s="13"/>
+      <c r="AD17" s="13"/>
+      <c r="AE17" s="13"/>
+      <c r="AF17" s="13"/>
+      <c r="AG17" s="18"/>
+    </row>
+    <row r="18" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A18" s="16"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="13"/>
+      <c r="J18" s="13"/>
+      <c r="K18" s="13"/>
+      <c r="L18" s="13"/>
+      <c r="M18" s="13"/>
+      <c r="N18" s="13"/>
+      <c r="O18" s="13"/>
+      <c r="P18" s="36"/>
+      <c r="Q18" s="13"/>
+      <c r="R18" s="13"/>
+      <c r="S18" s="13"/>
+      <c r="T18" s="13"/>
+      <c r="U18" s="13"/>
+      <c r="V18" s="36"/>
+      <c r="W18" s="36"/>
+      <c r="X18" s="13"/>
+      <c r="Y18" s="13"/>
+      <c r="Z18" s="13"/>
+      <c r="AA18" s="13"/>
+      <c r="AB18" s="13"/>
+      <c r="AC18" s="13"/>
+      <c r="AD18" s="13"/>
+      <c r="AE18" s="13"/>
+      <c r="AF18" s="13"/>
+      <c r="AG18" s="18"/>
+    </row>
+    <row r="19" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A19" s="16"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="13"/>
+      <c r="J19" s="13"/>
+      <c r="K19" s="13"/>
+      <c r="L19" s="13"/>
+      <c r="M19" s="13"/>
+      <c r="N19" s="13"/>
+      <c r="O19" s="13"/>
+      <c r="P19" s="36"/>
+      <c r="Q19" s="13"/>
+      <c r="R19" s="13"/>
+      <c r="S19" s="13"/>
+      <c r="T19" s="13"/>
+      <c r="U19" s="13"/>
+      <c r="V19" s="13"/>
+      <c r="W19" s="13"/>
+      <c r="X19" s="13"/>
+      <c r="Y19" s="13"/>
+      <c r="Z19" s="13"/>
+      <c r="AA19" s="13"/>
+      <c r="AB19" s="13"/>
+      <c r="AC19" s="13"/>
+      <c r="AD19" s="13"/>
+      <c r="AE19" s="13"/>
+      <c r="AF19" s="13"/>
+      <c r="AG19" s="18"/>
+    </row>
+    <row r="20" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A20" s="16"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="13"/>
+      <c r="J20" s="13"/>
+      <c r="K20" s="13"/>
+      <c r="L20" s="13"/>
+      <c r="M20" s="13"/>
+      <c r="N20" s="13"/>
+      <c r="O20" s="13"/>
+      <c r="P20" s="36"/>
+      <c r="Q20" s="13"/>
+      <c r="R20" s="13"/>
+      <c r="S20" s="13"/>
+      <c r="T20" s="13"/>
+      <c r="U20" s="13"/>
+      <c r="V20" s="13"/>
+      <c r="W20" s="13"/>
+      <c r="X20" s="13"/>
+      <c r="Y20" s="13"/>
+      <c r="Z20" s="13"/>
+      <c r="AA20" s="13"/>
+      <c r="AB20" s="13"/>
+      <c r="AC20" s="13"/>
+      <c r="AD20" s="13"/>
+      <c r="AE20" s="13"/>
+      <c r="AF20" s="13"/>
+      <c r="AG20" s="18"/>
+    </row>
+    <row r="21" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A21" s="16"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="13"/>
+      <c r="J21" s="13"/>
+      <c r="K21" s="13"/>
+      <c r="L21" s="13"/>
+      <c r="M21" s="13"/>
+      <c r="N21" s="13"/>
+      <c r="O21" s="13"/>
+      <c r="P21" s="36"/>
+      <c r="Q21" s="13"/>
+      <c r="R21" s="13"/>
+      <c r="S21" s="36"/>
+      <c r="T21" s="36"/>
+      <c r="U21" s="36"/>
+      <c r="V21" s="36"/>
+      <c r="W21" s="36"/>
+      <c r="X21" s="36"/>
+      <c r="Y21" s="36"/>
+      <c r="Z21" s="13"/>
+      <c r="AA21" s="13"/>
+      <c r="AB21" s="13"/>
+      <c r="AC21" s="13"/>
+      <c r="AD21" s="13"/>
+      <c r="AE21" s="13"/>
+      <c r="AF21" s="13"/>
+      <c r="AG21" s="18"/>
+    </row>
+    <row r="22" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A22" s="16"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="13"/>
+      <c r="J22" s="13"/>
+      <c r="K22" s="13"/>
+      <c r="L22" s="13"/>
+      <c r="M22" s="13"/>
+      <c r="N22" s="13"/>
+      <c r="O22" s="13"/>
+      <c r="P22" s="36"/>
+      <c r="Q22" s="13"/>
+      <c r="R22" s="13"/>
+      <c r="S22" s="13"/>
+      <c r="T22" s="36"/>
+      <c r="U22" s="36"/>
+      <c r="V22" s="36"/>
+      <c r="W22" s="36"/>
+      <c r="X22" s="36"/>
+      <c r="Y22" s="36"/>
+      <c r="Z22" s="13"/>
+      <c r="AA22" s="13"/>
+      <c r="AB22" s="13"/>
+      <c r="AC22" s="13"/>
+      <c r="AD22" s="13"/>
+      <c r="AE22" s="13"/>
+      <c r="AF22" s="13"/>
+      <c r="AG22" s="18"/>
+    </row>
+    <row r="23" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A23" s="16"/>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13"/>
+      <c r="I23" s="13"/>
+      <c r="J23" s="13"/>
+      <c r="K23" s="13"/>
+      <c r="L23" s="13"/>
+      <c r="M23" s="13"/>
+      <c r="N23" s="13"/>
+      <c r="O23" s="13"/>
+      <c r="P23" s="36"/>
+      <c r="Q23" s="13"/>
+      <c r="R23" s="13"/>
+      <c r="S23" s="36"/>
+      <c r="T23" s="36"/>
+      <c r="U23" s="36"/>
+      <c r="V23" s="36"/>
+      <c r="W23" s="36"/>
+      <c r="X23" s="36"/>
+      <c r="Y23" s="36"/>
+      <c r="Z23" s="13"/>
+      <c r="AA23" s="13"/>
+      <c r="AB23" s="13"/>
+      <c r="AC23" s="13"/>
+      <c r="AD23" s="13"/>
+      <c r="AE23" s="13"/>
+      <c r="AF23" s="13"/>
+      <c r="AG23" s="18"/>
+    </row>
+    <row r="24" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A24" s="16"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="13"/>
+      <c r="J24" s="13"/>
+      <c r="K24" s="13"/>
+      <c r="L24" s="13"/>
+      <c r="M24" s="13"/>
+      <c r="N24" s="13"/>
+      <c r="O24" s="13"/>
+      <c r="P24" s="36"/>
+      <c r="Q24" s="13"/>
+      <c r="R24" s="13"/>
+      <c r="S24" s="36"/>
+      <c r="T24" s="36"/>
+      <c r="U24" s="36"/>
+      <c r="V24" s="36"/>
+      <c r="W24" s="36"/>
+      <c r="X24" s="36"/>
+      <c r="Y24" s="36"/>
+      <c r="Z24" s="13"/>
+      <c r="AA24" s="13"/>
+      <c r="AB24" s="13"/>
+      <c r="AC24" s="13"/>
+      <c r="AD24" s="13"/>
+      <c r="AE24" s="13"/>
+      <c r="AF24" s="13"/>
+      <c r="AG24" s="18"/>
+    </row>
+    <row r="25" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A25" s="16"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="13"/>
+      <c r="H25" s="13"/>
+      <c r="I25" s="13"/>
+      <c r="J25" s="13"/>
+      <c r="K25" s="13"/>
+      <c r="L25" s="13"/>
+      <c r="M25" s="13"/>
+      <c r="N25" s="13"/>
+      <c r="O25" s="13"/>
+      <c r="P25" s="36"/>
+      <c r="Q25" s="13"/>
+      <c r="R25" s="13"/>
+      <c r="S25" s="36"/>
+      <c r="T25" s="36"/>
+      <c r="U25" s="36"/>
+      <c r="V25" s="36"/>
+      <c r="W25" s="36"/>
+      <c r="X25" s="36"/>
+      <c r="Y25" s="36"/>
+      <c r="Z25" s="13"/>
+      <c r="AA25" s="13"/>
+      <c r="AB25" s="13"/>
+      <c r="AC25" s="13"/>
+      <c r="AD25" s="13"/>
+      <c r="AE25" s="13"/>
+      <c r="AF25" s="13"/>
+      <c r="AG25" s="18"/>
+    </row>
+    <row r="26" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A26" s="16"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="13"/>
+      <c r="I26" s="13"/>
+      <c r="J26" s="13"/>
+      <c r="K26" s="13"/>
+      <c r="L26" s="13"/>
+      <c r="M26" s="13"/>
+      <c r="N26" s="13"/>
+      <c r="O26" s="13"/>
+      <c r="P26" s="36"/>
+      <c r="Q26" s="13"/>
+      <c r="R26" s="13"/>
+      <c r="S26" s="36"/>
+      <c r="T26" s="36"/>
+      <c r="U26" s="36"/>
+      <c r="V26" s="36"/>
+      <c r="W26" s="36"/>
+      <c r="X26" s="36"/>
+      <c r="Y26" s="36"/>
+      <c r="Z26" s="13"/>
+      <c r="AA26" s="13"/>
+      <c r="AB26" s="13"/>
+      <c r="AC26" s="13"/>
+      <c r="AD26" s="13"/>
+      <c r="AE26" s="13"/>
+      <c r="AF26" s="13"/>
+      <c r="AG26" s="18"/>
+    </row>
+    <row r="27" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A27" s="16"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="13"/>
+      <c r="H27" s="13"/>
+      <c r="I27" s="13"/>
+      <c r="J27" s="13"/>
+      <c r="K27" s="13"/>
+      <c r="L27" s="13"/>
+      <c r="M27" s="13"/>
+      <c r="N27" s="13"/>
+      <c r="O27" s="13"/>
+      <c r="P27" s="36"/>
+      <c r="Q27" s="13"/>
+      <c r="R27" s="13"/>
+      <c r="S27" s="36"/>
+      <c r="T27" s="36"/>
+      <c r="U27" s="36"/>
+      <c r="V27" s="36"/>
+      <c r="W27" s="36"/>
+      <c r="X27" s="36"/>
+      <c r="Y27" s="36"/>
+      <c r="Z27" s="13"/>
+      <c r="AA27" s="13"/>
+      <c r="AB27" s="13"/>
+      <c r="AC27" s="13"/>
+      <c r="AD27" s="13"/>
+      <c r="AE27" s="13"/>
+      <c r="AF27" s="13"/>
+      <c r="AG27" s="18"/>
+    </row>
+    <row r="28" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A28" s="16"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="13"/>
+      <c r="J28" s="13"/>
+      <c r="K28" s="13"/>
+      <c r="L28" s="13"/>
+      <c r="M28" s="13"/>
+      <c r="N28" s="13"/>
+      <c r="O28" s="13"/>
+      <c r="P28" s="36"/>
+      <c r="Q28" s="13"/>
+      <c r="R28" s="13"/>
+      <c r="S28" s="36"/>
+      <c r="T28" s="36"/>
+      <c r="U28" s="36"/>
+      <c r="V28" s="36"/>
+      <c r="W28" s="36"/>
+      <c r="X28" s="36"/>
+      <c r="Y28" s="36"/>
+      <c r="Z28" s="13"/>
+      <c r="AA28" s="13"/>
+      <c r="AB28" s="13"/>
+      <c r="AC28" s="13"/>
+      <c r="AD28" s="13"/>
+      <c r="AE28" s="13"/>
+      <c r="AF28" s="13"/>
+      <c r="AG28" s="18"/>
+    </row>
+    <row r="29" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A29" s="16"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="13"/>
+      <c r="I29" s="13"/>
+      <c r="J29" s="13"/>
+      <c r="K29" s="13"/>
+      <c r="L29" s="13"/>
+      <c r="M29" s="13"/>
+      <c r="N29" s="13"/>
+      <c r="O29" s="13"/>
+      <c r="P29" s="13"/>
+      <c r="Q29" s="13"/>
+      <c r="R29" s="13"/>
+      <c r="S29" s="13"/>
+      <c r="T29" s="13"/>
+      <c r="U29" s="13"/>
+      <c r="V29" s="13"/>
+      <c r="W29" s="13"/>
+      <c r="X29" s="13"/>
+      <c r="Y29" s="13"/>
+      <c r="Z29" s="13"/>
+      <c r="AA29" s="13"/>
+      <c r="AB29" s="13"/>
+      <c r="AC29" s="13"/>
+      <c r="AD29" s="13"/>
+      <c r="AE29" s="13"/>
+      <c r="AF29" s="13"/>
+      <c r="AG29" s="18"/>
+    </row>
+    <row r="30" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A30" s="16"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="13"/>
+      <c r="J30" s="13"/>
+      <c r="K30" s="13"/>
+      <c r="L30" s="13"/>
+      <c r="M30" s="13"/>
+      <c r="N30" s="13"/>
+      <c r="O30" s="13"/>
+      <c r="P30" s="13"/>
+      <c r="Q30" s="13"/>
+      <c r="R30" s="13"/>
+      <c r="S30" s="13"/>
+      <c r="T30" s="13"/>
+      <c r="U30" s="13"/>
+      <c r="V30" s="13"/>
+      <c r="W30" s="13"/>
+      <c r="X30" s="13"/>
+      <c r="Y30" s="13"/>
+      <c r="Z30" s="13"/>
+      <c r="AA30" s="13"/>
+      <c r="AB30" s="13"/>
+      <c r="AC30" s="13"/>
+      <c r="AD30" s="13"/>
+      <c r="AE30" s="13"/>
+      <c r="AF30" s="13"/>
+      <c r="AG30" s="18"/>
+    </row>
+    <row r="31" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A31" s="16"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13"/>
+      <c r="G31" s="13"/>
+      <c r="H31" s="13"/>
+      <c r="I31" s="13"/>
+      <c r="J31" s="13"/>
+      <c r="K31" s="13"/>
+      <c r="L31" s="13"/>
+      <c r="M31" s="13"/>
+      <c r="N31" s="13"/>
+      <c r="O31" s="13"/>
+      <c r="P31" s="13"/>
+      <c r="Q31" s="13"/>
+      <c r="R31" s="13"/>
+      <c r="S31" s="13"/>
+      <c r="T31" s="13"/>
+      <c r="U31" s="13"/>
+      <c r="V31" s="13"/>
+      <c r="W31" s="13"/>
+      <c r="X31" s="13"/>
+      <c r="Y31" s="13"/>
+      <c r="Z31" s="13"/>
+      <c r="AA31" s="13"/>
+      <c r="AB31" s="13"/>
+      <c r="AC31" s="13"/>
+      <c r="AD31" s="13"/>
+      <c r="AE31" s="13"/>
+      <c r="AF31" s="13"/>
+      <c r="AG31" s="18"/>
+    </row>
+    <row r="32" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A32" s="16"/>
+      <c r="B32" s="13"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+      <c r="H32" s="13"/>
+      <c r="I32" s="13"/>
+      <c r="J32" s="13"/>
+      <c r="K32" s="13"/>
+      <c r="L32" s="13"/>
+      <c r="M32" s="13"/>
+      <c r="N32" s="13"/>
+      <c r="O32" s="13"/>
+      <c r="P32" s="13"/>
+      <c r="Q32" s="13"/>
+      <c r="R32" s="13"/>
+      <c r="S32" s="13"/>
+      <c r="T32" s="13"/>
+      <c r="U32" s="13"/>
+      <c r="V32" s="13"/>
+      <c r="W32" s="13"/>
+      <c r="X32" s="13"/>
+      <c r="Y32" s="13"/>
+      <c r="Z32" s="13"/>
+      <c r="AA32" s="13"/>
+      <c r="AB32" s="13"/>
+      <c r="AC32" s="13"/>
+      <c r="AD32" s="13"/>
+      <c r="AE32" s="13"/>
+      <c r="AF32" s="13"/>
+      <c r="AG32" s="18"/>
+    </row>
+    <row r="33" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A33" s="16"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="13"/>
+      <c r="F33" s="13"/>
+      <c r="G33" s="13"/>
+      <c r="H33" s="13"/>
+      <c r="I33" s="13"/>
+      <c r="J33" s="13"/>
+      <c r="K33" s="13"/>
+      <c r="L33" s="13"/>
+      <c r="M33" s="13"/>
+      <c r="N33" s="13"/>
+      <c r="O33" s="13"/>
+      <c r="P33" s="13"/>
+      <c r="Q33" s="13"/>
+      <c r="R33" s="13"/>
+      <c r="S33" s="13"/>
+      <c r="T33" s="13"/>
+      <c r="U33" s="13"/>
+      <c r="V33" s="13"/>
+      <c r="W33" s="13"/>
+      <c r="X33" s="13"/>
+      <c r="Y33" s="13"/>
+      <c r="Z33" s="13"/>
+      <c r="AA33" s="13"/>
+      <c r="AB33" s="13"/>
+      <c r="AC33" s="13"/>
+      <c r="AD33" s="13"/>
+      <c r="AE33" s="13"/>
+      <c r="AF33" s="13"/>
+      <c r="AG33" s="18"/>
+    </row>
+    <row r="34" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A34" s="16"/>
+      <c r="B34" s="13"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="13"/>
+      <c r="H34" s="13"/>
+      <c r="I34" s="13"/>
+      <c r="J34" s="13"/>
+      <c r="K34" s="13"/>
+      <c r="L34" s="13"/>
+      <c r="M34" s="13"/>
+      <c r="N34" s="13"/>
+      <c r="O34" s="13"/>
+      <c r="P34" s="13"/>
+      <c r="Q34" s="13"/>
+      <c r="R34" s="13"/>
+      <c r="S34" s="13"/>
+      <c r="T34" s="13"/>
+      <c r="U34" s="13"/>
+      <c r="V34" s="13"/>
+      <c r="W34" s="13"/>
+      <c r="X34" s="13"/>
+      <c r="Y34" s="13"/>
+      <c r="Z34" s="13"/>
+      <c r="AA34" s="13"/>
+      <c r="AB34" s="13"/>
+      <c r="AC34" s="13"/>
+      <c r="AD34" s="13"/>
+      <c r="AE34" s="13"/>
+      <c r="AF34" s="13"/>
+      <c r="AG34" s="18"/>
+    </row>
+    <row r="35" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A35" s="16"/>
+      <c r="B35" s="13"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
+      <c r="H35" s="13"/>
+      <c r="I35" s="13"/>
+      <c r="J35" s="13"/>
+      <c r="K35" s="13"/>
+      <c r="L35" s="13"/>
+      <c r="M35" s="13"/>
+      <c r="N35" s="13"/>
+      <c r="O35" s="13"/>
+      <c r="P35" s="13"/>
+      <c r="Q35" s="13"/>
+      <c r="R35" s="13"/>
+      <c r="S35" s="13"/>
+      <c r="T35" s="13"/>
+      <c r="U35" s="13"/>
+      <c r="V35" s="13"/>
+      <c r="W35" s="13"/>
+      <c r="X35" s="13"/>
+      <c r="Y35" s="13"/>
+      <c r="Z35" s="13"/>
+      <c r="AA35" s="13"/>
+      <c r="AB35" s="13"/>
+      <c r="AC35" s="13"/>
+      <c r="AD35" s="13"/>
+      <c r="AE35" s="13"/>
+      <c r="AF35" s="13"/>
+      <c r="AG35" s="18"/>
+    </row>
+    <row r="36" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A36" s="16"/>
+      <c r="B36" s="13"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="13"/>
+      <c r="H36" s="13"/>
+      <c r="I36" s="13"/>
+      <c r="J36" s="13"/>
+      <c r="K36" s="13"/>
+      <c r="L36" s="13"/>
+      <c r="M36" s="13"/>
+      <c r="N36" s="13"/>
+      <c r="O36" s="13"/>
+      <c r="P36" s="13"/>
+      <c r="Q36" s="13"/>
+      <c r="R36" s="13"/>
+      <c r="S36" s="13"/>
+      <c r="T36" s="13"/>
+      <c r="U36" s="13"/>
+      <c r="V36" s="13"/>
+      <c r="W36" s="13"/>
+      <c r="X36" s="13"/>
+      <c r="Y36" s="13"/>
+      <c r="Z36" s="13"/>
+      <c r="AA36" s="13"/>
+      <c r="AB36" s="13"/>
+      <c r="AC36" s="13"/>
+      <c r="AD36" s="13"/>
+      <c r="AE36" s="13"/>
+      <c r="AF36" s="13"/>
+      <c r="AG36" s="18"/>
+    </row>
+    <row r="37" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A37" s="16"/>
+      <c r="B37" s="13"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="13"/>
+      <c r="H37" s="13"/>
+      <c r="I37" s="13"/>
+      <c r="J37" s="13"/>
+      <c r="K37" s="13"/>
+      <c r="L37" s="13"/>
+      <c r="M37" s="13"/>
+      <c r="N37" s="13"/>
+      <c r="O37" s="13"/>
+      <c r="P37" s="13"/>
+      <c r="Q37" s="13"/>
+      <c r="R37" s="13"/>
+      <c r="S37" s="13"/>
+      <c r="T37" s="13"/>
+      <c r="U37" s="13"/>
+      <c r="V37" s="13"/>
+      <c r="W37" s="13"/>
+      <c r="X37" s="13"/>
+      <c r="Y37" s="13"/>
+      <c r="Z37" s="13"/>
+      <c r="AA37" s="13"/>
+      <c r="AB37" s="13"/>
+      <c r="AC37" s="13"/>
+      <c r="AD37" s="13"/>
+      <c r="AE37" s="13"/>
+      <c r="AF37" s="13"/>
+      <c r="AG37" s="18"/>
+    </row>
+    <row r="38" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A38" s="27"/>
+      <c r="B38" s="28"/>
+      <c r="C38" s="28"/>
+      <c r="D38" s="28"/>
+      <c r="E38" s="28"/>
+      <c r="F38" s="28"/>
+      <c r="G38" s="28"/>
+      <c r="H38" s="28"/>
+      <c r="I38" s="28"/>
+      <c r="J38" s="28"/>
+      <c r="K38" s="28"/>
+      <c r="L38" s="28"/>
+      <c r="M38" s="28"/>
+      <c r="N38" s="28"/>
+      <c r="O38" s="28"/>
+      <c r="P38" s="28"/>
+      <c r="Q38" s="28"/>
+      <c r="R38" s="28"/>
+      <c r="S38" s="28"/>
+      <c r="T38" s="28"/>
+      <c r="U38" s="28"/>
+      <c r="V38" s="28"/>
+      <c r="W38" s="28"/>
+      <c r="X38" s="28"/>
+      <c r="Y38" s="28"/>
+      <c r="Z38" s="28"/>
+      <c r="AA38" s="28"/>
+      <c r="AB38" s="28"/>
+      <c r="AC38" s="28"/>
+      <c r="AD38" s="28"/>
+      <c r="AE38" s="28"/>
+      <c r="AF38" s="28"/>
+      <c r="AG38" s="30"/>
+    </row>
+    <row r="39" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A39" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="B39" s="13"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="13"/>
+      <c r="F39" s="13"/>
+      <c r="G39" s="13"/>
+      <c r="H39" s="13"/>
+      <c r="I39" s="13"/>
+      <c r="J39" s="13"/>
+      <c r="K39" s="13"/>
+      <c r="L39" s="13"/>
+      <c r="M39" s="13"/>
+      <c r="N39" s="13"/>
+      <c r="O39" s="13"/>
+      <c r="P39" s="13"/>
+      <c r="Q39" s="13"/>
+      <c r="R39" s="13"/>
+      <c r="S39" s="13"/>
+      <c r="T39" s="13"/>
+      <c r="U39" s="13"/>
+      <c r="V39" s="13"/>
+      <c r="W39" s="13"/>
+      <c r="X39" s="13"/>
+      <c r="Y39" s="13"/>
+      <c r="Z39" s="13"/>
+      <c r="AA39" s="13"/>
+      <c r="AB39" s="13"/>
+      <c r="AC39" s="13"/>
+      <c r="AD39" s="13"/>
+      <c r="AE39" s="13"/>
+      <c r="AF39" s="13"/>
+      <c r="AG39" s="18"/>
+    </row>
+    <row r="40" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A40" s="16"/>
+      <c r="B40" s="13"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="13"/>
+      <c r="E40" s="13"/>
+      <c r="F40" s="13"/>
+      <c r="G40" s="13"/>
+      <c r="H40" s="13"/>
+      <c r="I40" s="13"/>
+      <c r="J40" s="13"/>
+      <c r="K40" s="13"/>
+      <c r="L40" s="13"/>
+      <c r="M40" s="13"/>
+      <c r="N40" s="13"/>
+      <c r="O40" s="13"/>
+      <c r="P40" s="13"/>
+      <c r="Q40" s="13"/>
+      <c r="R40" s="13"/>
+      <c r="S40" s="13"/>
+      <c r="T40" s="13"/>
+      <c r="U40" s="13"/>
+      <c r="V40" s="13"/>
+      <c r="W40" s="13"/>
+      <c r="X40" s="13"/>
+      <c r="Y40" s="13"/>
+      <c r="Z40" s="13"/>
+      <c r="AA40" s="13"/>
+      <c r="AB40" s="13"/>
+      <c r="AC40" s="13"/>
+      <c r="AD40" s="13"/>
+      <c r="AE40" s="13"/>
+      <c r="AF40" s="13"/>
+      <c r="AG40" s="18"/>
+    </row>
+    <row r="41" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A41" s="16"/>
+      <c r="B41" s="13"/>
+      <c r="C41" s="13"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="13"/>
+      <c r="F41" s="13"/>
+      <c r="G41" s="13"/>
+      <c r="H41" s="13"/>
+      <c r="I41" s="13"/>
+      <c r="J41" s="13"/>
+      <c r="K41" s="13"/>
+      <c r="L41" s="13"/>
+      <c r="M41" s="13"/>
+      <c r="N41" s="13"/>
+      <c r="O41" s="13"/>
+      <c r="P41" s="13"/>
+      <c r="Q41" s="13"/>
+      <c r="R41" s="13"/>
+      <c r="S41" s="13"/>
+      <c r="T41" s="13"/>
+      <c r="U41" s="13"/>
+      <c r="V41" s="13"/>
+      <c r="W41" s="13"/>
+      <c r="X41" s="13"/>
+      <c r="Y41" s="13"/>
+      <c r="Z41" s="13"/>
+      <c r="AA41" s="13"/>
+      <c r="AB41" s="13"/>
+      <c r="AC41" s="13"/>
+      <c r="AD41" s="13"/>
+      <c r="AE41" s="13"/>
+      <c r="AF41" s="13"/>
+      <c r="AG41" s="18"/>
+    </row>
+    <row r="42" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A42" s="27"/>
+      <c r="B42" s="28"/>
+      <c r="C42" s="28"/>
+      <c r="D42" s="28"/>
+      <c r="E42" s="28"/>
+      <c r="F42" s="28"/>
+      <c r="G42" s="28"/>
+      <c r="H42" s="28"/>
+      <c r="I42" s="28"/>
+      <c r="J42" s="28"/>
+      <c r="K42" s="28"/>
+      <c r="L42" s="28"/>
+      <c r="M42" s="28"/>
+      <c r="N42" s="28"/>
+      <c r="O42" s="28"/>
+      <c r="P42" s="28"/>
+      <c r="Q42" s="28"/>
+      <c r="R42" s="28"/>
+      <c r="S42" s="28"/>
+      <c r="T42" s="28"/>
+      <c r="U42" s="28"/>
+      <c r="V42" s="28"/>
+      <c r="W42" s="28"/>
+      <c r="X42" s="28"/>
+      <c r="Y42" s="28"/>
+      <c r="Z42" s="28"/>
+      <c r="AA42" s="28"/>
+      <c r="AB42" s="28"/>
+      <c r="AC42" s="28"/>
+      <c r="AD42" s="28"/>
+      <c r="AE42" s="28"/>
+      <c r="AF42" s="28"/>
+      <c r="AG42" s="30"/>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="G3:AC3"/>
+    <mergeCell ref="AD3:AE3"/>
+    <mergeCell ref="AF3:AG3"/>
+    <mergeCell ref="A1:AG1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="G2:AC2"/>
+    <mergeCell ref="AD2:AE2"/>
+    <mergeCell ref="AF2:AG2"/>
+  </mergeCells>
+  <phoneticPr fontId="4"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.59055118110236227" bottom="0.39370078740157483" header="0.51181102362204722" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <headerFooter alignWithMargins="0">
+    <oddFooter>&amp;LCopyright© 2005 System Integrator Corp.&amp;C&amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C1E6855-304D-4E72-A746-EC9944D8D8EE}">
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
@@ -6774,127 +9805,127 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:177" ht="12.75" customHeight="1">
-      <c r="A1" s="86" t="s">
+      <c r="A1" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="86"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="86"/>
-      <c r="E1" s="86"/>
-      <c r="F1" s="86"/>
-      <c r="G1" s="86"/>
-      <c r="H1" s="86"/>
-      <c r="I1" s="86"/>
-      <c r="J1" s="86"/>
-      <c r="K1" s="86"/>
-      <c r="L1" s="86"/>
-      <c r="M1" s="86"/>
-      <c r="N1" s="86"/>
-      <c r="O1" s="86"/>
-      <c r="P1" s="86"/>
-      <c r="Q1" s="86"/>
-      <c r="R1" s="86"/>
-      <c r="S1" s="86"/>
-      <c r="T1" s="86"/>
-      <c r="U1" s="86"/>
-      <c r="V1" s="86"/>
-      <c r="W1" s="86"/>
-      <c r="X1" s="86"/>
-      <c r="Y1" s="86"/>
-      <c r="Z1" s="86"/>
-      <c r="AA1" s="86"/>
-      <c r="AB1" s="86"/>
-      <c r="AC1" s="86"/>
-      <c r="AD1" s="86"/>
-      <c r="AE1" s="86"/>
-      <c r="AF1" s="86"/>
-      <c r="AG1" s="86"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
+      <c r="O1" s="78"/>
+      <c r="P1" s="78"/>
+      <c r="Q1" s="78"/>
+      <c r="R1" s="78"/>
+      <c r="S1" s="78"/>
+      <c r="T1" s="78"/>
+      <c r="U1" s="78"/>
+      <c r="V1" s="78"/>
+      <c r="W1" s="78"/>
+      <c r="X1" s="78"/>
+      <c r="Y1" s="78"/>
+      <c r="Z1" s="78"/>
+      <c r="AA1" s="78"/>
+      <c r="AB1" s="78"/>
+      <c r="AC1" s="78"/>
+      <c r="AD1" s="78"/>
+      <c r="AE1" s="78"/>
+      <c r="AF1" s="78"/>
+      <c r="AG1" s="78"/>
     </row>
     <row r="2" spans="1:177" ht="13" customHeight="1">
-      <c r="A2" s="87" t="s">
+      <c r="A2" s="79" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="88"/>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="87" t="s">
+      <c r="B2" s="80"/>
+      <c r="C2" s="80"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="79" t="s">
         <v>48</v>
       </c>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
-      <c r="K2" s="88"/>
-      <c r="L2" s="88"/>
-      <c r="M2" s="88"/>
-      <c r="N2" s="88"/>
-      <c r="O2" s="88"/>
-      <c r="P2" s="88"/>
-      <c r="Q2" s="88"/>
-      <c r="R2" s="88"/>
-      <c r="S2" s="88"/>
-      <c r="T2" s="88"/>
-      <c r="U2" s="88"/>
-      <c r="V2" s="88"/>
-      <c r="W2" s="88"/>
-      <c r="X2" s="88"/>
-      <c r="Y2" s="88"/>
-      <c r="Z2" s="88"/>
-      <c r="AA2" s="88"/>
-      <c r="AB2" s="88"/>
-      <c r="AC2" s="89"/>
-      <c r="AD2" s="87" t="s">
+      <c r="H2" s="80"/>
+      <c r="I2" s="80"/>
+      <c r="J2" s="80"/>
+      <c r="K2" s="80"/>
+      <c r="L2" s="80"/>
+      <c r="M2" s="80"/>
+      <c r="N2" s="80"/>
+      <c r="O2" s="80"/>
+      <c r="P2" s="80"/>
+      <c r="Q2" s="80"/>
+      <c r="R2" s="80"/>
+      <c r="S2" s="80"/>
+      <c r="T2" s="80"/>
+      <c r="U2" s="80"/>
+      <c r="V2" s="80"/>
+      <c r="W2" s="80"/>
+      <c r="X2" s="80"/>
+      <c r="Y2" s="80"/>
+      <c r="Z2" s="80"/>
+      <c r="AA2" s="80"/>
+      <c r="AB2" s="80"/>
+      <c r="AC2" s="81"/>
+      <c r="AD2" s="79" t="s">
         <v>1</v>
       </c>
-      <c r="AE2" s="89"/>
-      <c r="AF2" s="87" t="s">
+      <c r="AE2" s="81"/>
+      <c r="AF2" s="79" t="s">
         <v>2</v>
       </c>
-      <c r="AG2" s="89"/>
+      <c r="AG2" s="81"/>
     </row>
     <row r="3" spans="1:177" s="15" customFormat="1" ht="12.75" customHeight="1">
-      <c r="A3" s="87" t="s">
+      <c r="A3" s="79" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="88"/>
-      <c r="C3" s="88"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="88"/>
-      <c r="F3" s="89"/>
-      <c r="G3" s="87" t="s">
+      <c r="B3" s="80"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="81"/>
+      <c r="G3" s="79" t="s">
         <v>52</v>
       </c>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
-      <c r="K3" s="88"/>
-      <c r="L3" s="88"/>
-      <c r="M3" s="88"/>
-      <c r="N3" s="88"/>
-      <c r="O3" s="88"/>
-      <c r="P3" s="88"/>
-      <c r="Q3" s="88"/>
-      <c r="R3" s="88"/>
-      <c r="S3" s="88"/>
-      <c r="T3" s="88"/>
-      <c r="U3" s="88"/>
-      <c r="V3" s="88"/>
-      <c r="W3" s="88"/>
-      <c r="X3" s="88"/>
-      <c r="Y3" s="88"/>
-      <c r="Z3" s="88"/>
-      <c r="AA3" s="88"/>
-      <c r="AB3" s="88"/>
-      <c r="AC3" s="89"/>
-      <c r="AD3" s="87" t="s">
+      <c r="H3" s="80"/>
+      <c r="I3" s="80"/>
+      <c r="J3" s="80"/>
+      <c r="K3" s="80"/>
+      <c r="L3" s="80"/>
+      <c r="M3" s="80"/>
+      <c r="N3" s="80"/>
+      <c r="O3" s="80"/>
+      <c r="P3" s="80"/>
+      <c r="Q3" s="80"/>
+      <c r="R3" s="80"/>
+      <c r="S3" s="80"/>
+      <c r="T3" s="80"/>
+      <c r="U3" s="80"/>
+      <c r="V3" s="80"/>
+      <c r="W3" s="80"/>
+      <c r="X3" s="80"/>
+      <c r="Y3" s="80"/>
+      <c r="Z3" s="80"/>
+      <c r="AA3" s="80"/>
+      <c r="AB3" s="80"/>
+      <c r="AC3" s="81"/>
+      <c r="AD3" s="79" t="s">
         <v>15</v>
       </c>
-      <c r="AE3" s="89"/>
-      <c r="AF3" s="87" t="s">
+      <c r="AE3" s="81"/>
+      <c r="AF3" s="79" t="s">
         <v>47</v>
       </c>
-      <c r="AG3" s="89"/>
+      <c r="AG3" s="81"/>
       <c r="AH3" s="13"/>
       <c r="AI3" s="14"/>
       <c r="AJ3" s="14"/>
@@ -7366,98 +10397,98 @@
     </row>
     <row r="12" spans="1:177" ht="12.75" customHeight="1">
       <c r="A12" s="16"/>
-      <c r="B12" s="81" t="s">
+      <c r="B12" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="C12" s="84"/>
-      <c r="D12" s="81" t="s">
+      <c r="C12" s="76"/>
+      <c r="D12" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="E12" s="85"/>
-      <c r="F12" s="85"/>
-      <c r="G12" s="84"/>
-      <c r="H12" s="81" t="s">
+      <c r="E12" s="77"/>
+      <c r="F12" s="77"/>
+      <c r="G12" s="76"/>
+      <c r="H12" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="I12" s="85"/>
-      <c r="J12" s="84"/>
-      <c r="K12" s="81" t="s">
+      <c r="I12" s="77"/>
+      <c r="J12" s="76"/>
+      <c r="K12" s="62" t="s">
         <v>26</v>
       </c>
-      <c r="L12" s="85"/>
-      <c r="M12" s="84"/>
-      <c r="N12" s="81" t="s">
+      <c r="L12" s="77"/>
+      <c r="M12" s="76"/>
+      <c r="N12" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="O12" s="82"/>
-      <c r="P12" s="83"/>
-      <c r="Q12" s="81" t="s">
+      <c r="O12" s="63"/>
+      <c r="P12" s="64"/>
+      <c r="Q12" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="R12" s="83"/>
-      <c r="S12" s="81" t="s">
+      <c r="R12" s="64"/>
+      <c r="S12" s="62" t="s">
         <v>30</v>
       </c>
-      <c r="T12" s="82"/>
-      <c r="U12" s="83"/>
-      <c r="V12" s="81" t="s">
+      <c r="T12" s="63"/>
+      <c r="U12" s="64"/>
+      <c r="V12" s="62" t="s">
         <v>31</v>
       </c>
-      <c r="W12" s="82"/>
-      <c r="X12" s="83"/>
-      <c r="Y12" s="81" t="s">
+      <c r="W12" s="63"/>
+      <c r="X12" s="64"/>
+      <c r="Y12" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="Z12" s="82"/>
-      <c r="AA12" s="82"/>
-      <c r="AB12" s="82"/>
-      <c r="AC12" s="82"/>
-      <c r="AD12" s="82"/>
-      <c r="AE12" s="83"/>
+      <c r="Z12" s="63"/>
+      <c r="AA12" s="63"/>
+      <c r="AB12" s="63"/>
+      <c r="AC12" s="63"/>
+      <c r="AD12" s="63"/>
+      <c r="AE12" s="64"/>
       <c r="AF12" s="45"/>
       <c r="AG12" s="18"/>
     </row>
     <row r="13" spans="1:177" ht="12.75" customHeight="1">
       <c r="A13" s="16"/>
-      <c r="B13" s="90" t="s">
+      <c r="B13" s="65" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="91"/>
+      <c r="C13" s="66"/>
       <c r="D13" s="46" t="s">
         <v>19</v>
       </c>
       <c r="E13" s="38"/>
       <c r="F13" s="38"/>
       <c r="G13" s="47"/>
-      <c r="H13" s="92" t="s">
+      <c r="H13" s="67" t="s">
         <v>40</v>
       </c>
-      <c r="I13" s="93"/>
-      <c r="J13" s="94"/>
-      <c r="K13" s="98" t="s">
+      <c r="I13" s="68"/>
+      <c r="J13" s="69"/>
+      <c r="K13" s="70" t="s">
         <v>25</v>
       </c>
-      <c r="L13" s="100"/>
-      <c r="M13" s="99"/>
+      <c r="L13" s="71"/>
+      <c r="M13" s="72"/>
       <c r="N13" s="46" t="s">
         <v>28</v>
       </c>
       <c r="O13" s="38"/>
       <c r="P13" s="47"/>
-      <c r="Q13" s="98" t="s">
+      <c r="Q13" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="R13" s="99"/>
-      <c r="S13" s="95" t="s">
+      <c r="R13" s="72"/>
+      <c r="S13" s="73" t="s">
         <v>39</v>
       </c>
-      <c r="T13" s="96"/>
-      <c r="U13" s="97"/>
-      <c r="V13" s="92" t="s">
+      <c r="T13" s="74"/>
+      <c r="U13" s="75"/>
+      <c r="V13" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="W13" s="93"/>
-      <c r="X13" s="94"/>
+      <c r="W13" s="68"/>
+      <c r="X13" s="69"/>
       <c r="Y13" s="48" t="s">
         <v>33</v>
       </c>
@@ -8476,6 +11507,15 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="G3:AC3"/>
+    <mergeCell ref="AD3:AE3"/>
+    <mergeCell ref="AF3:AG3"/>
+    <mergeCell ref="A1:AG1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="G2:AC2"/>
+    <mergeCell ref="AD2:AE2"/>
+    <mergeCell ref="AF2:AG2"/>
     <mergeCell ref="S12:U12"/>
     <mergeCell ref="V12:X12"/>
     <mergeCell ref="Y12:AE12"/>
@@ -8491,15 +11531,6 @@
     <mergeCell ref="K12:M12"/>
     <mergeCell ref="N12:P12"/>
     <mergeCell ref="Q12:R12"/>
-    <mergeCell ref="A1:AG1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="G2:AC2"/>
-    <mergeCell ref="AD2:AE2"/>
-    <mergeCell ref="AF2:AG2"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="G3:AC3"/>
-    <mergeCell ref="AD3:AE3"/>
-    <mergeCell ref="AF3:AG3"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <printOptions horizontalCentered="1"/>
@@ -8512,7 +11543,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:IV43"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" customHeight="1"/>
@@ -8988,20 +12019,20 @@
       <c r="C8" s="19"/>
       <c r="D8" s="19"/>
       <c r="E8" s="20"/>
-      <c r="F8" s="58" t="s">
+      <c r="F8" s="82" t="s">
         <v>55</v>
       </c>
-      <c r="G8" s="59"/>
-      <c r="H8" s="59"/>
-      <c r="I8" s="59"/>
-      <c r="J8" s="59"/>
-      <c r="K8" s="59"/>
-      <c r="L8" s="59"/>
-      <c r="M8" s="59"/>
-      <c r="N8" s="59"/>
-      <c r="O8" s="59"/>
-      <c r="P8" s="59"/>
-      <c r="Q8" s="60"/>
+      <c r="G8" s="83"/>
+      <c r="H8" s="83"/>
+      <c r="I8" s="83"/>
+      <c r="J8" s="83"/>
+      <c r="K8" s="83"/>
+      <c r="L8" s="83"/>
+      <c r="M8" s="83"/>
+      <c r="N8" s="83"/>
+      <c r="O8" s="83"/>
+      <c r="P8" s="83"/>
+      <c r="Q8" s="84"/>
       <c r="R8" s="13"/>
       <c r="S8" s="13"/>
       <c r="T8" s="13"/>
@@ -9020,26 +12051,26 @@
     </row>
     <row r="9" spans="1:256" ht="13" customHeight="1">
       <c r="A9" s="16"/>
-      <c r="B9" s="61" t="s">
+      <c r="B9" s="85" t="s">
         <v>43</v>
       </c>
-      <c r="C9" s="62"/>
-      <c r="D9" s="62"/>
-      <c r="E9" s="63"/>
-      <c r="F9" s="67" t="s">
+      <c r="C9" s="86"/>
+      <c r="D9" s="86"/>
+      <c r="E9" s="87"/>
+      <c r="F9" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="G9" s="68"/>
-      <c r="H9" s="68"/>
-      <c r="I9" s="68"/>
-      <c r="J9" s="68"/>
-      <c r="K9" s="68"/>
-      <c r="L9" s="68"/>
-      <c r="M9" s="68"/>
-      <c r="N9" s="68"/>
-      <c r="O9" s="68"/>
-      <c r="P9" s="68"/>
-      <c r="Q9" s="69"/>
+      <c r="G9" s="92"/>
+      <c r="H9" s="92"/>
+      <c r="I9" s="92"/>
+      <c r="J9" s="92"/>
+      <c r="K9" s="92"/>
+      <c r="L9" s="92"/>
+      <c r="M9" s="92"/>
+      <c r="N9" s="92"/>
+      <c r="O9" s="92"/>
+      <c r="P9" s="92"/>
+      <c r="Q9" s="93"/>
       <c r="R9" s="13"/>
       <c r="S9" s="13"/>
       <c r="T9" s="13"/>
@@ -9058,22 +12089,22 @@
     </row>
     <row r="10" spans="1:256" ht="13" customHeight="1">
       <c r="A10" s="16"/>
-      <c r="B10" s="64"/>
-      <c r="C10" s="65"/>
-      <c r="D10" s="65"/>
-      <c r="E10" s="66"/>
-      <c r="F10" s="70"/>
-      <c r="G10" s="71"/>
-      <c r="H10" s="71"/>
-      <c r="I10" s="71"/>
-      <c r="J10" s="71"/>
-      <c r="K10" s="71"/>
-      <c r="L10" s="71"/>
-      <c r="M10" s="71"/>
-      <c r="N10" s="71"/>
-      <c r="O10" s="71"/>
-      <c r="P10" s="71"/>
-      <c r="Q10" s="72"/>
+      <c r="B10" s="88"/>
+      <c r="C10" s="89"/>
+      <c r="D10" s="89"/>
+      <c r="E10" s="90"/>
+      <c r="F10" s="94"/>
+      <c r="G10" s="95"/>
+      <c r="H10" s="95"/>
+      <c r="I10" s="95"/>
+      <c r="J10" s="95"/>
+      <c r="K10" s="95"/>
+      <c r="L10" s="95"/>
+      <c r="M10" s="95"/>
+      <c r="N10" s="95"/>
+      <c r="O10" s="95"/>
+      <c r="P10" s="95"/>
+      <c r="Q10" s="96"/>
       <c r="R10" s="13"/>
       <c r="S10" s="13"/>
       <c r="T10" s="13"/>
@@ -9284,26 +12315,26 @@
       <c r="E17" s="13"/>
       <c r="F17" s="13"/>
       <c r="G17" s="13"/>
-      <c r="H17" s="73" t="s">
+      <c r="H17" s="97" t="s">
         <v>53</v>
       </c>
-      <c r="I17" s="73"/>
-      <c r="J17" s="73"/>
-      <c r="K17" s="73"/>
-      <c r="L17" s="73"/>
-      <c r="M17" s="73"/>
-      <c r="N17" s="73"/>
-      <c r="O17" s="73"/>
-      <c r="P17" s="73"/>
-      <c r="Q17" s="73"/>
-      <c r="R17" s="73"/>
-      <c r="S17" s="73"/>
-      <c r="T17" s="73"/>
-      <c r="U17" s="73"/>
-      <c r="V17" s="73"/>
-      <c r="W17" s="73"/>
-      <c r="X17" s="73"/>
-      <c r="Y17" s="73"/>
+      <c r="I17" s="97"/>
+      <c r="J17" s="97"/>
+      <c r="K17" s="97"/>
+      <c r="L17" s="97"/>
+      <c r="M17" s="97"/>
+      <c r="N17" s="97"/>
+      <c r="O17" s="97"/>
+      <c r="P17" s="97"/>
+      <c r="Q17" s="97"/>
+      <c r="R17" s="97"/>
+      <c r="S17" s="97"/>
+      <c r="T17" s="97"/>
+      <c r="U17" s="97"/>
+      <c r="V17" s="97"/>
+      <c r="W17" s="97"/>
+      <c r="X17" s="97"/>
+      <c r="Y17" s="97"/>
       <c r="AA17" s="13"/>
       <c r="AB17" s="13"/>
       <c r="AC17" s="13"/>
@@ -9319,24 +12350,24 @@
       <c r="E18" s="13"/>
       <c r="F18" s="13"/>
       <c r="G18" s="13"/>
-      <c r="H18" s="73"/>
-      <c r="I18" s="73"/>
-      <c r="J18" s="73"/>
-      <c r="K18" s="73"/>
-      <c r="L18" s="73"/>
-      <c r="M18" s="73"/>
-      <c r="N18" s="73"/>
-      <c r="O18" s="73"/>
-      <c r="P18" s="73"/>
-      <c r="Q18" s="73"/>
-      <c r="R18" s="73"/>
-      <c r="S18" s="73"/>
-      <c r="T18" s="73"/>
-      <c r="U18" s="73"/>
-      <c r="V18" s="73"/>
-      <c r="W18" s="73"/>
-      <c r="X18" s="73"/>
-      <c r="Y18" s="73"/>
+      <c r="H18" s="97"/>
+      <c r="I18" s="97"/>
+      <c r="J18" s="97"/>
+      <c r="K18" s="97"/>
+      <c r="L18" s="97"/>
+      <c r="M18" s="97"/>
+      <c r="N18" s="97"/>
+      <c r="O18" s="97"/>
+      <c r="P18" s="97"/>
+      <c r="Q18" s="97"/>
+      <c r="R18" s="97"/>
+      <c r="S18" s="97"/>
+      <c r="T18" s="97"/>
+      <c r="U18" s="97"/>
+      <c r="V18" s="97"/>
+      <c r="W18" s="97"/>
+      <c r="X18" s="97"/>
+      <c r="Y18" s="97"/>
       <c r="AA18" s="13"/>
       <c r="AB18" s="13"/>
       <c r="AC18" s="13"/>
@@ -9352,24 +12383,24 @@
       <c r="E19" s="13"/>
       <c r="F19" s="13"/>
       <c r="G19" s="13"/>
-      <c r="H19" s="73"/>
-      <c r="I19" s="73"/>
-      <c r="J19" s="73"/>
-      <c r="K19" s="73"/>
-      <c r="L19" s="73"/>
-      <c r="M19" s="73"/>
-      <c r="N19" s="73"/>
-      <c r="O19" s="73"/>
-      <c r="P19" s="73"/>
-      <c r="Q19" s="73"/>
-      <c r="R19" s="73"/>
-      <c r="S19" s="73"/>
-      <c r="T19" s="73"/>
-      <c r="U19" s="73"/>
-      <c r="V19" s="73"/>
-      <c r="W19" s="73"/>
-      <c r="X19" s="73"/>
-      <c r="Y19" s="73"/>
+      <c r="H19" s="97"/>
+      <c r="I19" s="97"/>
+      <c r="J19" s="97"/>
+      <c r="K19" s="97"/>
+      <c r="L19" s="97"/>
+      <c r="M19" s="97"/>
+      <c r="N19" s="97"/>
+      <c r="O19" s="97"/>
+      <c r="P19" s="97"/>
+      <c r="Q19" s="97"/>
+      <c r="R19" s="97"/>
+      <c r="S19" s="97"/>
+      <c r="T19" s="97"/>
+      <c r="U19" s="97"/>
+      <c r="V19" s="97"/>
+      <c r="W19" s="97"/>
+      <c r="X19" s="97"/>
+      <c r="Y19" s="97"/>
       <c r="Z19" s="13"/>
       <c r="AA19" s="13"/>
       <c r="AB19" s="13"/>
@@ -9595,10 +12626,10 @@
       <c r="C26" s="23"/>
       <c r="D26" s="23"/>
       <c r="E26" s="23"/>
-      <c r="F26" s="74"/>
-      <c r="G26" s="75"/>
-      <c r="H26" s="75"/>
-      <c r="I26" s="76"/>
+      <c r="F26" s="98"/>
+      <c r="G26" s="99"/>
+      <c r="H26" s="99"/>
+      <c r="I26" s="100"/>
       <c r="J26" s="22"/>
       <c r="K26" s="23"/>
       <c r="L26" s="23"/>
@@ -10219,8 +13250,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDA89FA2-5389-4B04-B72F-09589A64BB33}">
   <dimension ref="A1:FU42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
@@ -10232,123 +13263,123 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:177" ht="12.75" customHeight="1">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
-      <c r="L1" s="77"/>
-      <c r="M1" s="77"/>
-      <c r="N1" s="77"/>
-      <c r="O1" s="77"/>
-      <c r="P1" s="77"/>
-      <c r="Q1" s="77"/>
-      <c r="R1" s="77"/>
-      <c r="S1" s="77"/>
-      <c r="T1" s="77"/>
-      <c r="U1" s="77"/>
-      <c r="V1" s="77"/>
-      <c r="W1" s="77"/>
-      <c r="X1" s="77"/>
-      <c r="Y1" s="77"/>
-      <c r="Z1" s="77"/>
-      <c r="AA1" s="77"/>
-      <c r="AB1" s="77"/>
-      <c r="AC1" s="77"/>
-      <c r="AD1" s="77"/>
-      <c r="AE1" s="77"/>
-      <c r="AF1" s="77"/>
-      <c r="AG1" s="77"/>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
+      <c r="H1" s="58"/>
+      <c r="I1" s="58"/>
+      <c r="J1" s="58"/>
+      <c r="K1" s="58"/>
+      <c r="L1" s="58"/>
+      <c r="M1" s="58"/>
+      <c r="N1" s="58"/>
+      <c r="O1" s="58"/>
+      <c r="P1" s="58"/>
+      <c r="Q1" s="58"/>
+      <c r="R1" s="58"/>
+      <c r="S1" s="58"/>
+      <c r="T1" s="58"/>
+      <c r="U1" s="58"/>
+      <c r="V1" s="58"/>
+      <c r="W1" s="58"/>
+      <c r="X1" s="58"/>
+      <c r="Y1" s="58"/>
+      <c r="Z1" s="58"/>
+      <c r="AA1" s="58"/>
+      <c r="AB1" s="58"/>
+      <c r="AC1" s="58"/>
+      <c r="AD1" s="58"/>
+      <c r="AE1" s="58"/>
+      <c r="AF1" s="58"/>
+      <c r="AG1" s="58"/>
     </row>
     <row r="2" spans="1:177" ht="13" customHeight="1">
-      <c r="A2" s="78" t="s">
+      <c r="A2" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="78" t="s">
+      <c r="B2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="59" t="s">
         <v>48</v>
       </c>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
-      <c r="J2" s="79"/>
-      <c r="K2" s="79"/>
-      <c r="L2" s="79"/>
-      <c r="M2" s="79"/>
-      <c r="N2" s="79"/>
-      <c r="O2" s="79"/>
-      <c r="P2" s="79"/>
-      <c r="Q2" s="79"/>
-      <c r="R2" s="79"/>
-      <c r="S2" s="79"/>
-      <c r="T2" s="79"/>
-      <c r="U2" s="79"/>
-      <c r="V2" s="79"/>
-      <c r="W2" s="79"/>
-      <c r="X2" s="79"/>
-      <c r="Y2" s="79"/>
-      <c r="Z2" s="79"/>
-      <c r="AA2" s="79"/>
-      <c r="AB2" s="79"/>
-      <c r="AC2" s="80"/>
-      <c r="AD2" s="78" t="s">
+      <c r="H2" s="60"/>
+      <c r="I2" s="60"/>
+      <c r="J2" s="60"/>
+      <c r="K2" s="60"/>
+      <c r="L2" s="60"/>
+      <c r="M2" s="60"/>
+      <c r="N2" s="60"/>
+      <c r="O2" s="60"/>
+      <c r="P2" s="60"/>
+      <c r="Q2" s="60"/>
+      <c r="R2" s="60"/>
+      <c r="S2" s="60"/>
+      <c r="T2" s="60"/>
+      <c r="U2" s="60"/>
+      <c r="V2" s="60"/>
+      <c r="W2" s="60"/>
+      <c r="X2" s="60"/>
+      <c r="Y2" s="60"/>
+      <c r="Z2" s="60"/>
+      <c r="AA2" s="60"/>
+      <c r="AB2" s="60"/>
+      <c r="AC2" s="61"/>
+      <c r="AD2" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="AE2" s="80"/>
-      <c r="AF2" s="78" t="s">
+      <c r="AE2" s="61"/>
+      <c r="AF2" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="AG2" s="80"/>
+      <c r="AG2" s="61"/>
     </row>
     <row r="3" spans="1:177" s="3" customFormat="1" ht="12.75" customHeight="1">
-      <c r="A3" s="78" t="s">
+      <c r="A3" s="59" t="s">
         <v>54</v>
       </c>
-      <c r="B3" s="79"/>
-      <c r="C3" s="79"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="79"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="78" t="s">
-        <v>56</v>
+      <c r="B3" s="60"/>
+      <c r="C3" s="60"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="59" t="s">
+        <v>57</v>
       </c>
-      <c r="H3" s="79"/>
-      <c r="I3" s="79"/>
-      <c r="J3" s="79"/>
-      <c r="K3" s="79"/>
-      <c r="L3" s="79"/>
-      <c r="M3" s="79"/>
-      <c r="N3" s="79"/>
-      <c r="O3" s="79"/>
-      <c r="P3" s="79"/>
-      <c r="Q3" s="79"/>
-      <c r="R3" s="79"/>
-      <c r="S3" s="79"/>
-      <c r="T3" s="79"/>
-      <c r="U3" s="79"/>
-      <c r="V3" s="79"/>
-      <c r="W3" s="79"/>
-      <c r="X3" s="79"/>
-      <c r="Y3" s="79"/>
-      <c r="Z3" s="79"/>
-      <c r="AA3" s="79"/>
-      <c r="AB3" s="79"/>
-      <c r="AC3" s="80"/>
-      <c r="AD3" s="78"/>
-      <c r="AE3" s="80"/>
-      <c r="AF3" s="78"/>
-      <c r="AG3" s="80"/>
+      <c r="H3" s="60"/>
+      <c r="I3" s="60"/>
+      <c r="J3" s="60"/>
+      <c r="K3" s="60"/>
+      <c r="L3" s="60"/>
+      <c r="M3" s="60"/>
+      <c r="N3" s="60"/>
+      <c r="O3" s="60"/>
+      <c r="P3" s="60"/>
+      <c r="Q3" s="60"/>
+      <c r="R3" s="60"/>
+      <c r="S3" s="60"/>
+      <c r="T3" s="60"/>
+      <c r="U3" s="60"/>
+      <c r="V3" s="60"/>
+      <c r="W3" s="60"/>
+      <c r="X3" s="60"/>
+      <c r="Y3" s="60"/>
+      <c r="Z3" s="60"/>
+      <c r="AA3" s="60"/>
+      <c r="AB3" s="60"/>
+      <c r="AC3" s="61"/>
+      <c r="AD3" s="59"/>
+      <c r="AE3" s="61"/>
+      <c r="AF3" s="59"/>
+      <c r="AG3" s="61"/>
       <c r="AH3" s="2"/>
       <c r="AI3" s="5"/>
       <c r="AJ3" s="5"/>
@@ -11865,13 +14896,13 @@
   <mergeCells count="9">
     <mergeCell ref="A1:AG1"/>
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="G2:AC2"/>
+    <mergeCell ref="AD2:AE2"/>
     <mergeCell ref="AF2:AG2"/>
     <mergeCell ref="A3:F3"/>
+    <mergeCell ref="G3:AC3"/>
+    <mergeCell ref="AD3:AE3"/>
     <mergeCell ref="AF3:AG3"/>
-    <mergeCell ref="AD3:AE3"/>
-    <mergeCell ref="AD2:AE2"/>
-    <mergeCell ref="G3:AC3"/>
-    <mergeCell ref="G2:AC2"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <printOptions horizontalCentered="1"/>
@@ -11884,8 +14915,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16D17071-3033-4D1C-885F-96E2F44F8283}">
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:FU42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
@@ -11897,127 +14928,123 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:177" ht="12.75" customHeight="1">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
-      <c r="L1" s="77"/>
-      <c r="M1" s="77"/>
-      <c r="N1" s="77"/>
-      <c r="O1" s="77"/>
-      <c r="P1" s="77"/>
-      <c r="Q1" s="77"/>
-      <c r="R1" s="77"/>
-      <c r="S1" s="77"/>
-      <c r="T1" s="77"/>
-      <c r="U1" s="77"/>
-      <c r="V1" s="77"/>
-      <c r="W1" s="77"/>
-      <c r="X1" s="77"/>
-      <c r="Y1" s="77"/>
-      <c r="Z1" s="77"/>
-      <c r="AA1" s="77"/>
-      <c r="AB1" s="77"/>
-      <c r="AC1" s="77"/>
-      <c r="AD1" s="77"/>
-      <c r="AE1" s="77"/>
-      <c r="AF1" s="77"/>
-      <c r="AG1" s="77"/>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
+      <c r="H1" s="58"/>
+      <c r="I1" s="58"/>
+      <c r="J1" s="58"/>
+      <c r="K1" s="58"/>
+      <c r="L1" s="58"/>
+      <c r="M1" s="58"/>
+      <c r="N1" s="58"/>
+      <c r="O1" s="58"/>
+      <c r="P1" s="58"/>
+      <c r="Q1" s="58"/>
+      <c r="R1" s="58"/>
+      <c r="S1" s="58"/>
+      <c r="T1" s="58"/>
+      <c r="U1" s="58"/>
+      <c r="V1" s="58"/>
+      <c r="W1" s="58"/>
+      <c r="X1" s="58"/>
+      <c r="Y1" s="58"/>
+      <c r="Z1" s="58"/>
+      <c r="AA1" s="58"/>
+      <c r="AB1" s="58"/>
+      <c r="AC1" s="58"/>
+      <c r="AD1" s="58"/>
+      <c r="AE1" s="58"/>
+      <c r="AF1" s="58"/>
+      <c r="AG1" s="58"/>
     </row>
     <row r="2" spans="1:177" ht="13" customHeight="1">
-      <c r="A2" s="78" t="s">
+      <c r="A2" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="78" t="s">
+      <c r="B2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="59" t="s">
         <v>48</v>
       </c>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
-      <c r="J2" s="79"/>
-      <c r="K2" s="79"/>
-      <c r="L2" s="79"/>
-      <c r="M2" s="79"/>
-      <c r="N2" s="79"/>
-      <c r="O2" s="79"/>
-      <c r="P2" s="79"/>
-      <c r="Q2" s="79"/>
-      <c r="R2" s="79"/>
-      <c r="S2" s="79"/>
-      <c r="T2" s="79"/>
-      <c r="U2" s="79"/>
-      <c r="V2" s="79"/>
-      <c r="W2" s="79"/>
-      <c r="X2" s="79"/>
-      <c r="Y2" s="79"/>
-      <c r="Z2" s="79"/>
-      <c r="AA2" s="79"/>
-      <c r="AB2" s="79"/>
-      <c r="AC2" s="80"/>
-      <c r="AD2" s="78" t="s">
+      <c r="H2" s="60"/>
+      <c r="I2" s="60"/>
+      <c r="J2" s="60"/>
+      <c r="K2" s="60"/>
+      <c r="L2" s="60"/>
+      <c r="M2" s="60"/>
+      <c r="N2" s="60"/>
+      <c r="O2" s="60"/>
+      <c r="P2" s="60"/>
+      <c r="Q2" s="60"/>
+      <c r="R2" s="60"/>
+      <c r="S2" s="60"/>
+      <c r="T2" s="60"/>
+      <c r="U2" s="60"/>
+      <c r="V2" s="60"/>
+      <c r="W2" s="60"/>
+      <c r="X2" s="60"/>
+      <c r="Y2" s="60"/>
+      <c r="Z2" s="60"/>
+      <c r="AA2" s="60"/>
+      <c r="AB2" s="60"/>
+      <c r="AC2" s="61"/>
+      <c r="AD2" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="AE2" s="80"/>
-      <c r="AF2" s="78" t="s">
+      <c r="AE2" s="61"/>
+      <c r="AF2" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="AG2" s="80"/>
+      <c r="AG2" s="61"/>
     </row>
     <row r="3" spans="1:177" s="3" customFormat="1" ht="12.75" customHeight="1">
-      <c r="A3" s="78" t="s">
+      <c r="A3" s="59" t="s">
         <v>54</v>
       </c>
-      <c r="B3" s="79"/>
-      <c r="C3" s="79"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="79"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="78" t="s">
+      <c r="B3" s="60"/>
+      <c r="C3" s="60"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="59" t="s">
         <v>56</v>
       </c>
-      <c r="H3" s="79"/>
-      <c r="I3" s="79"/>
-      <c r="J3" s="79"/>
-      <c r="K3" s="79"/>
-      <c r="L3" s="79"/>
-      <c r="M3" s="79"/>
-      <c r="N3" s="79"/>
-      <c r="O3" s="79"/>
-      <c r="P3" s="79"/>
-      <c r="Q3" s="79"/>
-      <c r="R3" s="79"/>
-      <c r="S3" s="79"/>
-      <c r="T3" s="79"/>
-      <c r="U3" s="79"/>
-      <c r="V3" s="79"/>
-      <c r="W3" s="79"/>
-      <c r="X3" s="79"/>
-      <c r="Y3" s="79"/>
-      <c r="Z3" s="79"/>
-      <c r="AA3" s="79"/>
-      <c r="AB3" s="79"/>
-      <c r="AC3" s="80"/>
-      <c r="AD3" s="78" t="s">
-        <v>15</v>
-      </c>
-      <c r="AE3" s="80"/>
-      <c r="AF3" s="78" t="s">
-        <v>47</v>
-      </c>
-      <c r="AG3" s="80"/>
+      <c r="H3" s="60"/>
+      <c r="I3" s="60"/>
+      <c r="J3" s="60"/>
+      <c r="K3" s="60"/>
+      <c r="L3" s="60"/>
+      <c r="M3" s="60"/>
+      <c r="N3" s="60"/>
+      <c r="O3" s="60"/>
+      <c r="P3" s="60"/>
+      <c r="Q3" s="60"/>
+      <c r="R3" s="60"/>
+      <c r="S3" s="60"/>
+      <c r="T3" s="60"/>
+      <c r="U3" s="60"/>
+      <c r="V3" s="60"/>
+      <c r="W3" s="60"/>
+      <c r="X3" s="60"/>
+      <c r="Y3" s="60"/>
+      <c r="Z3" s="60"/>
+      <c r="AA3" s="60"/>
+      <c r="AB3" s="60"/>
+      <c r="AC3" s="61"/>
+      <c r="AD3" s="59"/>
+      <c r="AE3" s="61"/>
+      <c r="AF3" s="59"/>
+      <c r="AG3" s="61"/>
       <c r="AH3" s="2"/>
       <c r="AI3" s="5"/>
       <c r="AJ3" s="5"/>
@@ -13534,13 +16561,13 @@
   <mergeCells count="9">
     <mergeCell ref="A1:AG1"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="G2:AC2"/>
-    <mergeCell ref="AD2:AE2"/>
     <mergeCell ref="AF2:AG2"/>
     <mergeCell ref="A3:F3"/>
+    <mergeCell ref="AF3:AG3"/>
+    <mergeCell ref="AD3:AE3"/>
+    <mergeCell ref="AD2:AE2"/>
     <mergeCell ref="G3:AC3"/>
-    <mergeCell ref="AD3:AE3"/>
-    <mergeCell ref="AF3:AG3"/>
+    <mergeCell ref="G2:AC2"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <printOptions horizontalCentered="1"/>
@@ -13553,7 +16580,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:FU42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" customHeight="1"/>
@@ -13566,127 +16593,127 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:177" ht="12.75" customHeight="1">
-      <c r="A1" s="86" t="s">
+      <c r="A1" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="86"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="86"/>
-      <c r="E1" s="86"/>
-      <c r="F1" s="86"/>
-      <c r="G1" s="86"/>
-      <c r="H1" s="86"/>
-      <c r="I1" s="86"/>
-      <c r="J1" s="86"/>
-      <c r="K1" s="86"/>
-      <c r="L1" s="86"/>
-      <c r="M1" s="86"/>
-      <c r="N1" s="86"/>
-      <c r="O1" s="86"/>
-      <c r="P1" s="86"/>
-      <c r="Q1" s="86"/>
-      <c r="R1" s="86"/>
-      <c r="S1" s="86"/>
-      <c r="T1" s="86"/>
-      <c r="U1" s="86"/>
-      <c r="V1" s="86"/>
-      <c r="W1" s="86"/>
-      <c r="X1" s="86"/>
-      <c r="Y1" s="86"/>
-      <c r="Z1" s="86"/>
-      <c r="AA1" s="86"/>
-      <c r="AB1" s="86"/>
-      <c r="AC1" s="86"/>
-      <c r="AD1" s="86"/>
-      <c r="AE1" s="86"/>
-      <c r="AF1" s="86"/>
-      <c r="AG1" s="86"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
+      <c r="O1" s="78"/>
+      <c r="P1" s="78"/>
+      <c r="Q1" s="78"/>
+      <c r="R1" s="78"/>
+      <c r="S1" s="78"/>
+      <c r="T1" s="78"/>
+      <c r="U1" s="78"/>
+      <c r="V1" s="78"/>
+      <c r="W1" s="78"/>
+      <c r="X1" s="78"/>
+      <c r="Y1" s="78"/>
+      <c r="Z1" s="78"/>
+      <c r="AA1" s="78"/>
+      <c r="AB1" s="78"/>
+      <c r="AC1" s="78"/>
+      <c r="AD1" s="78"/>
+      <c r="AE1" s="78"/>
+      <c r="AF1" s="78"/>
+      <c r="AG1" s="78"/>
     </row>
     <row r="2" spans="1:177" ht="13" customHeight="1">
-      <c r="A2" s="87" t="s">
+      <c r="A2" s="79" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="88"/>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="87" t="s">
+      <c r="B2" s="80"/>
+      <c r="C2" s="80"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="79" t="s">
         <v>48</v>
       </c>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
-      <c r="K2" s="88"/>
-      <c r="L2" s="88"/>
-      <c r="M2" s="88"/>
-      <c r="N2" s="88"/>
-      <c r="O2" s="88"/>
-      <c r="P2" s="88"/>
-      <c r="Q2" s="88"/>
-      <c r="R2" s="88"/>
-      <c r="S2" s="88"/>
-      <c r="T2" s="88"/>
-      <c r="U2" s="88"/>
-      <c r="V2" s="88"/>
-      <c r="W2" s="88"/>
-      <c r="X2" s="88"/>
-      <c r="Y2" s="88"/>
-      <c r="Z2" s="88"/>
-      <c r="AA2" s="88"/>
-      <c r="AB2" s="88"/>
-      <c r="AC2" s="89"/>
-      <c r="AD2" s="87" t="s">
+      <c r="H2" s="80"/>
+      <c r="I2" s="80"/>
+      <c r="J2" s="80"/>
+      <c r="K2" s="80"/>
+      <c r="L2" s="80"/>
+      <c r="M2" s="80"/>
+      <c r="N2" s="80"/>
+      <c r="O2" s="80"/>
+      <c r="P2" s="80"/>
+      <c r="Q2" s="80"/>
+      <c r="R2" s="80"/>
+      <c r="S2" s="80"/>
+      <c r="T2" s="80"/>
+      <c r="U2" s="80"/>
+      <c r="V2" s="80"/>
+      <c r="W2" s="80"/>
+      <c r="X2" s="80"/>
+      <c r="Y2" s="80"/>
+      <c r="Z2" s="80"/>
+      <c r="AA2" s="80"/>
+      <c r="AB2" s="80"/>
+      <c r="AC2" s="81"/>
+      <c r="AD2" s="79" t="s">
         <v>1</v>
       </c>
-      <c r="AE2" s="89"/>
-      <c r="AF2" s="87" t="s">
+      <c r="AE2" s="81"/>
+      <c r="AF2" s="79" t="s">
         <v>2</v>
       </c>
-      <c r="AG2" s="89"/>
+      <c r="AG2" s="81"/>
     </row>
     <row r="3" spans="1:177" s="15" customFormat="1" ht="12.75" customHeight="1">
-      <c r="A3" s="87" t="s">
+      <c r="A3" s="79" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="88"/>
-      <c r="C3" s="88"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="88"/>
-      <c r="F3" s="89"/>
-      <c r="G3" s="87" t="s">
+      <c r="B3" s="80"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="81"/>
+      <c r="G3" s="79" t="s">
         <v>52</v>
       </c>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
-      <c r="K3" s="88"/>
-      <c r="L3" s="88"/>
-      <c r="M3" s="88"/>
-      <c r="N3" s="88"/>
-      <c r="O3" s="88"/>
-      <c r="P3" s="88"/>
-      <c r="Q3" s="88"/>
-      <c r="R3" s="88"/>
-      <c r="S3" s="88"/>
-      <c r="T3" s="88"/>
-      <c r="U3" s="88"/>
-      <c r="V3" s="88"/>
-      <c r="W3" s="88"/>
-      <c r="X3" s="88"/>
-      <c r="Y3" s="88"/>
-      <c r="Z3" s="88"/>
-      <c r="AA3" s="88"/>
-      <c r="AB3" s="88"/>
-      <c r="AC3" s="89"/>
-      <c r="AD3" s="87" t="s">
+      <c r="H3" s="80"/>
+      <c r="I3" s="80"/>
+      <c r="J3" s="80"/>
+      <c r="K3" s="80"/>
+      <c r="L3" s="80"/>
+      <c r="M3" s="80"/>
+      <c r="N3" s="80"/>
+      <c r="O3" s="80"/>
+      <c r="P3" s="80"/>
+      <c r="Q3" s="80"/>
+      <c r="R3" s="80"/>
+      <c r="S3" s="80"/>
+      <c r="T3" s="80"/>
+      <c r="U3" s="80"/>
+      <c r="V3" s="80"/>
+      <c r="W3" s="80"/>
+      <c r="X3" s="80"/>
+      <c r="Y3" s="80"/>
+      <c r="Z3" s="80"/>
+      <c r="AA3" s="80"/>
+      <c r="AB3" s="80"/>
+      <c r="AC3" s="81"/>
+      <c r="AD3" s="79" t="s">
         <v>15</v>
       </c>
-      <c r="AE3" s="89"/>
-      <c r="AF3" s="87" t="s">
+      <c r="AE3" s="81"/>
+      <c r="AF3" s="79" t="s">
         <v>47</v>
       </c>
-      <c r="AG3" s="89"/>
+      <c r="AG3" s="81"/>
       <c r="AH3" s="13"/>
       <c r="AI3" s="14"/>
       <c r="AJ3" s="14"/>
@@ -14158,98 +17185,98 @@
     </row>
     <row r="12" spans="1:177" ht="12.75" customHeight="1">
       <c r="A12" s="16"/>
-      <c r="B12" s="81" t="s">
+      <c r="B12" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="C12" s="84"/>
-      <c r="D12" s="81" t="s">
+      <c r="C12" s="76"/>
+      <c r="D12" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="E12" s="85"/>
-      <c r="F12" s="85"/>
-      <c r="G12" s="84"/>
-      <c r="H12" s="81" t="s">
+      <c r="E12" s="77"/>
+      <c r="F12" s="77"/>
+      <c r="G12" s="76"/>
+      <c r="H12" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="I12" s="85"/>
-      <c r="J12" s="84"/>
-      <c r="K12" s="81" t="s">
+      <c r="I12" s="77"/>
+      <c r="J12" s="76"/>
+      <c r="K12" s="62" t="s">
         <v>26</v>
       </c>
-      <c r="L12" s="85"/>
-      <c r="M12" s="84"/>
-      <c r="N12" s="81" t="s">
+      <c r="L12" s="77"/>
+      <c r="M12" s="76"/>
+      <c r="N12" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="O12" s="82"/>
-      <c r="P12" s="83"/>
-      <c r="Q12" s="81" t="s">
+      <c r="O12" s="63"/>
+      <c r="P12" s="64"/>
+      <c r="Q12" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="R12" s="83"/>
-      <c r="S12" s="81" t="s">
+      <c r="R12" s="64"/>
+      <c r="S12" s="62" t="s">
         <v>30</v>
       </c>
-      <c r="T12" s="82"/>
-      <c r="U12" s="83"/>
-      <c r="V12" s="81" t="s">
+      <c r="T12" s="63"/>
+      <c r="U12" s="64"/>
+      <c r="V12" s="62" t="s">
         <v>31</v>
       </c>
-      <c r="W12" s="82"/>
-      <c r="X12" s="83"/>
-      <c r="Y12" s="81" t="s">
+      <c r="W12" s="63"/>
+      <c r="X12" s="64"/>
+      <c r="Y12" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="Z12" s="82"/>
-      <c r="AA12" s="82"/>
-      <c r="AB12" s="82"/>
-      <c r="AC12" s="82"/>
-      <c r="AD12" s="82"/>
-      <c r="AE12" s="83"/>
+      <c r="Z12" s="63"/>
+      <c r="AA12" s="63"/>
+      <c r="AB12" s="63"/>
+      <c r="AC12" s="63"/>
+      <c r="AD12" s="63"/>
+      <c r="AE12" s="64"/>
       <c r="AF12" s="45"/>
       <c r="AG12" s="18"/>
     </row>
     <row r="13" spans="1:177" ht="12.75" customHeight="1">
       <c r="A13" s="16"/>
-      <c r="B13" s="90" t="s">
+      <c r="B13" s="65" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="91"/>
+      <c r="C13" s="66"/>
       <c r="D13" s="46" t="s">
         <v>37</v>
       </c>
       <c r="E13" s="38"/>
       <c r="F13" s="38"/>
       <c r="G13" s="47"/>
-      <c r="H13" s="92" t="s">
+      <c r="H13" s="67" t="s">
         <v>40</v>
       </c>
-      <c r="I13" s="93"/>
-      <c r="J13" s="94"/>
-      <c r="K13" s="98" t="s">
+      <c r="I13" s="68"/>
+      <c r="J13" s="69"/>
+      <c r="K13" s="70" t="s">
         <v>27</v>
       </c>
-      <c r="L13" s="100"/>
-      <c r="M13" s="99"/>
+      <c r="L13" s="71"/>
+      <c r="M13" s="72"/>
       <c r="N13" s="46" t="s">
         <v>28</v>
       </c>
       <c r="O13" s="38"/>
       <c r="P13" s="47"/>
-      <c r="Q13" s="98" t="s">
+      <c r="Q13" s="70" t="s">
         <v>29</v>
       </c>
-      <c r="R13" s="99"/>
-      <c r="S13" s="95" t="s">
+      <c r="R13" s="72"/>
+      <c r="S13" s="73" t="s">
         <v>39</v>
       </c>
-      <c r="T13" s="96"/>
-      <c r="U13" s="97"/>
-      <c r="V13" s="92" t="s">
+      <c r="T13" s="74"/>
+      <c r="U13" s="75"/>
+      <c r="V13" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="W13" s="93"/>
-      <c r="X13" s="94"/>
+      <c r="W13" s="68"/>
+      <c r="X13" s="69"/>
       <c r="Y13" s="48" t="s">
         <v>33</v>
       </c>
@@ -15268,16 +18295,6 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="Q12:R12"/>
-    <mergeCell ref="S12:U12"/>
-    <mergeCell ref="V12:X12"/>
-    <mergeCell ref="V13:X13"/>
-    <mergeCell ref="H13:J13"/>
-    <mergeCell ref="S13:U13"/>
-    <mergeCell ref="Q13:R13"/>
-    <mergeCell ref="K13:M13"/>
     <mergeCell ref="Y12:AE12"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="D12:G12"/>
@@ -15292,6 +18309,16 @@
     <mergeCell ref="G2:AC2"/>
     <mergeCell ref="AD2:AE2"/>
     <mergeCell ref="AF2:AG2"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="Q12:R12"/>
+    <mergeCell ref="S12:U12"/>
+    <mergeCell ref="V12:X12"/>
+    <mergeCell ref="V13:X13"/>
+    <mergeCell ref="H13:J13"/>
+    <mergeCell ref="S13:U13"/>
+    <mergeCell ref="Q13:R13"/>
+    <mergeCell ref="K13:M13"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <printOptions horizontalCentered="1"/>

--- a/基本設計書.xlsx
+++ b/基本設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\7_Programing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23AE07A2-4AB8-423E-8AE6-2F5622417071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FC9690F-41D7-4856-8623-13E916B893ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="774" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="774" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IO関連図（アカウント検索・一覧） (2)" sheetId="31" r:id="rId1"/>
@@ -19,21 +19,24 @@
     <sheet name="表紙" sheetId="26" r:id="rId4"/>
     <sheet name="IO関連図（アカウント登録）" sheetId="30" r:id="rId5"/>
     <sheet name="IO関連図（アカウント検索・一覧）" sheetId="13" r:id="rId6"/>
-    <sheet name="画面レイアウト" sheetId="15" r:id="rId7"/>
+    <sheet name="IO関連図（アカウント更新・削除）" sheetId="32" r:id="rId7"/>
+    <sheet name="画面レイアウト" sheetId="15" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'IO関連図　原本・見本'!$A$1:$AG$42</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'IO関連図（アカウント検索・一覧）'!$A$1:$AG$42</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'IO関連図（アカウント検索・一覧） (2)'!$A$1:$AG$42</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'IO関連図（アカウント更新・削除）'!$A$1:$AG$42</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'IO関連図（アカウント登録）'!$A$1:$AG$42</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">画面レイアウト!$A$1:$AG$42</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">画面レイアウト!$A$1:$AG$42</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'画面レイアウト　原本・見本'!$A$1:$AG$42</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">表紙!$A$1:$AF$43</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'IO関連図　原本・見本'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'IO関連図（アカウント検索・一覧）'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'IO関連図（アカウント検索・一覧） (2)'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'IO関連図（アカウント更新・削除）'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'IO関連図（アカウント登録）'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="6">画面レイアウト!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">画面レイアウト!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'画面レイアウト　原本・見本'!$1:$3</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
@@ -41,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="59">
   <si>
     <t>システム名</t>
     <rPh sb="4" eb="5">
@@ -447,6 +450,16 @@
     <t>アカウント登録</t>
     <rPh sb="5" eb="7">
       <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>アカウント更新・削除</t>
+    <rPh sb="5" eb="7">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>サクジョ</t>
     </rPh>
     <phoneticPr fontId="4"/>
   </si>
@@ -4473,14 +4486,14 @@
     <xdr:from>
       <xdr:col>11</xdr:col>
       <xdr:colOff>165100</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>156448</xdr:rowOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>127000</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>9202</xdr:rowOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>64421</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4497,8 +4510,8 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="3303288" y="3920434"/>
-          <a:ext cx="817770" cy="791449"/>
+          <a:off x="3303288" y="3920435"/>
+          <a:ext cx="817770" cy="690218"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartDocument">
           <a:avLst/>
@@ -4525,13 +4538,34 @@
             </a:lnSpc>
             <a:defRPr sz="1000"/>
           </a:pPr>
-          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:latin typeface="ＭＳ Ｐゴシック"/>
-            <a:ea typeface="ＭＳ Ｐゴシック"/>
-          </a:endParaRPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>DB</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1200"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>account</a:t>
+          </a:r>
         </a:p>
         <a:p>
           <a:pPr algn="ctr" rtl="0">
@@ -4548,32 +4582,7 @@
               <a:latin typeface="ＭＳ Ｐゴシック"/>
               <a:ea typeface="ＭＳ Ｐゴシック"/>
             </a:rPr>
-            <a:t>アカウント</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:latin typeface="ＭＳ Ｐゴシック"/>
-            <a:ea typeface="ＭＳ Ｐゴシック"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr" rtl="0">
-            <a:lnSpc>
-              <a:spcPts val="1200"/>
-            </a:lnSpc>
-            <a:defRPr sz="1000"/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="ja-JP" altLang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="ＭＳ Ｐゴシック"/>
-              <a:ea typeface="ＭＳ Ｐゴシック"/>
-            </a:rPr>
-            <a:t>登録確認画面</a:t>
+            <a:t>テーブル</a:t>
           </a:r>
           <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
             <a:solidFill>
@@ -5219,15 +5228,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>184150</xdr:colOff>
+      <xdr:colOff>202556</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>63500</xdr:rowOff>
+      <xdr:rowOff>72702</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>184150</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:colOff>202556</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>5152</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -5244,8 +5253,8 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="4184650" y="2425700"/>
-          <a:ext cx="0" cy="565150"/>
+          <a:off x="4196614" y="2115745"/>
+          <a:ext cx="0" cy="558248"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -5710,15 +5719,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>171450</xdr:colOff>
+      <xdr:colOff>199059</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
+      <xdr:rowOff>6994</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>171450</xdr:colOff>
+      <xdr:colOff>199059</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:rowOff>38744</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -5735,8 +5744,8 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="4171950" y="3816350"/>
-          <a:ext cx="0" cy="349250"/>
+          <a:off x="4193117" y="3458081"/>
+          <a:ext cx="0" cy="344649"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -5951,6 +5960,1330 @@
 </file>
 
 <file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>31750</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="computr1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6C6EBD3F-7350-4A4D-B8C2-766A522F6243}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noEditPoints="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1619250" y="2705100"/>
+          <a:ext cx="698500" cy="762000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst>
+            <a:gd name="T0" fmla="*/ 19535 w 21600"/>
+            <a:gd name="T1" fmla="*/ 0 h 21600"/>
+            <a:gd name="T2" fmla="*/ 10800 w 21600"/>
+            <a:gd name="T3" fmla="*/ 0 h 21600"/>
+            <a:gd name="T4" fmla="*/ 2065 w 21600"/>
+            <a:gd name="T5" fmla="*/ 0 h 21600"/>
+            <a:gd name="T6" fmla="*/ 0 w 21600"/>
+            <a:gd name="T7" fmla="*/ 15388 h 21600"/>
+            <a:gd name="T8" fmla="*/ 0 w 21600"/>
+            <a:gd name="T9" fmla="*/ 21600 h 21600"/>
+            <a:gd name="T10" fmla="*/ 10800 w 21600"/>
+            <a:gd name="T11" fmla="*/ 21600 h 21600"/>
+            <a:gd name="T12" fmla="*/ 21600 w 21600"/>
+            <a:gd name="T13" fmla="*/ 21600 h 21600"/>
+            <a:gd name="T14" fmla="*/ 21600 w 21600"/>
+            <a:gd name="T15" fmla="*/ 15388 h 21600"/>
+            <a:gd name="T16" fmla="*/ 19535 w 21600"/>
+            <a:gd name="T17" fmla="*/ 13553 h 21600"/>
+            <a:gd name="T18" fmla="*/ 2065 w 21600"/>
+            <a:gd name="T19" fmla="*/ 13553 h 21600"/>
+            <a:gd name="T20" fmla="*/ 2065 w 21600"/>
+            <a:gd name="T21" fmla="*/ 6776 h 21600"/>
+            <a:gd name="T22" fmla="*/ 19535 w 21600"/>
+            <a:gd name="T23" fmla="*/ 6776 h 21600"/>
+            <a:gd name="T24" fmla="*/ 0 w 21600"/>
+            <a:gd name="T25" fmla="*/ 18494 h 21600"/>
+            <a:gd name="T26" fmla="*/ 21600 w 21600"/>
+            <a:gd name="T27" fmla="*/ 18494 h 21600"/>
+            <a:gd name="T28" fmla="*/ 4923 w 21600"/>
+            <a:gd name="T29" fmla="*/ 2541 h 21600"/>
+            <a:gd name="T30" fmla="*/ 16756 w 21600"/>
+            <a:gd name="T31" fmla="*/ 11153 h 21600"/>
+          </a:gdLst>
+          <a:ahLst/>
+          <a:cxnLst>
+            <a:cxn ang="0">
+              <a:pos x="T0" y="T1"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="T2" y="T3"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="T4" y="T5"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="T6" y="T7"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="T8" y="T9"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="T10" y="T11"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="T12" y="T13"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="T14" y="T15"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="T16" y="T17"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="T18" y="T19"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="T20" y="T21"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="T22" y="T23"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="T24" y="T25"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="T26" y="T27"/>
+            </a:cxn>
+          </a:cxnLst>
+          <a:rect l="T28" t="T29" r="T30" b="T31"/>
+          <a:pathLst>
+            <a:path w="21600" h="21600" extrusionOk="0">
+              <a:moveTo>
+                <a:pt x="16994" y="15388"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="16994" y="13553"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="19535" y="13553"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="19535" y="10729"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="19535" y="6776"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="19535" y="0"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="10800" y="0"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="2065" y="0"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="2065" y="6776"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="2065" y="10729"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="2065" y="13553"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="4606" y="13553"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="4606" y="15388"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="0" y="15388"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="0" y="21600"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="10800" y="21600"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="21600" y="21600"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="21600" y="15388"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="16994" y="15388"/>
+              </a:lnTo>
+              <a:close/>
+            </a:path>
+            <a:path w="21600" h="21600" extrusionOk="0">
+              <a:moveTo>
+                <a:pt x="4606" y="15388"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="4606" y="13553"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="16994" y="13553"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="16994" y="15388"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="4606" y="15388"/>
+              </a:lnTo>
+            </a:path>
+            <a:path w="21600" h="21600" extrusionOk="0">
+              <a:moveTo>
+                <a:pt x="4606" y="11294"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="4606" y="2259"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="16994" y="2259"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="16994" y="11294"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="4606" y="11294"/>
+              </a:lnTo>
+              <a:moveTo>
+                <a:pt x="13976" y="17082"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="13976" y="16376"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="20171" y="16376"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="20171" y="17082"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="13976" y="17082"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFCC"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+        <a:effectLst/>
+        <a:extLst>
+          <a:ext uri="{AF507438-7753-43E0-B8FC-AC1667EBCBE1}">
+            <a14:hiddenEffects xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:effectLst>
+                <a:outerShdw dist="107763" dir="13500000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="808080"/>
+                </a:outerShdw>
+              </a:effectLst>
+            </a14:hiddenEffects>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>174855</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>266885</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>138044</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="Rectangle 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F6599C1-BC10-4A9C-B596-E381F5EF0A29}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="2457174" y="635000"/>
+          <a:ext cx="3515508" cy="1389638"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="22860" rIns="0" bIns="0" anchor="t" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1300"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>【</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>アカウント更新画面</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>】</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>　　　　　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>【</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>アカウント削除画面</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>】</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1300"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:latin typeface="ＭＳ Ｐゴシック"/>
+            <a:ea typeface="ＭＳ Ｐゴシック"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1300"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>・名前（性）、名前（名）　　　　　・アカウント内容表示　　</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1300"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>・カナ（性）、カナ（名） 　　　　　→「確認する」ボタン</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1300"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>・メールアドレス</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1300"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>・性別</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1300"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>・アカウント権限</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1200"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>→「確認する」ボタン</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>202556</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>72703</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>202556</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>5153</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="Line 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{623C273A-AADB-41BC-94F0-087EB3CA9300}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeShapeType="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4196614" y="2115746"/>
+          <a:ext cx="0" cy="558248"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd type="triangle" w="med" len="med"/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:noFill/>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>44450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>260350</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>44450</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="Line 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{569EF67D-6059-4418-8C46-AC702156080A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeShapeType="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm flipH="1">
+          <a:off x="2400300" y="3067050"/>
+          <a:ext cx="717550" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd type="triangle" w="med" len="med"/>
+          <a:tailEnd/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:noFill/>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>249123</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>92028</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>71783</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>55217</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="Rectangle 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{82BD3C3C-D765-4A9B-ACA3-16BA2F9FC24A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="6240210" y="1978622"/>
+          <a:ext cx="2960848" cy="2153479"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="22860" rIns="0" bIns="0" anchor="t" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1300"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>【</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>アカウント更新確認画面</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>】</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1300"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>・名前（性）、名前（名）、カナ（性）、カナ（名）</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1300"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>・メールアドレス</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1300"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>・パスワード</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1300"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>・性別</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1300"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>・郵便番号</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1300"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>・住所（都道府県、市区町村、番地）</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1300"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>・アカウント権限</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1300"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>・「前に戻る」ボタン、「更新する」ボタン</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:latin typeface="ＭＳ Ｐゴシック"/>
+            <a:ea typeface="ＭＳ Ｐゴシック"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1300"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:latin typeface="ＭＳ Ｐゴシック"/>
+            <a:ea typeface="ＭＳ Ｐゴシック"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1300"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>【</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>アカウント削除確認画面</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>】</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1300"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>・「前に戻る」ボタン、「削除する」ボタン</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1300"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:latin typeface="ＭＳ Ｐゴシック"/>
+            <a:ea typeface="ＭＳ Ｐゴシック"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>146050</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="Line 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7A0E5ED9-CBF5-44CD-B8C4-ABE7BFB5A3DB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeShapeType="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5448300" y="3060700"/>
+          <a:ext cx="698500" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd type="triangle" w="med" len="med"/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:noFill/>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="Line 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{01BB57D9-9118-4317-ADAD-B4E50C284F3F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeShapeType="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4171950" y="3524250"/>
+          <a:ext cx="0" cy="349250"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd type="triangle" w="med" len="med"/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:noFill/>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>55217</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="AutoShape 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D7122556-4414-45DD-ACB5-2C88A4C30C87}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4292600" y="3892550"/>
+          <a:ext cx="850900" cy="772767"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartMagneticDisk">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="22860" rIns="36576" bIns="0" anchor="t" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1200"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:latin typeface="ＭＳ Ｐゴシック"/>
+            <a:ea typeface="ＭＳ Ｐゴシック"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>165100</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>127000</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>73623</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="AutoShape 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{88C1B3C7-FCAC-4B38-9435-43D6D3009E19}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3308350" y="3975100"/>
+          <a:ext cx="819150" cy="708623"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartDocument">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="22860" rIns="36576" bIns="0" anchor="t" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1200"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:latin typeface="ＭＳ Ｐゴシック"/>
+            <a:ea typeface="ＭＳ Ｐゴシック"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>170714</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>91476</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>17853</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="Rectangle 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{519668AD-123A-486D-8211-B02A66194BFB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3308902" y="2760317"/>
+          <a:ext cx="1826315" cy="708623"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="22860" rIns="36576" bIns="0" anchor="ctr" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1200"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:latin typeface="ＭＳ Ｐゴシック"/>
+            <a:ea typeface="ＭＳ Ｐゴシック"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1200"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1600" b="1" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>アカウント更新</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1600" b="1" i="0" u="none" strike="noStrike" baseline="0">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:latin typeface="ＭＳ Ｐゴシック"/>
+            <a:ea typeface="ＭＳ Ｐゴシック"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1200"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1600" b="1" i="0" u="none" strike="noStrike" baseline="0">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:latin typeface="ＭＳ Ｐゴシック"/>
+            <a:ea typeface="ＭＳ Ｐゴシック"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:lnSpc>
+              <a:spcPts val="1200"/>
+            </a:lnSpc>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1600" b="1" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>削除フラグ更新</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1600" b="1" i="0" u="none" strike="noStrike" baseline="0">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:latin typeface="ＭＳ Ｐゴシック"/>
+            <a:ea typeface="ＭＳ Ｐゴシック"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -16581,6 +17914,1671 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EA1CC15-A0F2-427E-9159-4A8BD2272778}">
+  <dimension ref="A1:FU42"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" customHeight="1"/>
+  <cols>
+    <col min="1" max="4" width="4.08984375" style="1" customWidth="1"/>
+    <col min="5" max="6" width="4.08984375" style="4" customWidth="1"/>
+    <col min="7" max="33" width="4.08984375" style="1" customWidth="1"/>
+    <col min="34" max="37" width="4" style="1" customWidth="1"/>
+    <col min="38" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:177" ht="12.75" customHeight="1">
+      <c r="A1" s="58" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
+      <c r="H1" s="58"/>
+      <c r="I1" s="58"/>
+      <c r="J1" s="58"/>
+      <c r="K1" s="58"/>
+      <c r="L1" s="58"/>
+      <c r="M1" s="58"/>
+      <c r="N1" s="58"/>
+      <c r="O1" s="58"/>
+      <c r="P1" s="58"/>
+      <c r="Q1" s="58"/>
+      <c r="R1" s="58"/>
+      <c r="S1" s="58"/>
+      <c r="T1" s="58"/>
+      <c r="U1" s="58"/>
+      <c r="V1" s="58"/>
+      <c r="W1" s="58"/>
+      <c r="X1" s="58"/>
+      <c r="Y1" s="58"/>
+      <c r="Z1" s="58"/>
+      <c r="AA1" s="58"/>
+      <c r="AB1" s="58"/>
+      <c r="AC1" s="58"/>
+      <c r="AD1" s="58"/>
+      <c r="AE1" s="58"/>
+      <c r="AF1" s="58"/>
+      <c r="AG1" s="58"/>
+    </row>
+    <row r="2" spans="1:177" ht="13" customHeight="1">
+      <c r="A2" s="59" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="59" t="s">
+        <v>48</v>
+      </c>
+      <c r="H2" s="60"/>
+      <c r="I2" s="60"/>
+      <c r="J2" s="60"/>
+      <c r="K2" s="60"/>
+      <c r="L2" s="60"/>
+      <c r="M2" s="60"/>
+      <c r="N2" s="60"/>
+      <c r="O2" s="60"/>
+      <c r="P2" s="60"/>
+      <c r="Q2" s="60"/>
+      <c r="R2" s="60"/>
+      <c r="S2" s="60"/>
+      <c r="T2" s="60"/>
+      <c r="U2" s="60"/>
+      <c r="V2" s="60"/>
+      <c r="W2" s="60"/>
+      <c r="X2" s="60"/>
+      <c r="Y2" s="60"/>
+      <c r="Z2" s="60"/>
+      <c r="AA2" s="60"/>
+      <c r="AB2" s="60"/>
+      <c r="AC2" s="61"/>
+      <c r="AD2" s="59" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE2" s="61"/>
+      <c r="AF2" s="59" t="s">
+        <v>2</v>
+      </c>
+      <c r="AG2" s="61"/>
+    </row>
+    <row r="3" spans="1:177" s="3" customFormat="1" ht="12.75" customHeight="1">
+      <c r="A3" s="59" t="s">
+        <v>54</v>
+      </c>
+      <c r="B3" s="60"/>
+      <c r="C3" s="60"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="59" t="s">
+        <v>58</v>
+      </c>
+      <c r="H3" s="60"/>
+      <c r="I3" s="60"/>
+      <c r="J3" s="60"/>
+      <c r="K3" s="60"/>
+      <c r="L3" s="60"/>
+      <c r="M3" s="60"/>
+      <c r="N3" s="60"/>
+      <c r="O3" s="60"/>
+      <c r="P3" s="60"/>
+      <c r="Q3" s="60"/>
+      <c r="R3" s="60"/>
+      <c r="S3" s="60"/>
+      <c r="T3" s="60"/>
+      <c r="U3" s="60"/>
+      <c r="V3" s="60"/>
+      <c r="W3" s="60"/>
+      <c r="X3" s="60"/>
+      <c r="Y3" s="60"/>
+      <c r="Z3" s="60"/>
+      <c r="AA3" s="60"/>
+      <c r="AB3" s="60"/>
+      <c r="AC3" s="61"/>
+      <c r="AD3" s="59"/>
+      <c r="AE3" s="61"/>
+      <c r="AF3" s="59"/>
+      <c r="AG3" s="61"/>
+      <c r="AH3" s="2"/>
+      <c r="AI3" s="5"/>
+      <c r="AJ3" s="5"/>
+      <c r="AK3" s="5"/>
+      <c r="AL3" s="5"/>
+      <c r="AM3" s="5"/>
+      <c r="AN3" s="5"/>
+      <c r="AO3" s="5"/>
+      <c r="AP3" s="5"/>
+      <c r="AQ3" s="5"/>
+      <c r="AR3" s="5"/>
+      <c r="AS3" s="5"/>
+      <c r="AT3" s="5"/>
+      <c r="AU3" s="5"/>
+      <c r="AV3" s="5"/>
+      <c r="AW3" s="5"/>
+      <c r="AX3" s="5"/>
+      <c r="AY3" s="5"/>
+      <c r="AZ3" s="5"/>
+      <c r="BA3" s="5"/>
+      <c r="BB3" s="5"/>
+      <c r="BC3" s="5"/>
+      <c r="BD3" s="5"/>
+      <c r="BE3" s="5"/>
+      <c r="BF3" s="5"/>
+      <c r="BG3" s="5"/>
+      <c r="BH3" s="5"/>
+      <c r="BI3" s="5"/>
+      <c r="BJ3" s="5"/>
+      <c r="BK3" s="5"/>
+      <c r="BL3" s="5"/>
+      <c r="BM3" s="5"/>
+      <c r="BN3" s="5"/>
+      <c r="BO3" s="5"/>
+      <c r="BP3" s="5"/>
+      <c r="BQ3" s="5"/>
+      <c r="BR3" s="5"/>
+      <c r="BS3" s="5"/>
+      <c r="BT3" s="5"/>
+      <c r="BU3" s="5"/>
+      <c r="BV3" s="5"/>
+      <c r="BW3" s="5"/>
+      <c r="BX3" s="5"/>
+      <c r="BY3" s="5"/>
+      <c r="BZ3" s="5"/>
+      <c r="CA3" s="5"/>
+      <c r="CB3" s="5"/>
+      <c r="CC3" s="5"/>
+      <c r="CD3" s="5"/>
+      <c r="CE3" s="5"/>
+      <c r="CF3" s="5"/>
+      <c r="CG3" s="5"/>
+      <c r="CH3" s="5"/>
+      <c r="CI3" s="5"/>
+      <c r="CJ3" s="5"/>
+      <c r="CK3" s="5"/>
+      <c r="CL3" s="5"/>
+      <c r="CM3" s="5"/>
+      <c r="CN3" s="5"/>
+      <c r="CO3" s="5"/>
+      <c r="CP3" s="5"/>
+      <c r="CQ3" s="5"/>
+      <c r="CR3" s="5"/>
+      <c r="CS3" s="5"/>
+      <c r="CT3" s="5"/>
+      <c r="CU3" s="5"/>
+      <c r="CV3" s="5"/>
+      <c r="CW3" s="5"/>
+      <c r="CX3" s="5"/>
+      <c r="CY3" s="5"/>
+      <c r="CZ3" s="5"/>
+      <c r="DA3" s="5"/>
+      <c r="DB3" s="5"/>
+      <c r="DC3" s="5"/>
+      <c r="DD3" s="5"/>
+      <c r="DE3" s="5"/>
+      <c r="DF3" s="5"/>
+      <c r="DG3" s="5"/>
+      <c r="DH3" s="5"/>
+      <c r="DI3" s="5"/>
+      <c r="DJ3" s="5"/>
+      <c r="DK3" s="5"/>
+      <c r="DL3" s="5"/>
+      <c r="DM3" s="5"/>
+      <c r="DN3" s="5"/>
+      <c r="DO3" s="5"/>
+      <c r="DP3" s="5"/>
+      <c r="DQ3" s="5"/>
+      <c r="DR3" s="5"/>
+      <c r="DS3" s="5"/>
+      <c r="DT3" s="5"/>
+      <c r="DU3" s="5"/>
+      <c r="DV3" s="5"/>
+      <c r="DW3" s="5"/>
+      <c r="DX3" s="5"/>
+      <c r="DY3" s="5"/>
+      <c r="DZ3" s="5"/>
+      <c r="EA3" s="5"/>
+      <c r="EB3" s="5"/>
+      <c r="EC3" s="5"/>
+      <c r="ED3" s="5"/>
+      <c r="EE3" s="5"/>
+      <c r="EF3" s="5"/>
+      <c r="EG3" s="5"/>
+      <c r="EH3" s="5"/>
+      <c r="EI3" s="5"/>
+      <c r="EJ3" s="5"/>
+      <c r="EK3" s="5"/>
+      <c r="EL3" s="5"/>
+      <c r="EM3" s="5"/>
+      <c r="EN3" s="5"/>
+      <c r="EO3" s="5"/>
+      <c r="EP3" s="5"/>
+      <c r="EQ3" s="5"/>
+      <c r="ER3" s="5"/>
+      <c r="ES3" s="5"/>
+      <c r="ET3" s="5"/>
+      <c r="EU3" s="5"/>
+      <c r="EV3" s="5"/>
+      <c r="EW3" s="5"/>
+      <c r="EX3" s="5"/>
+      <c r="EY3" s="5"/>
+      <c r="EZ3" s="5"/>
+      <c r="FA3" s="5"/>
+      <c r="FB3" s="5"/>
+      <c r="FC3" s="5"/>
+      <c r="FD3" s="5"/>
+      <c r="FE3" s="5"/>
+      <c r="FF3" s="5"/>
+      <c r="FG3" s="5"/>
+      <c r="FH3" s="5"/>
+      <c r="FI3" s="5"/>
+      <c r="FJ3" s="5"/>
+      <c r="FK3" s="5"/>
+      <c r="FL3" s="5"/>
+      <c r="FM3" s="5"/>
+      <c r="FN3" s="5"/>
+      <c r="FO3" s="5"/>
+      <c r="FP3" s="5"/>
+      <c r="FQ3" s="5"/>
+      <c r="FR3" s="5"/>
+      <c r="FS3" s="5"/>
+      <c r="FT3" s="5"/>
+      <c r="FU3" s="5"/>
+    </row>
+    <row r="4" spans="1:177" ht="12.75" customHeight="1">
+      <c r="A4" s="32"/>
+      <c r="B4" s="33"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="33"/>
+      <c r="H4" s="33"/>
+      <c r="I4" s="33"/>
+      <c r="J4" s="33"/>
+      <c r="K4" s="33"/>
+      <c r="L4" s="33"/>
+      <c r="M4" s="33"/>
+      <c r="N4" s="33"/>
+      <c r="O4" s="33"/>
+      <c r="P4" s="33"/>
+      <c r="Q4" s="33"/>
+      <c r="R4" s="33"/>
+      <c r="S4" s="33"/>
+      <c r="T4" s="33"/>
+      <c r="U4" s="33"/>
+      <c r="V4" s="33"/>
+      <c r="W4" s="33"/>
+      <c r="X4" s="33"/>
+      <c r="Y4" s="33"/>
+      <c r="Z4" s="33"/>
+      <c r="AA4" s="33"/>
+      <c r="AB4" s="33"/>
+      <c r="AC4" s="33"/>
+      <c r="AD4" s="33"/>
+      <c r="AE4" s="33"/>
+      <c r="AF4" s="33"/>
+      <c r="AG4" s="34"/>
+    </row>
+    <row r="5" spans="1:177" ht="12.75" customHeight="1">
+      <c r="A5" s="16"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="35"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="13"/>
+      <c r="M5" s="13"/>
+      <c r="N5" s="13"/>
+      <c r="O5" s="13"/>
+      <c r="P5" s="13"/>
+      <c r="Q5" s="13"/>
+      <c r="R5" s="13"/>
+      <c r="S5" s="13"/>
+      <c r="T5" s="13"/>
+      <c r="U5" s="13"/>
+      <c r="V5" s="13"/>
+      <c r="W5" s="13"/>
+      <c r="X5" s="13"/>
+      <c r="Y5" s="13"/>
+      <c r="Z5" s="13"/>
+      <c r="AA5" s="13"/>
+      <c r="AB5" s="13"/>
+      <c r="AC5" s="13"/>
+      <c r="AD5" s="13"/>
+      <c r="AE5" s="13"/>
+      <c r="AF5" s="13"/>
+      <c r="AG5" s="18"/>
+    </row>
+    <row r="6" spans="1:177" ht="12.75" customHeight="1">
+      <c r="A6" s="16"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="35"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="13"/>
+      <c r="N6" s="13"/>
+      <c r="O6" s="13"/>
+      <c r="P6" s="36"/>
+      <c r="Q6" s="13"/>
+      <c r="R6" s="13"/>
+      <c r="S6" s="13"/>
+      <c r="T6" s="13"/>
+      <c r="U6" s="13"/>
+      <c r="V6" s="13"/>
+      <c r="W6" s="13"/>
+      <c r="X6" s="13"/>
+      <c r="Y6" s="13"/>
+      <c r="Z6" s="13"/>
+      <c r="AA6" s="13"/>
+      <c r="AB6" s="13"/>
+      <c r="AC6" s="13"/>
+      <c r="AD6" s="13"/>
+      <c r="AE6" s="13"/>
+      <c r="AF6" s="13"/>
+      <c r="AG6" s="18"/>
+    </row>
+    <row r="7" spans="1:177" ht="12.75" customHeight="1">
+      <c r="A7" s="16"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="13"/>
+      <c r="L7" s="13"/>
+      <c r="M7" s="13"/>
+      <c r="N7" s="13"/>
+      <c r="O7" s="13"/>
+      <c r="P7" s="36"/>
+      <c r="Q7" s="13"/>
+      <c r="R7" s="13"/>
+      <c r="S7" s="36"/>
+      <c r="T7" s="36"/>
+      <c r="U7" s="36"/>
+      <c r="V7" s="36"/>
+      <c r="W7" s="36"/>
+      <c r="X7" s="36"/>
+      <c r="Y7" s="36"/>
+      <c r="Z7" s="13"/>
+      <c r="AA7" s="13"/>
+      <c r="AB7" s="13"/>
+      <c r="AC7" s="13"/>
+      <c r="AD7" s="13"/>
+      <c r="AE7" s="13"/>
+      <c r="AF7" s="13"/>
+      <c r="AG7" s="18"/>
+    </row>
+    <row r="8" spans="1:177" ht="12.75" customHeight="1">
+      <c r="A8" s="16"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="13"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="13"/>
+      <c r="M8" s="13"/>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13"/>
+      <c r="P8" s="36"/>
+      <c r="Q8" s="13"/>
+      <c r="R8" s="13"/>
+      <c r="S8" s="13"/>
+      <c r="T8" s="36"/>
+      <c r="U8" s="36"/>
+      <c r="V8" s="36"/>
+      <c r="W8" s="36"/>
+      <c r="X8" s="36"/>
+      <c r="Y8" s="36"/>
+      <c r="Z8" s="13"/>
+      <c r="AA8" s="13"/>
+      <c r="AB8" s="13"/>
+      <c r="AC8" s="13"/>
+      <c r="AD8" s="13"/>
+      <c r="AE8" s="13"/>
+      <c r="AF8" s="13"/>
+      <c r="AG8" s="18"/>
+    </row>
+    <row r="9" spans="1:177" ht="12.75" customHeight="1">
+      <c r="A9" s="16"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="13"/>
+      <c r="P9" s="36"/>
+      <c r="Q9" s="13"/>
+      <c r="R9" s="13"/>
+      <c r="S9" s="13"/>
+      <c r="T9" s="36"/>
+      <c r="U9" s="36"/>
+      <c r="V9" s="36"/>
+      <c r="W9" s="36"/>
+      <c r="X9" s="36"/>
+      <c r="Y9" s="36"/>
+      <c r="Z9" s="13"/>
+      <c r="AA9" s="13"/>
+      <c r="AB9" s="13"/>
+      <c r="AC9" s="13"/>
+      <c r="AD9" s="13"/>
+      <c r="AE9" s="13"/>
+      <c r="AF9" s="13"/>
+      <c r="AG9" s="18"/>
+    </row>
+    <row r="10" spans="1:177" ht="12.75" customHeight="1">
+      <c r="A10" s="16"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="13"/>
+      <c r="L10" s="13"/>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13"/>
+      <c r="P10" s="36"/>
+      <c r="Q10" s="13"/>
+      <c r="R10" s="13"/>
+      <c r="S10" s="36"/>
+      <c r="T10" s="36"/>
+      <c r="U10" s="36"/>
+      <c r="V10" s="36"/>
+      <c r="W10" s="36"/>
+      <c r="X10" s="36"/>
+      <c r="Y10" s="36"/>
+      <c r="Z10" s="13"/>
+      <c r="AA10" s="13"/>
+      <c r="AB10" s="13"/>
+      <c r="AC10" s="13"/>
+      <c r="AD10" s="13"/>
+      <c r="AE10" s="13"/>
+      <c r="AF10" s="13"/>
+      <c r="AG10" s="18"/>
+    </row>
+    <row r="11" spans="1:177" ht="12.75" customHeight="1">
+      <c r="A11" s="16"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="13"/>
+      <c r="L11" s="13"/>
+      <c r="M11" s="13"/>
+      <c r="N11" s="13"/>
+      <c r="O11" s="13"/>
+      <c r="P11" s="36"/>
+      <c r="Q11" s="13"/>
+      <c r="R11" s="13"/>
+      <c r="S11" s="13"/>
+      <c r="T11" s="13"/>
+      <c r="U11" s="13"/>
+      <c r="V11" s="13"/>
+      <c r="W11" s="13"/>
+      <c r="X11" s="13"/>
+      <c r="Y11" s="13"/>
+      <c r="Z11" s="13"/>
+      <c r="AA11" s="13"/>
+      <c r="AB11" s="13"/>
+      <c r="AC11" s="13"/>
+      <c r="AD11" s="13"/>
+      <c r="AE11" s="13"/>
+      <c r="AF11" s="13"/>
+      <c r="AG11" s="18"/>
+    </row>
+    <row r="12" spans="1:177" ht="12.75" customHeight="1">
+      <c r="A12" s="16"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="13"/>
+      <c r="K12" s="13"/>
+      <c r="L12" s="13"/>
+      <c r="M12" s="13"/>
+      <c r="N12" s="13"/>
+      <c r="O12" s="13"/>
+      <c r="P12" s="36"/>
+      <c r="Q12" s="13"/>
+      <c r="R12" s="13"/>
+      <c r="S12" s="13"/>
+      <c r="T12" s="13"/>
+      <c r="U12" s="13"/>
+      <c r="V12" s="13"/>
+      <c r="W12" s="13"/>
+      <c r="X12" s="13"/>
+      <c r="Y12" s="13"/>
+      <c r="Z12" s="13"/>
+      <c r="AA12" s="13"/>
+      <c r="AB12" s="13"/>
+      <c r="AC12" s="13"/>
+      <c r="AD12" s="13"/>
+      <c r="AE12" s="13"/>
+      <c r="AF12" s="13"/>
+      <c r="AG12" s="18"/>
+    </row>
+    <row r="13" spans="1:177" ht="12.75" customHeight="1">
+      <c r="A13" s="16"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="13"/>
+      <c r="J13" s="13"/>
+      <c r="K13" s="13"/>
+      <c r="L13" s="13"/>
+      <c r="M13" s="13"/>
+      <c r="N13" s="13"/>
+      <c r="O13" s="13"/>
+      <c r="P13" s="36"/>
+      <c r="Q13" s="13"/>
+      <c r="R13" s="13"/>
+      <c r="S13" s="13"/>
+      <c r="T13" s="13"/>
+      <c r="U13" s="13"/>
+      <c r="V13" s="36"/>
+      <c r="W13" s="36"/>
+      <c r="X13" s="13"/>
+      <c r="Y13" s="13"/>
+      <c r="Z13" s="13"/>
+      <c r="AA13" s="13"/>
+      <c r="AB13" s="13"/>
+      <c r="AC13" s="13"/>
+      <c r="AD13" s="13"/>
+      <c r="AE13" s="13"/>
+      <c r="AF13" s="13"/>
+      <c r="AG13" s="18"/>
+    </row>
+    <row r="14" spans="1:177" ht="12.75" customHeight="1">
+      <c r="A14" s="16"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="13"/>
+      <c r="K14" s="13"/>
+      <c r="L14" s="13"/>
+      <c r="M14" s="13"/>
+      <c r="N14" s="13"/>
+      <c r="O14" s="13"/>
+      <c r="P14" s="36"/>
+      <c r="Q14" s="13"/>
+      <c r="R14" s="13"/>
+      <c r="S14" s="13"/>
+      <c r="T14" s="13"/>
+      <c r="U14" s="13"/>
+      <c r="V14" s="13"/>
+      <c r="W14" s="13"/>
+      <c r="X14" s="13"/>
+      <c r="Y14" s="13"/>
+      <c r="Z14" s="13"/>
+      <c r="AA14" s="13"/>
+      <c r="AB14" s="13"/>
+      <c r="AC14" s="13"/>
+      <c r="AD14" s="13"/>
+      <c r="AE14" s="13"/>
+      <c r="AF14" s="13"/>
+      <c r="AG14" s="18"/>
+    </row>
+    <row r="15" spans="1:177" ht="12.75" customHeight="1">
+      <c r="A15" s="16"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="13"/>
+      <c r="J15" s="13"/>
+      <c r="K15" s="13"/>
+      <c r="L15" s="13"/>
+      <c r="M15" s="13"/>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13"/>
+      <c r="P15" s="36"/>
+      <c r="Q15" s="13"/>
+      <c r="R15" s="13"/>
+      <c r="S15" s="13"/>
+      <c r="T15" s="13"/>
+      <c r="U15" s="13"/>
+      <c r="V15" s="13"/>
+      <c r="W15" s="13"/>
+      <c r="X15" s="13"/>
+      <c r="Y15" s="13"/>
+      <c r="Z15" s="13"/>
+      <c r="AA15" s="13"/>
+      <c r="AB15" s="13"/>
+      <c r="AC15" s="13"/>
+      <c r="AD15" s="13"/>
+      <c r="AE15" s="13"/>
+      <c r="AF15" s="13"/>
+      <c r="AG15" s="18"/>
+    </row>
+    <row r="16" spans="1:177" ht="12.75" customHeight="1">
+      <c r="A16" s="16"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="13"/>
+      <c r="I16" s="13"/>
+      <c r="J16" s="13"/>
+      <c r="K16" s="13"/>
+      <c r="L16" s="13"/>
+      <c r="M16" s="13"/>
+      <c r="N16" s="13"/>
+      <c r="O16" s="13"/>
+      <c r="P16" s="36"/>
+      <c r="Q16" s="13"/>
+      <c r="R16" s="13"/>
+      <c r="S16" s="36"/>
+      <c r="T16" s="13"/>
+      <c r="U16" s="13"/>
+      <c r="V16" s="13"/>
+      <c r="W16" s="13"/>
+      <c r="X16" s="13"/>
+      <c r="Y16" s="13"/>
+      <c r="Z16" s="13"/>
+      <c r="AA16" s="13"/>
+      <c r="AB16" s="13"/>
+      <c r="AC16" s="13"/>
+      <c r="AD16" s="13"/>
+      <c r="AE16" s="13"/>
+      <c r="AF16" s="13"/>
+      <c r="AG16" s="18"/>
+    </row>
+    <row r="17" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A17" s="16"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="13"/>
+      <c r="K17" s="13"/>
+      <c r="L17" s="13"/>
+      <c r="M17" s="13"/>
+      <c r="N17" s="13"/>
+      <c r="O17" s="13"/>
+      <c r="P17" s="36"/>
+      <c r="Q17" s="13"/>
+      <c r="R17" s="13"/>
+      <c r="S17" s="13"/>
+      <c r="T17" s="13"/>
+      <c r="U17" s="13"/>
+      <c r="V17" s="13"/>
+      <c r="W17" s="36"/>
+      <c r="X17" s="13"/>
+      <c r="Y17" s="13"/>
+      <c r="Z17" s="13"/>
+      <c r="AA17" s="13"/>
+      <c r="AB17" s="13"/>
+      <c r="AC17" s="13"/>
+      <c r="AD17" s="13"/>
+      <c r="AE17" s="13"/>
+      <c r="AF17" s="13"/>
+      <c r="AG17" s="18"/>
+    </row>
+    <row r="18" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A18" s="16"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="13"/>
+      <c r="J18" s="13"/>
+      <c r="K18" s="13"/>
+      <c r="L18" s="13"/>
+      <c r="M18" s="13"/>
+      <c r="N18" s="13"/>
+      <c r="O18" s="13"/>
+      <c r="P18" s="36"/>
+      <c r="Q18" s="13"/>
+      <c r="R18" s="13"/>
+      <c r="S18" s="13"/>
+      <c r="T18" s="13"/>
+      <c r="U18" s="13"/>
+      <c r="V18" s="36"/>
+      <c r="W18" s="36"/>
+      <c r="X18" s="13"/>
+      <c r="Y18" s="13"/>
+      <c r="Z18" s="13"/>
+      <c r="AA18" s="13"/>
+      <c r="AB18" s="13"/>
+      <c r="AC18" s="13"/>
+      <c r="AD18" s="13"/>
+      <c r="AE18" s="13"/>
+      <c r="AF18" s="13"/>
+      <c r="AG18" s="18"/>
+    </row>
+    <row r="19" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A19" s="16"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="13"/>
+      <c r="J19" s="13"/>
+      <c r="K19" s="13"/>
+      <c r="L19" s="13"/>
+      <c r="M19" s="13"/>
+      <c r="N19" s="13"/>
+      <c r="O19" s="13"/>
+      <c r="P19" s="36"/>
+      <c r="Q19" s="13"/>
+      <c r="R19" s="13"/>
+      <c r="S19" s="13"/>
+      <c r="T19" s="13"/>
+      <c r="U19" s="13"/>
+      <c r="V19" s="13"/>
+      <c r="W19" s="13"/>
+      <c r="X19" s="13"/>
+      <c r="Y19" s="13"/>
+      <c r="Z19" s="13"/>
+      <c r="AA19" s="13"/>
+      <c r="AB19" s="13"/>
+      <c r="AC19" s="13"/>
+      <c r="AD19" s="13"/>
+      <c r="AE19" s="13"/>
+      <c r="AF19" s="13"/>
+      <c r="AG19" s="18"/>
+    </row>
+    <row r="20" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A20" s="16"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="13"/>
+      <c r="J20" s="13"/>
+      <c r="K20" s="13"/>
+      <c r="L20" s="13"/>
+      <c r="M20" s="13"/>
+      <c r="N20" s="13"/>
+      <c r="O20" s="13"/>
+      <c r="P20" s="36"/>
+      <c r="Q20" s="13"/>
+      <c r="R20" s="13"/>
+      <c r="S20" s="13"/>
+      <c r="T20" s="13"/>
+      <c r="U20" s="13"/>
+      <c r="V20" s="13"/>
+      <c r="W20" s="13"/>
+      <c r="X20" s="13"/>
+      <c r="Y20" s="13"/>
+      <c r="Z20" s="13"/>
+      <c r="AA20" s="13"/>
+      <c r="AB20" s="13"/>
+      <c r="AC20" s="13"/>
+      <c r="AD20" s="13"/>
+      <c r="AE20" s="13"/>
+      <c r="AF20" s="13"/>
+      <c r="AG20" s="18"/>
+    </row>
+    <row r="21" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A21" s="16"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="13"/>
+      <c r="J21" s="13"/>
+      <c r="K21" s="13"/>
+      <c r="L21" s="13"/>
+      <c r="M21" s="13"/>
+      <c r="N21" s="13"/>
+      <c r="O21" s="13"/>
+      <c r="P21" s="36"/>
+      <c r="Q21" s="13"/>
+      <c r="R21" s="13"/>
+      <c r="S21" s="36"/>
+      <c r="T21" s="36"/>
+      <c r="U21" s="36"/>
+      <c r="V21" s="36"/>
+      <c r="W21" s="36"/>
+      <c r="X21" s="36"/>
+      <c r="Y21" s="36"/>
+      <c r="Z21" s="13"/>
+      <c r="AA21" s="13"/>
+      <c r="AB21" s="13"/>
+      <c r="AC21" s="13"/>
+      <c r="AD21" s="13"/>
+      <c r="AE21" s="13"/>
+      <c r="AF21" s="13"/>
+      <c r="AG21" s="18"/>
+    </row>
+    <row r="22" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A22" s="16"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="13"/>
+      <c r="J22" s="13"/>
+      <c r="K22" s="13"/>
+      <c r="L22" s="13"/>
+      <c r="M22" s="13"/>
+      <c r="N22" s="13"/>
+      <c r="O22" s="13"/>
+      <c r="P22" s="36"/>
+      <c r="Q22" s="13"/>
+      <c r="R22" s="13"/>
+      <c r="S22" s="13"/>
+      <c r="T22" s="36"/>
+      <c r="U22" s="36"/>
+      <c r="V22" s="36"/>
+      <c r="W22" s="36"/>
+      <c r="X22" s="36"/>
+      <c r="Y22" s="36"/>
+      <c r="Z22" s="13"/>
+      <c r="AA22" s="13"/>
+      <c r="AB22" s="13"/>
+      <c r="AC22" s="13"/>
+      <c r="AD22" s="13"/>
+      <c r="AE22" s="13"/>
+      <c r="AF22" s="13"/>
+      <c r="AG22" s="18"/>
+    </row>
+    <row r="23" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A23" s="16"/>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13"/>
+      <c r="I23" s="13"/>
+      <c r="J23" s="13"/>
+      <c r="K23" s="13"/>
+      <c r="L23" s="13"/>
+      <c r="M23" s="13"/>
+      <c r="N23" s="13"/>
+      <c r="O23" s="13"/>
+      <c r="P23" s="36"/>
+      <c r="Q23" s="13"/>
+      <c r="R23" s="13"/>
+      <c r="S23" s="36"/>
+      <c r="T23" s="36"/>
+      <c r="U23" s="36"/>
+      <c r="V23" s="36"/>
+      <c r="W23" s="36"/>
+      <c r="X23" s="36"/>
+      <c r="Y23" s="36"/>
+      <c r="Z23" s="13"/>
+      <c r="AA23" s="13"/>
+      <c r="AB23" s="13"/>
+      <c r="AC23" s="13"/>
+      <c r="AD23" s="13"/>
+      <c r="AE23" s="13"/>
+      <c r="AF23" s="13"/>
+      <c r="AG23" s="18"/>
+    </row>
+    <row r="24" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A24" s="16"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="13"/>
+      <c r="J24" s="13"/>
+      <c r="K24" s="13"/>
+      <c r="L24" s="13"/>
+      <c r="M24" s="13"/>
+      <c r="N24" s="13"/>
+      <c r="O24" s="13"/>
+      <c r="P24" s="36"/>
+      <c r="Q24" s="13"/>
+      <c r="R24" s="13"/>
+      <c r="S24" s="36"/>
+      <c r="T24" s="36"/>
+      <c r="U24" s="36"/>
+      <c r="V24" s="36"/>
+      <c r="W24" s="36"/>
+      <c r="X24" s="36"/>
+      <c r="Y24" s="36"/>
+      <c r="Z24" s="13"/>
+      <c r="AA24" s="13"/>
+      <c r="AB24" s="13"/>
+      <c r="AC24" s="13"/>
+      <c r="AD24" s="13"/>
+      <c r="AE24" s="13"/>
+      <c r="AF24" s="13"/>
+      <c r="AG24" s="18"/>
+    </row>
+    <row r="25" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A25" s="16"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="13"/>
+      <c r="H25" s="13"/>
+      <c r="I25" s="13"/>
+      <c r="J25" s="13"/>
+      <c r="K25" s="13"/>
+      <c r="L25" s="13"/>
+      <c r="M25" s="13"/>
+      <c r="N25" s="13"/>
+      <c r="O25" s="13"/>
+      <c r="P25" s="36"/>
+      <c r="Q25" s="13"/>
+      <c r="R25" s="13"/>
+      <c r="S25" s="36"/>
+      <c r="T25" s="36"/>
+      <c r="U25" s="36"/>
+      <c r="V25" s="36"/>
+      <c r="W25" s="36"/>
+      <c r="X25" s="36"/>
+      <c r="Y25" s="36"/>
+      <c r="Z25" s="13"/>
+      <c r="AA25" s="13"/>
+      <c r="AB25" s="13"/>
+      <c r="AC25" s="13"/>
+      <c r="AD25" s="13"/>
+      <c r="AE25" s="13"/>
+      <c r="AF25" s="13"/>
+      <c r="AG25" s="18"/>
+    </row>
+    <row r="26" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A26" s="16"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="13"/>
+      <c r="I26" s="13"/>
+      <c r="J26" s="13"/>
+      <c r="K26" s="13"/>
+      <c r="L26" s="13"/>
+      <c r="M26" s="13"/>
+      <c r="N26" s="13"/>
+      <c r="O26" s="13"/>
+      <c r="P26" s="36"/>
+      <c r="Q26" s="13"/>
+      <c r="R26" s="13"/>
+      <c r="S26" s="36"/>
+      <c r="T26" s="36"/>
+      <c r="U26" s="36"/>
+      <c r="V26" s="36"/>
+      <c r="W26" s="36"/>
+      <c r="X26" s="36"/>
+      <c r="Y26" s="36"/>
+      <c r="Z26" s="13"/>
+      <c r="AA26" s="13"/>
+      <c r="AB26" s="13"/>
+      <c r="AC26" s="13"/>
+      <c r="AD26" s="13"/>
+      <c r="AE26" s="13"/>
+      <c r="AF26" s="13"/>
+      <c r="AG26" s="18"/>
+    </row>
+    <row r="27" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A27" s="16"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="13"/>
+      <c r="H27" s="13"/>
+      <c r="I27" s="13"/>
+      <c r="J27" s="13"/>
+      <c r="K27" s="13"/>
+      <c r="L27" s="13"/>
+      <c r="M27" s="13"/>
+      <c r="N27" s="13"/>
+      <c r="O27" s="13"/>
+      <c r="P27" s="36"/>
+      <c r="Q27" s="13"/>
+      <c r="R27" s="13"/>
+      <c r="S27" s="36"/>
+      <c r="T27" s="36"/>
+      <c r="U27" s="36"/>
+      <c r="V27" s="36"/>
+      <c r="W27" s="36"/>
+      <c r="X27" s="36"/>
+      <c r="Y27" s="36"/>
+      <c r="Z27" s="13"/>
+      <c r="AA27" s="13"/>
+      <c r="AB27" s="13"/>
+      <c r="AC27" s="13"/>
+      <c r="AD27" s="13"/>
+      <c r="AE27" s="13"/>
+      <c r="AF27" s="13"/>
+      <c r="AG27" s="18"/>
+    </row>
+    <row r="28" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A28" s="16"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="13"/>
+      <c r="J28" s="13"/>
+      <c r="K28" s="13"/>
+      <c r="L28" s="13"/>
+      <c r="M28" s="13"/>
+      <c r="N28" s="13"/>
+      <c r="O28" s="13"/>
+      <c r="P28" s="36"/>
+      <c r="Q28" s="13"/>
+      <c r="R28" s="13"/>
+      <c r="S28" s="36"/>
+      <c r="T28" s="36"/>
+      <c r="U28" s="36"/>
+      <c r="V28" s="36"/>
+      <c r="W28" s="36"/>
+      <c r="X28" s="36"/>
+      <c r="Y28" s="36"/>
+      <c r="Z28" s="13"/>
+      <c r="AA28" s="13"/>
+      <c r="AB28" s="13"/>
+      <c r="AC28" s="13"/>
+      <c r="AD28" s="13"/>
+      <c r="AE28" s="13"/>
+      <c r="AF28" s="13"/>
+      <c r="AG28" s="18"/>
+    </row>
+    <row r="29" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A29" s="16"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="13"/>
+      <c r="I29" s="13"/>
+      <c r="J29" s="13"/>
+      <c r="K29" s="13"/>
+      <c r="L29" s="13"/>
+      <c r="M29" s="13"/>
+      <c r="N29" s="13"/>
+      <c r="O29" s="13"/>
+      <c r="P29" s="13"/>
+      <c r="Q29" s="13"/>
+      <c r="R29" s="13"/>
+      <c r="S29" s="13"/>
+      <c r="T29" s="13"/>
+      <c r="U29" s="13"/>
+      <c r="V29" s="13"/>
+      <c r="W29" s="13"/>
+      <c r="X29" s="13"/>
+      <c r="Y29" s="13"/>
+      <c r="Z29" s="13"/>
+      <c r="AA29" s="13"/>
+      <c r="AB29" s="13"/>
+      <c r="AC29" s="13"/>
+      <c r="AD29" s="13"/>
+      <c r="AE29" s="13"/>
+      <c r="AF29" s="13"/>
+      <c r="AG29" s="18"/>
+    </row>
+    <row r="30" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A30" s="16"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="13"/>
+      <c r="J30" s="13"/>
+      <c r="K30" s="13"/>
+      <c r="L30" s="13"/>
+      <c r="M30" s="13"/>
+      <c r="N30" s="13"/>
+      <c r="O30" s="13"/>
+      <c r="P30" s="13"/>
+      <c r="Q30" s="13"/>
+      <c r="R30" s="13"/>
+      <c r="S30" s="13"/>
+      <c r="T30" s="13"/>
+      <c r="U30" s="13"/>
+      <c r="V30" s="13"/>
+      <c r="W30" s="13"/>
+      <c r="X30" s="13"/>
+      <c r="Y30" s="13"/>
+      <c r="Z30" s="13"/>
+      <c r="AA30" s="13"/>
+      <c r="AB30" s="13"/>
+      <c r="AC30" s="13"/>
+      <c r="AD30" s="13"/>
+      <c r="AE30" s="13"/>
+      <c r="AF30" s="13"/>
+      <c r="AG30" s="18"/>
+    </row>
+    <row r="31" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A31" s="16"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13"/>
+      <c r="G31" s="13"/>
+      <c r="H31" s="13"/>
+      <c r="I31" s="13"/>
+      <c r="J31" s="13"/>
+      <c r="K31" s="13"/>
+      <c r="L31" s="13"/>
+      <c r="M31" s="13"/>
+      <c r="N31" s="13"/>
+      <c r="O31" s="13"/>
+      <c r="P31" s="13"/>
+      <c r="Q31" s="13"/>
+      <c r="R31" s="13"/>
+      <c r="S31" s="13"/>
+      <c r="T31" s="13"/>
+      <c r="U31" s="13"/>
+      <c r="V31" s="13"/>
+      <c r="W31" s="13"/>
+      <c r="X31" s="13"/>
+      <c r="Y31" s="13"/>
+      <c r="Z31" s="13"/>
+      <c r="AA31" s="13"/>
+      <c r="AB31" s="13"/>
+      <c r="AC31" s="13"/>
+      <c r="AD31" s="13"/>
+      <c r="AE31" s="13"/>
+      <c r="AF31" s="13"/>
+      <c r="AG31" s="18"/>
+    </row>
+    <row r="32" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A32" s="16"/>
+      <c r="B32" s="13"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+      <c r="H32" s="13"/>
+      <c r="I32" s="13"/>
+      <c r="J32" s="13"/>
+      <c r="K32" s="13"/>
+      <c r="L32" s="13"/>
+      <c r="M32" s="13"/>
+      <c r="N32" s="13"/>
+      <c r="O32" s="13"/>
+      <c r="P32" s="13"/>
+      <c r="Q32" s="13"/>
+      <c r="R32" s="13"/>
+      <c r="S32" s="13"/>
+      <c r="T32" s="13"/>
+      <c r="U32" s="13"/>
+      <c r="V32" s="13"/>
+      <c r="W32" s="13"/>
+      <c r="X32" s="13"/>
+      <c r="Y32" s="13"/>
+      <c r="Z32" s="13"/>
+      <c r="AA32" s="13"/>
+      <c r="AB32" s="13"/>
+      <c r="AC32" s="13"/>
+      <c r="AD32" s="13"/>
+      <c r="AE32" s="13"/>
+      <c r="AF32" s="13"/>
+      <c r="AG32" s="18"/>
+    </row>
+    <row r="33" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A33" s="16"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="13"/>
+      <c r="F33" s="13"/>
+      <c r="G33" s="13"/>
+      <c r="H33" s="13"/>
+      <c r="I33" s="13"/>
+      <c r="J33" s="13"/>
+      <c r="K33" s="13"/>
+      <c r="L33" s="13"/>
+      <c r="M33" s="13"/>
+      <c r="N33" s="13"/>
+      <c r="O33" s="13"/>
+      <c r="P33" s="13"/>
+      <c r="Q33" s="13"/>
+      <c r="R33" s="13"/>
+      <c r="S33" s="13"/>
+      <c r="T33" s="13"/>
+      <c r="U33" s="13"/>
+      <c r="V33" s="13"/>
+      <c r="W33" s="13"/>
+      <c r="X33" s="13"/>
+      <c r="Y33" s="13"/>
+      <c r="Z33" s="13"/>
+      <c r="AA33" s="13"/>
+      <c r="AB33" s="13"/>
+      <c r="AC33" s="13"/>
+      <c r="AD33" s="13"/>
+      <c r="AE33" s="13"/>
+      <c r="AF33" s="13"/>
+      <c r="AG33" s="18"/>
+    </row>
+    <row r="34" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A34" s="16"/>
+      <c r="B34" s="13"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="13"/>
+      <c r="H34" s="13"/>
+      <c r="I34" s="13"/>
+      <c r="J34" s="13"/>
+      <c r="K34" s="13"/>
+      <c r="L34" s="13"/>
+      <c r="M34" s="13"/>
+      <c r="N34" s="13"/>
+      <c r="O34" s="13"/>
+      <c r="P34" s="13"/>
+      <c r="Q34" s="13"/>
+      <c r="R34" s="13"/>
+      <c r="S34" s="13"/>
+      <c r="T34" s="13"/>
+      <c r="U34" s="13"/>
+      <c r="V34" s="13"/>
+      <c r="W34" s="13"/>
+      <c r="X34" s="13"/>
+      <c r="Y34" s="13"/>
+      <c r="Z34" s="13"/>
+      <c r="AA34" s="13"/>
+      <c r="AB34" s="13"/>
+      <c r="AC34" s="13"/>
+      <c r="AD34" s="13"/>
+      <c r="AE34" s="13"/>
+      <c r="AF34" s="13"/>
+      <c r="AG34" s="18"/>
+    </row>
+    <row r="35" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A35" s="16"/>
+      <c r="B35" s="13"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
+      <c r="H35" s="13"/>
+      <c r="I35" s="13"/>
+      <c r="J35" s="13"/>
+      <c r="K35" s="13"/>
+      <c r="L35" s="13"/>
+      <c r="M35" s="13"/>
+      <c r="N35" s="13"/>
+      <c r="O35" s="13"/>
+      <c r="P35" s="13"/>
+      <c r="Q35" s="13"/>
+      <c r="R35" s="13"/>
+      <c r="S35" s="13"/>
+      <c r="T35" s="13"/>
+      <c r="U35" s="13"/>
+      <c r="V35" s="13"/>
+      <c r="W35" s="13"/>
+      <c r="X35" s="13"/>
+      <c r="Y35" s="13"/>
+      <c r="Z35" s="13"/>
+      <c r="AA35" s="13"/>
+      <c r="AB35" s="13"/>
+      <c r="AC35" s="13"/>
+      <c r="AD35" s="13"/>
+      <c r="AE35" s="13"/>
+      <c r="AF35" s="13"/>
+      <c r="AG35" s="18"/>
+    </row>
+    <row r="36" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A36" s="16"/>
+      <c r="B36" s="13"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="13"/>
+      <c r="H36" s="13"/>
+      <c r="I36" s="13"/>
+      <c r="J36" s="13"/>
+      <c r="K36" s="13"/>
+      <c r="L36" s="13"/>
+      <c r="M36" s="13"/>
+      <c r="N36" s="13"/>
+      <c r="O36" s="13"/>
+      <c r="P36" s="13"/>
+      <c r="Q36" s="13"/>
+      <c r="R36" s="13"/>
+      <c r="S36" s="13"/>
+      <c r="T36" s="13"/>
+      <c r="U36" s="13"/>
+      <c r="V36" s="13"/>
+      <c r="W36" s="13"/>
+      <c r="X36" s="13"/>
+      <c r="Y36" s="13"/>
+      <c r="Z36" s="13"/>
+      <c r="AA36" s="13"/>
+      <c r="AB36" s="13"/>
+      <c r="AC36" s="13"/>
+      <c r="AD36" s="13"/>
+      <c r="AE36" s="13"/>
+      <c r="AF36" s="13"/>
+      <c r="AG36" s="18"/>
+    </row>
+    <row r="37" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A37" s="16"/>
+      <c r="B37" s="13"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="13"/>
+      <c r="H37" s="13"/>
+      <c r="I37" s="13"/>
+      <c r="J37" s="13"/>
+      <c r="K37" s="13"/>
+      <c r="L37" s="13"/>
+      <c r="M37" s="13"/>
+      <c r="N37" s="13"/>
+      <c r="O37" s="13"/>
+      <c r="P37" s="13"/>
+      <c r="Q37" s="13"/>
+      <c r="R37" s="13"/>
+      <c r="S37" s="13"/>
+      <c r="T37" s="13"/>
+      <c r="U37" s="13"/>
+      <c r="V37" s="13"/>
+      <c r="W37" s="13"/>
+      <c r="X37" s="13"/>
+      <c r="Y37" s="13"/>
+      <c r="Z37" s="13"/>
+      <c r="AA37" s="13"/>
+      <c r="AB37" s="13"/>
+      <c r="AC37" s="13"/>
+      <c r="AD37" s="13"/>
+      <c r="AE37" s="13"/>
+      <c r="AF37" s="13"/>
+      <c r="AG37" s="18"/>
+    </row>
+    <row r="38" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A38" s="27"/>
+      <c r="B38" s="28"/>
+      <c r="C38" s="28"/>
+      <c r="D38" s="28"/>
+      <c r="E38" s="28"/>
+      <c r="F38" s="28"/>
+      <c r="G38" s="28"/>
+      <c r="H38" s="28"/>
+      <c r="I38" s="28"/>
+      <c r="J38" s="28"/>
+      <c r="K38" s="28"/>
+      <c r="L38" s="28"/>
+      <c r="M38" s="28"/>
+      <c r="N38" s="28"/>
+      <c r="O38" s="28"/>
+      <c r="P38" s="28"/>
+      <c r="Q38" s="28"/>
+      <c r="R38" s="28"/>
+      <c r="S38" s="28"/>
+      <c r="T38" s="28"/>
+      <c r="U38" s="28"/>
+      <c r="V38" s="28"/>
+      <c r="W38" s="28"/>
+      <c r="X38" s="28"/>
+      <c r="Y38" s="28"/>
+      <c r="Z38" s="28"/>
+      <c r="AA38" s="28"/>
+      <c r="AB38" s="28"/>
+      <c r="AC38" s="28"/>
+      <c r="AD38" s="28"/>
+      <c r="AE38" s="28"/>
+      <c r="AF38" s="28"/>
+      <c r="AG38" s="30"/>
+    </row>
+    <row r="39" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A39" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="B39" s="13"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="13"/>
+      <c r="F39" s="13"/>
+      <c r="G39" s="13"/>
+      <c r="H39" s="13"/>
+      <c r="I39" s="13"/>
+      <c r="J39" s="13"/>
+      <c r="K39" s="13"/>
+      <c r="L39" s="13"/>
+      <c r="M39" s="13"/>
+      <c r="N39" s="13"/>
+      <c r="O39" s="13"/>
+      <c r="P39" s="13"/>
+      <c r="Q39" s="13"/>
+      <c r="R39" s="13"/>
+      <c r="S39" s="13"/>
+      <c r="T39" s="13"/>
+      <c r="U39" s="13"/>
+      <c r="V39" s="13"/>
+      <c r="W39" s="13"/>
+      <c r="X39" s="13"/>
+      <c r="Y39" s="13"/>
+      <c r="Z39" s="13"/>
+      <c r="AA39" s="13"/>
+      <c r="AB39" s="13"/>
+      <c r="AC39" s="13"/>
+      <c r="AD39" s="13"/>
+      <c r="AE39" s="13"/>
+      <c r="AF39" s="13"/>
+      <c r="AG39" s="18"/>
+    </row>
+    <row r="40" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A40" s="16"/>
+      <c r="B40" s="13"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="13"/>
+      <c r="E40" s="13"/>
+      <c r="F40" s="13"/>
+      <c r="G40" s="13"/>
+      <c r="H40" s="13"/>
+      <c r="I40" s="13"/>
+      <c r="J40" s="13"/>
+      <c r="K40" s="13"/>
+      <c r="L40" s="13"/>
+      <c r="M40" s="13"/>
+      <c r="N40" s="13"/>
+      <c r="O40" s="13"/>
+      <c r="P40" s="13"/>
+      <c r="Q40" s="13"/>
+      <c r="R40" s="13"/>
+      <c r="S40" s="13"/>
+      <c r="T40" s="13"/>
+      <c r="U40" s="13"/>
+      <c r="V40" s="13"/>
+      <c r="W40" s="13"/>
+      <c r="X40" s="13"/>
+      <c r="Y40" s="13"/>
+      <c r="Z40" s="13"/>
+      <c r="AA40" s="13"/>
+      <c r="AB40" s="13"/>
+      <c r="AC40" s="13"/>
+      <c r="AD40" s="13"/>
+      <c r="AE40" s="13"/>
+      <c r="AF40" s="13"/>
+      <c r="AG40" s="18"/>
+    </row>
+    <row r="41" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A41" s="16"/>
+      <c r="B41" s="13"/>
+      <c r="C41" s="13"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="13"/>
+      <c r="F41" s="13"/>
+      <c r="G41" s="13"/>
+      <c r="H41" s="13"/>
+      <c r="I41" s="13"/>
+      <c r="J41" s="13"/>
+      <c r="K41" s="13"/>
+      <c r="L41" s="13"/>
+      <c r="M41" s="13"/>
+      <c r="N41" s="13"/>
+      <c r="O41" s="13"/>
+      <c r="P41" s="13"/>
+      <c r="Q41" s="13"/>
+      <c r="R41" s="13"/>
+      <c r="S41" s="13"/>
+      <c r="T41" s="13"/>
+      <c r="U41" s="13"/>
+      <c r="V41" s="13"/>
+      <c r="W41" s="13"/>
+      <c r="X41" s="13"/>
+      <c r="Y41" s="13"/>
+      <c r="Z41" s="13"/>
+      <c r="AA41" s="13"/>
+      <c r="AB41" s="13"/>
+      <c r="AC41" s="13"/>
+      <c r="AD41" s="13"/>
+      <c r="AE41" s="13"/>
+      <c r="AF41" s="13"/>
+      <c r="AG41" s="18"/>
+    </row>
+    <row r="42" spans="1:33" ht="12.75" customHeight="1">
+      <c r="A42" s="27"/>
+      <c r="B42" s="28"/>
+      <c r="C42" s="28"/>
+      <c r="D42" s="28"/>
+      <c r="E42" s="28"/>
+      <c r="F42" s="28"/>
+      <c r="G42" s="28"/>
+      <c r="H42" s="28"/>
+      <c r="I42" s="28"/>
+      <c r="J42" s="28"/>
+      <c r="K42" s="28"/>
+      <c r="L42" s="28"/>
+      <c r="M42" s="28"/>
+      <c r="N42" s="28"/>
+      <c r="O42" s="28"/>
+      <c r="P42" s="28"/>
+      <c r="Q42" s="28"/>
+      <c r="R42" s="28"/>
+      <c r="S42" s="28"/>
+      <c r="T42" s="28"/>
+      <c r="U42" s="28"/>
+      <c r="V42" s="28"/>
+      <c r="W42" s="28"/>
+      <c r="X42" s="28"/>
+      <c r="Y42" s="28"/>
+      <c r="Z42" s="28"/>
+      <c r="AA42" s="28"/>
+      <c r="AB42" s="28"/>
+      <c r="AC42" s="28"/>
+      <c r="AD42" s="28"/>
+      <c r="AE42" s="28"/>
+      <c r="AF42" s="28"/>
+      <c r="AG42" s="30"/>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A1:AG1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="G2:AC2"/>
+    <mergeCell ref="AD2:AE2"/>
+    <mergeCell ref="AF2:AG2"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="G3:AC3"/>
+    <mergeCell ref="AD3:AE3"/>
+    <mergeCell ref="AF3:AG3"/>
+  </mergeCells>
+  <phoneticPr fontId="4"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.59055118110236227" bottom="0.39370078740157483" header="0.51181102362204722" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <headerFooter alignWithMargins="0">
+    <oddFooter>&amp;LCopyright© 2005 System Integrator Corp.&amp;C&amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:FU42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" customHeight="1"/>

--- a/基本設計書.xlsx
+++ b/基本設計書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\7_Programing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DE72CCB-38E1-4090-8C8B-1B889A89E1DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6195F815-F6C7-4319-A9E8-8443F1602795}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="774" firstSheet="5" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="140">
   <si>
     <t>システム名</t>
     <rPh sb="4" eb="5">
@@ -849,6 +849,169 @@
     </rPh>
     <phoneticPr fontId="4"/>
   </si>
+  <si>
+    <t>神奈川</t>
+    <rPh sb="0" eb="3">
+      <t>カナガワ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>太郎</t>
+    <rPh sb="0" eb="2">
+      <t>タロウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>カナガワ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>タロウ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>taro@gmail.com</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>男</t>
+    <rPh sb="0" eb="1">
+      <t>オトコ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>一般</t>
+    <rPh sb="0" eb="2">
+      <t>イッパン</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>有効</t>
+    <rPh sb="0" eb="2">
+      <t>ユウコウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>無効</t>
+    <rPh sb="0" eb="2">
+      <t>ムコウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>2026-02-2４</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-11	</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-11-13	</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>2026-02-04</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>2025-10-29</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>2026-06-17</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>hiroto@icloud.com</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t xml:space="preserve">yuki@yahoo.co.jp	</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>yuto-77@gmail.com</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>hinata@yahoo.co.jp</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>高橋</t>
+    <rPh sb="0" eb="2">
+      <t>タカハシ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>宏斗</t>
+    <rPh sb="0" eb="2">
+      <t>ヒロト</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>タカハシ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ヒロト</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ユウキ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>イシカワ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ゆうき</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>いしかわ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>佐藤</t>
+    <rPh sb="0" eb="2">
+      <t>サトウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ゆうと</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>サトウ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ユウト</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ヒナタ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ひなた</t>
+    <phoneticPr fontId="4"/>
+  </si>
 </sst>
 </file>
 
@@ -1014,7 +1177,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="43">
+  <borders count="40">
     <border>
       <left/>
       <right/>
@@ -1477,45 +1640,14 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
+      <left style="medium">
         <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
+      </left>
+      <right style="medium">
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -1529,7 +1661,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="223">
+  <cellXfs count="233">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
@@ -1662,6 +1794,103 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="35" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="36" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1698,22 +1927,28 @@
     <xf numFmtId="0" fontId="17" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1721,6 +1956,21 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1732,6 +1982,9 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1817,26 +2070,44 @@
     <xf numFmtId="176" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="18" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1851,124 +2122,7 @@
     <xf numFmtId="14" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="35" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="36" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -9959,50 +10113,6 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>177800</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>6350</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>38</xdr:col>
-      <xdr:colOff>6917</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>6472</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="59" name="図 58">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C23E2237-C741-BB36-3D0B-E3982C9975C7}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="177800" y="10807700"/>
-          <a:ext cx="11036867" cy="2381372"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>22</xdr:col>
@@ -10066,6 +10176,776 @@
         <a:p>
           <a:pPr algn="l"/>
           <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>50800</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>120650</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="四角形: 角を丸くする 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{26619FF1-40BD-F00D-BD4A-5518C4879386}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9550400" y="9728200"/>
+          <a:ext cx="463550" cy="241300"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="6350">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1000" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>更新</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>50800</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="四角形: 角を丸くする 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6C88D6A3-8943-4D58-9F62-21F542224177}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9550400" y="10039350"/>
+          <a:ext cx="463550" cy="241300"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="6350">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1000" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>更新</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>234950</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>120650</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="四角形: 角を丸くする 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6C3EB4B1-22CC-4118-A594-B3EAAA0CCA97}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9556750" y="10363200"/>
+          <a:ext cx="463550" cy="241300"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="6350">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1000" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>更新</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>50800</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>107950</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="四角形: 角を丸くする 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{91F6AE7A-0FF2-4192-9F2F-2A8BB3FE81B8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9550400" y="10985500"/>
+          <a:ext cx="463550" cy="241300"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="6350">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1000" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>更新</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>50800</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="四角形: 角を丸くする 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FCC8BC64-937B-4E11-9FB6-AB67DCFFE1B7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9550400" y="10674350"/>
+          <a:ext cx="463550" cy="241300"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="6350">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1000" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>更新</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>44450</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>222250</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="四角形: 角を丸くする 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D2BA3A5C-D9F3-4094-8B01-D4727CF28B2B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10115550" y="9721850"/>
+          <a:ext cx="463550" cy="241300"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="6350">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1000" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>削除</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>234950</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>120650</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="四角形: 角を丸くする 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00264D35-AD1F-4F61-8992-6776656635F0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10128250" y="10045700"/>
+          <a:ext cx="463550" cy="241300"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="6350">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1000" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>削除</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>50800</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>44450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="22" name="四角形: 角を丸くする 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F18EB6A3-9C6A-4066-985C-C0D37E0B49E8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10121900" y="10369550"/>
+          <a:ext cx="463550" cy="241300"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="6350">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1000" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>削除</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>44450</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>222250</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>120650</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="23" name="四角形: 角を丸くする 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27797E1A-A9F7-4F6F-8415-704E23CAFEC8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10115550" y="10680700"/>
+          <a:ext cx="463550" cy="241300"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="6350">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1000" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>削除</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>44450</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>222250</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>120650</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="24" name="四角形: 角を丸くする 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FA932562-C578-486F-893A-974F331511B7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10115550" y="10998200"/>
+          <a:ext cx="463550" cy="241300"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="6350">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1000" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>削除</a:t>
+          </a:r>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -10385,127 +11265,127 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:177" ht="12.75" customHeight="1">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="165" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
-      <c r="E1" s="121"/>
-      <c r="F1" s="121"/>
-      <c r="G1" s="121"/>
-      <c r="H1" s="121"/>
-      <c r="I1" s="121"/>
-      <c r="J1" s="121"/>
-      <c r="K1" s="121"/>
-      <c r="L1" s="121"/>
-      <c r="M1" s="121"/>
-      <c r="N1" s="121"/>
-      <c r="O1" s="121"/>
-      <c r="P1" s="121"/>
-      <c r="Q1" s="121"/>
-      <c r="R1" s="121"/>
-      <c r="S1" s="121"/>
-      <c r="T1" s="121"/>
-      <c r="U1" s="121"/>
-      <c r="V1" s="121"/>
-      <c r="W1" s="121"/>
-      <c r="X1" s="121"/>
-      <c r="Y1" s="121"/>
-      <c r="Z1" s="121"/>
-      <c r="AA1" s="121"/>
-      <c r="AB1" s="121"/>
-      <c r="AC1" s="121"/>
-      <c r="AD1" s="121"/>
-      <c r="AE1" s="121"/>
-      <c r="AF1" s="121"/>
-      <c r="AG1" s="121"/>
+      <c r="B1" s="165"/>
+      <c r="C1" s="165"/>
+      <c r="D1" s="165"/>
+      <c r="E1" s="165"/>
+      <c r="F1" s="165"/>
+      <c r="G1" s="165"/>
+      <c r="H1" s="165"/>
+      <c r="I1" s="165"/>
+      <c r="J1" s="165"/>
+      <c r="K1" s="165"/>
+      <c r="L1" s="165"/>
+      <c r="M1" s="165"/>
+      <c r="N1" s="165"/>
+      <c r="O1" s="165"/>
+      <c r="P1" s="165"/>
+      <c r="Q1" s="165"/>
+      <c r="R1" s="165"/>
+      <c r="S1" s="165"/>
+      <c r="T1" s="165"/>
+      <c r="U1" s="165"/>
+      <c r="V1" s="165"/>
+      <c r="W1" s="165"/>
+      <c r="X1" s="165"/>
+      <c r="Y1" s="165"/>
+      <c r="Z1" s="165"/>
+      <c r="AA1" s="165"/>
+      <c r="AB1" s="165"/>
+      <c r="AC1" s="165"/>
+      <c r="AD1" s="165"/>
+      <c r="AE1" s="165"/>
+      <c r="AF1" s="165"/>
+      <c r="AG1" s="165"/>
     </row>
     <row r="2" spans="1:177" ht="13" customHeight="1">
-      <c r="A2" s="118" t="s">
+      <c r="A2" s="162" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="119"/>
-      <c r="C2" s="119"/>
-      <c r="D2" s="119"/>
-      <c r="E2" s="119"/>
-      <c r="F2" s="120"/>
-      <c r="G2" s="118" t="s">
+      <c r="B2" s="163"/>
+      <c r="C2" s="163"/>
+      <c r="D2" s="163"/>
+      <c r="E2" s="163"/>
+      <c r="F2" s="164"/>
+      <c r="G2" s="162" t="s">
         <v>42</v>
       </c>
-      <c r="H2" s="119"/>
-      <c r="I2" s="119"/>
-      <c r="J2" s="119"/>
-      <c r="K2" s="119"/>
-      <c r="L2" s="119"/>
-      <c r="M2" s="119"/>
-      <c r="N2" s="119"/>
-      <c r="O2" s="119"/>
-      <c r="P2" s="119"/>
-      <c r="Q2" s="119"/>
-      <c r="R2" s="119"/>
-      <c r="S2" s="119"/>
-      <c r="T2" s="119"/>
-      <c r="U2" s="119"/>
-      <c r="V2" s="119"/>
-      <c r="W2" s="119"/>
-      <c r="X2" s="119"/>
-      <c r="Y2" s="119"/>
-      <c r="Z2" s="119"/>
-      <c r="AA2" s="119"/>
-      <c r="AB2" s="119"/>
-      <c r="AC2" s="120"/>
-      <c r="AD2" s="118" t="s">
+      <c r="H2" s="163"/>
+      <c r="I2" s="163"/>
+      <c r="J2" s="163"/>
+      <c r="K2" s="163"/>
+      <c r="L2" s="163"/>
+      <c r="M2" s="163"/>
+      <c r="N2" s="163"/>
+      <c r="O2" s="163"/>
+      <c r="P2" s="163"/>
+      <c r="Q2" s="163"/>
+      <c r="R2" s="163"/>
+      <c r="S2" s="163"/>
+      <c r="T2" s="163"/>
+      <c r="U2" s="163"/>
+      <c r="V2" s="163"/>
+      <c r="W2" s="163"/>
+      <c r="X2" s="163"/>
+      <c r="Y2" s="163"/>
+      <c r="Z2" s="163"/>
+      <c r="AA2" s="163"/>
+      <c r="AB2" s="163"/>
+      <c r="AC2" s="164"/>
+      <c r="AD2" s="162" t="s">
         <v>1</v>
       </c>
-      <c r="AE2" s="120"/>
-      <c r="AF2" s="118" t="s">
+      <c r="AE2" s="164"/>
+      <c r="AF2" s="162" t="s">
         <v>2</v>
       </c>
-      <c r="AG2" s="120"/>
+      <c r="AG2" s="164"/>
     </row>
     <row r="3" spans="1:177" s="3" customFormat="1" ht="12.75" customHeight="1">
-      <c r="A3" s="118" t="s">
+      <c r="A3" s="162" t="s">
         <v>43</v>
       </c>
-      <c r="B3" s="119"/>
-      <c r="C3" s="119"/>
-      <c r="D3" s="119"/>
-      <c r="E3" s="119"/>
-      <c r="F3" s="120"/>
-      <c r="G3" s="118" t="s">
+      <c r="B3" s="163"/>
+      <c r="C3" s="163"/>
+      <c r="D3" s="163"/>
+      <c r="E3" s="163"/>
+      <c r="F3" s="164"/>
+      <c r="G3" s="162" t="s">
         <v>45</v>
       </c>
-      <c r="H3" s="119"/>
-      <c r="I3" s="119"/>
-      <c r="J3" s="119"/>
-      <c r="K3" s="119"/>
-      <c r="L3" s="119"/>
-      <c r="M3" s="119"/>
-      <c r="N3" s="119"/>
-      <c r="O3" s="119"/>
-      <c r="P3" s="119"/>
-      <c r="Q3" s="119"/>
-      <c r="R3" s="119"/>
-      <c r="S3" s="119"/>
-      <c r="T3" s="119"/>
-      <c r="U3" s="119"/>
-      <c r="V3" s="119"/>
-      <c r="W3" s="119"/>
-      <c r="X3" s="119"/>
-      <c r="Y3" s="119"/>
-      <c r="Z3" s="119"/>
-      <c r="AA3" s="119"/>
-      <c r="AB3" s="119"/>
-      <c r="AC3" s="120"/>
-      <c r="AD3" s="118" t="s">
+      <c r="H3" s="163"/>
+      <c r="I3" s="163"/>
+      <c r="J3" s="163"/>
+      <c r="K3" s="163"/>
+      <c r="L3" s="163"/>
+      <c r="M3" s="163"/>
+      <c r="N3" s="163"/>
+      <c r="O3" s="163"/>
+      <c r="P3" s="163"/>
+      <c r="Q3" s="163"/>
+      <c r="R3" s="163"/>
+      <c r="S3" s="163"/>
+      <c r="T3" s="163"/>
+      <c r="U3" s="163"/>
+      <c r="V3" s="163"/>
+      <c r="W3" s="163"/>
+      <c r="X3" s="163"/>
+      <c r="Y3" s="163"/>
+      <c r="Z3" s="163"/>
+      <c r="AA3" s="163"/>
+      <c r="AB3" s="163"/>
+      <c r="AC3" s="164"/>
+      <c r="AD3" s="162" t="s">
         <v>13</v>
       </c>
-      <c r="AE3" s="120"/>
-      <c r="AF3" s="118" t="s">
+      <c r="AE3" s="164"/>
+      <c r="AF3" s="162" t="s">
         <v>41</v>
       </c>
-      <c r="AG3" s="120"/>
+      <c r="AG3" s="164"/>
       <c r="AH3" s="2"/>
       <c r="AI3" s="5"/>
       <c r="AJ3" s="5"/>
@@ -12057,127 +12937,127 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:177" ht="12.75" customHeight="1">
-      <c r="A1" s="114" t="s">
+      <c r="A1" s="166" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="114"/>
-      <c r="C1" s="114"/>
-      <c r="D1" s="114"/>
-      <c r="E1" s="114"/>
-      <c r="F1" s="114"/>
-      <c r="G1" s="114"/>
-      <c r="H1" s="114"/>
-      <c r="I1" s="114"/>
-      <c r="J1" s="114"/>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="114"/>
-      <c r="N1" s="114"/>
-      <c r="O1" s="114"/>
-      <c r="P1" s="114"/>
-      <c r="Q1" s="114"/>
-      <c r="R1" s="114"/>
-      <c r="S1" s="114"/>
-      <c r="T1" s="114"/>
-      <c r="U1" s="114"/>
-      <c r="V1" s="114"/>
-      <c r="W1" s="114"/>
-      <c r="X1" s="114"/>
-      <c r="Y1" s="114"/>
-      <c r="Z1" s="114"/>
-      <c r="AA1" s="114"/>
-      <c r="AB1" s="114"/>
-      <c r="AC1" s="114"/>
-      <c r="AD1" s="114"/>
-      <c r="AE1" s="114"/>
-      <c r="AF1" s="114"/>
-      <c r="AG1" s="114"/>
+      <c r="B1" s="166"/>
+      <c r="C1" s="166"/>
+      <c r="D1" s="166"/>
+      <c r="E1" s="166"/>
+      <c r="F1" s="166"/>
+      <c r="G1" s="166"/>
+      <c r="H1" s="166"/>
+      <c r="I1" s="166"/>
+      <c r="J1" s="166"/>
+      <c r="K1" s="166"/>
+      <c r="L1" s="166"/>
+      <c r="M1" s="166"/>
+      <c r="N1" s="166"/>
+      <c r="O1" s="166"/>
+      <c r="P1" s="166"/>
+      <c r="Q1" s="166"/>
+      <c r="R1" s="166"/>
+      <c r="S1" s="166"/>
+      <c r="T1" s="166"/>
+      <c r="U1" s="166"/>
+      <c r="V1" s="166"/>
+      <c r="W1" s="166"/>
+      <c r="X1" s="166"/>
+      <c r="Y1" s="166"/>
+      <c r="Z1" s="166"/>
+      <c r="AA1" s="166"/>
+      <c r="AB1" s="166"/>
+      <c r="AC1" s="166"/>
+      <c r="AD1" s="166"/>
+      <c r="AE1" s="166"/>
+      <c r="AF1" s="166"/>
+      <c r="AG1" s="166"/>
     </row>
     <row r="2" spans="1:177" ht="13" customHeight="1">
-      <c r="A2" s="115" t="s">
+      <c r="A2" s="157" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="116"/>
-      <c r="C2" s="116"/>
-      <c r="D2" s="116"/>
-      <c r="E2" s="116"/>
-      <c r="F2" s="117"/>
-      <c r="G2" s="115" t="s">
+      <c r="B2" s="155"/>
+      <c r="C2" s="155"/>
+      <c r="D2" s="155"/>
+      <c r="E2" s="155"/>
+      <c r="F2" s="156"/>
+      <c r="G2" s="157" t="s">
         <v>42</v>
       </c>
-      <c r="H2" s="116"/>
-      <c r="I2" s="116"/>
-      <c r="J2" s="116"/>
-      <c r="K2" s="116"/>
-      <c r="L2" s="116"/>
-      <c r="M2" s="116"/>
-      <c r="N2" s="116"/>
-      <c r="O2" s="116"/>
-      <c r="P2" s="116"/>
-      <c r="Q2" s="116"/>
-      <c r="R2" s="116"/>
-      <c r="S2" s="116"/>
-      <c r="T2" s="116"/>
-      <c r="U2" s="116"/>
-      <c r="V2" s="116"/>
-      <c r="W2" s="116"/>
-      <c r="X2" s="116"/>
-      <c r="Y2" s="116"/>
-      <c r="Z2" s="116"/>
-      <c r="AA2" s="116"/>
-      <c r="AB2" s="116"/>
-      <c r="AC2" s="117"/>
-      <c r="AD2" s="115" t="s">
+      <c r="H2" s="155"/>
+      <c r="I2" s="155"/>
+      <c r="J2" s="155"/>
+      <c r="K2" s="155"/>
+      <c r="L2" s="155"/>
+      <c r="M2" s="155"/>
+      <c r="N2" s="155"/>
+      <c r="O2" s="155"/>
+      <c r="P2" s="155"/>
+      <c r="Q2" s="155"/>
+      <c r="R2" s="155"/>
+      <c r="S2" s="155"/>
+      <c r="T2" s="155"/>
+      <c r="U2" s="155"/>
+      <c r="V2" s="155"/>
+      <c r="W2" s="155"/>
+      <c r="X2" s="155"/>
+      <c r="Y2" s="155"/>
+      <c r="Z2" s="155"/>
+      <c r="AA2" s="155"/>
+      <c r="AB2" s="155"/>
+      <c r="AC2" s="156"/>
+      <c r="AD2" s="157" t="s">
         <v>1</v>
       </c>
-      <c r="AE2" s="117"/>
-      <c r="AF2" s="115" t="s">
+      <c r="AE2" s="156"/>
+      <c r="AF2" s="157" t="s">
         <v>2</v>
       </c>
-      <c r="AG2" s="117"/>
+      <c r="AG2" s="156"/>
     </row>
     <row r="3" spans="1:177" s="15" customFormat="1" ht="12.75" customHeight="1">
-      <c r="A3" s="115" t="s">
+      <c r="A3" s="157" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="116"/>
-      <c r="C3" s="116"/>
-      <c r="D3" s="116"/>
-      <c r="E3" s="116"/>
-      <c r="F3" s="117"/>
-      <c r="G3" s="115" t="s">
+      <c r="B3" s="155"/>
+      <c r="C3" s="155"/>
+      <c r="D3" s="155"/>
+      <c r="E3" s="155"/>
+      <c r="F3" s="156"/>
+      <c r="G3" s="157" t="s">
         <v>46</v>
       </c>
-      <c r="H3" s="116"/>
-      <c r="I3" s="116"/>
-      <c r="J3" s="116"/>
-      <c r="K3" s="116"/>
-      <c r="L3" s="116"/>
-      <c r="M3" s="116"/>
-      <c r="N3" s="116"/>
-      <c r="O3" s="116"/>
-      <c r="P3" s="116"/>
-      <c r="Q3" s="116"/>
-      <c r="R3" s="116"/>
-      <c r="S3" s="116"/>
-      <c r="T3" s="116"/>
-      <c r="U3" s="116"/>
-      <c r="V3" s="116"/>
-      <c r="W3" s="116"/>
-      <c r="X3" s="116"/>
-      <c r="Y3" s="116"/>
-      <c r="Z3" s="116"/>
-      <c r="AA3" s="116"/>
-      <c r="AB3" s="116"/>
-      <c r="AC3" s="117"/>
-      <c r="AD3" s="115" t="s">
+      <c r="H3" s="155"/>
+      <c r="I3" s="155"/>
+      <c r="J3" s="155"/>
+      <c r="K3" s="155"/>
+      <c r="L3" s="155"/>
+      <c r="M3" s="155"/>
+      <c r="N3" s="155"/>
+      <c r="O3" s="155"/>
+      <c r="P3" s="155"/>
+      <c r="Q3" s="155"/>
+      <c r="R3" s="155"/>
+      <c r="S3" s="155"/>
+      <c r="T3" s="155"/>
+      <c r="U3" s="155"/>
+      <c r="V3" s="155"/>
+      <c r="W3" s="155"/>
+      <c r="X3" s="155"/>
+      <c r="Y3" s="155"/>
+      <c r="Z3" s="155"/>
+      <c r="AA3" s="155"/>
+      <c r="AB3" s="155"/>
+      <c r="AC3" s="156"/>
+      <c r="AD3" s="157" t="s">
         <v>13</v>
       </c>
-      <c r="AE3" s="117"/>
-      <c r="AF3" s="115" t="s">
+      <c r="AE3" s="156"/>
+      <c r="AF3" s="157" t="s">
         <v>41</v>
       </c>
-      <c r="AG3" s="117"/>
+      <c r="AG3" s="156"/>
       <c r="AH3" s="13"/>
       <c r="AI3" s="14"/>
       <c r="AJ3" s="14"/>
@@ -12649,98 +13529,98 @@
     </row>
     <row r="12" spans="1:177" ht="12.75" customHeight="1">
       <c r="A12" s="16"/>
-      <c r="B12" s="122" t="s">
+      <c r="B12" s="167" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="136"/>
-      <c r="D12" s="122" t="s">
+      <c r="C12" s="181"/>
+      <c r="D12" s="167" t="s">
         <v>31</v>
       </c>
-      <c r="E12" s="137"/>
-      <c r="F12" s="137"/>
-      <c r="G12" s="136"/>
-      <c r="H12" s="122" t="s">
+      <c r="E12" s="182"/>
+      <c r="F12" s="182"/>
+      <c r="G12" s="181"/>
+      <c r="H12" s="167" t="s">
         <v>29</v>
       </c>
-      <c r="I12" s="137"/>
-      <c r="J12" s="136"/>
-      <c r="K12" s="122" t="s">
+      <c r="I12" s="182"/>
+      <c r="J12" s="181"/>
+      <c r="K12" s="167" t="s">
         <v>23</v>
       </c>
-      <c r="L12" s="137"/>
-      <c r="M12" s="136"/>
-      <c r="N12" s="122" t="s">
+      <c r="L12" s="182"/>
+      <c r="M12" s="181"/>
+      <c r="N12" s="167" t="s">
         <v>2</v>
       </c>
-      <c r="O12" s="123"/>
-      <c r="P12" s="124"/>
-      <c r="Q12" s="122" t="s">
+      <c r="O12" s="168"/>
+      <c r="P12" s="169"/>
+      <c r="Q12" s="167" t="s">
         <v>19</v>
       </c>
-      <c r="R12" s="124"/>
-      <c r="S12" s="122" t="s">
+      <c r="R12" s="169"/>
+      <c r="S12" s="167" t="s">
         <v>25</v>
       </c>
-      <c r="T12" s="123"/>
-      <c r="U12" s="124"/>
-      <c r="V12" s="122" t="s">
+      <c r="T12" s="168"/>
+      <c r="U12" s="169"/>
+      <c r="V12" s="167" t="s">
         <v>26</v>
       </c>
-      <c r="W12" s="123"/>
-      <c r="X12" s="124"/>
-      <c r="Y12" s="122" t="s">
+      <c r="W12" s="168"/>
+      <c r="X12" s="169"/>
+      <c r="Y12" s="167" t="s">
         <v>27</v>
       </c>
-      <c r="Z12" s="123"/>
-      <c r="AA12" s="123"/>
-      <c r="AB12" s="123"/>
-      <c r="AC12" s="123"/>
-      <c r="AD12" s="123"/>
-      <c r="AE12" s="124"/>
+      <c r="Z12" s="168"/>
+      <c r="AA12" s="168"/>
+      <c r="AB12" s="168"/>
+      <c r="AC12" s="168"/>
+      <c r="AD12" s="168"/>
+      <c r="AE12" s="169"/>
       <c r="AF12" s="45"/>
       <c r="AG12" s="18"/>
     </row>
     <row r="13" spans="1:177" ht="12.75" customHeight="1">
       <c r="A13" s="16"/>
-      <c r="B13" s="125" t="s">
+      <c r="B13" s="170" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="126"/>
+      <c r="C13" s="171"/>
       <c r="D13" s="46" t="s">
         <v>17</v>
       </c>
       <c r="E13" s="38"/>
       <c r="F13" s="38"/>
       <c r="G13" s="47"/>
-      <c r="H13" s="127" t="s">
+      <c r="H13" s="172" t="s">
         <v>34</v>
       </c>
-      <c r="I13" s="128"/>
-      <c r="J13" s="129"/>
-      <c r="K13" s="130" t="s">
+      <c r="I13" s="173"/>
+      <c r="J13" s="174"/>
+      <c r="K13" s="175" t="s">
         <v>22</v>
       </c>
-      <c r="L13" s="131"/>
-      <c r="M13" s="132"/>
+      <c r="L13" s="176"/>
+      <c r="M13" s="177"/>
       <c r="N13" s="46" t="s">
         <v>24</v>
       </c>
       <c r="O13" s="38"/>
       <c r="P13" s="47"/>
-      <c r="Q13" s="130" t="s">
+      <c r="Q13" s="175" t="s">
         <v>20</v>
       </c>
-      <c r="R13" s="132"/>
-      <c r="S13" s="133" t="s">
+      <c r="R13" s="177"/>
+      <c r="S13" s="178" t="s">
         <v>33</v>
       </c>
-      <c r="T13" s="134"/>
-      <c r="U13" s="135"/>
-      <c r="V13" s="127" t="s">
+      <c r="T13" s="179"/>
+      <c r="U13" s="180"/>
+      <c r="V13" s="172" t="s">
         <v>35</v>
       </c>
-      <c r="W13" s="128"/>
-      <c r="X13" s="129"/>
+      <c r="W13" s="173"/>
+      <c r="X13" s="174"/>
       <c r="Y13" s="48" t="s">
         <v>28</v>
       </c>
@@ -13759,15 +14639,6 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="G3:AC3"/>
-    <mergeCell ref="AD3:AE3"/>
-    <mergeCell ref="AF3:AG3"/>
-    <mergeCell ref="A1:AG1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="G2:AC2"/>
-    <mergeCell ref="AD2:AE2"/>
-    <mergeCell ref="AF2:AG2"/>
     <mergeCell ref="S12:U12"/>
     <mergeCell ref="V12:X12"/>
     <mergeCell ref="Y12:AE12"/>
@@ -13783,6 +14654,15 @@
     <mergeCell ref="K12:M12"/>
     <mergeCell ref="N12:P12"/>
     <mergeCell ref="Q12:R12"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="G3:AC3"/>
+    <mergeCell ref="AD3:AE3"/>
+    <mergeCell ref="AF3:AG3"/>
+    <mergeCell ref="A1:AG1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="G2:AC2"/>
+    <mergeCell ref="AD2:AE2"/>
+    <mergeCell ref="AF2:AG2"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <printOptions horizontalCentered="1"/>
@@ -14271,20 +15151,20 @@
       <c r="C8" s="19"/>
       <c r="D8" s="19"/>
       <c r="E8" s="20"/>
-      <c r="F8" s="138" t="s">
+      <c r="F8" s="183" t="s">
         <v>49</v>
       </c>
-      <c r="G8" s="139"/>
-      <c r="H8" s="139"/>
-      <c r="I8" s="139"/>
-      <c r="J8" s="139"/>
-      <c r="K8" s="139"/>
-      <c r="L8" s="139"/>
-      <c r="M8" s="139"/>
-      <c r="N8" s="139"/>
-      <c r="O8" s="139"/>
-      <c r="P8" s="139"/>
-      <c r="Q8" s="140"/>
+      <c r="G8" s="184"/>
+      <c r="H8" s="184"/>
+      <c r="I8" s="184"/>
+      <c r="J8" s="184"/>
+      <c r="K8" s="184"/>
+      <c r="L8" s="184"/>
+      <c r="M8" s="184"/>
+      <c r="N8" s="184"/>
+      <c r="O8" s="184"/>
+      <c r="P8" s="184"/>
+      <c r="Q8" s="185"/>
       <c r="R8" s="13"/>
       <c r="S8" s="13"/>
       <c r="T8" s="13"/>
@@ -14303,26 +15183,26 @@
     </row>
     <row r="9" spans="1:256" ht="13" customHeight="1">
       <c r="A9" s="16"/>
-      <c r="B9" s="141" t="s">
+      <c r="B9" s="186" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="142"/>
-      <c r="D9" s="142"/>
-      <c r="E9" s="143"/>
-      <c r="F9" s="147" t="s">
+      <c r="C9" s="187"/>
+      <c r="D9" s="187"/>
+      <c r="E9" s="188"/>
+      <c r="F9" s="192" t="s">
         <v>48</v>
       </c>
-      <c r="G9" s="148"/>
-      <c r="H9" s="148"/>
-      <c r="I9" s="148"/>
-      <c r="J9" s="148"/>
-      <c r="K9" s="148"/>
-      <c r="L9" s="148"/>
-      <c r="M9" s="148"/>
-      <c r="N9" s="148"/>
-      <c r="O9" s="148"/>
-      <c r="P9" s="148"/>
-      <c r="Q9" s="149"/>
+      <c r="G9" s="193"/>
+      <c r="H9" s="193"/>
+      <c r="I9" s="193"/>
+      <c r="J9" s="193"/>
+      <c r="K9" s="193"/>
+      <c r="L9" s="193"/>
+      <c r="M9" s="193"/>
+      <c r="N9" s="193"/>
+      <c r="O9" s="193"/>
+      <c r="P9" s="193"/>
+      <c r="Q9" s="194"/>
       <c r="R9" s="13"/>
       <c r="S9" s="13"/>
       <c r="T9" s="13"/>
@@ -14341,22 +15221,22 @@
     </row>
     <row r="10" spans="1:256" ht="13" customHeight="1">
       <c r="A10" s="16"/>
-      <c r="B10" s="144"/>
-      <c r="C10" s="145"/>
-      <c r="D10" s="145"/>
-      <c r="E10" s="146"/>
-      <c r="F10" s="150"/>
-      <c r="G10" s="151"/>
-      <c r="H10" s="151"/>
-      <c r="I10" s="151"/>
-      <c r="J10" s="151"/>
-      <c r="K10" s="151"/>
-      <c r="L10" s="151"/>
-      <c r="M10" s="151"/>
-      <c r="N10" s="151"/>
-      <c r="O10" s="151"/>
-      <c r="P10" s="151"/>
-      <c r="Q10" s="152"/>
+      <c r="B10" s="189"/>
+      <c r="C10" s="190"/>
+      <c r="D10" s="190"/>
+      <c r="E10" s="191"/>
+      <c r="F10" s="195"/>
+      <c r="G10" s="196"/>
+      <c r="H10" s="196"/>
+      <c r="I10" s="196"/>
+      <c r="J10" s="196"/>
+      <c r="K10" s="196"/>
+      <c r="L10" s="196"/>
+      <c r="M10" s="196"/>
+      <c r="N10" s="196"/>
+      <c r="O10" s="196"/>
+      <c r="P10" s="196"/>
+      <c r="Q10" s="197"/>
       <c r="R10" s="13"/>
       <c r="S10" s="13"/>
       <c r="T10" s="13"/>
@@ -14567,26 +15447,26 @@
       <c r="E17" s="13"/>
       <c r="F17" s="13"/>
       <c r="G17" s="13"/>
-      <c r="H17" s="153" t="s">
+      <c r="H17" s="198" t="s">
         <v>47</v>
       </c>
-      <c r="I17" s="153"/>
-      <c r="J17" s="153"/>
-      <c r="K17" s="153"/>
-      <c r="L17" s="153"/>
-      <c r="M17" s="153"/>
-      <c r="N17" s="153"/>
-      <c r="O17" s="153"/>
-      <c r="P17" s="153"/>
-      <c r="Q17" s="153"/>
-      <c r="R17" s="153"/>
-      <c r="S17" s="153"/>
-      <c r="T17" s="153"/>
-      <c r="U17" s="153"/>
-      <c r="V17" s="153"/>
-      <c r="W17" s="153"/>
-      <c r="X17" s="153"/>
-      <c r="Y17" s="153"/>
+      <c r="I17" s="198"/>
+      <c r="J17" s="198"/>
+      <c r="K17" s="198"/>
+      <c r="L17" s="198"/>
+      <c r="M17" s="198"/>
+      <c r="N17" s="198"/>
+      <c r="O17" s="198"/>
+      <c r="P17" s="198"/>
+      <c r="Q17" s="198"/>
+      <c r="R17" s="198"/>
+      <c r="S17" s="198"/>
+      <c r="T17" s="198"/>
+      <c r="U17" s="198"/>
+      <c r="V17" s="198"/>
+      <c r="W17" s="198"/>
+      <c r="X17" s="198"/>
+      <c r="Y17" s="198"/>
       <c r="AA17" s="13"/>
       <c r="AB17" s="13"/>
       <c r="AC17" s="13"/>
@@ -14602,24 +15482,24 @@
       <c r="E18" s="13"/>
       <c r="F18" s="13"/>
       <c r="G18" s="13"/>
-      <c r="H18" s="153"/>
-      <c r="I18" s="153"/>
-      <c r="J18" s="153"/>
-      <c r="K18" s="153"/>
-      <c r="L18" s="153"/>
-      <c r="M18" s="153"/>
-      <c r="N18" s="153"/>
-      <c r="O18" s="153"/>
-      <c r="P18" s="153"/>
-      <c r="Q18" s="153"/>
-      <c r="R18" s="153"/>
-      <c r="S18" s="153"/>
-      <c r="T18" s="153"/>
-      <c r="U18" s="153"/>
-      <c r="V18" s="153"/>
-      <c r="W18" s="153"/>
-      <c r="X18" s="153"/>
-      <c r="Y18" s="153"/>
+      <c r="H18" s="198"/>
+      <c r="I18" s="198"/>
+      <c r="J18" s="198"/>
+      <c r="K18" s="198"/>
+      <c r="L18" s="198"/>
+      <c r="M18" s="198"/>
+      <c r="N18" s="198"/>
+      <c r="O18" s="198"/>
+      <c r="P18" s="198"/>
+      <c r="Q18" s="198"/>
+      <c r="R18" s="198"/>
+      <c r="S18" s="198"/>
+      <c r="T18" s="198"/>
+      <c r="U18" s="198"/>
+      <c r="V18" s="198"/>
+      <c r="W18" s="198"/>
+      <c r="X18" s="198"/>
+      <c r="Y18" s="198"/>
       <c r="AA18" s="13"/>
       <c r="AB18" s="13"/>
       <c r="AC18" s="13"/>
@@ -14635,24 +15515,24 @@
       <c r="E19" s="13"/>
       <c r="F19" s="13"/>
       <c r="G19" s="13"/>
-      <c r="H19" s="153"/>
-      <c r="I19" s="153"/>
-      <c r="J19" s="153"/>
-      <c r="K19" s="153"/>
-      <c r="L19" s="153"/>
-      <c r="M19" s="153"/>
-      <c r="N19" s="153"/>
-      <c r="O19" s="153"/>
-      <c r="P19" s="153"/>
-      <c r="Q19" s="153"/>
-      <c r="R19" s="153"/>
-      <c r="S19" s="153"/>
-      <c r="T19" s="153"/>
-      <c r="U19" s="153"/>
-      <c r="V19" s="153"/>
-      <c r="W19" s="153"/>
-      <c r="X19" s="153"/>
-      <c r="Y19" s="153"/>
+      <c r="H19" s="198"/>
+      <c r="I19" s="198"/>
+      <c r="J19" s="198"/>
+      <c r="K19" s="198"/>
+      <c r="L19" s="198"/>
+      <c r="M19" s="198"/>
+      <c r="N19" s="198"/>
+      <c r="O19" s="198"/>
+      <c r="P19" s="198"/>
+      <c r="Q19" s="198"/>
+      <c r="R19" s="198"/>
+      <c r="S19" s="198"/>
+      <c r="T19" s="198"/>
+      <c r="U19" s="198"/>
+      <c r="V19" s="198"/>
+      <c r="W19" s="198"/>
+      <c r="X19" s="198"/>
+      <c r="Y19" s="198"/>
       <c r="Z19" s="13"/>
       <c r="AA19" s="13"/>
       <c r="AB19" s="13"/>
@@ -14878,10 +15758,10 @@
       <c r="C26" s="23"/>
       <c r="D26" s="23"/>
       <c r="E26" s="23"/>
-      <c r="F26" s="154"/>
-      <c r="G26" s="155"/>
-      <c r="H26" s="155"/>
-      <c r="I26" s="156"/>
+      <c r="F26" s="199"/>
+      <c r="G26" s="200"/>
+      <c r="H26" s="200"/>
+      <c r="I26" s="201"/>
       <c r="J26" s="22"/>
       <c r="K26" s="23"/>
       <c r="L26" s="23"/>
@@ -15518,123 +16398,123 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:177" ht="12.75" customHeight="1">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="165" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
-      <c r="E1" s="121"/>
-      <c r="F1" s="121"/>
-      <c r="G1" s="121"/>
-      <c r="H1" s="121"/>
-      <c r="I1" s="121"/>
-      <c r="J1" s="121"/>
-      <c r="K1" s="121"/>
-      <c r="L1" s="121"/>
-      <c r="M1" s="121"/>
-      <c r="N1" s="121"/>
-      <c r="O1" s="121"/>
-      <c r="P1" s="121"/>
-      <c r="Q1" s="121"/>
-      <c r="R1" s="121"/>
-      <c r="S1" s="121"/>
-      <c r="T1" s="121"/>
-      <c r="U1" s="121"/>
-      <c r="V1" s="121"/>
-      <c r="W1" s="121"/>
-      <c r="X1" s="121"/>
-      <c r="Y1" s="121"/>
-      <c r="Z1" s="121"/>
-      <c r="AA1" s="121"/>
-      <c r="AB1" s="121"/>
-      <c r="AC1" s="121"/>
-      <c r="AD1" s="121"/>
-      <c r="AE1" s="121"/>
-      <c r="AF1" s="121"/>
-      <c r="AG1" s="121"/>
+      <c r="B1" s="165"/>
+      <c r="C1" s="165"/>
+      <c r="D1" s="165"/>
+      <c r="E1" s="165"/>
+      <c r="F1" s="165"/>
+      <c r="G1" s="165"/>
+      <c r="H1" s="165"/>
+      <c r="I1" s="165"/>
+      <c r="J1" s="165"/>
+      <c r="K1" s="165"/>
+      <c r="L1" s="165"/>
+      <c r="M1" s="165"/>
+      <c r="N1" s="165"/>
+      <c r="O1" s="165"/>
+      <c r="P1" s="165"/>
+      <c r="Q1" s="165"/>
+      <c r="R1" s="165"/>
+      <c r="S1" s="165"/>
+      <c r="T1" s="165"/>
+      <c r="U1" s="165"/>
+      <c r="V1" s="165"/>
+      <c r="W1" s="165"/>
+      <c r="X1" s="165"/>
+      <c r="Y1" s="165"/>
+      <c r="Z1" s="165"/>
+      <c r="AA1" s="165"/>
+      <c r="AB1" s="165"/>
+      <c r="AC1" s="165"/>
+      <c r="AD1" s="165"/>
+      <c r="AE1" s="165"/>
+      <c r="AF1" s="165"/>
+      <c r="AG1" s="165"/>
     </row>
     <row r="2" spans="1:177" ht="13" customHeight="1">
-      <c r="A2" s="118" t="s">
+      <c r="A2" s="162" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="119"/>
-      <c r="C2" s="119"/>
-      <c r="D2" s="119"/>
-      <c r="E2" s="119"/>
-      <c r="F2" s="120"/>
-      <c r="G2" s="118" t="s">
+      <c r="B2" s="163"/>
+      <c r="C2" s="163"/>
+      <c r="D2" s="163"/>
+      <c r="E2" s="163"/>
+      <c r="F2" s="164"/>
+      <c r="G2" s="162" t="s">
         <v>42</v>
       </c>
-      <c r="H2" s="119"/>
-      <c r="I2" s="119"/>
-      <c r="J2" s="119"/>
-      <c r="K2" s="119"/>
-      <c r="L2" s="119"/>
-      <c r="M2" s="119"/>
-      <c r="N2" s="119"/>
-      <c r="O2" s="119"/>
-      <c r="P2" s="119"/>
-      <c r="Q2" s="119"/>
-      <c r="R2" s="119"/>
-      <c r="S2" s="119"/>
-      <c r="T2" s="119"/>
-      <c r="U2" s="119"/>
-      <c r="V2" s="119"/>
-      <c r="W2" s="119"/>
-      <c r="X2" s="119"/>
-      <c r="Y2" s="119"/>
-      <c r="Z2" s="119"/>
-      <c r="AA2" s="119"/>
-      <c r="AB2" s="119"/>
-      <c r="AC2" s="120"/>
-      <c r="AD2" s="118" t="s">
+      <c r="H2" s="163"/>
+      <c r="I2" s="163"/>
+      <c r="J2" s="163"/>
+      <c r="K2" s="163"/>
+      <c r="L2" s="163"/>
+      <c r="M2" s="163"/>
+      <c r="N2" s="163"/>
+      <c r="O2" s="163"/>
+      <c r="P2" s="163"/>
+      <c r="Q2" s="163"/>
+      <c r="R2" s="163"/>
+      <c r="S2" s="163"/>
+      <c r="T2" s="163"/>
+      <c r="U2" s="163"/>
+      <c r="V2" s="163"/>
+      <c r="W2" s="163"/>
+      <c r="X2" s="163"/>
+      <c r="Y2" s="163"/>
+      <c r="Z2" s="163"/>
+      <c r="AA2" s="163"/>
+      <c r="AB2" s="163"/>
+      <c r="AC2" s="164"/>
+      <c r="AD2" s="162" t="s">
         <v>1</v>
       </c>
-      <c r="AE2" s="120"/>
-      <c r="AF2" s="118" t="s">
+      <c r="AE2" s="164"/>
+      <c r="AF2" s="162" t="s">
         <v>2</v>
       </c>
-      <c r="AG2" s="120"/>
+      <c r="AG2" s="164"/>
     </row>
     <row r="3" spans="1:177" s="3" customFormat="1" ht="12.75" customHeight="1">
-      <c r="A3" s="118" t="s">
+      <c r="A3" s="162" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="119"/>
-      <c r="C3" s="119"/>
-      <c r="D3" s="119"/>
-      <c r="E3" s="119"/>
-      <c r="F3" s="120"/>
-      <c r="G3" s="118" t="s">
+      <c r="B3" s="163"/>
+      <c r="C3" s="163"/>
+      <c r="D3" s="163"/>
+      <c r="E3" s="163"/>
+      <c r="F3" s="164"/>
+      <c r="G3" s="162" t="s">
         <v>51</v>
       </c>
-      <c r="H3" s="119"/>
-      <c r="I3" s="119"/>
-      <c r="J3" s="119"/>
-      <c r="K3" s="119"/>
-      <c r="L3" s="119"/>
-      <c r="M3" s="119"/>
-      <c r="N3" s="119"/>
-      <c r="O3" s="119"/>
-      <c r="P3" s="119"/>
-      <c r="Q3" s="119"/>
-      <c r="R3" s="119"/>
-      <c r="S3" s="119"/>
-      <c r="T3" s="119"/>
-      <c r="U3" s="119"/>
-      <c r="V3" s="119"/>
-      <c r="W3" s="119"/>
-      <c r="X3" s="119"/>
-      <c r="Y3" s="119"/>
-      <c r="Z3" s="119"/>
-      <c r="AA3" s="119"/>
-      <c r="AB3" s="119"/>
-      <c r="AC3" s="120"/>
-      <c r="AD3" s="118"/>
-      <c r="AE3" s="120"/>
-      <c r="AF3" s="118"/>
-      <c r="AG3" s="120"/>
+      <c r="H3" s="163"/>
+      <c r="I3" s="163"/>
+      <c r="J3" s="163"/>
+      <c r="K3" s="163"/>
+      <c r="L3" s="163"/>
+      <c r="M3" s="163"/>
+      <c r="N3" s="163"/>
+      <c r="O3" s="163"/>
+      <c r="P3" s="163"/>
+      <c r="Q3" s="163"/>
+      <c r="R3" s="163"/>
+      <c r="S3" s="163"/>
+      <c r="T3" s="163"/>
+      <c r="U3" s="163"/>
+      <c r="V3" s="163"/>
+      <c r="W3" s="163"/>
+      <c r="X3" s="163"/>
+      <c r="Y3" s="163"/>
+      <c r="Z3" s="163"/>
+      <c r="AA3" s="163"/>
+      <c r="AB3" s="163"/>
+      <c r="AC3" s="164"/>
+      <c r="AD3" s="162"/>
+      <c r="AE3" s="164"/>
+      <c r="AF3" s="162"/>
+      <c r="AG3" s="164"/>
       <c r="AH3" s="2"/>
       <c r="AI3" s="5"/>
       <c r="AJ3" s="5"/>
@@ -17186,123 +18066,123 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:177" ht="12.75" customHeight="1">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="165" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
-      <c r="E1" s="121"/>
-      <c r="F1" s="121"/>
-      <c r="G1" s="121"/>
-      <c r="H1" s="121"/>
-      <c r="I1" s="121"/>
-      <c r="J1" s="121"/>
-      <c r="K1" s="121"/>
-      <c r="L1" s="121"/>
-      <c r="M1" s="121"/>
-      <c r="N1" s="121"/>
-      <c r="O1" s="121"/>
-      <c r="P1" s="121"/>
-      <c r="Q1" s="121"/>
-      <c r="R1" s="121"/>
-      <c r="S1" s="121"/>
-      <c r="T1" s="121"/>
-      <c r="U1" s="121"/>
-      <c r="V1" s="121"/>
-      <c r="W1" s="121"/>
-      <c r="X1" s="121"/>
-      <c r="Y1" s="121"/>
-      <c r="Z1" s="121"/>
-      <c r="AA1" s="121"/>
-      <c r="AB1" s="121"/>
-      <c r="AC1" s="121"/>
-      <c r="AD1" s="121"/>
-      <c r="AE1" s="121"/>
-      <c r="AF1" s="121"/>
-      <c r="AG1" s="121"/>
+      <c r="B1" s="165"/>
+      <c r="C1" s="165"/>
+      <c r="D1" s="165"/>
+      <c r="E1" s="165"/>
+      <c r="F1" s="165"/>
+      <c r="G1" s="165"/>
+      <c r="H1" s="165"/>
+      <c r="I1" s="165"/>
+      <c r="J1" s="165"/>
+      <c r="K1" s="165"/>
+      <c r="L1" s="165"/>
+      <c r="M1" s="165"/>
+      <c r="N1" s="165"/>
+      <c r="O1" s="165"/>
+      <c r="P1" s="165"/>
+      <c r="Q1" s="165"/>
+      <c r="R1" s="165"/>
+      <c r="S1" s="165"/>
+      <c r="T1" s="165"/>
+      <c r="U1" s="165"/>
+      <c r="V1" s="165"/>
+      <c r="W1" s="165"/>
+      <c r="X1" s="165"/>
+      <c r="Y1" s="165"/>
+      <c r="Z1" s="165"/>
+      <c r="AA1" s="165"/>
+      <c r="AB1" s="165"/>
+      <c r="AC1" s="165"/>
+      <c r="AD1" s="165"/>
+      <c r="AE1" s="165"/>
+      <c r="AF1" s="165"/>
+      <c r="AG1" s="165"/>
     </row>
     <row r="2" spans="1:177" ht="13" customHeight="1">
-      <c r="A2" s="118" t="s">
+      <c r="A2" s="162" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="119"/>
-      <c r="C2" s="119"/>
-      <c r="D2" s="119"/>
-      <c r="E2" s="119"/>
-      <c r="F2" s="120"/>
-      <c r="G2" s="118" t="s">
+      <c r="B2" s="163"/>
+      <c r="C2" s="163"/>
+      <c r="D2" s="163"/>
+      <c r="E2" s="163"/>
+      <c r="F2" s="164"/>
+      <c r="G2" s="162" t="s">
         <v>42</v>
       </c>
-      <c r="H2" s="119"/>
-      <c r="I2" s="119"/>
-      <c r="J2" s="119"/>
-      <c r="K2" s="119"/>
-      <c r="L2" s="119"/>
-      <c r="M2" s="119"/>
-      <c r="N2" s="119"/>
-      <c r="O2" s="119"/>
-      <c r="P2" s="119"/>
-      <c r="Q2" s="119"/>
-      <c r="R2" s="119"/>
-      <c r="S2" s="119"/>
-      <c r="T2" s="119"/>
-      <c r="U2" s="119"/>
-      <c r="V2" s="119"/>
-      <c r="W2" s="119"/>
-      <c r="X2" s="119"/>
-      <c r="Y2" s="119"/>
-      <c r="Z2" s="119"/>
-      <c r="AA2" s="119"/>
-      <c r="AB2" s="119"/>
-      <c r="AC2" s="120"/>
-      <c r="AD2" s="118" t="s">
+      <c r="H2" s="163"/>
+      <c r="I2" s="163"/>
+      <c r="J2" s="163"/>
+      <c r="K2" s="163"/>
+      <c r="L2" s="163"/>
+      <c r="M2" s="163"/>
+      <c r="N2" s="163"/>
+      <c r="O2" s="163"/>
+      <c r="P2" s="163"/>
+      <c r="Q2" s="163"/>
+      <c r="R2" s="163"/>
+      <c r="S2" s="163"/>
+      <c r="T2" s="163"/>
+      <c r="U2" s="163"/>
+      <c r="V2" s="163"/>
+      <c r="W2" s="163"/>
+      <c r="X2" s="163"/>
+      <c r="Y2" s="163"/>
+      <c r="Z2" s="163"/>
+      <c r="AA2" s="163"/>
+      <c r="AB2" s="163"/>
+      <c r="AC2" s="164"/>
+      <c r="AD2" s="162" t="s">
         <v>1</v>
       </c>
-      <c r="AE2" s="120"/>
-      <c r="AF2" s="118" t="s">
+      <c r="AE2" s="164"/>
+      <c r="AF2" s="162" t="s">
         <v>2</v>
       </c>
-      <c r="AG2" s="120"/>
+      <c r="AG2" s="164"/>
     </row>
     <row r="3" spans="1:177" s="3" customFormat="1" ht="12.75" customHeight="1">
-      <c r="A3" s="118" t="s">
+      <c r="A3" s="162" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="119"/>
-      <c r="C3" s="119"/>
-      <c r="D3" s="119"/>
-      <c r="E3" s="119"/>
-      <c r="F3" s="120"/>
-      <c r="G3" s="118" t="s">
+      <c r="B3" s="163"/>
+      <c r="C3" s="163"/>
+      <c r="D3" s="163"/>
+      <c r="E3" s="163"/>
+      <c r="F3" s="164"/>
+      <c r="G3" s="162" t="s">
         <v>50</v>
       </c>
-      <c r="H3" s="119"/>
-      <c r="I3" s="119"/>
-      <c r="J3" s="119"/>
-      <c r="K3" s="119"/>
-      <c r="L3" s="119"/>
-      <c r="M3" s="119"/>
-      <c r="N3" s="119"/>
-      <c r="O3" s="119"/>
-      <c r="P3" s="119"/>
-      <c r="Q3" s="119"/>
-      <c r="R3" s="119"/>
-      <c r="S3" s="119"/>
-      <c r="T3" s="119"/>
-      <c r="U3" s="119"/>
-      <c r="V3" s="119"/>
-      <c r="W3" s="119"/>
-      <c r="X3" s="119"/>
-      <c r="Y3" s="119"/>
-      <c r="Z3" s="119"/>
-      <c r="AA3" s="119"/>
-      <c r="AB3" s="119"/>
-      <c r="AC3" s="120"/>
-      <c r="AD3" s="118"/>
-      <c r="AE3" s="120"/>
-      <c r="AF3" s="118"/>
-      <c r="AG3" s="120"/>
+      <c r="H3" s="163"/>
+      <c r="I3" s="163"/>
+      <c r="J3" s="163"/>
+      <c r="K3" s="163"/>
+      <c r="L3" s="163"/>
+      <c r="M3" s="163"/>
+      <c r="N3" s="163"/>
+      <c r="O3" s="163"/>
+      <c r="P3" s="163"/>
+      <c r="Q3" s="163"/>
+      <c r="R3" s="163"/>
+      <c r="S3" s="163"/>
+      <c r="T3" s="163"/>
+      <c r="U3" s="163"/>
+      <c r="V3" s="163"/>
+      <c r="W3" s="163"/>
+      <c r="X3" s="163"/>
+      <c r="Y3" s="163"/>
+      <c r="Z3" s="163"/>
+      <c r="AA3" s="163"/>
+      <c r="AB3" s="163"/>
+      <c r="AC3" s="164"/>
+      <c r="AD3" s="162"/>
+      <c r="AE3" s="164"/>
+      <c r="AF3" s="162"/>
+      <c r="AG3" s="164"/>
       <c r="AH3" s="2"/>
       <c r="AI3" s="5"/>
       <c r="AJ3" s="5"/>
@@ -18854,123 +19734,123 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:177" ht="12.75" customHeight="1">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="165" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
-      <c r="E1" s="121"/>
-      <c r="F1" s="121"/>
-      <c r="G1" s="121"/>
-      <c r="H1" s="121"/>
-      <c r="I1" s="121"/>
-      <c r="J1" s="121"/>
-      <c r="K1" s="121"/>
-      <c r="L1" s="121"/>
-      <c r="M1" s="121"/>
-      <c r="N1" s="121"/>
-      <c r="O1" s="121"/>
-      <c r="P1" s="121"/>
-      <c r="Q1" s="121"/>
-      <c r="R1" s="121"/>
-      <c r="S1" s="121"/>
-      <c r="T1" s="121"/>
-      <c r="U1" s="121"/>
-      <c r="V1" s="121"/>
-      <c r="W1" s="121"/>
-      <c r="X1" s="121"/>
-      <c r="Y1" s="121"/>
-      <c r="Z1" s="121"/>
-      <c r="AA1" s="121"/>
-      <c r="AB1" s="121"/>
-      <c r="AC1" s="121"/>
-      <c r="AD1" s="121"/>
-      <c r="AE1" s="121"/>
-      <c r="AF1" s="121"/>
-      <c r="AG1" s="121"/>
+      <c r="B1" s="165"/>
+      <c r="C1" s="165"/>
+      <c r="D1" s="165"/>
+      <c r="E1" s="165"/>
+      <c r="F1" s="165"/>
+      <c r="G1" s="165"/>
+      <c r="H1" s="165"/>
+      <c r="I1" s="165"/>
+      <c r="J1" s="165"/>
+      <c r="K1" s="165"/>
+      <c r="L1" s="165"/>
+      <c r="M1" s="165"/>
+      <c r="N1" s="165"/>
+      <c r="O1" s="165"/>
+      <c r="P1" s="165"/>
+      <c r="Q1" s="165"/>
+      <c r="R1" s="165"/>
+      <c r="S1" s="165"/>
+      <c r="T1" s="165"/>
+      <c r="U1" s="165"/>
+      <c r="V1" s="165"/>
+      <c r="W1" s="165"/>
+      <c r="X1" s="165"/>
+      <c r="Y1" s="165"/>
+      <c r="Z1" s="165"/>
+      <c r="AA1" s="165"/>
+      <c r="AB1" s="165"/>
+      <c r="AC1" s="165"/>
+      <c r="AD1" s="165"/>
+      <c r="AE1" s="165"/>
+      <c r="AF1" s="165"/>
+      <c r="AG1" s="165"/>
     </row>
     <row r="2" spans="1:177" ht="13" customHeight="1">
-      <c r="A2" s="118" t="s">
+      <c r="A2" s="162" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="119"/>
-      <c r="C2" s="119"/>
-      <c r="D2" s="119"/>
-      <c r="E2" s="119"/>
-      <c r="F2" s="120"/>
-      <c r="G2" s="118" t="s">
+      <c r="B2" s="163"/>
+      <c r="C2" s="163"/>
+      <c r="D2" s="163"/>
+      <c r="E2" s="163"/>
+      <c r="F2" s="164"/>
+      <c r="G2" s="162" t="s">
         <v>42</v>
       </c>
-      <c r="H2" s="119"/>
-      <c r="I2" s="119"/>
-      <c r="J2" s="119"/>
-      <c r="K2" s="119"/>
-      <c r="L2" s="119"/>
-      <c r="M2" s="119"/>
-      <c r="N2" s="119"/>
-      <c r="O2" s="119"/>
-      <c r="P2" s="119"/>
-      <c r="Q2" s="119"/>
-      <c r="R2" s="119"/>
-      <c r="S2" s="119"/>
-      <c r="T2" s="119"/>
-      <c r="U2" s="119"/>
-      <c r="V2" s="119"/>
-      <c r="W2" s="119"/>
-      <c r="X2" s="119"/>
-      <c r="Y2" s="119"/>
-      <c r="Z2" s="119"/>
-      <c r="AA2" s="119"/>
-      <c r="AB2" s="119"/>
-      <c r="AC2" s="120"/>
-      <c r="AD2" s="118" t="s">
+      <c r="H2" s="163"/>
+      <c r="I2" s="163"/>
+      <c r="J2" s="163"/>
+      <c r="K2" s="163"/>
+      <c r="L2" s="163"/>
+      <c r="M2" s="163"/>
+      <c r="N2" s="163"/>
+      <c r="O2" s="163"/>
+      <c r="P2" s="163"/>
+      <c r="Q2" s="163"/>
+      <c r="R2" s="163"/>
+      <c r="S2" s="163"/>
+      <c r="T2" s="163"/>
+      <c r="U2" s="163"/>
+      <c r="V2" s="163"/>
+      <c r="W2" s="163"/>
+      <c r="X2" s="163"/>
+      <c r="Y2" s="163"/>
+      <c r="Z2" s="163"/>
+      <c r="AA2" s="163"/>
+      <c r="AB2" s="163"/>
+      <c r="AC2" s="164"/>
+      <c r="AD2" s="162" t="s">
         <v>1</v>
       </c>
-      <c r="AE2" s="120"/>
-      <c r="AF2" s="118" t="s">
+      <c r="AE2" s="164"/>
+      <c r="AF2" s="162" t="s">
         <v>2</v>
       </c>
-      <c r="AG2" s="120"/>
+      <c r="AG2" s="164"/>
     </row>
     <row r="3" spans="1:177" s="3" customFormat="1" ht="12.75" customHeight="1">
-      <c r="A3" s="118" t="s">
+      <c r="A3" s="162" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="119"/>
-      <c r="C3" s="119"/>
-      <c r="D3" s="119"/>
-      <c r="E3" s="119"/>
-      <c r="F3" s="120"/>
-      <c r="G3" s="118" t="s">
+      <c r="B3" s="163"/>
+      <c r="C3" s="163"/>
+      <c r="D3" s="163"/>
+      <c r="E3" s="163"/>
+      <c r="F3" s="164"/>
+      <c r="G3" s="162" t="s">
         <v>52</v>
       </c>
-      <c r="H3" s="119"/>
-      <c r="I3" s="119"/>
-      <c r="J3" s="119"/>
-      <c r="K3" s="119"/>
-      <c r="L3" s="119"/>
-      <c r="M3" s="119"/>
-      <c r="N3" s="119"/>
-      <c r="O3" s="119"/>
-      <c r="P3" s="119"/>
-      <c r="Q3" s="119"/>
-      <c r="R3" s="119"/>
-      <c r="S3" s="119"/>
-      <c r="T3" s="119"/>
-      <c r="U3" s="119"/>
-      <c r="V3" s="119"/>
-      <c r="W3" s="119"/>
-      <c r="X3" s="119"/>
-      <c r="Y3" s="119"/>
-      <c r="Z3" s="119"/>
-      <c r="AA3" s="119"/>
-      <c r="AB3" s="119"/>
-      <c r="AC3" s="120"/>
-      <c r="AD3" s="118"/>
-      <c r="AE3" s="120"/>
-      <c r="AF3" s="118"/>
-      <c r="AG3" s="120"/>
+      <c r="H3" s="163"/>
+      <c r="I3" s="163"/>
+      <c r="J3" s="163"/>
+      <c r="K3" s="163"/>
+      <c r="L3" s="163"/>
+      <c r="M3" s="163"/>
+      <c r="N3" s="163"/>
+      <c r="O3" s="163"/>
+      <c r="P3" s="163"/>
+      <c r="Q3" s="163"/>
+      <c r="R3" s="163"/>
+      <c r="S3" s="163"/>
+      <c r="T3" s="163"/>
+      <c r="U3" s="163"/>
+      <c r="V3" s="163"/>
+      <c r="W3" s="163"/>
+      <c r="X3" s="163"/>
+      <c r="Y3" s="163"/>
+      <c r="Z3" s="163"/>
+      <c r="AA3" s="163"/>
+      <c r="AB3" s="163"/>
+      <c r="AC3" s="164"/>
+      <c r="AD3" s="162"/>
+      <c r="AE3" s="164"/>
+      <c r="AF3" s="162"/>
+      <c r="AG3" s="164"/>
       <c r="AH3" s="2"/>
       <c r="AI3" s="5"/>
       <c r="AJ3" s="5"/>
@@ -20524,64 +21404,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:167" ht="12.75" customHeight="1">
-      <c r="A1" s="114" t="s">
+      <c r="A1" s="166" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="114"/>
-      <c r="C1" s="114"/>
-      <c r="D1" s="114"/>
-      <c r="E1" s="114"/>
-      <c r="F1" s="114"/>
-      <c r="G1" s="114"/>
-      <c r="H1" s="114"/>
-      <c r="I1" s="114"/>
-      <c r="J1" s="114"/>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="114"/>
-      <c r="N1" s="114"/>
-      <c r="O1" s="114"/>
-      <c r="P1" s="114"/>
-      <c r="Q1" s="114"/>
-      <c r="R1" s="114"/>
-      <c r="S1" s="114"/>
-      <c r="T1" s="114"/>
-      <c r="U1" s="114"/>
-      <c r="V1" s="114"/>
-      <c r="W1" s="114"/>
+      <c r="B1" s="166"/>
+      <c r="C1" s="166"/>
+      <c r="D1" s="166"/>
+      <c r="E1" s="166"/>
+      <c r="F1" s="166"/>
+      <c r="G1" s="166"/>
+      <c r="H1" s="166"/>
+      <c r="I1" s="166"/>
+      <c r="J1" s="166"/>
+      <c r="K1" s="166"/>
+      <c r="L1" s="166"/>
+      <c r="M1" s="166"/>
+      <c r="N1" s="166"/>
+      <c r="O1" s="166"/>
+      <c r="P1" s="166"/>
+      <c r="Q1" s="166"/>
+      <c r="R1" s="166"/>
+      <c r="S1" s="166"/>
+      <c r="T1" s="166"/>
+      <c r="U1" s="166"/>
+      <c r="V1" s="166"/>
+      <c r="W1" s="166"/>
     </row>
     <row r="2" spans="1:167" ht="13" customHeight="1">
-      <c r="A2" s="115" t="s">
+      <c r="A2" s="157" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="116"/>
-      <c r="C2" s="116"/>
-      <c r="D2" s="116"/>
-      <c r="E2" s="116"/>
-      <c r="F2" s="117"/>
-      <c r="G2" s="116" t="s">
+      <c r="B2" s="155"/>
+      <c r="C2" s="155"/>
+      <c r="D2" s="155"/>
+      <c r="E2" s="155"/>
+      <c r="F2" s="156"/>
+      <c r="G2" s="155" t="s">
         <v>53</v>
       </c>
-      <c r="H2" s="116"/>
-      <c r="I2" s="116"/>
-      <c r="J2" s="116"/>
-      <c r="K2" s="116"/>
-      <c r="L2" s="116"/>
-      <c r="M2" s="116"/>
-      <c r="N2" s="116"/>
-      <c r="O2" s="116"/>
-      <c r="P2" s="116"/>
-      <c r="Q2" s="116"/>
-      <c r="R2" s="116"/>
-      <c r="S2" s="117"/>
-      <c r="T2" s="115" t="s">
+      <c r="H2" s="155"/>
+      <c r="I2" s="155"/>
+      <c r="J2" s="155"/>
+      <c r="K2" s="155"/>
+      <c r="L2" s="155"/>
+      <c r="M2" s="155"/>
+      <c r="N2" s="155"/>
+      <c r="O2" s="155"/>
+      <c r="P2" s="155"/>
+      <c r="Q2" s="155"/>
+      <c r="R2" s="155"/>
+      <c r="S2" s="156"/>
+      <c r="T2" s="157" t="s">
         <v>1</v>
       </c>
-      <c r="U2" s="117"/>
-      <c r="V2" s="115" t="s">
+      <c r="U2" s="156"/>
+      <c r="V2" s="157" t="s">
         <v>2</v>
       </c>
-      <c r="W2" s="117"/>
+      <c r="W2" s="156"/>
     </row>
     <row r="3" spans="1:167" s="15" customFormat="1" ht="12.75" customHeight="1">
       <c r="A3" s="59" t="s">
@@ -20592,25 +21472,25 @@
       <c r="D3" s="60"/>
       <c r="E3" s="60"/>
       <c r="F3" s="61"/>
-      <c r="G3" s="115" t="s">
+      <c r="G3" s="157" t="s">
         <v>92</v>
       </c>
-      <c r="H3" s="116"/>
-      <c r="I3" s="116"/>
-      <c r="J3" s="116"/>
-      <c r="K3" s="116"/>
-      <c r="L3" s="116"/>
-      <c r="M3" s="116"/>
-      <c r="N3" s="116"/>
-      <c r="O3" s="116"/>
-      <c r="P3" s="116"/>
-      <c r="Q3" s="116"/>
-      <c r="R3" s="116"/>
-      <c r="S3" s="116"/>
-      <c r="T3" s="157"/>
-      <c r="U3" s="157"/>
-      <c r="V3" s="157"/>
-      <c r="W3" s="157"/>
+      <c r="H3" s="155"/>
+      <c r="I3" s="155"/>
+      <c r="J3" s="155"/>
+      <c r="K3" s="155"/>
+      <c r="L3" s="155"/>
+      <c r="M3" s="155"/>
+      <c r="N3" s="155"/>
+      <c r="O3" s="155"/>
+      <c r="P3" s="155"/>
+      <c r="Q3" s="155"/>
+      <c r="R3" s="155"/>
+      <c r="S3" s="155"/>
+      <c r="T3" s="202"/>
+      <c r="U3" s="202"/>
+      <c r="V3" s="202"/>
+      <c r="W3" s="202"/>
       <c r="X3" s="13"/>
       <c r="Y3" s="14"/>
       <c r="Z3" s="14"/>
@@ -22257,12 +23137,12 @@
       <c r="H61" s="44"/>
       <c r="I61" s="38"/>
       <c r="J61" s="38"/>
-      <c r="K61" s="158">
+      <c r="K61" s="203">
         <v>1111111</v>
       </c>
-      <c r="L61" s="158"/>
-      <c r="M61" s="158"/>
-      <c r="N61" s="158"/>
+      <c r="L61" s="203"/>
+      <c r="M61" s="203"/>
+      <c r="N61" s="203"/>
       <c r="O61" s="38"/>
       <c r="P61" s="38"/>
       <c r="Q61" s="38"/>
@@ -22419,11 +23299,11 @@
       <c r="H67" s="44"/>
       <c r="I67" s="38"/>
       <c r="J67" s="38"/>
-      <c r="K67" s="159" t="s">
+      <c r="K67" s="204" t="s">
         <v>79</v>
       </c>
-      <c r="L67" s="159"/>
-      <c r="M67" s="159"/>
+      <c r="L67" s="204"/>
+      <c r="M67" s="204"/>
       <c r="N67" s="38"/>
       <c r="O67" s="38"/>
       <c r="P67" s="38"/>
@@ -23048,17 +23928,17 @@
       <c r="E92" s="73"/>
       <c r="F92" s="73"/>
       <c r="G92" s="73"/>
-      <c r="H92" s="160" t="s">
+      <c r="H92" s="205" t="s">
         <v>82</v>
       </c>
-      <c r="I92" s="160"/>
-      <c r="J92" s="160"/>
-      <c r="K92" s="160"/>
-      <c r="L92" s="160"/>
-      <c r="M92" s="160"/>
-      <c r="N92" s="160"/>
-      <c r="O92" s="160"/>
-      <c r="P92" s="160"/>
+      <c r="I92" s="205"/>
+      <c r="J92" s="205"/>
+      <c r="K92" s="205"/>
+      <c r="L92" s="205"/>
+      <c r="M92" s="205"/>
+      <c r="N92" s="205"/>
+      <c r="O92" s="205"/>
+      <c r="P92" s="205"/>
       <c r="Q92" s="38"/>
       <c r="R92" s="38"/>
       <c r="S92" s="44"/>
@@ -23075,15 +23955,15 @@
       <c r="E93" s="73"/>
       <c r="F93" s="73"/>
       <c r="G93" s="73"/>
-      <c r="H93" s="160"/>
-      <c r="I93" s="160"/>
-      <c r="J93" s="160"/>
-      <c r="K93" s="160"/>
-      <c r="L93" s="160"/>
-      <c r="M93" s="160"/>
-      <c r="N93" s="160"/>
-      <c r="O93" s="160"/>
-      <c r="P93" s="160"/>
+      <c r="H93" s="205"/>
+      <c r="I93" s="205"/>
+      <c r="J93" s="205"/>
+      <c r="K93" s="205"/>
+      <c r="L93" s="205"/>
+      <c r="M93" s="205"/>
+      <c r="N93" s="205"/>
+      <c r="O93" s="205"/>
+      <c r="P93" s="205"/>
       <c r="Q93" s="38"/>
       <c r="R93" s="38"/>
       <c r="S93" s="44"/>
@@ -23100,15 +23980,15 @@
       <c r="E94" s="73"/>
       <c r="F94" s="73"/>
       <c r="G94" s="73"/>
-      <c r="H94" s="160"/>
-      <c r="I94" s="160"/>
-      <c r="J94" s="160"/>
-      <c r="K94" s="160"/>
-      <c r="L94" s="160"/>
-      <c r="M94" s="160"/>
-      <c r="N94" s="160"/>
-      <c r="O94" s="160"/>
-      <c r="P94" s="160"/>
+      <c r="H94" s="205"/>
+      <c r="I94" s="205"/>
+      <c r="J94" s="205"/>
+      <c r="K94" s="205"/>
+      <c r="L94" s="205"/>
+      <c r="M94" s="205"/>
+      <c r="N94" s="205"/>
+      <c r="O94" s="205"/>
+      <c r="P94" s="205"/>
       <c r="Q94" s="38"/>
       <c r="R94" s="38"/>
       <c r="S94" s="44"/>
@@ -23203,10 +24083,10 @@
       <c r="H98" s="44"/>
       <c r="I98" s="38"/>
       <c r="J98" s="38"/>
-      <c r="K98" s="158"/>
-      <c r="L98" s="158"/>
-      <c r="M98" s="158"/>
-      <c r="N98" s="158"/>
+      <c r="K98" s="203"/>
+      <c r="L98" s="203"/>
+      <c r="M98" s="203"/>
+      <c r="N98" s="203"/>
       <c r="O98" s="38"/>
       <c r="P98" s="38"/>
       <c r="Q98" s="38"/>
@@ -23353,9 +24233,9 @@
       <c r="H104" s="44"/>
       <c r="I104" s="38"/>
       <c r="J104" s="38"/>
-      <c r="K104" s="159"/>
-      <c r="L104" s="159"/>
-      <c r="M104" s="159"/>
+      <c r="K104" s="204"/>
+      <c r="L104" s="204"/>
+      <c r="M104" s="204"/>
       <c r="N104" s="38"/>
       <c r="O104" s="38"/>
       <c r="P104" s="38"/>
@@ -23618,6 +24498,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="K61:N61"/>
+    <mergeCell ref="K67:M67"/>
+    <mergeCell ref="K98:N98"/>
+    <mergeCell ref="K104:M104"/>
+    <mergeCell ref="H92:P94"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:W1"/>
     <mergeCell ref="G3:S3"/>
@@ -23626,11 +24511,6 @@
     <mergeCell ref="T2:U2"/>
     <mergeCell ref="V2:W2"/>
     <mergeCell ref="G2:S2"/>
-    <mergeCell ref="K61:N61"/>
-    <mergeCell ref="K67:M67"/>
-    <mergeCell ref="K98:N98"/>
-    <mergeCell ref="K104:M104"/>
-    <mergeCell ref="H92:P94"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <printOptions horizontalCentered="1"/>
@@ -23667,139 +24547,139 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:181" ht="12.75" customHeight="1">
-      <c r="A1" s="179" t="s">
+      <c r="A1" s="159" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="180"/>
-      <c r="C1" s="180"/>
-      <c r="D1" s="180"/>
-      <c r="E1" s="180"/>
-      <c r="F1" s="180"/>
-      <c r="G1" s="180"/>
-      <c r="H1" s="180"/>
-      <c r="I1" s="180"/>
-      <c r="J1" s="180"/>
-      <c r="K1" s="180"/>
-      <c r="L1" s="180"/>
-      <c r="M1" s="180"/>
-      <c r="N1" s="180"/>
-      <c r="O1" s="180"/>
-      <c r="P1" s="180"/>
-      <c r="Q1" s="180"/>
-      <c r="R1" s="180"/>
-      <c r="S1" s="180"/>
-      <c r="T1" s="180"/>
-      <c r="U1" s="180"/>
-      <c r="V1" s="180"/>
-      <c r="W1" s="180"/>
-      <c r="X1" s="180"/>
-      <c r="Y1" s="180"/>
-      <c r="Z1" s="180"/>
-      <c r="AA1" s="180"/>
-      <c r="AB1" s="180"/>
-      <c r="AC1" s="180"/>
-      <c r="AD1" s="180"/>
-      <c r="AE1" s="180"/>
-      <c r="AF1" s="180"/>
-      <c r="AG1" s="180"/>
-      <c r="AH1" s="180"/>
-      <c r="AI1" s="180"/>
-      <c r="AJ1" s="180"/>
-      <c r="AK1" s="181"/>
+      <c r="B1" s="160"/>
+      <c r="C1" s="160"/>
+      <c r="D1" s="160"/>
+      <c r="E1" s="160"/>
+      <c r="F1" s="160"/>
+      <c r="G1" s="160"/>
+      <c r="H1" s="160"/>
+      <c r="I1" s="160"/>
+      <c r="J1" s="160"/>
+      <c r="K1" s="160"/>
+      <c r="L1" s="160"/>
+      <c r="M1" s="160"/>
+      <c r="N1" s="160"/>
+      <c r="O1" s="160"/>
+      <c r="P1" s="160"/>
+      <c r="Q1" s="160"/>
+      <c r="R1" s="160"/>
+      <c r="S1" s="160"/>
+      <c r="T1" s="160"/>
+      <c r="U1" s="160"/>
+      <c r="V1" s="160"/>
+      <c r="W1" s="160"/>
+      <c r="X1" s="160"/>
+      <c r="Y1" s="160"/>
+      <c r="Z1" s="160"/>
+      <c r="AA1" s="160"/>
+      <c r="AB1" s="160"/>
+      <c r="AC1" s="160"/>
+      <c r="AD1" s="160"/>
+      <c r="AE1" s="160"/>
+      <c r="AF1" s="160"/>
+      <c r="AG1" s="160"/>
+      <c r="AH1" s="160"/>
+      <c r="AI1" s="160"/>
+      <c r="AJ1" s="160"/>
+      <c r="AK1" s="161"/>
     </row>
     <row r="2" spans="1:181" ht="13" customHeight="1">
-      <c r="A2" s="182" t="s">
+      <c r="A2" s="154" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="116"/>
-      <c r="C2" s="116"/>
-      <c r="D2" s="116"/>
-      <c r="E2" s="116"/>
-      <c r="F2" s="116"/>
-      <c r="G2" s="116"/>
-      <c r="H2" s="117"/>
-      <c r="I2" s="115" t="s">
+      <c r="B2" s="155"/>
+      <c r="C2" s="155"/>
+      <c r="D2" s="155"/>
+      <c r="E2" s="155"/>
+      <c r="F2" s="155"/>
+      <c r="G2" s="155"/>
+      <c r="H2" s="156"/>
+      <c r="I2" s="157" t="s">
         <v>42</v>
       </c>
-      <c r="J2" s="116"/>
-      <c r="K2" s="116"/>
-      <c r="L2" s="116"/>
-      <c r="M2" s="116"/>
-      <c r="N2" s="116"/>
-      <c r="O2" s="116"/>
-      <c r="P2" s="116"/>
-      <c r="Q2" s="116"/>
-      <c r="R2" s="116"/>
-      <c r="S2" s="116"/>
-      <c r="T2" s="116"/>
-      <c r="U2" s="116"/>
-      <c r="V2" s="116"/>
-      <c r="W2" s="116"/>
-      <c r="X2" s="116"/>
-      <c r="Y2" s="116"/>
-      <c r="Z2" s="116"/>
-      <c r="AA2" s="116"/>
-      <c r="AB2" s="116"/>
-      <c r="AC2" s="116"/>
-      <c r="AD2" s="117"/>
-      <c r="AE2" s="115" t="s">
+      <c r="J2" s="155"/>
+      <c r="K2" s="155"/>
+      <c r="L2" s="155"/>
+      <c r="M2" s="155"/>
+      <c r="N2" s="155"/>
+      <c r="O2" s="155"/>
+      <c r="P2" s="155"/>
+      <c r="Q2" s="155"/>
+      <c r="R2" s="155"/>
+      <c r="S2" s="155"/>
+      <c r="T2" s="155"/>
+      <c r="U2" s="155"/>
+      <c r="V2" s="155"/>
+      <c r="W2" s="155"/>
+      <c r="X2" s="155"/>
+      <c r="Y2" s="155"/>
+      <c r="Z2" s="155"/>
+      <c r="AA2" s="155"/>
+      <c r="AB2" s="155"/>
+      <c r="AC2" s="155"/>
+      <c r="AD2" s="156"/>
+      <c r="AE2" s="157" t="s">
         <v>1</v>
       </c>
-      <c r="AF2" s="116"/>
-      <c r="AG2" s="117"/>
+      <c r="AF2" s="155"/>
+      <c r="AG2" s="156"/>
       <c r="AH2" s="58"/>
       <c r="AI2" s="58"/>
-      <c r="AJ2" s="115" t="s">
+      <c r="AJ2" s="157" t="s">
         <v>2</v>
       </c>
-      <c r="AK2" s="183"/>
+      <c r="AK2" s="158"/>
     </row>
     <row r="3" spans="1:181" s="15" customFormat="1" ht="12.75" customHeight="1">
-      <c r="A3" s="182" t="s">
+      <c r="A3" s="154" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="116"/>
-      <c r="C3" s="116"/>
-      <c r="D3" s="116"/>
-      <c r="E3" s="116"/>
-      <c r="F3" s="116"/>
-      <c r="G3" s="116"/>
-      <c r="H3" s="117"/>
-      <c r="I3" s="115" t="s">
+      <c r="B3" s="155"/>
+      <c r="C3" s="155"/>
+      <c r="D3" s="155"/>
+      <c r="E3" s="155"/>
+      <c r="F3" s="155"/>
+      <c r="G3" s="155"/>
+      <c r="H3" s="156"/>
+      <c r="I3" s="157" t="s">
         <v>93</v>
       </c>
-      <c r="J3" s="116"/>
-      <c r="K3" s="116"/>
-      <c r="L3" s="116"/>
-      <c r="M3" s="116"/>
-      <c r="N3" s="116"/>
-      <c r="O3" s="116"/>
-      <c r="P3" s="116"/>
-      <c r="Q3" s="116"/>
-      <c r="R3" s="116"/>
-      <c r="S3" s="116"/>
-      <c r="T3" s="116"/>
-      <c r="U3" s="116"/>
-      <c r="V3" s="116"/>
-      <c r="W3" s="116"/>
-      <c r="X3" s="116"/>
-      <c r="Y3" s="116"/>
-      <c r="Z3" s="116"/>
-      <c r="AA3" s="116"/>
-      <c r="AB3" s="116"/>
-      <c r="AC3" s="116"/>
-      <c r="AD3" s="117"/>
-      <c r="AE3" s="115" t="s">
+      <c r="J3" s="155"/>
+      <c r="K3" s="155"/>
+      <c r="L3" s="155"/>
+      <c r="M3" s="155"/>
+      <c r="N3" s="155"/>
+      <c r="O3" s="155"/>
+      <c r="P3" s="155"/>
+      <c r="Q3" s="155"/>
+      <c r="R3" s="155"/>
+      <c r="S3" s="155"/>
+      <c r="T3" s="155"/>
+      <c r="U3" s="155"/>
+      <c r="V3" s="155"/>
+      <c r="W3" s="155"/>
+      <c r="X3" s="155"/>
+      <c r="Y3" s="155"/>
+      <c r="Z3" s="155"/>
+      <c r="AA3" s="155"/>
+      <c r="AB3" s="155"/>
+      <c r="AC3" s="155"/>
+      <c r="AD3" s="156"/>
+      <c r="AE3" s="157" t="s">
         <v>13</v>
       </c>
-      <c r="AF3" s="116"/>
-      <c r="AG3" s="117"/>
+      <c r="AF3" s="155"/>
+      <c r="AG3" s="156"/>
       <c r="AH3" s="58"/>
       <c r="AI3" s="58"/>
-      <c r="AJ3" s="115" t="s">
+      <c r="AJ3" s="157" t="s">
         <v>41</v>
       </c>
-      <c r="AK3" s="183"/>
+      <c r="AK3" s="158"/>
       <c r="AL3" s="13"/>
       <c r="AM3" s="14"/>
       <c r="AN3" s="14"/>
@@ -23946,7 +24826,7 @@
       <c r="FY3" s="14"/>
     </row>
     <row r="4" spans="1:181" ht="12.75" customHeight="1">
-      <c r="A4" s="184"/>
+      <c r="A4" s="98"/>
       <c r="B4" s="65"/>
       <c r="C4" s="65"/>
       <c r="D4" s="65"/>
@@ -23982,3175 +24862,3228 @@
       <c r="AH4" s="65"/>
       <c r="AI4" s="65"/>
       <c r="AJ4" s="65"/>
-      <c r="AK4" s="185"/>
+      <c r="AK4" s="99"/>
     </row>
     <row r="5" spans="1:181" ht="12.75" customHeight="1">
-      <c r="A5" s="186"/>
-      <c r="B5" s="167"/>
-      <c r="C5" s="167"/>
-      <c r="D5" s="167"/>
-      <c r="E5" s="167"/>
-      <c r="F5" s="167"/>
-      <c r="G5" s="167"/>
-      <c r="H5" s="167"/>
-      <c r="I5" s="167"/>
-      <c r="J5" s="167"/>
-      <c r="K5" s="167"/>
-      <c r="L5" s="167"/>
-      <c r="M5" s="167"/>
-      <c r="N5" s="167"/>
-      <c r="O5" s="167"/>
-      <c r="P5" s="167"/>
-      <c r="Q5" s="167"/>
-      <c r="R5" s="167"/>
-      <c r="S5" s="167"/>
-      <c r="T5" s="167"/>
-      <c r="U5" s="167"/>
-      <c r="V5" s="167"/>
-      <c r="W5" s="167"/>
-      <c r="X5" s="167"/>
-      <c r="Y5" s="167"/>
-      <c r="Z5" s="167"/>
-      <c r="AA5" s="167"/>
-      <c r="AB5" s="167"/>
-      <c r="AC5" s="167"/>
-      <c r="AD5" s="167"/>
-      <c r="AE5" s="167"/>
-      <c r="AF5" s="167"/>
-      <c r="AG5" s="167"/>
-      <c r="AH5" s="167"/>
-      <c r="AI5" s="167"/>
-      <c r="AJ5" s="167"/>
-      <c r="AK5" s="187"/>
+      <c r="A5" s="100"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="67"/>
+      <c r="K5" s="67"/>
+      <c r="L5" s="67"/>
+      <c r="M5" s="67"/>
+      <c r="N5" s="67"/>
+      <c r="O5" s="67"/>
+      <c r="P5" s="67"/>
+      <c r="Q5" s="67"/>
+      <c r="R5" s="67"/>
+      <c r="S5" s="67"/>
+      <c r="T5" s="67"/>
+      <c r="U5" s="67"/>
+      <c r="V5" s="67"/>
+      <c r="W5" s="67"/>
+      <c r="X5" s="67"/>
+      <c r="Y5" s="67"/>
+      <c r="Z5" s="67"/>
+      <c r="AA5" s="67"/>
+      <c r="AB5" s="67"/>
+      <c r="AC5" s="67"/>
+      <c r="AD5" s="67"/>
+      <c r="AE5" s="67"/>
+      <c r="AF5" s="67"/>
+      <c r="AG5" s="67"/>
+      <c r="AH5" s="67"/>
+      <c r="AI5" s="67"/>
+      <c r="AJ5" s="67"/>
+      <c r="AK5" s="101"/>
     </row>
     <row r="6" spans="1:181" ht="12.75" customHeight="1">
       <c r="A6" s="93"/>
-      <c r="B6" s="169" t="s">
+      <c r="B6" s="73" t="s">
         <v>83</v>
       </c>
-      <c r="C6" s="170"/>
-      <c r="D6" s="170"/>
-      <c r="E6" s="170"/>
-      <c r="F6" s="170"/>
-      <c r="G6" s="170"/>
-      <c r="H6" s="170"/>
-      <c r="I6" s="170"/>
-      <c r="J6" s="170"/>
-      <c r="K6" s="170"/>
-      <c r="L6" s="170"/>
-      <c r="M6" s="170"/>
-      <c r="N6" s="170"/>
-      <c r="O6" s="170"/>
-      <c r="P6" s="170"/>
-      <c r="Q6" s="170"/>
-      <c r="R6" s="170"/>
-      <c r="S6" s="170"/>
-      <c r="T6" s="170"/>
-      <c r="U6" s="170"/>
-      <c r="V6" s="170"/>
-      <c r="W6" s="170"/>
-      <c r="X6" s="170"/>
-      <c r="Y6" s="170"/>
-      <c r="Z6" s="170"/>
-      <c r="AA6" s="170"/>
-      <c r="AB6" s="170"/>
-      <c r="AC6" s="170"/>
-      <c r="AD6" s="170"/>
-      <c r="AE6" s="170"/>
-      <c r="AF6" s="170"/>
-      <c r="AG6" s="170"/>
-      <c r="AH6" s="170"/>
-      <c r="AI6" s="170"/>
-      <c r="AJ6" s="170"/>
+      <c r="C6" s="38"/>
+      <c r="D6" s="38"/>
+      <c r="E6" s="38"/>
+      <c r="F6" s="38"/>
+      <c r="G6" s="38"/>
+      <c r="H6" s="38"/>
+      <c r="I6" s="38"/>
+      <c r="J6" s="38"/>
+      <c r="K6" s="38"/>
+      <c r="L6" s="38"/>
+      <c r="M6" s="38"/>
+      <c r="N6" s="38"/>
+      <c r="O6" s="38"/>
+      <c r="P6" s="38"/>
+      <c r="Q6" s="38"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="38"/>
+      <c r="T6" s="38"/>
+      <c r="U6" s="38"/>
+      <c r="V6" s="38"/>
+      <c r="W6" s="38"/>
+      <c r="X6" s="38"/>
+      <c r="Y6" s="38"/>
+      <c r="Z6" s="38"/>
+      <c r="AA6" s="38"/>
+      <c r="AB6" s="38"/>
+      <c r="AC6" s="38"/>
+      <c r="AD6" s="38"/>
+      <c r="AE6" s="38"/>
+      <c r="AF6" s="38"/>
+      <c r="AG6" s="38"/>
+      <c r="AH6" s="38"/>
+      <c r="AI6" s="38"/>
+      <c r="AJ6" s="38"/>
       <c r="AK6" s="94"/>
     </row>
     <row r="7" spans="1:181" ht="12.75" customHeight="1" thickBot="1">
       <c r="A7" s="93"/>
-      <c r="B7" s="170"/>
-      <c r="C7" s="170"/>
-      <c r="D7" s="170"/>
-      <c r="E7" s="170"/>
-      <c r="F7" s="170"/>
-      <c r="G7" s="170"/>
-      <c r="H7" s="170"/>
-      <c r="I7" s="170"/>
-      <c r="J7" s="170"/>
-      <c r="K7" s="170"/>
-      <c r="L7" s="171"/>
-      <c r="M7" s="170"/>
-      <c r="N7" s="170"/>
-      <c r="O7" s="170"/>
-      <c r="P7" s="170"/>
-      <c r="Q7" s="170"/>
-      <c r="R7" s="170"/>
-      <c r="S7" s="170"/>
-      <c r="T7" s="170"/>
-      <c r="U7" s="170"/>
-      <c r="V7" s="171"/>
-      <c r="W7" s="171"/>
-      <c r="X7" s="170"/>
-      <c r="Y7" s="170"/>
-      <c r="Z7" s="171"/>
-      <c r="AA7" s="170"/>
-      <c r="AB7" s="170"/>
-      <c r="AC7" s="170"/>
-      <c r="AD7" s="170"/>
-      <c r="AE7" s="170"/>
-      <c r="AF7" s="170"/>
-      <c r="AG7" s="170"/>
-      <c r="AH7" s="170"/>
-      <c r="AI7" s="170"/>
-      <c r="AJ7" s="170"/>
+      <c r="B7" s="38"/>
+      <c r="C7" s="38"/>
+      <c r="D7" s="38"/>
+      <c r="E7" s="38"/>
+      <c r="F7" s="38"/>
+      <c r="G7" s="38"/>
+      <c r="H7" s="38"/>
+      <c r="I7" s="38"/>
+      <c r="J7" s="38"/>
+      <c r="K7" s="38"/>
+      <c r="L7" s="42"/>
+      <c r="M7" s="38"/>
+      <c r="N7" s="38"/>
+      <c r="O7" s="38"/>
+      <c r="P7" s="38"/>
+      <c r="Q7" s="38"/>
+      <c r="R7" s="38"/>
+      <c r="S7" s="38"/>
+      <c r="T7" s="38"/>
+      <c r="U7" s="38"/>
+      <c r="V7" s="42"/>
+      <c r="W7" s="42"/>
+      <c r="X7" s="38"/>
+      <c r="Y7" s="38"/>
+      <c r="Z7" s="42"/>
+      <c r="AA7" s="38"/>
+      <c r="AB7" s="38"/>
+      <c r="AC7" s="38"/>
+      <c r="AD7" s="38"/>
+      <c r="AE7" s="38"/>
+      <c r="AF7" s="38"/>
+      <c r="AG7" s="38"/>
+      <c r="AH7" s="38"/>
+      <c r="AI7" s="38"/>
+      <c r="AJ7" s="38"/>
       <c r="AK7" s="94"/>
     </row>
     <row r="8" spans="1:181" ht="12.75" customHeight="1">
       <c r="A8" s="93"/>
-      <c r="B8" s="170"/>
-      <c r="C8" s="170"/>
-      <c r="D8" s="170"/>
-      <c r="E8" s="170"/>
-      <c r="F8" s="170"/>
-      <c r="G8" s="110" t="s">
+      <c r="B8" s="38"/>
+      <c r="C8" s="38"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="131" t="s">
         <v>84</v>
       </c>
-      <c r="H8" s="111"/>
-      <c r="I8" s="111"/>
-      <c r="J8" s="98"/>
-      <c r="K8" s="99"/>
-      <c r="L8" s="99"/>
-      <c r="M8" s="99"/>
-      <c r="N8" s="99"/>
-      <c r="O8" s="99"/>
-      <c r="P8" s="99"/>
-      <c r="Q8" s="99"/>
-      <c r="R8" s="100"/>
-      <c r="S8" s="104" t="s">
+      <c r="H8" s="132"/>
+      <c r="I8" s="132"/>
+      <c r="J8" s="135"/>
+      <c r="K8" s="136"/>
+      <c r="L8" s="136"/>
+      <c r="M8" s="136"/>
+      <c r="N8" s="136"/>
+      <c r="O8" s="136"/>
+      <c r="P8" s="136"/>
+      <c r="Q8" s="136"/>
+      <c r="R8" s="137"/>
+      <c r="S8" s="141" t="s">
         <v>88</v>
       </c>
-      <c r="T8" s="105"/>
-      <c r="U8" s="106"/>
-      <c r="V8" s="98"/>
-      <c r="W8" s="99"/>
-      <c r="X8" s="99"/>
-      <c r="Y8" s="99"/>
-      <c r="Z8" s="99"/>
-      <c r="AA8" s="99"/>
-      <c r="AB8" s="99"/>
-      <c r="AC8" s="99"/>
-      <c r="AD8" s="100"/>
-      <c r="AE8" s="170"/>
-      <c r="AF8" s="170"/>
-      <c r="AG8" s="170"/>
-      <c r="AH8" s="170"/>
-      <c r="AI8" s="170"/>
-      <c r="AJ8" s="170"/>
+      <c r="T8" s="142"/>
+      <c r="U8" s="143"/>
+      <c r="V8" s="135"/>
+      <c r="W8" s="136"/>
+      <c r="X8" s="136"/>
+      <c r="Y8" s="136"/>
+      <c r="Z8" s="136"/>
+      <c r="AA8" s="136"/>
+      <c r="AB8" s="136"/>
+      <c r="AC8" s="136"/>
+      <c r="AD8" s="137"/>
+      <c r="AE8" s="38"/>
+      <c r="AF8" s="38"/>
+      <c r="AG8" s="38"/>
+      <c r="AH8" s="38"/>
+      <c r="AI8" s="38"/>
+      <c r="AJ8" s="38"/>
       <c r="AK8" s="94"/>
     </row>
     <row r="9" spans="1:181" ht="12.75" customHeight="1" thickBot="1">
       <c r="A9" s="93"/>
-      <c r="B9" s="170"/>
-      <c r="C9" s="170"/>
-      <c r="D9" s="170"/>
-      <c r="E9" s="170"/>
-      <c r="F9" s="170"/>
-      <c r="G9" s="112"/>
-      <c r="H9" s="113"/>
-      <c r="I9" s="113"/>
-      <c r="J9" s="101"/>
-      <c r="K9" s="102"/>
-      <c r="L9" s="102"/>
-      <c r="M9" s="102"/>
-      <c r="N9" s="102"/>
-      <c r="O9" s="102"/>
-      <c r="P9" s="102"/>
-      <c r="Q9" s="102"/>
-      <c r="R9" s="103"/>
-      <c r="S9" s="107"/>
-      <c r="T9" s="108"/>
-      <c r="U9" s="109"/>
-      <c r="V9" s="101"/>
-      <c r="W9" s="102"/>
-      <c r="X9" s="102"/>
-      <c r="Y9" s="102"/>
-      <c r="Z9" s="102"/>
-      <c r="AA9" s="102"/>
-      <c r="AB9" s="102"/>
-      <c r="AC9" s="102"/>
-      <c r="AD9" s="103"/>
-      <c r="AE9" s="170"/>
-      <c r="AF9" s="170"/>
-      <c r="AG9" s="170"/>
-      <c r="AH9" s="170"/>
-      <c r="AI9" s="170"/>
-      <c r="AJ9" s="170"/>
+      <c r="B9" s="38"/>
+      <c r="C9" s="38"/>
+      <c r="D9" s="38"/>
+      <c r="E9" s="38"/>
+      <c r="F9" s="38"/>
+      <c r="G9" s="133"/>
+      <c r="H9" s="134"/>
+      <c r="I9" s="134"/>
+      <c r="J9" s="138"/>
+      <c r="K9" s="139"/>
+      <c r="L9" s="139"/>
+      <c r="M9" s="139"/>
+      <c r="N9" s="139"/>
+      <c r="O9" s="139"/>
+      <c r="P9" s="139"/>
+      <c r="Q9" s="139"/>
+      <c r="R9" s="140"/>
+      <c r="S9" s="144"/>
+      <c r="T9" s="145"/>
+      <c r="U9" s="146"/>
+      <c r="V9" s="138"/>
+      <c r="W9" s="139"/>
+      <c r="X9" s="139"/>
+      <c r="Y9" s="139"/>
+      <c r="Z9" s="139"/>
+      <c r="AA9" s="139"/>
+      <c r="AB9" s="139"/>
+      <c r="AC9" s="139"/>
+      <c r="AD9" s="140"/>
+      <c r="AE9" s="38"/>
+      <c r="AF9" s="38"/>
+      <c r="AG9" s="38"/>
+      <c r="AH9" s="38"/>
+      <c r="AI9" s="38"/>
+      <c r="AJ9" s="38"/>
       <c r="AK9" s="94"/>
     </row>
     <row r="10" spans="1:181" ht="12.75" customHeight="1">
       <c r="A10" s="93"/>
-      <c r="B10" s="170"/>
-      <c r="C10" s="170"/>
-      <c r="D10" s="170"/>
-      <c r="E10" s="170"/>
-      <c r="F10" s="170"/>
-      <c r="G10" s="110" t="s">
+      <c r="B10" s="38"/>
+      <c r="C10" s="38"/>
+      <c r="D10" s="38"/>
+      <c r="E10" s="38"/>
+      <c r="F10" s="38"/>
+      <c r="G10" s="131" t="s">
         <v>85</v>
       </c>
-      <c r="H10" s="111"/>
-      <c r="I10" s="111"/>
-      <c r="J10" s="98"/>
-      <c r="K10" s="99"/>
-      <c r="L10" s="99"/>
-      <c r="M10" s="99"/>
-      <c r="N10" s="99"/>
-      <c r="O10" s="99"/>
-      <c r="P10" s="99"/>
-      <c r="Q10" s="99"/>
-      <c r="R10" s="100"/>
-      <c r="S10" s="104" t="s">
+      <c r="H10" s="132"/>
+      <c r="I10" s="132"/>
+      <c r="J10" s="135"/>
+      <c r="K10" s="136"/>
+      <c r="L10" s="136"/>
+      <c r="M10" s="136"/>
+      <c r="N10" s="136"/>
+      <c r="O10" s="136"/>
+      <c r="P10" s="136"/>
+      <c r="Q10" s="136"/>
+      <c r="R10" s="137"/>
+      <c r="S10" s="141" t="s">
         <v>89</v>
       </c>
-      <c r="T10" s="105"/>
-      <c r="U10" s="106"/>
-      <c r="V10" s="98"/>
-      <c r="W10" s="99"/>
-      <c r="X10" s="99"/>
-      <c r="Y10" s="99"/>
-      <c r="Z10" s="99"/>
-      <c r="AA10" s="99"/>
-      <c r="AB10" s="99"/>
-      <c r="AC10" s="99"/>
-      <c r="AD10" s="100"/>
-      <c r="AE10" s="170"/>
-      <c r="AF10" s="170"/>
-      <c r="AG10" s="170"/>
-      <c r="AH10" s="170"/>
-      <c r="AI10" s="170"/>
-      <c r="AJ10" s="170"/>
+      <c r="T10" s="142"/>
+      <c r="U10" s="143"/>
+      <c r="V10" s="135"/>
+      <c r="W10" s="136"/>
+      <c r="X10" s="136"/>
+      <c r="Y10" s="136"/>
+      <c r="Z10" s="136"/>
+      <c r="AA10" s="136"/>
+      <c r="AB10" s="136"/>
+      <c r="AC10" s="136"/>
+      <c r="AD10" s="137"/>
+      <c r="AE10" s="38"/>
+      <c r="AF10" s="38"/>
+      <c r="AG10" s="38"/>
+      <c r="AH10" s="38"/>
+      <c r="AI10" s="38"/>
+      <c r="AJ10" s="38"/>
       <c r="AK10" s="94"/>
     </row>
     <row r="11" spans="1:181" ht="12.75" customHeight="1" thickBot="1">
       <c r="A11" s="93"/>
-      <c r="B11" s="170"/>
-      <c r="C11" s="170"/>
-      <c r="D11" s="170"/>
-      <c r="E11" s="170"/>
-      <c r="F11" s="170"/>
-      <c r="G11" s="112"/>
-      <c r="H11" s="113"/>
-      <c r="I11" s="113"/>
-      <c r="J11" s="101"/>
-      <c r="K11" s="102"/>
-      <c r="L11" s="102"/>
-      <c r="M11" s="102"/>
-      <c r="N11" s="102"/>
-      <c r="O11" s="102"/>
-      <c r="P11" s="102"/>
-      <c r="Q11" s="102"/>
-      <c r="R11" s="103"/>
-      <c r="S11" s="107"/>
-      <c r="T11" s="108"/>
-      <c r="U11" s="109"/>
-      <c r="V11" s="101"/>
-      <c r="W11" s="102"/>
-      <c r="X11" s="102"/>
-      <c r="Y11" s="102"/>
-      <c r="Z11" s="102"/>
-      <c r="AA11" s="102"/>
-      <c r="AB11" s="102"/>
-      <c r="AC11" s="102"/>
-      <c r="AD11" s="103"/>
-      <c r="AE11" s="170"/>
-      <c r="AF11" s="170"/>
-      <c r="AG11" s="170"/>
-      <c r="AH11" s="170"/>
-      <c r="AI11" s="170"/>
-      <c r="AJ11" s="170"/>
+      <c r="B11" s="38"/>
+      <c r="C11" s="38"/>
+      <c r="D11" s="38"/>
+      <c r="E11" s="38"/>
+      <c r="F11" s="38"/>
+      <c r="G11" s="133"/>
+      <c r="H11" s="134"/>
+      <c r="I11" s="134"/>
+      <c r="J11" s="138"/>
+      <c r="K11" s="139"/>
+      <c r="L11" s="139"/>
+      <c r="M11" s="139"/>
+      <c r="N11" s="139"/>
+      <c r="O11" s="139"/>
+      <c r="P11" s="139"/>
+      <c r="Q11" s="139"/>
+      <c r="R11" s="140"/>
+      <c r="S11" s="144"/>
+      <c r="T11" s="145"/>
+      <c r="U11" s="146"/>
+      <c r="V11" s="138"/>
+      <c r="W11" s="139"/>
+      <c r="X11" s="139"/>
+      <c r="Y11" s="139"/>
+      <c r="Z11" s="139"/>
+      <c r="AA11" s="139"/>
+      <c r="AB11" s="139"/>
+      <c r="AC11" s="139"/>
+      <c r="AD11" s="140"/>
+      <c r="AE11" s="38"/>
+      <c r="AF11" s="38"/>
+      <c r="AG11" s="38"/>
+      <c r="AH11" s="38"/>
+      <c r="AI11" s="38"/>
+      <c r="AJ11" s="38"/>
       <c r="AK11" s="94"/>
     </row>
     <row r="12" spans="1:181" ht="12.75" customHeight="1">
       <c r="A12" s="93"/>
-      <c r="B12" s="170"/>
-      <c r="C12" s="170"/>
-      <c r="D12" s="170"/>
-      <c r="E12" s="170"/>
-      <c r="F12" s="170"/>
-      <c r="G12" s="110" t="s">
+      <c r="B12" s="38"/>
+      <c r="C12" s="38"/>
+      <c r="D12" s="38"/>
+      <c r="E12" s="38"/>
+      <c r="F12" s="38"/>
+      <c r="G12" s="131" t="s">
         <v>86</v>
       </c>
-      <c r="H12" s="111"/>
-      <c r="I12" s="111"/>
-      <c r="J12" s="98"/>
-      <c r="K12" s="99"/>
-      <c r="L12" s="99"/>
-      <c r="M12" s="99"/>
-      <c r="N12" s="99"/>
-      <c r="O12" s="99"/>
-      <c r="P12" s="99"/>
-      <c r="Q12" s="99"/>
-      <c r="R12" s="100"/>
-      <c r="S12" s="104" t="s">
+      <c r="H12" s="132"/>
+      <c r="I12" s="132"/>
+      <c r="J12" s="135"/>
+      <c r="K12" s="136"/>
+      <c r="L12" s="136"/>
+      <c r="M12" s="136"/>
+      <c r="N12" s="136"/>
+      <c r="O12" s="136"/>
+      <c r="P12" s="136"/>
+      <c r="Q12" s="136"/>
+      <c r="R12" s="137"/>
+      <c r="S12" s="141" t="s">
         <v>90</v>
       </c>
-      <c r="T12" s="105"/>
-      <c r="U12" s="106"/>
-      <c r="V12" s="161" t="s">
+      <c r="T12" s="142"/>
+      <c r="U12" s="143"/>
+      <c r="V12" s="147" t="s">
         <v>91</v>
       </c>
-      <c r="W12" s="162"/>
-      <c r="X12" s="162"/>
-      <c r="Y12" s="162"/>
-      <c r="Z12" s="162"/>
-      <c r="AA12" s="162"/>
-      <c r="AB12" s="162"/>
-      <c r="AC12" s="162"/>
-      <c r="AD12" s="163"/>
-      <c r="AE12" s="172"/>
-      <c r="AF12" s="172"/>
-      <c r="AG12" s="172"/>
-      <c r="AH12" s="172"/>
-      <c r="AI12" s="172"/>
-      <c r="AJ12" s="170"/>
+      <c r="W12" s="148"/>
+      <c r="X12" s="148"/>
+      <c r="Y12" s="148"/>
+      <c r="Z12" s="148"/>
+      <c r="AA12" s="148"/>
+      <c r="AB12" s="148"/>
+      <c r="AC12" s="148"/>
+      <c r="AD12" s="149"/>
+      <c r="AE12" s="63"/>
+      <c r="AF12" s="63"/>
+      <c r="AG12" s="63"/>
+      <c r="AH12" s="63"/>
+      <c r="AI12" s="63"/>
+      <c r="AJ12" s="38"/>
       <c r="AK12" s="94"/>
     </row>
     <row r="13" spans="1:181" ht="12.75" customHeight="1" thickBot="1">
       <c r="A13" s="93"/>
-      <c r="B13" s="173"/>
-      <c r="C13" s="173"/>
-      <c r="D13" s="173"/>
-      <c r="E13" s="173"/>
-      <c r="F13" s="170"/>
-      <c r="G13" s="112"/>
-      <c r="H13" s="113"/>
-      <c r="I13" s="113"/>
-      <c r="J13" s="101"/>
-      <c r="K13" s="102"/>
-      <c r="L13" s="102"/>
-      <c r="M13" s="102"/>
-      <c r="N13" s="102"/>
-      <c r="O13" s="102"/>
-      <c r="P13" s="102"/>
-      <c r="Q13" s="102"/>
-      <c r="R13" s="103"/>
-      <c r="S13" s="107"/>
-      <c r="T13" s="108"/>
-      <c r="U13" s="109"/>
-      <c r="V13" s="164"/>
-      <c r="W13" s="165"/>
-      <c r="X13" s="165"/>
-      <c r="Y13" s="165"/>
-      <c r="Z13" s="165"/>
-      <c r="AA13" s="165"/>
-      <c r="AB13" s="165"/>
-      <c r="AC13" s="165"/>
-      <c r="AD13" s="166"/>
-      <c r="AE13" s="170"/>
-      <c r="AF13" s="170"/>
-      <c r="AG13" s="170"/>
-      <c r="AH13" s="170"/>
-      <c r="AI13" s="170"/>
-      <c r="AJ13" s="171"/>
+      <c r="B13" s="62"/>
+      <c r="C13" s="62"/>
+      <c r="D13" s="62"/>
+      <c r="E13" s="62"/>
+      <c r="F13" s="38"/>
+      <c r="G13" s="133"/>
+      <c r="H13" s="134"/>
+      <c r="I13" s="134"/>
+      <c r="J13" s="138"/>
+      <c r="K13" s="139"/>
+      <c r="L13" s="139"/>
+      <c r="M13" s="139"/>
+      <c r="N13" s="139"/>
+      <c r="O13" s="139"/>
+      <c r="P13" s="139"/>
+      <c r="Q13" s="139"/>
+      <c r="R13" s="140"/>
+      <c r="S13" s="144"/>
+      <c r="T13" s="145"/>
+      <c r="U13" s="146"/>
+      <c r="V13" s="150"/>
+      <c r="W13" s="151"/>
+      <c r="X13" s="151"/>
+      <c r="Y13" s="151"/>
+      <c r="Z13" s="151"/>
+      <c r="AA13" s="151"/>
+      <c r="AB13" s="151"/>
+      <c r="AC13" s="151"/>
+      <c r="AD13" s="152"/>
+      <c r="AE13" s="38"/>
+      <c r="AF13" s="38"/>
+      <c r="AG13" s="38"/>
+      <c r="AH13" s="38"/>
+      <c r="AI13" s="38"/>
+      <c r="AJ13" s="42"/>
       <c r="AK13" s="94"/>
     </row>
     <row r="14" spans="1:181" ht="12.75" customHeight="1">
       <c r="A14" s="93"/>
-      <c r="B14" s="170"/>
-      <c r="C14" s="170"/>
-      <c r="D14" s="170"/>
-      <c r="E14" s="170"/>
-      <c r="F14" s="170"/>
-      <c r="G14" s="110" t="s">
+      <c r="B14" s="38"/>
+      <c r="C14" s="38"/>
+      <c r="D14" s="38"/>
+      <c r="E14" s="38"/>
+      <c r="F14" s="38"/>
+      <c r="G14" s="131" t="s">
         <v>87</v>
       </c>
-      <c r="H14" s="111"/>
-      <c r="I14" s="111"/>
-      <c r="J14" s="98"/>
-      <c r="K14" s="99"/>
-      <c r="L14" s="99"/>
-      <c r="M14" s="99"/>
-      <c r="N14" s="99"/>
-      <c r="O14" s="99"/>
-      <c r="P14" s="99"/>
-      <c r="Q14" s="99"/>
-      <c r="R14" s="100"/>
-      <c r="S14" s="98"/>
-      <c r="T14" s="99"/>
-      <c r="U14" s="100"/>
-      <c r="V14" s="98"/>
-      <c r="W14" s="99"/>
-      <c r="X14" s="99"/>
-      <c r="Y14" s="99"/>
-      <c r="Z14" s="99"/>
-      <c r="AA14" s="99"/>
-      <c r="AB14" s="99"/>
-      <c r="AC14" s="99"/>
-      <c r="AD14" s="100"/>
-      <c r="AE14" s="170"/>
-      <c r="AF14" s="170"/>
-      <c r="AG14" s="170"/>
-      <c r="AH14" s="170"/>
-      <c r="AI14" s="170"/>
-      <c r="AJ14" s="171"/>
+      <c r="H14" s="132"/>
+      <c r="I14" s="132"/>
+      <c r="J14" s="135"/>
+      <c r="K14" s="136"/>
+      <c r="L14" s="136"/>
+      <c r="M14" s="136"/>
+      <c r="N14" s="136"/>
+      <c r="O14" s="136"/>
+      <c r="P14" s="136"/>
+      <c r="Q14" s="136"/>
+      <c r="R14" s="137"/>
+      <c r="S14" s="135"/>
+      <c r="T14" s="136"/>
+      <c r="U14" s="137"/>
+      <c r="V14" s="135"/>
+      <c r="W14" s="136"/>
+      <c r="X14" s="136"/>
+      <c r="Y14" s="136"/>
+      <c r="Z14" s="136"/>
+      <c r="AA14" s="136"/>
+      <c r="AB14" s="136"/>
+      <c r="AC14" s="136"/>
+      <c r="AD14" s="137"/>
+      <c r="AE14" s="38"/>
+      <c r="AF14" s="38"/>
+      <c r="AG14" s="38"/>
+      <c r="AH14" s="38"/>
+      <c r="AI14" s="38"/>
+      <c r="AJ14" s="42"/>
       <c r="AK14" s="94"/>
     </row>
     <row r="15" spans="1:181" ht="12.75" customHeight="1" thickBot="1">
       <c r="A15" s="93"/>
-      <c r="B15" s="170"/>
-      <c r="C15" s="170"/>
-      <c r="D15" s="170"/>
-      <c r="E15" s="170"/>
-      <c r="F15" s="170"/>
-      <c r="G15" s="112"/>
-      <c r="H15" s="113"/>
-      <c r="I15" s="113"/>
-      <c r="J15" s="101"/>
-      <c r="K15" s="102"/>
-      <c r="L15" s="102"/>
-      <c r="M15" s="102"/>
-      <c r="N15" s="102"/>
-      <c r="O15" s="102"/>
-      <c r="P15" s="102"/>
-      <c r="Q15" s="102"/>
-      <c r="R15" s="103"/>
-      <c r="S15" s="101"/>
-      <c r="T15" s="102"/>
-      <c r="U15" s="103"/>
-      <c r="V15" s="101"/>
-      <c r="W15" s="102"/>
-      <c r="X15" s="102"/>
-      <c r="Y15" s="102"/>
-      <c r="Z15" s="102"/>
-      <c r="AA15" s="102"/>
-      <c r="AB15" s="102"/>
-      <c r="AC15" s="102"/>
-      <c r="AD15" s="103"/>
-      <c r="AE15" s="170"/>
-      <c r="AF15" s="170"/>
-      <c r="AG15" s="170"/>
-      <c r="AH15" s="170"/>
-      <c r="AI15" s="170"/>
-      <c r="AJ15" s="171"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="38"/>
+      <c r="D15" s="38"/>
+      <c r="E15" s="38"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="133"/>
+      <c r="H15" s="134"/>
+      <c r="I15" s="134"/>
+      <c r="J15" s="138"/>
+      <c r="K15" s="139"/>
+      <c r="L15" s="139"/>
+      <c r="M15" s="139"/>
+      <c r="N15" s="139"/>
+      <c r="O15" s="139"/>
+      <c r="P15" s="139"/>
+      <c r="Q15" s="139"/>
+      <c r="R15" s="140"/>
+      <c r="S15" s="138"/>
+      <c r="T15" s="139"/>
+      <c r="U15" s="140"/>
+      <c r="V15" s="138"/>
+      <c r="W15" s="139"/>
+      <c r="X15" s="139"/>
+      <c r="Y15" s="139"/>
+      <c r="Z15" s="139"/>
+      <c r="AA15" s="139"/>
+      <c r="AB15" s="139"/>
+      <c r="AC15" s="139"/>
+      <c r="AD15" s="140"/>
+      <c r="AE15" s="38"/>
+      <c r="AF15" s="38"/>
+      <c r="AG15" s="38"/>
+      <c r="AH15" s="38"/>
+      <c r="AI15" s="38"/>
+      <c r="AJ15" s="42"/>
       <c r="AK15" s="94"/>
     </row>
     <row r="16" spans="1:181" ht="12.75" customHeight="1">
       <c r="A16" s="93"/>
-      <c r="B16" s="170"/>
-      <c r="C16" s="170"/>
-      <c r="D16" s="170"/>
-      <c r="E16" s="170"/>
-      <c r="F16" s="170"/>
-      <c r="G16" s="174"/>
-      <c r="H16" s="174"/>
-      <c r="I16" s="174"/>
-      <c r="J16" s="175"/>
-      <c r="K16" s="170"/>
-      <c r="L16" s="170"/>
-      <c r="M16" s="170"/>
-      <c r="N16" s="170"/>
-      <c r="O16" s="170"/>
-      <c r="P16" s="170"/>
-      <c r="Q16" s="170"/>
-      <c r="R16" s="170"/>
-      <c r="S16" s="174"/>
-      <c r="T16" s="174"/>
-      <c r="U16" s="174"/>
-      <c r="V16" s="174"/>
-      <c r="W16" s="174"/>
-      <c r="X16" s="174"/>
-      <c r="Y16" s="174"/>
-      <c r="Z16" s="174"/>
-      <c r="AA16" s="174"/>
-      <c r="AB16" s="174"/>
-      <c r="AC16" s="174"/>
-      <c r="AD16" s="174"/>
-      <c r="AE16" s="170"/>
-      <c r="AF16" s="170"/>
-      <c r="AG16" s="170"/>
-      <c r="AH16" s="170"/>
-      <c r="AI16" s="170"/>
-      <c r="AJ16" s="171"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="38"/>
+      <c r="D16" s="38"/>
+      <c r="E16" s="38"/>
+      <c r="F16" s="38"/>
+      <c r="G16" s="153"/>
+      <c r="H16" s="153"/>
+      <c r="I16" s="153"/>
+      <c r="J16" s="44"/>
+      <c r="K16" s="38"/>
+      <c r="L16" s="38"/>
+      <c r="M16" s="38"/>
+      <c r="N16" s="38"/>
+      <c r="O16" s="38"/>
+      <c r="P16" s="38"/>
+      <c r="Q16" s="38"/>
+      <c r="R16" s="38"/>
+      <c r="S16" s="153"/>
+      <c r="T16" s="153"/>
+      <c r="U16" s="153"/>
+      <c r="V16" s="153"/>
+      <c r="W16" s="153"/>
+      <c r="X16" s="153"/>
+      <c r="Y16" s="153"/>
+      <c r="Z16" s="153"/>
+      <c r="AA16" s="153"/>
+      <c r="AB16" s="153"/>
+      <c r="AC16" s="153"/>
+      <c r="AD16" s="153"/>
+      <c r="AE16" s="38"/>
+      <c r="AF16" s="38"/>
+      <c r="AG16" s="38"/>
+      <c r="AH16" s="38"/>
+      <c r="AI16" s="38"/>
+      <c r="AJ16" s="42"/>
       <c r="AK16" s="94"/>
     </row>
     <row r="17" spans="1:37" ht="12.75" customHeight="1">
       <c r="A17" s="93"/>
-      <c r="B17" s="170"/>
-      <c r="C17" s="170"/>
-      <c r="D17" s="170"/>
-      <c r="E17" s="170"/>
-      <c r="F17" s="170"/>
-      <c r="G17" s="174"/>
-      <c r="H17" s="174"/>
-      <c r="I17" s="174"/>
-      <c r="J17" s="175"/>
-      <c r="K17" s="170"/>
-      <c r="L17" s="170"/>
-      <c r="M17" s="170"/>
-      <c r="N17" s="170"/>
-      <c r="O17" s="170"/>
-      <c r="P17" s="170"/>
-      <c r="Q17" s="170"/>
-      <c r="R17" s="170"/>
-      <c r="S17" s="174"/>
-      <c r="T17" s="174"/>
-      <c r="U17" s="174"/>
-      <c r="V17" s="174"/>
-      <c r="W17" s="174"/>
-      <c r="X17" s="174"/>
-      <c r="Y17" s="174"/>
-      <c r="Z17" s="174"/>
-      <c r="AA17" s="174"/>
-      <c r="AB17" s="174"/>
-      <c r="AC17" s="174"/>
-      <c r="AD17" s="174"/>
-      <c r="AE17" s="170"/>
-      <c r="AF17" s="170"/>
-      <c r="AG17" s="170"/>
-      <c r="AH17" s="170"/>
-      <c r="AI17" s="170"/>
-      <c r="AJ17" s="171"/>
+      <c r="B17" s="38"/>
+      <c r="C17" s="38"/>
+      <c r="D17" s="38"/>
+      <c r="E17" s="38"/>
+      <c r="F17" s="38"/>
+      <c r="G17" s="153"/>
+      <c r="H17" s="153"/>
+      <c r="I17" s="153"/>
+      <c r="J17" s="44"/>
+      <c r="K17" s="38"/>
+      <c r="L17" s="38"/>
+      <c r="M17" s="38"/>
+      <c r="N17" s="38"/>
+      <c r="O17" s="38"/>
+      <c r="P17" s="38"/>
+      <c r="Q17" s="38"/>
+      <c r="R17" s="38"/>
+      <c r="S17" s="153"/>
+      <c r="T17" s="153"/>
+      <c r="U17" s="153"/>
+      <c r="V17" s="153"/>
+      <c r="W17" s="153"/>
+      <c r="X17" s="153"/>
+      <c r="Y17" s="153"/>
+      <c r="Z17" s="153"/>
+      <c r="AA17" s="153"/>
+      <c r="AB17" s="153"/>
+      <c r="AC17" s="153"/>
+      <c r="AD17" s="153"/>
+      <c r="AE17" s="38"/>
+      <c r="AF17" s="38"/>
+      <c r="AG17" s="38"/>
+      <c r="AH17" s="38"/>
+      <c r="AI17" s="38"/>
+      <c r="AJ17" s="42"/>
       <c r="AK17" s="94"/>
     </row>
     <row r="18" spans="1:37" ht="12.75" customHeight="1">
       <c r="A18" s="93"/>
-      <c r="B18" s="170"/>
-      <c r="C18" s="170"/>
-      <c r="D18" s="170"/>
-      <c r="E18" s="170"/>
-      <c r="F18" s="170"/>
-      <c r="G18" s="170"/>
-      <c r="H18" s="170"/>
-      <c r="I18" s="170"/>
-      <c r="J18" s="175"/>
-      <c r="K18" s="170"/>
-      <c r="L18" s="170"/>
-      <c r="M18" s="170"/>
-      <c r="N18" s="170"/>
-      <c r="O18" s="170"/>
-      <c r="P18" s="170"/>
-      <c r="Q18" s="170"/>
-      <c r="R18" s="170"/>
-      <c r="S18" s="170"/>
-      <c r="T18" s="170"/>
-      <c r="U18" s="170"/>
-      <c r="V18" s="170"/>
-      <c r="W18" s="175"/>
-      <c r="X18" s="170"/>
-      <c r="Y18" s="170"/>
-      <c r="Z18" s="175"/>
-      <c r="AA18" s="170"/>
-      <c r="AB18" s="170"/>
-      <c r="AC18" s="170"/>
-      <c r="AD18" s="170"/>
-      <c r="AE18" s="170"/>
-      <c r="AF18" s="170"/>
-      <c r="AG18" s="170"/>
-      <c r="AH18" s="170"/>
-      <c r="AI18" s="170"/>
-      <c r="AJ18" s="171"/>
+      <c r="B18" s="38"/>
+      <c r="C18" s="38"/>
+      <c r="D18" s="38"/>
+      <c r="E18" s="38"/>
+      <c r="F18" s="38"/>
+      <c r="G18" s="38"/>
+      <c r="H18" s="38"/>
+      <c r="I18" s="38"/>
+      <c r="J18" s="44"/>
+      <c r="K18" s="38"/>
+      <c r="L18" s="38"/>
+      <c r="M18" s="38"/>
+      <c r="N18" s="38"/>
+      <c r="O18" s="38"/>
+      <c r="P18" s="38"/>
+      <c r="Q18" s="38"/>
+      <c r="R18" s="38"/>
+      <c r="S18" s="38"/>
+      <c r="T18" s="38"/>
+      <c r="U18" s="38"/>
+      <c r="V18" s="38"/>
+      <c r="W18" s="44"/>
+      <c r="X18" s="38"/>
+      <c r="Y18" s="38"/>
+      <c r="Z18" s="44"/>
+      <c r="AA18" s="38"/>
+      <c r="AB18" s="38"/>
+      <c r="AC18" s="38"/>
+      <c r="AD18" s="38"/>
+      <c r="AE18" s="38"/>
+      <c r="AF18" s="38"/>
+      <c r="AG18" s="38"/>
+      <c r="AH18" s="38"/>
+      <c r="AI18" s="38"/>
+      <c r="AJ18" s="42"/>
       <c r="AK18" s="94"/>
     </row>
     <row r="19" spans="1:37" ht="12.75" customHeight="1">
       <c r="A19" s="93"/>
-      <c r="B19" s="170"/>
-      <c r="C19" s="170"/>
-      <c r="D19" s="170"/>
-      <c r="E19" s="170"/>
-      <c r="F19" s="170"/>
-      <c r="G19" s="170"/>
-      <c r="H19" s="170"/>
-      <c r="I19" s="170"/>
-      <c r="J19" s="175"/>
-      <c r="K19" s="170"/>
-      <c r="L19" s="170"/>
-      <c r="M19" s="170"/>
-      <c r="N19" s="170"/>
-      <c r="O19" s="170"/>
-      <c r="P19" s="170"/>
-      <c r="Q19" s="170"/>
-      <c r="R19" s="170"/>
-      <c r="S19" s="170"/>
-      <c r="T19" s="170"/>
-      <c r="U19" s="170"/>
-      <c r="V19" s="170"/>
-      <c r="W19" s="175"/>
-      <c r="X19" s="170"/>
-      <c r="Y19" s="170"/>
-      <c r="Z19" s="175"/>
-      <c r="AA19" s="170"/>
-      <c r="AB19" s="170"/>
-      <c r="AC19" s="170"/>
-      <c r="AD19" s="170"/>
-      <c r="AE19" s="170"/>
-      <c r="AF19" s="170"/>
-      <c r="AG19" s="170"/>
-      <c r="AH19" s="170"/>
-      <c r="AI19" s="170"/>
-      <c r="AJ19" s="171"/>
+      <c r="B19" s="38"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="38"/>
+      <c r="E19" s="38"/>
+      <c r="F19" s="38"/>
+      <c r="G19" s="38"/>
+      <c r="H19" s="38"/>
+      <c r="I19" s="38"/>
+      <c r="J19" s="44"/>
+      <c r="K19" s="38"/>
+      <c r="L19" s="38"/>
+      <c r="M19" s="38"/>
+      <c r="N19" s="38"/>
+      <c r="O19" s="38"/>
+      <c r="P19" s="38"/>
+      <c r="Q19" s="38"/>
+      <c r="R19" s="38"/>
+      <c r="S19" s="38"/>
+      <c r="T19" s="38"/>
+      <c r="U19" s="38"/>
+      <c r="V19" s="38"/>
+      <c r="W19" s="44"/>
+      <c r="X19" s="38"/>
+      <c r="Y19" s="38"/>
+      <c r="Z19" s="44"/>
+      <c r="AA19" s="38"/>
+      <c r="AB19" s="38"/>
+      <c r="AC19" s="38"/>
+      <c r="AD19" s="38"/>
+      <c r="AE19" s="38"/>
+      <c r="AF19" s="38"/>
+      <c r="AG19" s="38"/>
+      <c r="AH19" s="38"/>
+      <c r="AI19" s="38"/>
+      <c r="AJ19" s="42"/>
       <c r="AK19" s="94"/>
     </row>
     <row r="20" spans="1:37" ht="12.75" customHeight="1">
       <c r="A20" s="93"/>
-      <c r="B20" s="170"/>
-      <c r="C20" s="170"/>
-      <c r="D20" s="170"/>
-      <c r="E20" s="170"/>
-      <c r="F20" s="170"/>
-      <c r="G20" s="170"/>
-      <c r="H20" s="170"/>
-      <c r="I20" s="170"/>
-      <c r="J20" s="175"/>
-      <c r="K20" s="170"/>
-      <c r="L20" s="170"/>
-      <c r="M20" s="170"/>
-      <c r="N20" s="170"/>
-      <c r="O20" s="170"/>
-      <c r="P20" s="170"/>
-      <c r="Q20" s="170"/>
-      <c r="R20" s="170"/>
-      <c r="S20" s="170"/>
-      <c r="T20" s="175"/>
-      <c r="U20" s="170"/>
-      <c r="V20" s="170"/>
-      <c r="W20" s="175"/>
-      <c r="X20" s="170"/>
-      <c r="Y20" s="170"/>
-      <c r="Z20" s="175"/>
-      <c r="AA20" s="170"/>
-      <c r="AB20" s="170"/>
-      <c r="AC20" s="170"/>
-      <c r="AD20" s="170"/>
-      <c r="AE20" s="170"/>
-      <c r="AF20" s="170"/>
-      <c r="AG20" s="170"/>
-      <c r="AH20" s="170"/>
-      <c r="AI20" s="170"/>
-      <c r="AJ20" s="171"/>
+      <c r="B20" s="38"/>
+      <c r="C20" s="38"/>
+      <c r="D20" s="38"/>
+      <c r="E20" s="38"/>
+      <c r="F20" s="38"/>
+      <c r="G20" s="38"/>
+      <c r="H20" s="38"/>
+      <c r="I20" s="38"/>
+      <c r="J20" s="44"/>
+      <c r="K20" s="38"/>
+      <c r="L20" s="38"/>
+      <c r="M20" s="38"/>
+      <c r="N20" s="38"/>
+      <c r="O20" s="38"/>
+      <c r="P20" s="38"/>
+      <c r="Q20" s="38"/>
+      <c r="R20" s="38"/>
+      <c r="S20" s="38"/>
+      <c r="T20" s="44"/>
+      <c r="U20" s="38"/>
+      <c r="V20" s="38"/>
+      <c r="W20" s="44"/>
+      <c r="X20" s="38"/>
+      <c r="Y20" s="38"/>
+      <c r="Z20" s="44"/>
+      <c r="AA20" s="38"/>
+      <c r="AB20" s="38"/>
+      <c r="AC20" s="38"/>
+      <c r="AD20" s="38"/>
+      <c r="AE20" s="38"/>
+      <c r="AF20" s="38"/>
+      <c r="AG20" s="38"/>
+      <c r="AH20" s="38"/>
+      <c r="AI20" s="38"/>
+      <c r="AJ20" s="42"/>
       <c r="AK20" s="94"/>
     </row>
     <row r="21" spans="1:37" ht="12.75" customHeight="1">
       <c r="A21" s="93"/>
-      <c r="B21" s="170"/>
-      <c r="C21" s="170"/>
-      <c r="D21" s="170"/>
-      <c r="E21" s="170"/>
-      <c r="F21" s="170"/>
-      <c r="G21" s="170"/>
-      <c r="H21" s="170"/>
-      <c r="I21" s="170"/>
-      <c r="J21" s="175"/>
-      <c r="K21" s="170"/>
-      <c r="L21" s="170"/>
-      <c r="M21" s="170"/>
-      <c r="N21" s="170"/>
-      <c r="O21" s="170"/>
-      <c r="P21" s="170"/>
-      <c r="Q21" s="170"/>
-      <c r="R21" s="170"/>
-      <c r="S21" s="170"/>
-      <c r="T21" s="175"/>
-      <c r="U21" s="170"/>
-      <c r="V21" s="170"/>
-      <c r="W21" s="175"/>
-      <c r="X21" s="170"/>
-      <c r="Y21" s="170"/>
-      <c r="Z21" s="175"/>
-      <c r="AA21" s="170"/>
-      <c r="AB21" s="170"/>
-      <c r="AC21" s="170"/>
-      <c r="AD21" s="170"/>
-      <c r="AE21" s="170"/>
-      <c r="AF21" s="170"/>
-      <c r="AG21" s="170"/>
-      <c r="AH21" s="170"/>
-      <c r="AI21" s="170"/>
-      <c r="AJ21" s="171"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="38"/>
+      <c r="D21" s="38"/>
+      <c r="E21" s="38"/>
+      <c r="F21" s="38"/>
+      <c r="G21" s="38"/>
+      <c r="H21" s="38"/>
+      <c r="I21" s="38"/>
+      <c r="J21" s="44"/>
+      <c r="K21" s="38"/>
+      <c r="L21" s="38"/>
+      <c r="M21" s="38"/>
+      <c r="N21" s="38"/>
+      <c r="O21" s="38"/>
+      <c r="P21" s="38"/>
+      <c r="Q21" s="38"/>
+      <c r="R21" s="38"/>
+      <c r="S21" s="38"/>
+      <c r="T21" s="44"/>
+      <c r="U21" s="38"/>
+      <c r="V21" s="38"/>
+      <c r="W21" s="44"/>
+      <c r="X21" s="38"/>
+      <c r="Y21" s="38"/>
+      <c r="Z21" s="44"/>
+      <c r="AA21" s="38"/>
+      <c r="AB21" s="38"/>
+      <c r="AC21" s="38"/>
+      <c r="AD21" s="38"/>
+      <c r="AE21" s="38"/>
+      <c r="AF21" s="38"/>
+      <c r="AG21" s="38"/>
+      <c r="AH21" s="38"/>
+      <c r="AI21" s="38"/>
+      <c r="AJ21" s="42"/>
       <c r="AK21" s="94"/>
     </row>
     <row r="22" spans="1:37" ht="12.75" customHeight="1">
       <c r="A22" s="93"/>
-      <c r="B22" s="170"/>
-      <c r="C22" s="170"/>
-      <c r="D22" s="170"/>
-      <c r="E22" s="170"/>
-      <c r="F22" s="170"/>
-      <c r="G22" s="170"/>
-      <c r="H22" s="170"/>
-      <c r="I22" s="170"/>
-      <c r="J22" s="175"/>
-      <c r="K22" s="170"/>
-      <c r="L22" s="170"/>
-      <c r="M22" s="170"/>
-      <c r="N22" s="170"/>
-      <c r="O22" s="170"/>
-      <c r="P22" s="170"/>
-      <c r="Q22" s="170"/>
-      <c r="R22" s="170"/>
-      <c r="S22" s="170"/>
-      <c r="T22" s="175"/>
-      <c r="U22" s="170"/>
-      <c r="V22" s="170"/>
-      <c r="W22" s="175"/>
-      <c r="X22" s="170"/>
-      <c r="Y22" s="170"/>
-      <c r="Z22" s="175"/>
-      <c r="AA22" s="170"/>
-      <c r="AB22" s="170"/>
-      <c r="AC22" s="170"/>
-      <c r="AD22" s="170"/>
-      <c r="AE22" s="170"/>
-      <c r="AF22" s="170"/>
-      <c r="AG22" s="170"/>
-      <c r="AH22" s="170"/>
-      <c r="AI22" s="170"/>
-      <c r="AJ22" s="171"/>
+      <c r="B22" s="38"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="38"/>
+      <c r="E22" s="38"/>
+      <c r="F22" s="38"/>
+      <c r="G22" s="38"/>
+      <c r="H22" s="38"/>
+      <c r="I22" s="38"/>
+      <c r="J22" s="44"/>
+      <c r="K22" s="38"/>
+      <c r="L22" s="38"/>
+      <c r="M22" s="38"/>
+      <c r="N22" s="38"/>
+      <c r="O22" s="38"/>
+      <c r="P22" s="38"/>
+      <c r="Q22" s="38"/>
+      <c r="R22" s="38"/>
+      <c r="S22" s="38"/>
+      <c r="T22" s="44"/>
+      <c r="U22" s="38"/>
+      <c r="V22" s="38"/>
+      <c r="W22" s="44"/>
+      <c r="X22" s="38"/>
+      <c r="Y22" s="38"/>
+      <c r="Z22" s="44"/>
+      <c r="AA22" s="38"/>
+      <c r="AB22" s="38"/>
+      <c r="AC22" s="38"/>
+      <c r="AD22" s="38"/>
+      <c r="AE22" s="38"/>
+      <c r="AF22" s="38"/>
+      <c r="AG22" s="38"/>
+      <c r="AH22" s="38"/>
+      <c r="AI22" s="38"/>
+      <c r="AJ22" s="42"/>
       <c r="AK22" s="94"/>
     </row>
     <row r="23" spans="1:37" ht="12.75" customHeight="1">
       <c r="A23" s="93"/>
-      <c r="B23" s="170"/>
-      <c r="C23" s="170"/>
-      <c r="D23" s="170"/>
-      <c r="E23" s="170"/>
-      <c r="F23" s="170"/>
-      <c r="G23" s="170"/>
-      <c r="H23" s="170"/>
-      <c r="I23" s="175"/>
-      <c r="J23" s="175"/>
-      <c r="K23" s="170"/>
-      <c r="L23" s="170"/>
-      <c r="M23" s="170"/>
-      <c r="N23" s="170"/>
-      <c r="O23" s="170"/>
-      <c r="P23" s="170"/>
-      <c r="Q23" s="170"/>
-      <c r="R23" s="170"/>
-      <c r="S23" s="170"/>
-      <c r="T23" s="175"/>
-      <c r="U23" s="170"/>
-      <c r="V23" s="170"/>
-      <c r="W23" s="175"/>
-      <c r="X23" s="170"/>
-      <c r="Y23" s="170"/>
-      <c r="Z23" s="175"/>
-      <c r="AA23" s="170"/>
-      <c r="AB23" s="170"/>
-      <c r="AC23" s="170"/>
-      <c r="AD23" s="170"/>
-      <c r="AE23" s="170"/>
-      <c r="AF23" s="170"/>
-      <c r="AG23" s="170"/>
-      <c r="AH23" s="170"/>
-      <c r="AI23" s="170"/>
-      <c r="AJ23" s="171"/>
+      <c r="B23" s="38"/>
+      <c r="C23" s="38"/>
+      <c r="D23" s="38"/>
+      <c r="E23" s="38"/>
+      <c r="F23" s="38"/>
+      <c r="G23" s="38"/>
+      <c r="H23" s="38"/>
+      <c r="I23" s="44"/>
+      <c r="J23" s="44"/>
+      <c r="K23" s="38"/>
+      <c r="L23" s="38"/>
+      <c r="M23" s="38"/>
+      <c r="N23" s="38"/>
+      <c r="O23" s="38"/>
+      <c r="P23" s="38"/>
+      <c r="Q23" s="38"/>
+      <c r="R23" s="38"/>
+      <c r="S23" s="38"/>
+      <c r="T23" s="44"/>
+      <c r="U23" s="38"/>
+      <c r="V23" s="38"/>
+      <c r="W23" s="44"/>
+      <c r="X23" s="38"/>
+      <c r="Y23" s="38"/>
+      <c r="Z23" s="44"/>
+      <c r="AA23" s="38"/>
+      <c r="AB23" s="38"/>
+      <c r="AC23" s="38"/>
+      <c r="AD23" s="38"/>
+      <c r="AE23" s="38"/>
+      <c r="AF23" s="38"/>
+      <c r="AG23" s="38"/>
+      <c r="AH23" s="38"/>
+      <c r="AI23" s="38"/>
+      <c r="AJ23" s="42"/>
       <c r="AK23" s="94"/>
     </row>
     <row r="24" spans="1:37" ht="12.75" customHeight="1">
       <c r="A24" s="93"/>
-      <c r="B24" s="170"/>
-      <c r="C24" s="170"/>
-      <c r="D24" s="170"/>
-      <c r="E24" s="170"/>
-      <c r="F24" s="170"/>
-      <c r="G24" s="170"/>
-      <c r="H24" s="170"/>
-      <c r="I24" s="175"/>
-      <c r="J24" s="175"/>
-      <c r="K24" s="170"/>
-      <c r="L24" s="170"/>
-      <c r="M24" s="170"/>
-      <c r="N24" s="170"/>
-      <c r="O24" s="170"/>
-      <c r="P24" s="170"/>
-      <c r="Q24" s="170"/>
-      <c r="R24" s="170"/>
-      <c r="S24" s="170"/>
-      <c r="T24" s="175"/>
-      <c r="U24" s="170"/>
-      <c r="V24" s="170"/>
-      <c r="W24" s="175"/>
-      <c r="X24" s="170"/>
-      <c r="Y24" s="170"/>
-      <c r="Z24" s="175"/>
-      <c r="AA24" s="170"/>
-      <c r="AB24" s="170"/>
-      <c r="AC24" s="170"/>
-      <c r="AD24" s="170"/>
-      <c r="AE24" s="170"/>
-      <c r="AF24" s="170"/>
-      <c r="AG24" s="170"/>
-      <c r="AH24" s="170"/>
-      <c r="AI24" s="170"/>
-      <c r="AJ24" s="171"/>
+      <c r="B24" s="38"/>
+      <c r="C24" s="38"/>
+      <c r="D24" s="38"/>
+      <c r="E24" s="38"/>
+      <c r="F24" s="38"/>
+      <c r="G24" s="38"/>
+      <c r="H24" s="38"/>
+      <c r="I24" s="44"/>
+      <c r="J24" s="44"/>
+      <c r="K24" s="38"/>
+      <c r="L24" s="38"/>
+      <c r="M24" s="38"/>
+      <c r="N24" s="38"/>
+      <c r="O24" s="38"/>
+      <c r="P24" s="38"/>
+      <c r="Q24" s="38"/>
+      <c r="R24" s="38"/>
+      <c r="S24" s="38"/>
+      <c r="T24" s="44"/>
+      <c r="U24" s="38"/>
+      <c r="V24" s="38"/>
+      <c r="W24" s="44"/>
+      <c r="X24" s="38"/>
+      <c r="Y24" s="38"/>
+      <c r="Z24" s="44"/>
+      <c r="AA24" s="38"/>
+      <c r="AB24" s="38"/>
+      <c r="AC24" s="38"/>
+      <c r="AD24" s="38"/>
+      <c r="AE24" s="38"/>
+      <c r="AF24" s="38"/>
+      <c r="AG24" s="38"/>
+      <c r="AH24" s="38"/>
+      <c r="AI24" s="38"/>
+      <c r="AJ24" s="42"/>
       <c r="AK24" s="94"/>
     </row>
     <row r="25" spans="1:37" ht="12.75" customHeight="1">
       <c r="A25" s="93"/>
-      <c r="B25" s="170"/>
-      <c r="C25" s="170"/>
-      <c r="D25" s="170"/>
-      <c r="E25" s="170"/>
-      <c r="F25" s="170"/>
-      <c r="G25" s="170"/>
-      <c r="H25" s="170"/>
-      <c r="I25" s="175"/>
-      <c r="J25" s="175"/>
-      <c r="K25" s="170"/>
-      <c r="L25" s="170"/>
-      <c r="M25" s="170"/>
-      <c r="N25" s="170"/>
-      <c r="O25" s="170"/>
-      <c r="P25" s="170"/>
-      <c r="Q25" s="170"/>
-      <c r="R25" s="170"/>
-      <c r="S25" s="170"/>
-      <c r="T25" s="175"/>
-      <c r="U25" s="170"/>
-      <c r="V25" s="170"/>
-      <c r="W25" s="175"/>
-      <c r="X25" s="170"/>
-      <c r="Y25" s="170"/>
-      <c r="Z25" s="175"/>
-      <c r="AA25" s="170"/>
-      <c r="AB25" s="170"/>
-      <c r="AC25" s="170"/>
-      <c r="AD25" s="170"/>
-      <c r="AE25" s="170"/>
-      <c r="AF25" s="170"/>
-      <c r="AG25" s="170"/>
-      <c r="AH25" s="170"/>
-      <c r="AI25" s="170"/>
-      <c r="AJ25" s="171"/>
+      <c r="B25" s="38"/>
+      <c r="C25" s="38"/>
+      <c r="D25" s="38"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="38"/>
+      <c r="G25" s="38"/>
+      <c r="H25" s="38"/>
+      <c r="I25" s="44"/>
+      <c r="J25" s="44"/>
+      <c r="K25" s="38"/>
+      <c r="L25" s="38"/>
+      <c r="M25" s="38"/>
+      <c r="N25" s="38"/>
+      <c r="O25" s="38"/>
+      <c r="P25" s="38"/>
+      <c r="Q25" s="38"/>
+      <c r="R25" s="38"/>
+      <c r="S25" s="38"/>
+      <c r="T25" s="44"/>
+      <c r="U25" s="38"/>
+      <c r="V25" s="38"/>
+      <c r="W25" s="44"/>
+      <c r="X25" s="38"/>
+      <c r="Y25" s="38"/>
+      <c r="Z25" s="44"/>
+      <c r="AA25" s="38"/>
+      <c r="AB25" s="38"/>
+      <c r="AC25" s="38"/>
+      <c r="AD25" s="38"/>
+      <c r="AE25" s="38"/>
+      <c r="AF25" s="38"/>
+      <c r="AG25" s="38"/>
+      <c r="AH25" s="38"/>
+      <c r="AI25" s="38"/>
+      <c r="AJ25" s="42"/>
       <c r="AK25" s="94"/>
     </row>
     <row r="26" spans="1:37" ht="12.75" customHeight="1">
       <c r="A26" s="93"/>
-      <c r="B26" s="170"/>
-      <c r="C26" s="170"/>
-      <c r="D26" s="170"/>
-      <c r="E26" s="170"/>
-      <c r="F26" s="170"/>
-      <c r="G26" s="170"/>
-      <c r="H26" s="170"/>
-      <c r="I26" s="175"/>
-      <c r="J26" s="175"/>
-      <c r="K26" s="170"/>
-      <c r="L26" s="170"/>
-      <c r="M26" s="170"/>
-      <c r="N26" s="170"/>
-      <c r="O26" s="170"/>
-      <c r="P26" s="170"/>
-      <c r="Q26" s="170"/>
-      <c r="R26" s="170"/>
-      <c r="S26" s="170"/>
-      <c r="T26" s="175"/>
-      <c r="U26" s="170"/>
-      <c r="V26" s="170"/>
-      <c r="W26" s="175"/>
-      <c r="X26" s="170"/>
-      <c r="Y26" s="170"/>
-      <c r="Z26" s="175"/>
-      <c r="AA26" s="170"/>
-      <c r="AB26" s="170"/>
-      <c r="AC26" s="170"/>
-      <c r="AD26" s="170"/>
-      <c r="AE26" s="170"/>
-      <c r="AF26" s="170"/>
-      <c r="AG26" s="170"/>
-      <c r="AH26" s="170"/>
-      <c r="AI26" s="170"/>
-      <c r="AJ26" s="171"/>
+      <c r="B26" s="38"/>
+      <c r="C26" s="38"/>
+      <c r="D26" s="38"/>
+      <c r="E26" s="38"/>
+      <c r="F26" s="38"/>
+      <c r="G26" s="38"/>
+      <c r="H26" s="38"/>
+      <c r="I26" s="44"/>
+      <c r="J26" s="44"/>
+      <c r="K26" s="38"/>
+      <c r="L26" s="38"/>
+      <c r="M26" s="38"/>
+      <c r="N26" s="38"/>
+      <c r="O26" s="38"/>
+      <c r="P26" s="38"/>
+      <c r="Q26" s="38"/>
+      <c r="R26" s="38"/>
+      <c r="S26" s="38"/>
+      <c r="T26" s="44"/>
+      <c r="U26" s="38"/>
+      <c r="V26" s="38"/>
+      <c r="W26" s="44"/>
+      <c r="X26" s="38"/>
+      <c r="Y26" s="38"/>
+      <c r="Z26" s="44"/>
+      <c r="AA26" s="38"/>
+      <c r="AB26" s="38"/>
+      <c r="AC26" s="38"/>
+      <c r="AD26" s="38"/>
+      <c r="AE26" s="38"/>
+      <c r="AF26" s="38"/>
+      <c r="AG26" s="38"/>
+      <c r="AH26" s="38"/>
+      <c r="AI26" s="38"/>
+      <c r="AJ26" s="42"/>
       <c r="AK26" s="94"/>
     </row>
     <row r="27" spans="1:37" ht="12.75" customHeight="1">
       <c r="A27" s="93"/>
-      <c r="B27" s="170"/>
-      <c r="C27" s="170"/>
-      <c r="D27" s="170"/>
-      <c r="E27" s="170"/>
-      <c r="F27" s="170"/>
-      <c r="G27" s="170"/>
-      <c r="H27" s="170"/>
-      <c r="I27" s="175"/>
-      <c r="J27" s="175"/>
-      <c r="K27" s="170"/>
-      <c r="L27" s="170"/>
-      <c r="M27" s="170"/>
-      <c r="N27" s="170"/>
-      <c r="O27" s="170"/>
-      <c r="P27" s="170"/>
-      <c r="Q27" s="170"/>
-      <c r="R27" s="170"/>
-      <c r="S27" s="170"/>
-      <c r="T27" s="175"/>
-      <c r="U27" s="170"/>
-      <c r="V27" s="170"/>
-      <c r="W27" s="175"/>
-      <c r="X27" s="170"/>
-      <c r="Y27" s="170"/>
-      <c r="Z27" s="175"/>
-      <c r="AA27" s="170"/>
-      <c r="AB27" s="170"/>
-      <c r="AC27" s="170"/>
-      <c r="AD27" s="170"/>
-      <c r="AE27" s="170"/>
-      <c r="AF27" s="170"/>
-      <c r="AG27" s="170"/>
-      <c r="AH27" s="170"/>
-      <c r="AI27" s="170"/>
-      <c r="AJ27" s="171"/>
+      <c r="B27" s="38"/>
+      <c r="C27" s="38"/>
+      <c r="D27" s="38"/>
+      <c r="E27" s="38"/>
+      <c r="F27" s="38"/>
+      <c r="G27" s="38"/>
+      <c r="H27" s="38"/>
+      <c r="I27" s="44"/>
+      <c r="J27" s="44"/>
+      <c r="K27" s="38"/>
+      <c r="L27" s="38"/>
+      <c r="M27" s="38"/>
+      <c r="N27" s="38"/>
+      <c r="O27" s="38"/>
+      <c r="P27" s="38"/>
+      <c r="Q27" s="38"/>
+      <c r="R27" s="38"/>
+      <c r="S27" s="38"/>
+      <c r="T27" s="44"/>
+      <c r="U27" s="38"/>
+      <c r="V27" s="38"/>
+      <c r="W27" s="44"/>
+      <c r="X27" s="38"/>
+      <c r="Y27" s="38"/>
+      <c r="Z27" s="44"/>
+      <c r="AA27" s="38"/>
+      <c r="AB27" s="38"/>
+      <c r="AC27" s="38"/>
+      <c r="AD27" s="38"/>
+      <c r="AE27" s="38"/>
+      <c r="AF27" s="38"/>
+      <c r="AG27" s="38"/>
+      <c r="AH27" s="38"/>
+      <c r="AI27" s="38"/>
+      <c r="AJ27" s="42"/>
       <c r="AK27" s="94"/>
     </row>
     <row r="28" spans="1:37" ht="12.75" customHeight="1">
       <c r="A28" s="93"/>
-      <c r="B28" s="170"/>
-      <c r="C28" s="170"/>
-      <c r="D28" s="170"/>
-      <c r="E28" s="170"/>
-      <c r="F28" s="170"/>
-      <c r="G28" s="170"/>
-      <c r="H28" s="170"/>
-      <c r="I28" s="175"/>
-      <c r="J28" s="175"/>
-      <c r="K28" s="170"/>
-      <c r="L28" s="170"/>
-      <c r="M28" s="170"/>
-      <c r="N28" s="170"/>
-      <c r="O28" s="170"/>
-      <c r="P28" s="170"/>
-      <c r="Q28" s="170"/>
-      <c r="R28" s="170"/>
-      <c r="S28" s="170"/>
-      <c r="T28" s="175"/>
-      <c r="U28" s="170"/>
-      <c r="V28" s="170"/>
-      <c r="W28" s="175"/>
-      <c r="X28" s="170"/>
-      <c r="Y28" s="170"/>
-      <c r="Z28" s="175"/>
-      <c r="AA28" s="170"/>
-      <c r="AB28" s="170"/>
-      <c r="AC28" s="170"/>
-      <c r="AD28" s="170"/>
-      <c r="AE28" s="170"/>
-      <c r="AF28" s="170"/>
-      <c r="AG28" s="170"/>
-      <c r="AH28" s="170"/>
-      <c r="AI28" s="170"/>
-      <c r="AJ28" s="171"/>
+      <c r="B28" s="38"/>
+      <c r="C28" s="38"/>
+      <c r="D28" s="38"/>
+      <c r="E28" s="38"/>
+      <c r="F28" s="38"/>
+      <c r="G28" s="38"/>
+      <c r="H28" s="38"/>
+      <c r="I28" s="44"/>
+      <c r="J28" s="44"/>
+      <c r="K28" s="38"/>
+      <c r="L28" s="38"/>
+      <c r="M28" s="38"/>
+      <c r="N28" s="38"/>
+      <c r="O28" s="38"/>
+      <c r="P28" s="38"/>
+      <c r="Q28" s="38"/>
+      <c r="R28" s="38"/>
+      <c r="S28" s="38"/>
+      <c r="T28" s="44"/>
+      <c r="U28" s="38"/>
+      <c r="V28" s="38"/>
+      <c r="W28" s="44"/>
+      <c r="X28" s="38"/>
+      <c r="Y28" s="38"/>
+      <c r="Z28" s="44"/>
+      <c r="AA28" s="38"/>
+      <c r="AB28" s="38"/>
+      <c r="AC28" s="38"/>
+      <c r="AD28" s="38"/>
+      <c r="AE28" s="38"/>
+      <c r="AF28" s="38"/>
+      <c r="AG28" s="38"/>
+      <c r="AH28" s="38"/>
+      <c r="AI28" s="38"/>
+      <c r="AJ28" s="42"/>
       <c r="AK28" s="94"/>
     </row>
     <row r="29" spans="1:37" ht="12.75" customHeight="1">
       <c r="A29" s="93"/>
-      <c r="B29" s="170"/>
-      <c r="C29" s="170"/>
-      <c r="D29" s="170"/>
-      <c r="E29" s="170"/>
-      <c r="F29" s="170"/>
-      <c r="G29" s="170"/>
-      <c r="H29" s="170"/>
-      <c r="I29" s="175"/>
-      <c r="J29" s="175"/>
-      <c r="K29" s="170"/>
-      <c r="L29" s="170"/>
-      <c r="M29" s="170"/>
-      <c r="N29" s="170"/>
-      <c r="O29" s="170"/>
-      <c r="P29" s="170"/>
-      <c r="Q29" s="170"/>
-      <c r="R29" s="170"/>
-      <c r="S29" s="170"/>
-      <c r="T29" s="175"/>
-      <c r="U29" s="170"/>
-      <c r="V29" s="170"/>
-      <c r="W29" s="175"/>
-      <c r="X29" s="170"/>
-      <c r="Y29" s="170"/>
-      <c r="Z29" s="175"/>
-      <c r="AA29" s="170"/>
-      <c r="AB29" s="170"/>
-      <c r="AC29" s="170"/>
-      <c r="AD29" s="170"/>
-      <c r="AE29" s="170"/>
-      <c r="AF29" s="170"/>
-      <c r="AG29" s="170"/>
-      <c r="AH29" s="170"/>
-      <c r="AI29" s="170"/>
-      <c r="AJ29" s="171"/>
+      <c r="B29" s="38"/>
+      <c r="C29" s="38"/>
+      <c r="D29" s="38"/>
+      <c r="E29" s="38"/>
+      <c r="F29" s="38"/>
+      <c r="G29" s="38"/>
+      <c r="H29" s="38"/>
+      <c r="I29" s="44"/>
+      <c r="J29" s="44"/>
+      <c r="K29" s="38"/>
+      <c r="L29" s="38"/>
+      <c r="M29" s="38"/>
+      <c r="N29" s="38"/>
+      <c r="O29" s="38"/>
+      <c r="P29" s="38"/>
+      <c r="Q29" s="38"/>
+      <c r="R29" s="38"/>
+      <c r="S29" s="38"/>
+      <c r="T29" s="44"/>
+      <c r="U29" s="38"/>
+      <c r="V29" s="38"/>
+      <c r="W29" s="44"/>
+      <c r="X29" s="38"/>
+      <c r="Y29" s="38"/>
+      <c r="Z29" s="44"/>
+      <c r="AA29" s="38"/>
+      <c r="AB29" s="38"/>
+      <c r="AC29" s="38"/>
+      <c r="AD29" s="38"/>
+      <c r="AE29" s="38"/>
+      <c r="AF29" s="38"/>
+      <c r="AG29" s="38"/>
+      <c r="AH29" s="38"/>
+      <c r="AI29" s="38"/>
+      <c r="AJ29" s="42"/>
       <c r="AK29" s="94"/>
     </row>
     <row r="30" spans="1:37" ht="12.75" customHeight="1">
       <c r="A30" s="93"/>
-      <c r="B30" s="170"/>
-      <c r="C30" s="170"/>
-      <c r="D30" s="170"/>
-      <c r="E30" s="170"/>
-      <c r="F30" s="170"/>
-      <c r="G30" s="170"/>
-      <c r="H30" s="170"/>
-      <c r="I30" s="175"/>
-      <c r="J30" s="175"/>
-      <c r="K30" s="170"/>
-      <c r="L30" s="170"/>
-      <c r="M30" s="170"/>
-      <c r="N30" s="170"/>
-      <c r="O30" s="170"/>
-      <c r="P30" s="170"/>
-      <c r="Q30" s="170"/>
-      <c r="R30" s="170"/>
-      <c r="S30" s="170"/>
-      <c r="T30" s="175"/>
-      <c r="U30" s="170"/>
-      <c r="V30" s="170"/>
-      <c r="W30" s="175"/>
-      <c r="X30" s="170"/>
-      <c r="Y30" s="170"/>
-      <c r="Z30" s="175"/>
-      <c r="AA30" s="170"/>
-      <c r="AB30" s="170"/>
-      <c r="AC30" s="170"/>
-      <c r="AD30" s="170"/>
-      <c r="AE30" s="170"/>
-      <c r="AF30" s="170"/>
-      <c r="AG30" s="170"/>
-      <c r="AH30" s="170"/>
-      <c r="AI30" s="170"/>
-      <c r="AJ30" s="171"/>
+      <c r="B30" s="38"/>
+      <c r="C30" s="38"/>
+      <c r="D30" s="38"/>
+      <c r="E30" s="38"/>
+      <c r="F30" s="38"/>
+      <c r="G30" s="38"/>
+      <c r="H30" s="38"/>
+      <c r="I30" s="44"/>
+      <c r="J30" s="44"/>
+      <c r="K30" s="38"/>
+      <c r="L30" s="38"/>
+      <c r="M30" s="38"/>
+      <c r="N30" s="38"/>
+      <c r="O30" s="38"/>
+      <c r="P30" s="38"/>
+      <c r="Q30" s="38"/>
+      <c r="R30" s="38"/>
+      <c r="S30" s="38"/>
+      <c r="T30" s="44"/>
+      <c r="U30" s="38"/>
+      <c r="V30" s="38"/>
+      <c r="W30" s="44"/>
+      <c r="X30" s="38"/>
+      <c r="Y30" s="38"/>
+      <c r="Z30" s="44"/>
+      <c r="AA30" s="38"/>
+      <c r="AB30" s="38"/>
+      <c r="AC30" s="38"/>
+      <c r="AD30" s="38"/>
+      <c r="AE30" s="38"/>
+      <c r="AF30" s="38"/>
+      <c r="AG30" s="38"/>
+      <c r="AH30" s="38"/>
+      <c r="AI30" s="38"/>
+      <c r="AJ30" s="42"/>
       <c r="AK30" s="94"/>
     </row>
     <row r="31" spans="1:37" ht="12.75" customHeight="1">
       <c r="A31" s="93"/>
-      <c r="B31" s="170"/>
-      <c r="C31" s="170"/>
-      <c r="D31" s="170"/>
-      <c r="E31" s="170"/>
-      <c r="F31" s="170"/>
-      <c r="G31" s="170"/>
-      <c r="H31" s="170"/>
-      <c r="I31" s="175"/>
-      <c r="J31" s="175"/>
-      <c r="K31" s="170"/>
-      <c r="L31" s="170"/>
-      <c r="M31" s="170"/>
-      <c r="N31" s="170"/>
-      <c r="O31" s="170"/>
-      <c r="P31" s="170"/>
-      <c r="Q31" s="170"/>
-      <c r="R31" s="170"/>
-      <c r="S31" s="170"/>
-      <c r="T31" s="175"/>
-      <c r="U31" s="170"/>
-      <c r="V31" s="170"/>
-      <c r="W31" s="175"/>
-      <c r="X31" s="170"/>
-      <c r="Y31" s="170"/>
-      <c r="Z31" s="175"/>
-      <c r="AA31" s="170"/>
-      <c r="AB31" s="170"/>
-      <c r="AC31" s="170"/>
-      <c r="AD31" s="170"/>
-      <c r="AE31" s="170"/>
-      <c r="AF31" s="170"/>
-      <c r="AG31" s="170"/>
-      <c r="AH31" s="170"/>
-      <c r="AI31" s="170"/>
-      <c r="AJ31" s="171"/>
+      <c r="B31" s="38"/>
+      <c r="C31" s="38"/>
+      <c r="D31" s="38"/>
+      <c r="E31" s="38"/>
+      <c r="F31" s="38"/>
+      <c r="G31" s="38"/>
+      <c r="H31" s="38"/>
+      <c r="I31" s="44"/>
+      <c r="J31" s="44"/>
+      <c r="K31" s="38"/>
+      <c r="L31" s="38"/>
+      <c r="M31" s="38"/>
+      <c r="N31" s="38"/>
+      <c r="O31" s="38"/>
+      <c r="P31" s="38"/>
+      <c r="Q31" s="38"/>
+      <c r="R31" s="38"/>
+      <c r="S31" s="38"/>
+      <c r="T31" s="44"/>
+      <c r="U31" s="38"/>
+      <c r="V31" s="38"/>
+      <c r="W31" s="44"/>
+      <c r="X31" s="38"/>
+      <c r="Y31" s="38"/>
+      <c r="Z31" s="44"/>
+      <c r="AA31" s="38"/>
+      <c r="AB31" s="38"/>
+      <c r="AC31" s="38"/>
+      <c r="AD31" s="38"/>
+      <c r="AE31" s="38"/>
+      <c r="AF31" s="38"/>
+      <c r="AG31" s="38"/>
+      <c r="AH31" s="38"/>
+      <c r="AI31" s="38"/>
+      <c r="AJ31" s="42"/>
       <c r="AK31" s="94"/>
     </row>
     <row r="32" spans="1:37" ht="12.75" customHeight="1">
       <c r="A32" s="93"/>
-      <c r="B32" s="170"/>
-      <c r="C32" s="170"/>
-      <c r="D32" s="170"/>
-      <c r="E32" s="170"/>
-      <c r="F32" s="170"/>
-      <c r="G32" s="170"/>
-      <c r="H32" s="170"/>
-      <c r="I32" s="175"/>
-      <c r="J32" s="175"/>
-      <c r="K32" s="170"/>
-      <c r="L32" s="170"/>
-      <c r="M32" s="170"/>
-      <c r="N32" s="170"/>
-      <c r="O32" s="170"/>
-      <c r="P32" s="170"/>
-      <c r="Q32" s="170"/>
-      <c r="R32" s="170"/>
-      <c r="S32" s="170"/>
-      <c r="T32" s="175"/>
-      <c r="U32" s="170"/>
-      <c r="V32" s="170"/>
-      <c r="W32" s="175"/>
-      <c r="X32" s="170"/>
-      <c r="Y32" s="170"/>
-      <c r="Z32" s="175"/>
-      <c r="AA32" s="170"/>
-      <c r="AB32" s="170"/>
-      <c r="AC32" s="170"/>
-      <c r="AD32" s="170"/>
-      <c r="AE32" s="170"/>
-      <c r="AF32" s="170"/>
-      <c r="AG32" s="170"/>
-      <c r="AH32" s="170"/>
-      <c r="AI32" s="170"/>
-      <c r="AJ32" s="171"/>
+      <c r="B32" s="38"/>
+      <c r="C32" s="38"/>
+      <c r="D32" s="38"/>
+      <c r="E32" s="38"/>
+      <c r="F32" s="38"/>
+      <c r="G32" s="38"/>
+      <c r="H32" s="38"/>
+      <c r="I32" s="44"/>
+      <c r="J32" s="44"/>
+      <c r="K32" s="38"/>
+      <c r="L32" s="38"/>
+      <c r="M32" s="38"/>
+      <c r="N32" s="38"/>
+      <c r="O32" s="38"/>
+      <c r="P32" s="38"/>
+      <c r="Q32" s="38"/>
+      <c r="R32" s="38"/>
+      <c r="S32" s="38"/>
+      <c r="T32" s="44"/>
+      <c r="U32" s="38"/>
+      <c r="V32" s="38"/>
+      <c r="W32" s="44"/>
+      <c r="X32" s="38"/>
+      <c r="Y32" s="38"/>
+      <c r="Z32" s="44"/>
+      <c r="AA32" s="38"/>
+      <c r="AB32" s="38"/>
+      <c r="AC32" s="38"/>
+      <c r="AD32" s="38"/>
+      <c r="AE32" s="38"/>
+      <c r="AF32" s="38"/>
+      <c r="AG32" s="38"/>
+      <c r="AH32" s="38"/>
+      <c r="AI32" s="38"/>
+      <c r="AJ32" s="42"/>
       <c r="AK32" s="94"/>
     </row>
     <row r="33" spans="1:37" ht="12.75" customHeight="1">
       <c r="A33" s="93"/>
-      <c r="B33" s="170"/>
-      <c r="C33" s="170"/>
-      <c r="D33" s="170"/>
-      <c r="E33" s="170"/>
-      <c r="F33" s="170"/>
-      <c r="G33" s="170"/>
-      <c r="H33" s="170"/>
-      <c r="I33" s="175"/>
-      <c r="J33" s="175"/>
-      <c r="K33" s="170"/>
-      <c r="L33" s="170"/>
-      <c r="M33" s="170"/>
-      <c r="N33" s="170"/>
-      <c r="O33" s="170"/>
-      <c r="P33" s="170"/>
-      <c r="Q33" s="170"/>
-      <c r="R33" s="170"/>
-      <c r="S33" s="170"/>
-      <c r="T33" s="175"/>
-      <c r="U33" s="170"/>
-      <c r="V33" s="170"/>
-      <c r="W33" s="175"/>
-      <c r="X33" s="170"/>
-      <c r="Y33" s="170"/>
-      <c r="Z33" s="175"/>
-      <c r="AA33" s="170"/>
-      <c r="AB33" s="170"/>
-      <c r="AC33" s="170"/>
-      <c r="AD33" s="170"/>
-      <c r="AE33" s="170"/>
-      <c r="AF33" s="170"/>
-      <c r="AG33" s="170"/>
-      <c r="AH33" s="170"/>
-      <c r="AI33" s="170"/>
-      <c r="AJ33" s="171"/>
+      <c r="B33" s="38"/>
+      <c r="C33" s="38"/>
+      <c r="D33" s="38"/>
+      <c r="E33" s="38"/>
+      <c r="F33" s="38"/>
+      <c r="G33" s="38"/>
+      <c r="H33" s="38"/>
+      <c r="I33" s="44"/>
+      <c r="J33" s="44"/>
+      <c r="K33" s="38"/>
+      <c r="L33" s="38"/>
+      <c r="M33" s="38"/>
+      <c r="N33" s="38"/>
+      <c r="O33" s="38"/>
+      <c r="P33" s="38"/>
+      <c r="Q33" s="38"/>
+      <c r="R33" s="38"/>
+      <c r="S33" s="38"/>
+      <c r="T33" s="44"/>
+      <c r="U33" s="38"/>
+      <c r="V33" s="38"/>
+      <c r="W33" s="44"/>
+      <c r="X33" s="38"/>
+      <c r="Y33" s="38"/>
+      <c r="Z33" s="44"/>
+      <c r="AA33" s="38"/>
+      <c r="AB33" s="38"/>
+      <c r="AC33" s="38"/>
+      <c r="AD33" s="38"/>
+      <c r="AE33" s="38"/>
+      <c r="AF33" s="38"/>
+      <c r="AG33" s="38"/>
+      <c r="AH33" s="38"/>
+      <c r="AI33" s="38"/>
+      <c r="AJ33" s="42"/>
       <c r="AK33" s="94"/>
     </row>
     <row r="34" spans="1:37" ht="12.75" customHeight="1">
       <c r="A34" s="93"/>
-      <c r="B34" s="170"/>
-      <c r="C34" s="170"/>
-      <c r="D34" s="170"/>
-      <c r="E34" s="170"/>
-      <c r="F34" s="170"/>
-      <c r="G34" s="170"/>
-      <c r="H34" s="170"/>
-      <c r="I34" s="175"/>
-      <c r="J34" s="175"/>
-      <c r="K34" s="170"/>
-      <c r="L34" s="170"/>
-      <c r="M34" s="170"/>
-      <c r="N34" s="170"/>
-      <c r="O34" s="170"/>
-      <c r="P34" s="170"/>
-      <c r="Q34" s="170"/>
-      <c r="R34" s="170"/>
-      <c r="S34" s="170"/>
-      <c r="T34" s="175"/>
-      <c r="U34" s="170"/>
-      <c r="V34" s="170"/>
-      <c r="W34" s="175"/>
-      <c r="X34" s="170"/>
-      <c r="Y34" s="170"/>
-      <c r="Z34" s="175"/>
-      <c r="AA34" s="170"/>
-      <c r="AB34" s="170"/>
-      <c r="AC34" s="170"/>
-      <c r="AD34" s="170"/>
-      <c r="AE34" s="170"/>
-      <c r="AF34" s="170"/>
-      <c r="AG34" s="170"/>
-      <c r="AH34" s="170"/>
-      <c r="AI34" s="170"/>
-      <c r="AJ34" s="171"/>
+      <c r="B34" s="38"/>
+      <c r="C34" s="38"/>
+      <c r="D34" s="38"/>
+      <c r="E34" s="38"/>
+      <c r="F34" s="38"/>
+      <c r="G34" s="38"/>
+      <c r="H34" s="38"/>
+      <c r="I34" s="44"/>
+      <c r="J34" s="44"/>
+      <c r="K34" s="38"/>
+      <c r="L34" s="38"/>
+      <c r="M34" s="38"/>
+      <c r="N34" s="38"/>
+      <c r="O34" s="38"/>
+      <c r="P34" s="38"/>
+      <c r="Q34" s="38"/>
+      <c r="R34" s="38"/>
+      <c r="S34" s="38"/>
+      <c r="T34" s="44"/>
+      <c r="U34" s="38"/>
+      <c r="V34" s="38"/>
+      <c r="W34" s="44"/>
+      <c r="X34" s="38"/>
+      <c r="Y34" s="38"/>
+      <c r="Z34" s="44"/>
+      <c r="AA34" s="38"/>
+      <c r="AB34" s="38"/>
+      <c r="AC34" s="38"/>
+      <c r="AD34" s="38"/>
+      <c r="AE34" s="38"/>
+      <c r="AF34" s="38"/>
+      <c r="AG34" s="38"/>
+      <c r="AH34" s="38"/>
+      <c r="AI34" s="38"/>
+      <c r="AJ34" s="42"/>
       <c r="AK34" s="94"/>
     </row>
     <row r="35" spans="1:37" ht="12.75" customHeight="1">
       <c r="A35" s="93"/>
-      <c r="B35" s="170"/>
-      <c r="C35" s="170"/>
-      <c r="D35" s="170"/>
-      <c r="E35" s="170"/>
-      <c r="F35" s="170"/>
-      <c r="G35" s="170"/>
-      <c r="H35" s="170"/>
-      <c r="I35" s="175"/>
-      <c r="J35" s="175"/>
-      <c r="K35" s="170"/>
-      <c r="L35" s="170"/>
-      <c r="M35" s="170"/>
-      <c r="N35" s="170"/>
-      <c r="O35" s="170"/>
-      <c r="P35" s="170"/>
-      <c r="Q35" s="170"/>
-      <c r="R35" s="170"/>
-      <c r="S35" s="170"/>
-      <c r="T35" s="175"/>
-      <c r="U35" s="170"/>
-      <c r="V35" s="170"/>
-      <c r="W35" s="175"/>
-      <c r="X35" s="170"/>
-      <c r="Y35" s="170"/>
-      <c r="Z35" s="175"/>
-      <c r="AA35" s="170"/>
-      <c r="AB35" s="170"/>
-      <c r="AC35" s="170"/>
-      <c r="AD35" s="170"/>
-      <c r="AE35" s="170"/>
-      <c r="AF35" s="170"/>
-      <c r="AG35" s="170"/>
-      <c r="AH35" s="170"/>
-      <c r="AI35" s="170"/>
-      <c r="AJ35" s="171"/>
+      <c r="B35" s="38"/>
+      <c r="C35" s="38"/>
+      <c r="D35" s="38"/>
+      <c r="E35" s="38"/>
+      <c r="F35" s="38"/>
+      <c r="G35" s="38"/>
+      <c r="H35" s="38"/>
+      <c r="I35" s="44"/>
+      <c r="J35" s="44"/>
+      <c r="K35" s="38"/>
+      <c r="L35" s="38"/>
+      <c r="M35" s="38"/>
+      <c r="N35" s="38"/>
+      <c r="O35" s="38"/>
+      <c r="P35" s="38"/>
+      <c r="Q35" s="38"/>
+      <c r="R35" s="38"/>
+      <c r="S35" s="38"/>
+      <c r="T35" s="44"/>
+      <c r="U35" s="38"/>
+      <c r="V35" s="38"/>
+      <c r="W35" s="44"/>
+      <c r="X35" s="38"/>
+      <c r="Y35" s="38"/>
+      <c r="Z35" s="44"/>
+      <c r="AA35" s="38"/>
+      <c r="AB35" s="38"/>
+      <c r="AC35" s="38"/>
+      <c r="AD35" s="38"/>
+      <c r="AE35" s="38"/>
+      <c r="AF35" s="38"/>
+      <c r="AG35" s="38"/>
+      <c r="AH35" s="38"/>
+      <c r="AI35" s="38"/>
+      <c r="AJ35" s="42"/>
       <c r="AK35" s="94"/>
     </row>
     <row r="36" spans="1:37" ht="12.75" customHeight="1">
       <c r="A36" s="93"/>
-      <c r="B36" s="170"/>
-      <c r="C36" s="170"/>
-      <c r="D36" s="170"/>
-      <c r="E36" s="170"/>
-      <c r="F36" s="170"/>
-      <c r="G36" s="170"/>
-      <c r="H36" s="170"/>
-      <c r="I36" s="175"/>
-      <c r="J36" s="175"/>
-      <c r="K36" s="170"/>
-      <c r="L36" s="170"/>
-      <c r="M36" s="170"/>
-      <c r="N36" s="170"/>
-      <c r="O36" s="170"/>
-      <c r="P36" s="170"/>
-      <c r="Q36" s="170"/>
-      <c r="R36" s="170"/>
-      <c r="S36" s="170"/>
-      <c r="T36" s="175"/>
-      <c r="U36" s="170"/>
-      <c r="V36" s="170"/>
-      <c r="W36" s="175"/>
-      <c r="X36" s="170"/>
-      <c r="Y36" s="170"/>
-      <c r="Z36" s="175"/>
-      <c r="AA36" s="170"/>
-      <c r="AB36" s="170"/>
-      <c r="AC36" s="170"/>
-      <c r="AD36" s="170"/>
-      <c r="AE36" s="170"/>
-      <c r="AF36" s="170"/>
-      <c r="AG36" s="170"/>
-      <c r="AH36" s="170"/>
-      <c r="AI36" s="170"/>
-      <c r="AJ36" s="171"/>
+      <c r="B36" s="38"/>
+      <c r="C36" s="38"/>
+      <c r="D36" s="38"/>
+      <c r="E36" s="38"/>
+      <c r="F36" s="38"/>
+      <c r="G36" s="38"/>
+      <c r="H36" s="38"/>
+      <c r="I36" s="44"/>
+      <c r="J36" s="44"/>
+      <c r="K36" s="38"/>
+      <c r="L36" s="38"/>
+      <c r="M36" s="38"/>
+      <c r="N36" s="38"/>
+      <c r="O36" s="38"/>
+      <c r="P36" s="38"/>
+      <c r="Q36" s="38"/>
+      <c r="R36" s="38"/>
+      <c r="S36" s="38"/>
+      <c r="T36" s="44"/>
+      <c r="U36" s="38"/>
+      <c r="V36" s="38"/>
+      <c r="W36" s="44"/>
+      <c r="X36" s="38"/>
+      <c r="Y36" s="38"/>
+      <c r="Z36" s="44"/>
+      <c r="AA36" s="38"/>
+      <c r="AB36" s="38"/>
+      <c r="AC36" s="38"/>
+      <c r="AD36" s="38"/>
+      <c r="AE36" s="38"/>
+      <c r="AF36" s="38"/>
+      <c r="AG36" s="38"/>
+      <c r="AH36" s="38"/>
+      <c r="AI36" s="38"/>
+      <c r="AJ36" s="42"/>
       <c r="AK36" s="94"/>
     </row>
     <row r="37" spans="1:37" ht="12.75" customHeight="1">
       <c r="A37" s="93"/>
-      <c r="B37" s="170"/>
-      <c r="C37" s="170"/>
-      <c r="D37" s="170"/>
-      <c r="E37" s="170"/>
-      <c r="F37" s="170"/>
-      <c r="G37" s="170"/>
-      <c r="H37" s="170"/>
-      <c r="I37" s="175"/>
-      <c r="J37" s="175"/>
-      <c r="K37" s="170"/>
-      <c r="L37" s="170"/>
-      <c r="M37" s="170"/>
-      <c r="N37" s="170"/>
-      <c r="O37" s="170"/>
-      <c r="P37" s="170"/>
-      <c r="Q37" s="170"/>
-      <c r="R37" s="170"/>
-      <c r="S37" s="170"/>
-      <c r="T37" s="175"/>
-      <c r="U37" s="170"/>
-      <c r="V37" s="170"/>
-      <c r="W37" s="175"/>
-      <c r="X37" s="170"/>
-      <c r="Y37" s="170"/>
-      <c r="Z37" s="175"/>
-      <c r="AA37" s="170"/>
-      <c r="AB37" s="170"/>
-      <c r="AC37" s="170"/>
-      <c r="AD37" s="170"/>
-      <c r="AE37" s="170"/>
-      <c r="AF37" s="170"/>
-      <c r="AG37" s="170"/>
-      <c r="AH37" s="170"/>
-      <c r="AI37" s="170"/>
-      <c r="AJ37" s="171"/>
+      <c r="B37" s="38"/>
+      <c r="C37" s="38"/>
+      <c r="D37" s="38"/>
+      <c r="E37" s="38"/>
+      <c r="F37" s="38"/>
+      <c r="G37" s="38"/>
+      <c r="H37" s="38"/>
+      <c r="I37" s="44"/>
+      <c r="J37" s="44"/>
+      <c r="K37" s="38"/>
+      <c r="L37" s="38"/>
+      <c r="M37" s="38"/>
+      <c r="N37" s="38"/>
+      <c r="O37" s="38"/>
+      <c r="P37" s="38"/>
+      <c r="Q37" s="38"/>
+      <c r="R37" s="38"/>
+      <c r="S37" s="38"/>
+      <c r="T37" s="44"/>
+      <c r="U37" s="38"/>
+      <c r="V37" s="38"/>
+      <c r="W37" s="44"/>
+      <c r="X37" s="38"/>
+      <c r="Y37" s="38"/>
+      <c r="Z37" s="44"/>
+      <c r="AA37" s="38"/>
+      <c r="AB37" s="38"/>
+      <c r="AC37" s="38"/>
+      <c r="AD37" s="38"/>
+      <c r="AE37" s="38"/>
+      <c r="AF37" s="38"/>
+      <c r="AG37" s="38"/>
+      <c r="AH37" s="38"/>
+      <c r="AI37" s="38"/>
+      <c r="AJ37" s="42"/>
       <c r="AK37" s="94"/>
     </row>
     <row r="38" spans="1:37" ht="12.75" customHeight="1">
       <c r="A38" s="93"/>
-      <c r="B38" s="170"/>
-      <c r="C38" s="170"/>
-      <c r="D38" s="170"/>
-      <c r="E38" s="170"/>
-      <c r="F38" s="170"/>
-      <c r="G38" s="170"/>
-      <c r="H38" s="170"/>
-      <c r="I38" s="175"/>
-      <c r="J38" s="175"/>
-      <c r="K38" s="170"/>
-      <c r="L38" s="170"/>
-      <c r="M38" s="170"/>
-      <c r="N38" s="170"/>
-      <c r="O38" s="170"/>
-      <c r="P38" s="170"/>
-      <c r="Q38" s="170"/>
-      <c r="R38" s="170"/>
-      <c r="S38" s="170"/>
-      <c r="T38" s="175"/>
-      <c r="U38" s="170"/>
-      <c r="V38" s="170"/>
-      <c r="W38" s="175"/>
-      <c r="X38" s="170"/>
-      <c r="Y38" s="170"/>
-      <c r="Z38" s="175"/>
-      <c r="AA38" s="170"/>
-      <c r="AB38" s="170"/>
-      <c r="AC38" s="170"/>
-      <c r="AD38" s="170"/>
-      <c r="AE38" s="170"/>
-      <c r="AF38" s="170"/>
-      <c r="AG38" s="170"/>
-      <c r="AH38" s="170"/>
-      <c r="AI38" s="170"/>
-      <c r="AJ38" s="171"/>
+      <c r="B38" s="38"/>
+      <c r="C38" s="38"/>
+      <c r="D38" s="38"/>
+      <c r="E38" s="38"/>
+      <c r="F38" s="38"/>
+      <c r="G38" s="38"/>
+      <c r="H38" s="38"/>
+      <c r="I38" s="44"/>
+      <c r="J38" s="44"/>
+      <c r="K38" s="38"/>
+      <c r="L38" s="38"/>
+      <c r="M38" s="38"/>
+      <c r="N38" s="38"/>
+      <c r="O38" s="38"/>
+      <c r="P38" s="38"/>
+      <c r="Q38" s="38"/>
+      <c r="R38" s="38"/>
+      <c r="S38" s="38"/>
+      <c r="T38" s="44"/>
+      <c r="U38" s="38"/>
+      <c r="V38" s="38"/>
+      <c r="W38" s="44"/>
+      <c r="X38" s="38"/>
+      <c r="Y38" s="38"/>
+      <c r="Z38" s="44"/>
+      <c r="AA38" s="38"/>
+      <c r="AB38" s="38"/>
+      <c r="AC38" s="38"/>
+      <c r="AD38" s="38"/>
+      <c r="AE38" s="38"/>
+      <c r="AF38" s="38"/>
+      <c r="AG38" s="38"/>
+      <c r="AH38" s="38"/>
+      <c r="AI38" s="38"/>
+      <c r="AJ38" s="42"/>
       <c r="AK38" s="94"/>
     </row>
     <row r="39" spans="1:37" ht="12.75" customHeight="1">
       <c r="A39" s="93"/>
-      <c r="B39" s="170"/>
-      <c r="C39" s="170"/>
-      <c r="D39" s="170"/>
-      <c r="E39" s="170"/>
-      <c r="F39" s="170"/>
-      <c r="G39" s="170"/>
-      <c r="H39" s="170"/>
-      <c r="I39" s="175"/>
-      <c r="J39" s="170"/>
-      <c r="K39" s="170"/>
-      <c r="L39" s="170"/>
-      <c r="M39" s="170"/>
-      <c r="N39" s="170"/>
-      <c r="O39" s="170"/>
-      <c r="P39" s="170"/>
-      <c r="Q39" s="170"/>
-      <c r="R39" s="170"/>
-      <c r="S39" s="170"/>
-      <c r="T39" s="170"/>
-      <c r="U39" s="170"/>
-      <c r="V39" s="170"/>
-      <c r="W39" s="170"/>
-      <c r="X39" s="170"/>
-      <c r="Y39" s="170"/>
-      <c r="Z39" s="170"/>
-      <c r="AA39" s="170"/>
-      <c r="AB39" s="170"/>
-      <c r="AC39" s="170"/>
-      <c r="AD39" s="170"/>
-      <c r="AE39" s="170"/>
-      <c r="AF39" s="170"/>
-      <c r="AG39" s="170"/>
-      <c r="AH39" s="170"/>
-      <c r="AI39" s="170"/>
-      <c r="AJ39" s="171"/>
+      <c r="B39" s="38"/>
+      <c r="C39" s="38"/>
+      <c r="D39" s="38"/>
+      <c r="E39" s="38"/>
+      <c r="F39" s="38"/>
+      <c r="G39" s="38"/>
+      <c r="H39" s="38"/>
+      <c r="I39" s="44"/>
+      <c r="J39" s="38"/>
+      <c r="K39" s="38"/>
+      <c r="L39" s="38"/>
+      <c r="M39" s="38"/>
+      <c r="N39" s="38"/>
+      <c r="O39" s="38"/>
+      <c r="P39" s="38"/>
+      <c r="Q39" s="38"/>
+      <c r="R39" s="38"/>
+      <c r="S39" s="38"/>
+      <c r="T39" s="38"/>
+      <c r="U39" s="38"/>
+      <c r="V39" s="38"/>
+      <c r="W39" s="38"/>
+      <c r="X39" s="38"/>
+      <c r="Y39" s="38"/>
+      <c r="Z39" s="38"/>
+      <c r="AA39" s="38"/>
+      <c r="AB39" s="38"/>
+      <c r="AC39" s="38"/>
+      <c r="AD39" s="38"/>
+      <c r="AE39" s="38"/>
+      <c r="AF39" s="38"/>
+      <c r="AG39" s="38"/>
+      <c r="AH39" s="38"/>
+      <c r="AI39" s="38"/>
+      <c r="AJ39" s="42"/>
       <c r="AK39" s="94"/>
     </row>
     <row r="40" spans="1:37" ht="12.75" customHeight="1">
       <c r="A40" s="93"/>
-      <c r="B40" s="170"/>
-      <c r="C40" s="170"/>
-      <c r="D40" s="170"/>
-      <c r="E40" s="170"/>
-      <c r="F40" s="170"/>
-      <c r="G40" s="175"/>
-      <c r="H40" s="170"/>
-      <c r="I40" s="176"/>
-      <c r="J40" s="170"/>
-      <c r="K40" s="170"/>
-      <c r="L40" s="170"/>
-      <c r="M40" s="170"/>
-      <c r="N40" s="170"/>
-      <c r="O40" s="170"/>
-      <c r="P40" s="170"/>
-      <c r="Q40" s="170"/>
-      <c r="R40" s="170"/>
-      <c r="S40" s="170"/>
-      <c r="T40" s="170"/>
-      <c r="U40" s="170"/>
-      <c r="V40" s="170"/>
-      <c r="W40" s="170"/>
-      <c r="X40" s="170"/>
-      <c r="Y40" s="170"/>
-      <c r="Z40" s="170"/>
-      <c r="AA40" s="170"/>
-      <c r="AB40" s="170"/>
-      <c r="AC40" s="170"/>
-      <c r="AD40" s="170"/>
-      <c r="AE40" s="170"/>
-      <c r="AF40" s="170"/>
-      <c r="AG40" s="170"/>
-      <c r="AH40" s="170"/>
-      <c r="AI40" s="170"/>
-      <c r="AJ40" s="170"/>
+      <c r="B40" s="38"/>
+      <c r="C40" s="38"/>
+      <c r="D40" s="38"/>
+      <c r="E40" s="38"/>
+      <c r="F40" s="38"/>
+      <c r="G40" s="44"/>
+      <c r="H40" s="38"/>
+      <c r="I40" s="56"/>
+      <c r="J40" s="38"/>
+      <c r="K40" s="38"/>
+      <c r="L40" s="38"/>
+      <c r="M40" s="38"/>
+      <c r="N40" s="38"/>
+      <c r="O40" s="38"/>
+      <c r="P40" s="38"/>
+      <c r="Q40" s="38"/>
+      <c r="R40" s="38"/>
+      <c r="S40" s="38"/>
+      <c r="T40" s="38"/>
+      <c r="U40" s="38"/>
+      <c r="V40" s="38"/>
+      <c r="W40" s="38"/>
+      <c r="X40" s="38"/>
+      <c r="Y40" s="38"/>
+      <c r="Z40" s="38"/>
+      <c r="AA40" s="38"/>
+      <c r="AB40" s="38"/>
+      <c r="AC40" s="38"/>
+      <c r="AD40" s="38"/>
+      <c r="AE40" s="38"/>
+      <c r="AF40" s="38"/>
+      <c r="AG40" s="38"/>
+      <c r="AH40" s="38"/>
+      <c r="AI40" s="38"/>
+      <c r="AJ40" s="38"/>
       <c r="AK40" s="94"/>
     </row>
     <row r="41" spans="1:37" ht="12.75" customHeight="1">
-      <c r="A41" s="186"/>
-      <c r="B41" s="177"/>
-      <c r="C41" s="177"/>
-      <c r="D41" s="177"/>
-      <c r="E41" s="177"/>
-      <c r="F41" s="177"/>
-      <c r="G41" s="178"/>
-      <c r="H41" s="178"/>
-      <c r="I41" s="177"/>
-      <c r="J41" s="177"/>
-      <c r="K41" s="177"/>
-      <c r="L41" s="177"/>
-      <c r="M41" s="177"/>
-      <c r="N41" s="177"/>
-      <c r="O41" s="177"/>
-      <c r="P41" s="177"/>
-      <c r="Q41" s="177"/>
-      <c r="R41" s="177"/>
-      <c r="S41" s="177"/>
-      <c r="T41" s="168"/>
-      <c r="U41" s="168"/>
-      <c r="V41" s="168"/>
-      <c r="W41" s="168"/>
-      <c r="X41" s="168"/>
-      <c r="Y41" s="168"/>
-      <c r="Z41" s="168"/>
-      <c r="AA41" s="168"/>
-      <c r="AB41" s="168"/>
-      <c r="AC41" s="168"/>
-      <c r="AD41" s="168"/>
-      <c r="AE41" s="168"/>
-      <c r="AF41" s="168"/>
-      <c r="AG41" s="168"/>
-      <c r="AH41" s="168"/>
-      <c r="AI41" s="168"/>
-      <c r="AJ41" s="168"/>
-      <c r="AK41" s="187"/>
+      <c r="A41" s="100"/>
+      <c r="B41" s="68"/>
+      <c r="C41" s="68"/>
+      <c r="D41" s="68"/>
+      <c r="E41" s="68"/>
+      <c r="F41" s="68"/>
+      <c r="G41" s="69"/>
+      <c r="H41" s="69"/>
+      <c r="I41" s="68"/>
+      <c r="J41" s="68"/>
+      <c r="K41" s="68"/>
+      <c r="L41" s="68"/>
+      <c r="M41" s="68"/>
+      <c r="N41" s="68"/>
+      <c r="O41" s="68"/>
+      <c r="P41" s="68"/>
+      <c r="Q41" s="68"/>
+      <c r="R41" s="68"/>
+      <c r="S41" s="68"/>
+      <c r="T41" s="70"/>
+      <c r="U41" s="70"/>
+      <c r="V41" s="70"/>
+      <c r="W41" s="70"/>
+      <c r="X41" s="70"/>
+      <c r="Y41" s="70"/>
+      <c r="Z41" s="70"/>
+      <c r="AA41" s="70"/>
+      <c r="AB41" s="70"/>
+      <c r="AC41" s="70"/>
+      <c r="AD41" s="70"/>
+      <c r="AE41" s="70"/>
+      <c r="AF41" s="70"/>
+      <c r="AG41" s="70"/>
+      <c r="AH41" s="70"/>
+      <c r="AI41" s="70"/>
+      <c r="AJ41" s="70"/>
+      <c r="AK41" s="101"/>
     </row>
     <row r="42" spans="1:37" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A42" s="188"/>
-      <c r="B42" s="189"/>
-      <c r="C42" s="189"/>
-      <c r="D42" s="189"/>
-      <c r="E42" s="189"/>
-      <c r="F42" s="189"/>
-      <c r="G42" s="189"/>
-      <c r="H42" s="189"/>
-      <c r="I42" s="189"/>
-      <c r="J42" s="189"/>
-      <c r="K42" s="189"/>
-      <c r="L42" s="189"/>
-      <c r="M42" s="189"/>
-      <c r="N42" s="189"/>
-      <c r="O42" s="189"/>
-      <c r="P42" s="189"/>
-      <c r="Q42" s="189"/>
-      <c r="R42" s="189"/>
-      <c r="S42" s="189"/>
-      <c r="T42" s="189"/>
-      <c r="U42" s="189"/>
-      <c r="V42" s="189"/>
-      <c r="W42" s="189"/>
-      <c r="X42" s="189"/>
-      <c r="Y42" s="189"/>
-      <c r="Z42" s="189"/>
-      <c r="AA42" s="189"/>
-      <c r="AB42" s="189"/>
-      <c r="AC42" s="189"/>
-      <c r="AD42" s="189"/>
-      <c r="AE42" s="189"/>
-      <c r="AF42" s="189"/>
-      <c r="AG42" s="189"/>
-      <c r="AH42" s="189"/>
-      <c r="AI42" s="189"/>
-      <c r="AJ42" s="189"/>
-      <c r="AK42" s="190"/>
+      <c r="A42" s="102"/>
+      <c r="B42" s="103"/>
+      <c r="C42" s="103"/>
+      <c r="D42" s="103"/>
+      <c r="E42" s="103"/>
+      <c r="F42" s="103"/>
+      <c r="G42" s="103"/>
+      <c r="H42" s="103"/>
+      <c r="I42" s="103"/>
+      <c r="J42" s="103"/>
+      <c r="K42" s="103"/>
+      <c r="L42" s="103"/>
+      <c r="M42" s="103"/>
+      <c r="N42" s="103"/>
+      <c r="O42" s="103"/>
+      <c r="P42" s="103"/>
+      <c r="Q42" s="103"/>
+      <c r="R42" s="103"/>
+      <c r="S42" s="103"/>
+      <c r="T42" s="103"/>
+      <c r="U42" s="103"/>
+      <c r="V42" s="103"/>
+      <c r="W42" s="103"/>
+      <c r="X42" s="103"/>
+      <c r="Y42" s="103"/>
+      <c r="Z42" s="103"/>
+      <c r="AA42" s="103"/>
+      <c r="AB42" s="103"/>
+      <c r="AC42" s="103"/>
+      <c r="AD42" s="103"/>
+      <c r="AE42" s="103"/>
+      <c r="AF42" s="103"/>
+      <c r="AG42" s="103"/>
+      <c r="AH42" s="103"/>
+      <c r="AI42" s="103"/>
+      <c r="AJ42" s="103"/>
+      <c r="AK42" s="104"/>
     </row>
     <row r="43" spans="1:37" ht="12.75" customHeight="1">
-      <c r="A43" s="184"/>
-      <c r="B43" s="65"/>
-      <c r="C43" s="65"/>
-      <c r="D43" s="65"/>
-      <c r="E43" s="65"/>
-      <c r="F43" s="65"/>
-      <c r="G43" s="65"/>
-      <c r="H43" s="65"/>
-      <c r="I43" s="65"/>
-      <c r="J43" s="65"/>
-      <c r="K43" s="65"/>
-      <c r="L43" s="65"/>
-      <c r="M43" s="65"/>
-      <c r="N43" s="65"/>
-      <c r="O43" s="65"/>
-      <c r="P43" s="65"/>
-      <c r="Q43" s="65"/>
-      <c r="R43" s="65"/>
-      <c r="S43" s="65"/>
-      <c r="T43" s="65"/>
-      <c r="U43" s="65"/>
-      <c r="V43" s="65"/>
-      <c r="W43" s="65"/>
-      <c r="X43" s="65"/>
-      <c r="Y43" s="65"/>
-      <c r="Z43" s="65"/>
-      <c r="AA43" s="65"/>
-      <c r="AB43" s="65"/>
-      <c r="AC43" s="65"/>
-      <c r="AD43" s="65"/>
-      <c r="AE43" s="65"/>
-      <c r="AF43" s="65"/>
-      <c r="AG43" s="65"/>
-      <c r="AH43" s="65"/>
-      <c r="AI43" s="65"/>
-      <c r="AJ43" s="65"/>
-      <c r="AK43" s="185"/>
+      <c r="A43" s="218"/>
+      <c r="B43" s="219"/>
+      <c r="C43" s="219"/>
+      <c r="D43" s="219"/>
+      <c r="E43" s="219"/>
+      <c r="F43" s="219"/>
+      <c r="G43" s="219"/>
+      <c r="H43" s="219"/>
+      <c r="I43" s="219"/>
+      <c r="J43" s="219"/>
+      <c r="K43" s="219"/>
+      <c r="L43" s="219"/>
+      <c r="M43" s="219"/>
+      <c r="N43" s="219"/>
+      <c r="O43" s="219"/>
+      <c r="P43" s="219"/>
+      <c r="Q43" s="219"/>
+      <c r="R43" s="219"/>
+      <c r="S43" s="219"/>
+      <c r="T43" s="219"/>
+      <c r="U43" s="219"/>
+      <c r="V43" s="219"/>
+      <c r="W43" s="219"/>
+      <c r="X43" s="219"/>
+      <c r="Y43" s="219"/>
+      <c r="Z43" s="219"/>
+      <c r="AA43" s="219"/>
+      <c r="AB43" s="219"/>
+      <c r="AC43" s="219"/>
+      <c r="AD43" s="219"/>
+      <c r="AE43" s="219"/>
+      <c r="AF43" s="219"/>
+      <c r="AG43" s="219"/>
+      <c r="AH43" s="219"/>
+      <c r="AI43" s="219"/>
+      <c r="AJ43" s="219"/>
+      <c r="AK43" s="220"/>
     </row>
     <row r="44" spans="1:37" ht="12.75" customHeight="1">
-      <c r="A44" s="186"/>
-      <c r="B44" s="167"/>
-      <c r="C44" s="167"/>
-      <c r="D44" s="167"/>
-      <c r="E44" s="167"/>
-      <c r="F44" s="167"/>
-      <c r="G44" s="167"/>
-      <c r="H44" s="167"/>
-      <c r="I44" s="167"/>
-      <c r="J44" s="167"/>
-      <c r="K44" s="167"/>
-      <c r="L44" s="167"/>
-      <c r="M44" s="167"/>
-      <c r="N44" s="167"/>
-      <c r="O44" s="167"/>
-      <c r="P44" s="167"/>
-      <c r="Q44" s="167"/>
-      <c r="R44" s="167"/>
-      <c r="S44" s="167"/>
-      <c r="T44" s="167"/>
-      <c r="U44" s="167"/>
-      <c r="V44" s="167"/>
-      <c r="W44" s="167"/>
-      <c r="X44" s="167"/>
-      <c r="Y44" s="167"/>
-      <c r="Z44" s="167"/>
-      <c r="AA44" s="167"/>
-      <c r="AB44" s="167"/>
-      <c r="AC44" s="167"/>
-      <c r="AD44" s="167"/>
-      <c r="AE44" s="167"/>
-      <c r="AF44" s="167"/>
-      <c r="AG44" s="167"/>
-      <c r="AH44" s="167"/>
-      <c r="AI44" s="167"/>
-      <c r="AJ44" s="167"/>
-      <c r="AK44" s="187"/>
+      <c r="A44" s="100"/>
+      <c r="B44" s="221"/>
+      <c r="C44" s="221"/>
+      <c r="D44" s="221"/>
+      <c r="E44" s="221"/>
+      <c r="F44" s="221"/>
+      <c r="G44" s="221"/>
+      <c r="H44" s="221"/>
+      <c r="I44" s="221"/>
+      <c r="J44" s="221"/>
+      <c r="K44" s="221"/>
+      <c r="L44" s="221"/>
+      <c r="M44" s="221"/>
+      <c r="N44" s="221"/>
+      <c r="O44" s="221"/>
+      <c r="P44" s="221"/>
+      <c r="Q44" s="221"/>
+      <c r="R44" s="221"/>
+      <c r="S44" s="221"/>
+      <c r="T44" s="221"/>
+      <c r="U44" s="221"/>
+      <c r="V44" s="221"/>
+      <c r="W44" s="221"/>
+      <c r="X44" s="221"/>
+      <c r="Y44" s="221"/>
+      <c r="Z44" s="221"/>
+      <c r="AA44" s="221"/>
+      <c r="AB44" s="221"/>
+      <c r="AC44" s="221"/>
+      <c r="AD44" s="221"/>
+      <c r="AE44" s="221"/>
+      <c r="AF44" s="221"/>
+      <c r="AG44" s="221"/>
+      <c r="AH44" s="221"/>
+      <c r="AI44" s="221"/>
+      <c r="AJ44" s="221"/>
+      <c r="AK44" s="101"/>
     </row>
     <row r="45" spans="1:37" ht="12.75" customHeight="1">
       <c r="A45" s="93"/>
-      <c r="B45" s="169" t="s">
+      <c r="B45" s="222" t="s">
         <v>83</v>
       </c>
-      <c r="C45" s="170"/>
-      <c r="D45" s="170"/>
-      <c r="E45" s="170"/>
-      <c r="F45" s="170"/>
-      <c r="G45" s="170"/>
-      <c r="H45" s="170"/>
-      <c r="I45" s="170"/>
-      <c r="J45" s="170"/>
-      <c r="K45" s="170"/>
-      <c r="L45" s="170"/>
-      <c r="M45" s="170"/>
-      <c r="N45" s="170"/>
-      <c r="O45" s="170"/>
-      <c r="P45" s="170"/>
-      <c r="Q45" s="170"/>
-      <c r="R45" s="170"/>
-      <c r="S45" s="170"/>
-      <c r="T45" s="170"/>
-      <c r="U45" s="170"/>
-      <c r="V45" s="170"/>
-      <c r="W45" s="170"/>
-      <c r="X45" s="170"/>
-      <c r="Y45" s="170"/>
-      <c r="Z45" s="170"/>
-      <c r="AA45" s="170"/>
-      <c r="AB45" s="170"/>
-      <c r="AC45" s="170"/>
-      <c r="AD45" s="170"/>
-      <c r="AE45" s="170"/>
-      <c r="AF45" s="170"/>
-      <c r="AG45" s="170"/>
-      <c r="AH45" s="170"/>
-      <c r="AI45" s="170"/>
-      <c r="AJ45" s="170"/>
+      <c r="C45" s="223"/>
+      <c r="D45" s="223"/>
+      <c r="E45" s="223"/>
+      <c r="F45" s="223"/>
+      <c r="G45" s="223"/>
+      <c r="H45" s="223"/>
+      <c r="I45" s="223"/>
+      <c r="J45" s="223"/>
+      <c r="K45" s="223"/>
+      <c r="L45" s="223"/>
+      <c r="M45" s="223"/>
+      <c r="N45" s="223"/>
+      <c r="O45" s="223"/>
+      <c r="P45" s="223"/>
+      <c r="Q45" s="223"/>
+      <c r="R45" s="223"/>
+      <c r="S45" s="223"/>
+      <c r="T45" s="223"/>
+      <c r="U45" s="223"/>
+      <c r="V45" s="223"/>
+      <c r="W45" s="223"/>
+      <c r="X45" s="223"/>
+      <c r="Y45" s="223"/>
+      <c r="Z45" s="223"/>
+      <c r="AA45" s="223"/>
+      <c r="AB45" s="223"/>
+      <c r="AC45" s="223"/>
+      <c r="AD45" s="223"/>
+      <c r="AE45" s="223"/>
+      <c r="AF45" s="223"/>
+      <c r="AG45" s="223"/>
+      <c r="AH45" s="223"/>
+      <c r="AI45" s="223"/>
+      <c r="AJ45" s="223"/>
       <c r="AK45" s="94"/>
     </row>
     <row r="46" spans="1:37" ht="12.75" customHeight="1" thickBot="1">
       <c r="A46" s="93"/>
-      <c r="B46" s="170"/>
-      <c r="C46" s="170"/>
-      <c r="D46" s="170"/>
-      <c r="E46" s="170"/>
-      <c r="F46" s="170"/>
-      <c r="G46" s="170"/>
-      <c r="H46" s="170"/>
-      <c r="I46" s="170"/>
-      <c r="J46" s="170"/>
-      <c r="K46" s="170"/>
-      <c r="L46" s="171"/>
-      <c r="M46" s="170"/>
-      <c r="N46" s="170"/>
-      <c r="O46" s="170"/>
-      <c r="P46" s="170"/>
-      <c r="Q46" s="170"/>
-      <c r="R46" s="170"/>
-      <c r="S46" s="170"/>
-      <c r="T46" s="170"/>
-      <c r="U46" s="170"/>
-      <c r="V46" s="171"/>
-      <c r="W46" s="171"/>
-      <c r="X46" s="170"/>
-      <c r="Y46" s="170"/>
-      <c r="Z46" s="171"/>
-      <c r="AA46" s="170"/>
-      <c r="AB46" s="170"/>
-      <c r="AC46" s="170"/>
-      <c r="AD46" s="170"/>
-      <c r="AE46" s="170"/>
-      <c r="AF46" s="170"/>
-      <c r="AG46" s="170"/>
-      <c r="AH46" s="170"/>
-      <c r="AI46" s="170"/>
-      <c r="AJ46" s="170"/>
+      <c r="B46" s="223"/>
+      <c r="C46" s="223"/>
+      <c r="D46" s="223"/>
+      <c r="E46" s="223"/>
+      <c r="F46" s="223"/>
+      <c r="G46" s="223"/>
+      <c r="H46" s="223"/>
+      <c r="I46" s="223"/>
+      <c r="J46" s="223"/>
+      <c r="K46" s="223"/>
+      <c r="L46" s="224"/>
+      <c r="M46" s="223"/>
+      <c r="N46" s="223"/>
+      <c r="O46" s="223"/>
+      <c r="P46" s="223"/>
+      <c r="Q46" s="223"/>
+      <c r="R46" s="223"/>
+      <c r="S46" s="223"/>
+      <c r="T46" s="223"/>
+      <c r="U46" s="223"/>
+      <c r="V46" s="224"/>
+      <c r="W46" s="224"/>
+      <c r="X46" s="223"/>
+      <c r="Y46" s="223"/>
+      <c r="Z46" s="224"/>
+      <c r="AA46" s="223"/>
+      <c r="AB46" s="223"/>
+      <c r="AC46" s="223"/>
+      <c r="AD46" s="223"/>
+      <c r="AE46" s="223"/>
+      <c r="AF46" s="223"/>
+      <c r="AG46" s="223"/>
+      <c r="AH46" s="223"/>
+      <c r="AI46" s="223"/>
+      <c r="AJ46" s="223"/>
       <c r="AK46" s="94"/>
     </row>
     <row r="47" spans="1:37" ht="12.75" customHeight="1">
       <c r="A47" s="93"/>
-      <c r="B47" s="170"/>
-      <c r="C47" s="170"/>
-      <c r="D47" s="170"/>
-      <c r="E47" s="170"/>
-      <c r="F47" s="170"/>
-      <c r="G47" s="110" t="s">
+      <c r="B47" s="223"/>
+      <c r="C47" s="223"/>
+      <c r="D47" s="223"/>
+      <c r="E47" s="223"/>
+      <c r="F47" s="223"/>
+      <c r="G47" s="131" t="s">
         <v>55</v>
       </c>
-      <c r="H47" s="111"/>
-      <c r="I47" s="111"/>
-      <c r="J47" s="98"/>
-      <c r="K47" s="99"/>
-      <c r="L47" s="99"/>
-      <c r="M47" s="99"/>
-      <c r="N47" s="99"/>
-      <c r="O47" s="99"/>
-      <c r="P47" s="99"/>
-      <c r="Q47" s="99"/>
-      <c r="R47" s="100"/>
-      <c r="S47" s="104" t="s">
+      <c r="H47" s="132"/>
+      <c r="I47" s="132"/>
+      <c r="J47" s="135"/>
+      <c r="K47" s="136"/>
+      <c r="L47" s="136"/>
+      <c r="M47" s="136"/>
+      <c r="N47" s="136"/>
+      <c r="O47" s="136"/>
+      <c r="P47" s="136"/>
+      <c r="Q47" s="136"/>
+      <c r="R47" s="137"/>
+      <c r="S47" s="141" t="s">
         <v>56</v>
       </c>
-      <c r="T47" s="105"/>
-      <c r="U47" s="106"/>
-      <c r="V47" s="98"/>
-      <c r="W47" s="99"/>
-      <c r="X47" s="99"/>
-      <c r="Y47" s="99"/>
-      <c r="Z47" s="99"/>
-      <c r="AA47" s="99"/>
-      <c r="AB47" s="99"/>
-      <c r="AC47" s="99"/>
-      <c r="AD47" s="100"/>
-      <c r="AE47" s="170"/>
-      <c r="AF47" s="170"/>
-      <c r="AG47" s="170"/>
-      <c r="AH47" s="170"/>
-      <c r="AI47" s="170"/>
-      <c r="AJ47" s="170"/>
+      <c r="T47" s="142"/>
+      <c r="U47" s="143"/>
+      <c r="V47" s="135"/>
+      <c r="W47" s="136"/>
+      <c r="X47" s="136"/>
+      <c r="Y47" s="136"/>
+      <c r="Z47" s="136"/>
+      <c r="AA47" s="136"/>
+      <c r="AB47" s="136"/>
+      <c r="AC47" s="136"/>
+      <c r="AD47" s="137"/>
+      <c r="AE47" s="223"/>
+      <c r="AF47" s="223"/>
+      <c r="AG47" s="223"/>
+      <c r="AH47" s="223"/>
+      <c r="AI47" s="223"/>
+      <c r="AJ47" s="223"/>
       <c r="AK47" s="94"/>
     </row>
     <row r="48" spans="1:37" ht="12.75" customHeight="1" thickBot="1">
       <c r="A48" s="93"/>
-      <c r="B48" s="170"/>
-      <c r="C48" s="170"/>
-      <c r="D48" s="170"/>
-      <c r="E48" s="170"/>
-      <c r="F48" s="170"/>
-      <c r="G48" s="112"/>
-      <c r="H48" s="113"/>
-      <c r="I48" s="113"/>
-      <c r="J48" s="101"/>
-      <c r="K48" s="102"/>
-      <c r="L48" s="102"/>
-      <c r="M48" s="102"/>
-      <c r="N48" s="102"/>
-      <c r="O48" s="102"/>
-      <c r="P48" s="102"/>
-      <c r="Q48" s="102"/>
-      <c r="R48" s="103"/>
-      <c r="S48" s="107"/>
-      <c r="T48" s="108"/>
-      <c r="U48" s="109"/>
-      <c r="V48" s="101"/>
-      <c r="W48" s="102"/>
-      <c r="X48" s="102"/>
-      <c r="Y48" s="102"/>
-      <c r="Z48" s="102"/>
-      <c r="AA48" s="102"/>
-      <c r="AB48" s="102"/>
-      <c r="AC48" s="102"/>
-      <c r="AD48" s="103"/>
-      <c r="AE48" s="170"/>
-      <c r="AF48" s="170"/>
-      <c r="AG48" s="170"/>
-      <c r="AH48" s="170"/>
-      <c r="AI48" s="170"/>
-      <c r="AJ48" s="170"/>
+      <c r="B48" s="223"/>
+      <c r="C48" s="223"/>
+      <c r="D48" s="223"/>
+      <c r="E48" s="223"/>
+      <c r="F48" s="223"/>
+      <c r="G48" s="133"/>
+      <c r="H48" s="134"/>
+      <c r="I48" s="134"/>
+      <c r="J48" s="138"/>
+      <c r="K48" s="139"/>
+      <c r="L48" s="139"/>
+      <c r="M48" s="139"/>
+      <c r="N48" s="139"/>
+      <c r="O48" s="139"/>
+      <c r="P48" s="139"/>
+      <c r="Q48" s="139"/>
+      <c r="R48" s="140"/>
+      <c r="S48" s="144"/>
+      <c r="T48" s="145"/>
+      <c r="U48" s="146"/>
+      <c r="V48" s="138"/>
+      <c r="W48" s="139"/>
+      <c r="X48" s="139"/>
+      <c r="Y48" s="139"/>
+      <c r="Z48" s="139"/>
+      <c r="AA48" s="139"/>
+      <c r="AB48" s="139"/>
+      <c r="AC48" s="139"/>
+      <c r="AD48" s="140"/>
+      <c r="AE48" s="223"/>
+      <c r="AF48" s="223"/>
+      <c r="AG48" s="223"/>
+      <c r="AH48" s="223"/>
+      <c r="AI48" s="223"/>
+      <c r="AJ48" s="223"/>
       <c r="AK48" s="94"/>
     </row>
     <row r="49" spans="1:37" ht="12.75" customHeight="1">
       <c r="A49" s="93"/>
-      <c r="B49" s="170"/>
-      <c r="C49" s="170"/>
-      <c r="D49" s="170"/>
-      <c r="E49" s="170"/>
-      <c r="F49" s="170"/>
-      <c r="G49" s="110" t="s">
+      <c r="B49" s="223"/>
+      <c r="C49" s="223"/>
+      <c r="D49" s="223"/>
+      <c r="E49" s="223"/>
+      <c r="F49" s="223"/>
+      <c r="G49" s="131" t="s">
         <v>85</v>
       </c>
-      <c r="H49" s="111"/>
-      <c r="I49" s="111"/>
-      <c r="J49" s="98"/>
-      <c r="K49" s="99"/>
-      <c r="L49" s="99"/>
-      <c r="M49" s="99"/>
-      <c r="N49" s="99"/>
-      <c r="O49" s="99"/>
-      <c r="P49" s="99"/>
-      <c r="Q49" s="99"/>
-      <c r="R49" s="100"/>
-      <c r="S49" s="104" t="s">
+      <c r="H49" s="132"/>
+      <c r="I49" s="132"/>
+      <c r="J49" s="135"/>
+      <c r="K49" s="136"/>
+      <c r="L49" s="136"/>
+      <c r="M49" s="136"/>
+      <c r="N49" s="136"/>
+      <c r="O49" s="136"/>
+      <c r="P49" s="136"/>
+      <c r="Q49" s="136"/>
+      <c r="R49" s="137"/>
+      <c r="S49" s="141" t="s">
         <v>89</v>
       </c>
-      <c r="T49" s="105"/>
-      <c r="U49" s="106"/>
-      <c r="V49" s="98"/>
-      <c r="W49" s="99"/>
-      <c r="X49" s="99"/>
-      <c r="Y49" s="99"/>
-      <c r="Z49" s="99"/>
-      <c r="AA49" s="99"/>
-      <c r="AB49" s="99"/>
-      <c r="AC49" s="99"/>
-      <c r="AD49" s="100"/>
-      <c r="AE49" s="170"/>
-      <c r="AF49" s="170"/>
-      <c r="AG49" s="170"/>
-      <c r="AH49" s="170"/>
-      <c r="AI49" s="170"/>
-      <c r="AJ49" s="170"/>
+      <c r="T49" s="142"/>
+      <c r="U49" s="143"/>
+      <c r="V49" s="135"/>
+      <c r="W49" s="136"/>
+      <c r="X49" s="136"/>
+      <c r="Y49" s="136"/>
+      <c r="Z49" s="136"/>
+      <c r="AA49" s="136"/>
+      <c r="AB49" s="136"/>
+      <c r="AC49" s="136"/>
+      <c r="AD49" s="137"/>
+      <c r="AE49" s="223"/>
+      <c r="AF49" s="223"/>
+      <c r="AG49" s="223"/>
+      <c r="AH49" s="223"/>
+      <c r="AI49" s="223"/>
+      <c r="AJ49" s="223"/>
       <c r="AK49" s="94"/>
     </row>
     <row r="50" spans="1:37" ht="12.75" customHeight="1" thickBot="1">
       <c r="A50" s="93"/>
-      <c r="B50" s="170"/>
-      <c r="C50" s="170"/>
-      <c r="D50" s="170"/>
-      <c r="E50" s="170"/>
-      <c r="F50" s="170"/>
-      <c r="G50" s="112"/>
-      <c r="H50" s="113"/>
-      <c r="I50" s="113"/>
-      <c r="J50" s="101"/>
-      <c r="K50" s="102"/>
-      <c r="L50" s="102"/>
-      <c r="M50" s="102"/>
-      <c r="N50" s="102"/>
-      <c r="O50" s="102"/>
-      <c r="P50" s="102"/>
-      <c r="Q50" s="102"/>
-      <c r="R50" s="103"/>
-      <c r="S50" s="107"/>
-      <c r="T50" s="108"/>
-      <c r="U50" s="109"/>
-      <c r="V50" s="101"/>
-      <c r="W50" s="102"/>
-      <c r="X50" s="102"/>
-      <c r="Y50" s="102"/>
-      <c r="Z50" s="102"/>
-      <c r="AA50" s="102"/>
-      <c r="AB50" s="102"/>
-      <c r="AC50" s="102"/>
-      <c r="AD50" s="103"/>
-      <c r="AE50" s="170"/>
-      <c r="AF50" s="170"/>
-      <c r="AG50" s="170"/>
-      <c r="AH50" s="170"/>
-      <c r="AI50" s="170"/>
-      <c r="AJ50" s="170"/>
+      <c r="B50" s="223"/>
+      <c r="C50" s="223"/>
+      <c r="D50" s="223"/>
+      <c r="E50" s="223"/>
+      <c r="F50" s="223"/>
+      <c r="G50" s="133"/>
+      <c r="H50" s="134"/>
+      <c r="I50" s="134"/>
+      <c r="J50" s="138"/>
+      <c r="K50" s="139"/>
+      <c r="L50" s="139"/>
+      <c r="M50" s="139"/>
+      <c r="N50" s="139"/>
+      <c r="O50" s="139"/>
+      <c r="P50" s="139"/>
+      <c r="Q50" s="139"/>
+      <c r="R50" s="140"/>
+      <c r="S50" s="144"/>
+      <c r="T50" s="145"/>
+      <c r="U50" s="146"/>
+      <c r="V50" s="138"/>
+      <c r="W50" s="139"/>
+      <c r="X50" s="139"/>
+      <c r="Y50" s="139"/>
+      <c r="Z50" s="139"/>
+      <c r="AA50" s="139"/>
+      <c r="AB50" s="139"/>
+      <c r="AC50" s="139"/>
+      <c r="AD50" s="140"/>
+      <c r="AE50" s="223"/>
+      <c r="AF50" s="223"/>
+      <c r="AG50" s="223"/>
+      <c r="AH50" s="223"/>
+      <c r="AI50" s="223"/>
+      <c r="AJ50" s="223"/>
       <c r="AK50" s="94"/>
     </row>
     <row r="51" spans="1:37" ht="12.75" customHeight="1">
       <c r="A51" s="93"/>
-      <c r="B51" s="170"/>
-      <c r="C51" s="170"/>
-      <c r="D51" s="170"/>
-      <c r="E51" s="170"/>
-      <c r="F51" s="170"/>
-      <c r="G51" s="110" t="s">
+      <c r="B51" s="223"/>
+      <c r="C51" s="223"/>
+      <c r="D51" s="223"/>
+      <c r="E51" s="223"/>
+      <c r="F51" s="223"/>
+      <c r="G51" s="131" t="s">
         <v>59</v>
       </c>
-      <c r="H51" s="111"/>
-      <c r="I51" s="111"/>
-      <c r="J51" s="98"/>
-      <c r="K51" s="99"/>
-      <c r="L51" s="99"/>
-      <c r="M51" s="99"/>
-      <c r="N51" s="99"/>
-      <c r="O51" s="99"/>
-      <c r="P51" s="99"/>
-      <c r="Q51" s="99"/>
-      <c r="R51" s="100"/>
-      <c r="S51" s="104" t="s">
+      <c r="H51" s="132"/>
+      <c r="I51" s="132"/>
+      <c r="J51" s="135"/>
+      <c r="K51" s="136"/>
+      <c r="L51" s="136"/>
+      <c r="M51" s="136"/>
+      <c r="N51" s="136"/>
+      <c r="O51" s="136"/>
+      <c r="P51" s="136"/>
+      <c r="Q51" s="136"/>
+      <c r="R51" s="137"/>
+      <c r="S51" s="141" t="s">
         <v>61</v>
       </c>
-      <c r="T51" s="105"/>
-      <c r="U51" s="106"/>
-      <c r="V51" s="161" t="s">
+      <c r="T51" s="142"/>
+      <c r="U51" s="143"/>
+      <c r="V51" s="147" t="s">
         <v>91</v>
       </c>
-      <c r="W51" s="162"/>
-      <c r="X51" s="162"/>
-      <c r="Y51" s="162"/>
-      <c r="Z51" s="162"/>
-      <c r="AA51" s="162"/>
-      <c r="AB51" s="162"/>
-      <c r="AC51" s="162"/>
-      <c r="AD51" s="163"/>
-      <c r="AE51" s="172"/>
-      <c r="AF51" s="172"/>
-      <c r="AG51" s="172"/>
-      <c r="AH51" s="172"/>
-      <c r="AI51" s="172"/>
-      <c r="AJ51" s="170"/>
+      <c r="W51" s="148"/>
+      <c r="X51" s="148"/>
+      <c r="Y51" s="148"/>
+      <c r="Z51" s="148"/>
+      <c r="AA51" s="148"/>
+      <c r="AB51" s="148"/>
+      <c r="AC51" s="148"/>
+      <c r="AD51" s="149"/>
+      <c r="AE51" s="225"/>
+      <c r="AF51" s="225"/>
+      <c r="AG51" s="225"/>
+      <c r="AH51" s="225"/>
+      <c r="AI51" s="225"/>
+      <c r="AJ51" s="223"/>
       <c r="AK51" s="94"/>
     </row>
     <row r="52" spans="1:37" ht="12.75" customHeight="1" thickBot="1">
       <c r="A52" s="93"/>
-      <c r="B52" s="173"/>
-      <c r="C52" s="173"/>
-      <c r="D52" s="173"/>
-      <c r="E52" s="173"/>
-      <c r="F52" s="170"/>
-      <c r="G52" s="112"/>
-      <c r="H52" s="113"/>
-      <c r="I52" s="113"/>
-      <c r="J52" s="101"/>
-      <c r="K52" s="102"/>
-      <c r="L52" s="102"/>
-      <c r="M52" s="102"/>
-      <c r="N52" s="102"/>
-      <c r="O52" s="102"/>
-      <c r="P52" s="102"/>
-      <c r="Q52" s="102"/>
-      <c r="R52" s="103"/>
-      <c r="S52" s="107"/>
-      <c r="T52" s="108"/>
-      <c r="U52" s="109"/>
-      <c r="V52" s="164"/>
-      <c r="W52" s="165"/>
-      <c r="X52" s="165"/>
-      <c r="Y52" s="165"/>
-      <c r="Z52" s="165"/>
-      <c r="AA52" s="165"/>
-      <c r="AB52" s="165"/>
-      <c r="AC52" s="165"/>
-      <c r="AD52" s="166"/>
-      <c r="AE52" s="170"/>
-      <c r="AF52" s="170"/>
-      <c r="AG52" s="170"/>
-      <c r="AH52" s="170"/>
-      <c r="AI52" s="170"/>
-      <c r="AJ52" s="171"/>
+      <c r="B52" s="226"/>
+      <c r="C52" s="226"/>
+      <c r="D52" s="226"/>
+      <c r="E52" s="226"/>
+      <c r="F52" s="223"/>
+      <c r="G52" s="133"/>
+      <c r="H52" s="134"/>
+      <c r="I52" s="134"/>
+      <c r="J52" s="138"/>
+      <c r="K52" s="139"/>
+      <c r="L52" s="139"/>
+      <c r="M52" s="139"/>
+      <c r="N52" s="139"/>
+      <c r="O52" s="139"/>
+      <c r="P52" s="139"/>
+      <c r="Q52" s="139"/>
+      <c r="R52" s="140"/>
+      <c r="S52" s="144"/>
+      <c r="T52" s="145"/>
+      <c r="U52" s="146"/>
+      <c r="V52" s="150"/>
+      <c r="W52" s="151"/>
+      <c r="X52" s="151"/>
+      <c r="Y52" s="151"/>
+      <c r="Z52" s="151"/>
+      <c r="AA52" s="151"/>
+      <c r="AB52" s="151"/>
+      <c r="AC52" s="151"/>
+      <c r="AD52" s="152"/>
+      <c r="AE52" s="223"/>
+      <c r="AF52" s="223"/>
+      <c r="AG52" s="223"/>
+      <c r="AH52" s="223"/>
+      <c r="AI52" s="223"/>
+      <c r="AJ52" s="224"/>
       <c r="AK52" s="94"/>
     </row>
     <row r="53" spans="1:37" ht="12.75" customHeight="1">
       <c r="A53" s="93"/>
-      <c r="B53" s="170"/>
-      <c r="C53" s="170"/>
-      <c r="D53" s="170"/>
-      <c r="E53" s="170"/>
-      <c r="F53" s="170"/>
-      <c r="G53" s="110" t="s">
+      <c r="B53" s="223"/>
+      <c r="C53" s="223"/>
+      <c r="D53" s="223"/>
+      <c r="E53" s="223"/>
+      <c r="F53" s="223"/>
+      <c r="G53" s="131" t="s">
         <v>66</v>
       </c>
-      <c r="H53" s="111"/>
-      <c r="I53" s="111"/>
-      <c r="J53" s="98"/>
-      <c r="K53" s="99"/>
-      <c r="L53" s="99"/>
-      <c r="M53" s="99"/>
-      <c r="N53" s="99"/>
-      <c r="O53" s="99"/>
-      <c r="P53" s="99"/>
-      <c r="Q53" s="99"/>
-      <c r="R53" s="100"/>
-      <c r="S53" s="98"/>
-      <c r="T53" s="99"/>
-      <c r="U53" s="100"/>
-      <c r="V53" s="98"/>
-      <c r="W53" s="99"/>
-      <c r="X53" s="99"/>
-      <c r="Y53" s="99"/>
-      <c r="Z53" s="99"/>
-      <c r="AA53" s="99"/>
-      <c r="AB53" s="99"/>
-      <c r="AC53" s="99"/>
-      <c r="AD53" s="100"/>
-      <c r="AE53" s="170"/>
-      <c r="AF53" s="170"/>
-      <c r="AG53" s="170"/>
-      <c r="AH53" s="170"/>
-      <c r="AI53" s="170"/>
-      <c r="AJ53" s="171"/>
+      <c r="H53" s="132"/>
+      <c r="I53" s="132"/>
+      <c r="J53" s="135"/>
+      <c r="K53" s="136"/>
+      <c r="L53" s="136"/>
+      <c r="M53" s="136"/>
+      <c r="N53" s="136"/>
+      <c r="O53" s="136"/>
+      <c r="P53" s="136"/>
+      <c r="Q53" s="136"/>
+      <c r="R53" s="137"/>
+      <c r="S53" s="135"/>
+      <c r="T53" s="136"/>
+      <c r="U53" s="137"/>
+      <c r="V53" s="135"/>
+      <c r="W53" s="136"/>
+      <c r="X53" s="136"/>
+      <c r="Y53" s="136"/>
+      <c r="Z53" s="136"/>
+      <c r="AA53" s="136"/>
+      <c r="AB53" s="136"/>
+      <c r="AC53" s="136"/>
+      <c r="AD53" s="137"/>
+      <c r="AE53" s="223"/>
+      <c r="AF53" s="223"/>
+      <c r="AG53" s="223"/>
+      <c r="AH53" s="223"/>
+      <c r="AI53" s="223"/>
+      <c r="AJ53" s="224"/>
       <c r="AK53" s="94"/>
     </row>
     <row r="54" spans="1:37" ht="12.75" customHeight="1" thickBot="1">
       <c r="A54" s="93"/>
-      <c r="B54" s="170"/>
-      <c r="C54" s="170"/>
-      <c r="D54" s="170"/>
-      <c r="E54" s="170"/>
-      <c r="F54" s="170"/>
-      <c r="G54" s="112"/>
-      <c r="H54" s="113"/>
-      <c r="I54" s="113"/>
-      <c r="J54" s="101"/>
-      <c r="K54" s="102"/>
-      <c r="L54" s="102"/>
-      <c r="M54" s="102"/>
-      <c r="N54" s="102"/>
-      <c r="O54" s="102"/>
-      <c r="P54" s="102"/>
-      <c r="Q54" s="102"/>
-      <c r="R54" s="103"/>
-      <c r="S54" s="101"/>
-      <c r="T54" s="102"/>
-      <c r="U54" s="103"/>
-      <c r="V54" s="101"/>
-      <c r="W54" s="102"/>
-      <c r="X54" s="102"/>
-      <c r="Y54" s="102"/>
-      <c r="Z54" s="102"/>
-      <c r="AA54" s="102"/>
-      <c r="AB54" s="102"/>
-      <c r="AC54" s="102"/>
-      <c r="AD54" s="103"/>
-      <c r="AE54" s="170"/>
-      <c r="AF54" s="170"/>
-      <c r="AG54" s="170"/>
-      <c r="AH54" s="170"/>
-      <c r="AI54" s="170"/>
-      <c r="AJ54" s="171"/>
+      <c r="B54" s="223"/>
+      <c r="C54" s="223"/>
+      <c r="D54" s="223"/>
+      <c r="E54" s="223"/>
+      <c r="F54" s="223"/>
+      <c r="G54" s="133"/>
+      <c r="H54" s="134"/>
+      <c r="I54" s="134"/>
+      <c r="J54" s="138"/>
+      <c r="K54" s="139"/>
+      <c r="L54" s="139"/>
+      <c r="M54" s="139"/>
+      <c r="N54" s="139"/>
+      <c r="O54" s="139"/>
+      <c r="P54" s="139"/>
+      <c r="Q54" s="139"/>
+      <c r="R54" s="140"/>
+      <c r="S54" s="138"/>
+      <c r="T54" s="139"/>
+      <c r="U54" s="140"/>
+      <c r="V54" s="138"/>
+      <c r="W54" s="139"/>
+      <c r="X54" s="139"/>
+      <c r="Y54" s="139"/>
+      <c r="Z54" s="139"/>
+      <c r="AA54" s="139"/>
+      <c r="AB54" s="139"/>
+      <c r="AC54" s="139"/>
+      <c r="AD54" s="140"/>
+      <c r="AE54" s="223"/>
+      <c r="AF54" s="223"/>
+      <c r="AG54" s="223"/>
+      <c r="AH54" s="223"/>
+      <c r="AI54" s="223"/>
+      <c r="AJ54" s="224"/>
       <c r="AK54" s="94"/>
     </row>
     <row r="55" spans="1:37" ht="12.75" customHeight="1">
       <c r="A55" s="93"/>
-      <c r="B55" s="170"/>
-      <c r="C55" s="170"/>
-      <c r="D55" s="170"/>
-      <c r="E55" s="170"/>
-      <c r="F55" s="170"/>
-      <c r="G55" s="174"/>
-      <c r="H55" s="174"/>
-      <c r="I55" s="174"/>
-      <c r="J55" s="175"/>
-      <c r="K55" s="170"/>
-      <c r="L55" s="170"/>
-      <c r="M55" s="170"/>
-      <c r="N55" s="170"/>
-      <c r="O55" s="170"/>
-      <c r="P55" s="170"/>
-      <c r="Q55" s="170"/>
-      <c r="R55" s="170"/>
-      <c r="S55" s="174"/>
-      <c r="T55" s="174"/>
-      <c r="U55" s="174"/>
-      <c r="V55" s="174"/>
-      <c r="W55" s="174"/>
-      <c r="X55" s="174"/>
-      <c r="Y55" s="174"/>
-      <c r="Z55" s="174"/>
-      <c r="AA55" s="174"/>
-      <c r="AB55" s="174"/>
-      <c r="AC55" s="174"/>
-      <c r="AD55" s="174"/>
-      <c r="AE55" s="170"/>
-      <c r="AF55" s="170"/>
-      <c r="AG55" s="170"/>
-      <c r="AH55" s="170"/>
-      <c r="AI55" s="170"/>
-      <c r="AJ55" s="171"/>
+      <c r="B55" s="223"/>
+      <c r="C55" s="223"/>
+      <c r="D55" s="223"/>
+      <c r="E55" s="223"/>
+      <c r="F55" s="223"/>
+      <c r="G55" s="227"/>
+      <c r="H55" s="227"/>
+      <c r="I55" s="227"/>
+      <c r="J55" s="228"/>
+      <c r="K55" s="223"/>
+      <c r="L55" s="223"/>
+      <c r="M55" s="223"/>
+      <c r="N55" s="223"/>
+      <c r="O55" s="223"/>
+      <c r="P55" s="223"/>
+      <c r="Q55" s="223"/>
+      <c r="R55" s="223"/>
+      <c r="S55" s="227"/>
+      <c r="T55" s="227"/>
+      <c r="U55" s="227"/>
+      <c r="V55" s="227"/>
+      <c r="W55" s="227"/>
+      <c r="X55" s="227"/>
+      <c r="Y55" s="227"/>
+      <c r="Z55" s="227"/>
+      <c r="AA55" s="227"/>
+      <c r="AB55" s="227"/>
+      <c r="AC55" s="227"/>
+      <c r="AD55" s="227"/>
+      <c r="AE55" s="223"/>
+      <c r="AF55" s="223"/>
+      <c r="AG55" s="223"/>
+      <c r="AH55" s="223"/>
+      <c r="AI55" s="223"/>
+      <c r="AJ55" s="224"/>
       <c r="AK55" s="94"/>
     </row>
     <row r="56" spans="1:37" ht="12.75" customHeight="1">
       <c r="A56" s="93"/>
-      <c r="B56" s="170"/>
-      <c r="C56" s="170"/>
-      <c r="D56" s="170"/>
-      <c r="E56" s="170"/>
-      <c r="F56" s="170"/>
-      <c r="G56" s="174"/>
-      <c r="H56" s="174"/>
-      <c r="I56" s="174"/>
-      <c r="J56" s="175"/>
-      <c r="K56" s="170"/>
-      <c r="L56" s="170"/>
-      <c r="M56" s="170"/>
-      <c r="N56" s="170"/>
-      <c r="O56" s="170"/>
-      <c r="P56" s="170"/>
-      <c r="Q56" s="170"/>
-      <c r="R56" s="170"/>
-      <c r="S56" s="174"/>
-      <c r="T56" s="174"/>
-      <c r="U56" s="174"/>
-      <c r="V56" s="174"/>
-      <c r="W56" s="174"/>
-      <c r="X56" s="174"/>
-      <c r="Y56" s="174"/>
-      <c r="Z56" s="174"/>
-      <c r="AA56" s="174"/>
-      <c r="AB56" s="174"/>
-      <c r="AC56" s="174"/>
-      <c r="AD56" s="174"/>
-      <c r="AE56" s="170"/>
-      <c r="AF56" s="170"/>
-      <c r="AG56" s="170"/>
-      <c r="AH56" s="170"/>
-      <c r="AI56" s="170"/>
-      <c r="AJ56" s="171"/>
+      <c r="B56" s="223"/>
+      <c r="C56" s="223"/>
+      <c r="D56" s="223"/>
+      <c r="E56" s="223"/>
+      <c r="F56" s="223"/>
+      <c r="G56" s="227"/>
+      <c r="H56" s="227"/>
+      <c r="I56" s="227"/>
+      <c r="J56" s="228"/>
+      <c r="K56" s="223"/>
+      <c r="L56" s="223"/>
+      <c r="M56" s="223"/>
+      <c r="N56" s="223"/>
+      <c r="O56" s="223"/>
+      <c r="P56" s="223"/>
+      <c r="Q56" s="223"/>
+      <c r="R56" s="223"/>
+      <c r="S56" s="227"/>
+      <c r="T56" s="227"/>
+      <c r="U56" s="227"/>
+      <c r="V56" s="227"/>
+      <c r="W56" s="227"/>
+      <c r="X56" s="227"/>
+      <c r="Y56" s="227"/>
+      <c r="Z56" s="227"/>
+      <c r="AA56" s="227"/>
+      <c r="AB56" s="227"/>
+      <c r="AC56" s="227"/>
+      <c r="AD56" s="227"/>
+      <c r="AE56" s="223"/>
+      <c r="AF56" s="223"/>
+      <c r="AG56" s="223"/>
+      <c r="AH56" s="223"/>
+      <c r="AI56" s="223"/>
+      <c r="AJ56" s="224"/>
       <c r="AK56" s="94"/>
     </row>
     <row r="57" spans="1:37" ht="12.75" customHeight="1">
       <c r="A57" s="93"/>
-      <c r="B57" s="170"/>
-      <c r="C57" s="170"/>
-      <c r="D57" s="170"/>
-      <c r="E57" s="170"/>
-      <c r="F57" s="170"/>
-      <c r="G57" s="170"/>
-      <c r="H57" s="170"/>
-      <c r="I57" s="170"/>
-      <c r="J57" s="175"/>
-      <c r="K57" s="170"/>
-      <c r="L57" s="170"/>
-      <c r="M57" s="170"/>
-      <c r="N57" s="170"/>
-      <c r="O57" s="170"/>
-      <c r="P57" s="170"/>
-      <c r="Q57" s="170"/>
-      <c r="R57" s="170"/>
-      <c r="S57" s="170"/>
-      <c r="T57" s="170"/>
-      <c r="U57" s="170"/>
-      <c r="V57" s="170"/>
-      <c r="W57" s="175"/>
-      <c r="X57" s="170"/>
-      <c r="Y57" s="170"/>
-      <c r="Z57" s="175"/>
-      <c r="AA57" s="170"/>
-      <c r="AB57" s="170"/>
-      <c r="AC57" s="170"/>
-      <c r="AD57" s="170"/>
-      <c r="AE57" s="170"/>
-      <c r="AF57" s="170"/>
-      <c r="AG57" s="170"/>
-      <c r="AH57" s="170"/>
-      <c r="AI57" s="170"/>
-      <c r="AJ57" s="171"/>
+      <c r="B57" s="223"/>
+      <c r="C57" s="223"/>
+      <c r="D57" s="223"/>
+      <c r="E57" s="223"/>
+      <c r="F57" s="223"/>
+      <c r="G57" s="223"/>
+      <c r="H57" s="223"/>
+      <c r="I57" s="223"/>
+      <c r="J57" s="228"/>
+      <c r="K57" s="223"/>
+      <c r="L57" s="223"/>
+      <c r="M57" s="223"/>
+      <c r="N57" s="223"/>
+      <c r="O57" s="223"/>
+      <c r="P57" s="223"/>
+      <c r="Q57" s="223"/>
+      <c r="R57" s="223"/>
+      <c r="S57" s="223"/>
+      <c r="T57" s="223"/>
+      <c r="U57" s="223"/>
+      <c r="V57" s="223"/>
+      <c r="W57" s="228"/>
+      <c r="X57" s="223"/>
+      <c r="Y57" s="223"/>
+      <c r="Z57" s="228"/>
+      <c r="AA57" s="223"/>
+      <c r="AB57" s="223"/>
+      <c r="AC57" s="223"/>
+      <c r="AD57" s="223"/>
+      <c r="AE57" s="223"/>
+      <c r="AF57" s="223"/>
+      <c r="AG57" s="223"/>
+      <c r="AH57" s="223"/>
+      <c r="AI57" s="223"/>
+      <c r="AJ57" s="224"/>
       <c r="AK57" s="94"/>
     </row>
     <row r="58" spans="1:37" ht="12.75" customHeight="1">
       <c r="A58" s="93"/>
-      <c r="B58" s="170"/>
-      <c r="C58" s="170"/>
-      <c r="D58" s="170"/>
-      <c r="E58" s="170"/>
-      <c r="F58" s="170"/>
-      <c r="G58" s="170"/>
-      <c r="H58" s="170"/>
-      <c r="I58" s="170"/>
-      <c r="J58" s="175"/>
-      <c r="K58" s="170"/>
-      <c r="L58" s="170"/>
-      <c r="M58" s="170"/>
-      <c r="N58" s="170"/>
-      <c r="O58" s="170"/>
-      <c r="P58" s="170"/>
-      <c r="Q58" s="170"/>
-      <c r="R58" s="170"/>
-      <c r="S58" s="170"/>
-      <c r="T58" s="170"/>
-      <c r="U58" s="170"/>
-      <c r="V58" s="170"/>
-      <c r="W58" s="175"/>
-      <c r="X58" s="170"/>
-      <c r="Y58" s="170"/>
-      <c r="Z58" s="175"/>
-      <c r="AA58" s="170"/>
-      <c r="AB58" s="170"/>
-      <c r="AC58" s="170"/>
-      <c r="AD58" s="170"/>
-      <c r="AE58" s="170"/>
-      <c r="AF58" s="170"/>
-      <c r="AG58" s="170"/>
-      <c r="AH58" s="170"/>
-      <c r="AI58" s="170"/>
-      <c r="AJ58" s="171"/>
+      <c r="B58" s="223"/>
+      <c r="C58" s="223"/>
+      <c r="D58" s="223"/>
+      <c r="E58" s="223"/>
+      <c r="F58" s="223"/>
+      <c r="G58" s="223"/>
+      <c r="H58" s="223"/>
+      <c r="I58" s="223"/>
+      <c r="J58" s="228"/>
+      <c r="K58" s="223"/>
+      <c r="L58" s="223"/>
+      <c r="M58" s="223"/>
+      <c r="N58" s="223"/>
+      <c r="O58" s="223"/>
+      <c r="P58" s="223"/>
+      <c r="Q58" s="223"/>
+      <c r="R58" s="223"/>
+      <c r="S58" s="223"/>
+      <c r="T58" s="223"/>
+      <c r="U58" s="223"/>
+      <c r="V58" s="223"/>
+      <c r="W58" s="228"/>
+      <c r="X58" s="223"/>
+      <c r="Y58" s="223"/>
+      <c r="Z58" s="228"/>
+      <c r="AA58" s="223"/>
+      <c r="AB58" s="223"/>
+      <c r="AC58" s="223"/>
+      <c r="AD58" s="223"/>
+      <c r="AE58" s="223"/>
+      <c r="AF58" s="223"/>
+      <c r="AG58" s="223"/>
+      <c r="AH58" s="223"/>
+      <c r="AI58" s="223"/>
+      <c r="AJ58" s="224"/>
       <c r="AK58" s="94"/>
     </row>
     <row r="59" spans="1:37" ht="12.75" customHeight="1" thickBot="1">
       <c r="A59" s="93"/>
-      <c r="B59" s="170"/>
-      <c r="C59" s="170"/>
-      <c r="D59" s="170"/>
-      <c r="E59" s="170"/>
-      <c r="F59" s="170"/>
-      <c r="G59" s="170"/>
-      <c r="H59" s="170"/>
-      <c r="I59" s="170"/>
-      <c r="J59" s="175"/>
-      <c r="K59" s="170"/>
-      <c r="L59" s="170"/>
-      <c r="M59" s="170"/>
-      <c r="N59" s="170"/>
-      <c r="O59" s="170"/>
-      <c r="P59" s="170"/>
-      <c r="Q59" s="170"/>
-      <c r="R59" s="170"/>
-      <c r="S59" s="170"/>
-      <c r="T59" s="175"/>
-      <c r="U59" s="170"/>
-      <c r="V59" s="170"/>
-      <c r="W59" s="175"/>
-      <c r="X59" s="170"/>
-      <c r="Y59" s="170"/>
-      <c r="Z59" s="175"/>
-      <c r="AA59" s="170"/>
-      <c r="AB59" s="170"/>
-      <c r="AC59" s="170"/>
-      <c r="AD59" s="170"/>
-      <c r="AE59" s="170"/>
-      <c r="AF59" s="170"/>
-      <c r="AG59" s="170"/>
-      <c r="AH59" s="170"/>
-      <c r="AI59" s="170"/>
-      <c r="AJ59" s="171"/>
+      <c r="B59" s="223"/>
+      <c r="C59" s="223"/>
+      <c r="D59" s="223"/>
+      <c r="E59" s="223"/>
+      <c r="F59" s="223"/>
+      <c r="G59" s="223"/>
+      <c r="H59" s="223"/>
+      <c r="I59" s="223"/>
+      <c r="J59" s="228"/>
+      <c r="K59" s="223"/>
+      <c r="L59" s="223"/>
+      <c r="M59" s="223"/>
+      <c r="N59" s="223"/>
+      <c r="O59" s="223"/>
+      <c r="P59" s="223"/>
+      <c r="Q59" s="223"/>
+      <c r="R59" s="223"/>
+      <c r="S59" s="223"/>
+      <c r="T59" s="228"/>
+      <c r="U59" s="223"/>
+      <c r="V59" s="223"/>
+      <c r="W59" s="228"/>
+      <c r="X59" s="223"/>
+      <c r="Y59" s="223"/>
+      <c r="Z59" s="228"/>
+      <c r="AA59" s="223"/>
+      <c r="AB59" s="223"/>
+      <c r="AC59" s="223"/>
+      <c r="AD59" s="223"/>
+      <c r="AE59" s="223"/>
+      <c r="AF59" s="223"/>
+      <c r="AG59" s="223"/>
+      <c r="AH59" s="223"/>
+      <c r="AI59" s="223"/>
+      <c r="AJ59" s="224"/>
       <c r="AK59" s="94"/>
     </row>
     <row r="60" spans="1:37" ht="12.75" customHeight="1">
       <c r="A60" s="93"/>
-      <c r="B60" s="215" t="s">
+      <c r="B60" s="129" t="s">
         <v>94</v>
       </c>
-      <c r="C60" s="216" t="s">
+      <c r="C60" s="123" t="s">
         <v>95</v>
       </c>
-      <c r="D60" s="217"/>
-      <c r="E60" s="218"/>
-      <c r="F60" s="216" t="s">
+      <c r="D60" s="124"/>
+      <c r="E60" s="125"/>
+      <c r="F60" s="123" t="s">
         <v>96</v>
       </c>
-      <c r="G60" s="217"/>
-      <c r="H60" s="218"/>
-      <c r="I60" s="216" t="s">
+      <c r="G60" s="124"/>
+      <c r="H60" s="125"/>
+      <c r="I60" s="123" t="s">
         <v>97</v>
       </c>
-      <c r="J60" s="217"/>
-      <c r="K60" s="218"/>
-      <c r="L60" s="216" t="s">
+      <c r="J60" s="124"/>
+      <c r="K60" s="125"/>
+      <c r="L60" s="123" t="s">
         <v>98</v>
       </c>
-      <c r="M60" s="217"/>
-      <c r="N60" s="218"/>
-      <c r="O60" s="216" t="s">
+      <c r="M60" s="124"/>
+      <c r="N60" s="125"/>
+      <c r="O60" s="123" t="s">
         <v>99</v>
       </c>
-      <c r="P60" s="217"/>
-      <c r="Q60" s="217"/>
-      <c r="R60" s="217"/>
-      <c r="S60" s="218"/>
-      <c r="T60" s="215" t="s">
+      <c r="P60" s="124"/>
+      <c r="Q60" s="124"/>
+      <c r="R60" s="124"/>
+      <c r="S60" s="125"/>
+      <c r="T60" s="129" t="s">
         <v>100</v>
       </c>
-      <c r="U60" s="216" t="s">
+      <c r="U60" s="123" t="s">
         <v>101</v>
       </c>
-      <c r="V60" s="217"/>
-      <c r="W60" s="218"/>
-      <c r="X60" s="216" t="s">
+      <c r="V60" s="124"/>
+      <c r="W60" s="125"/>
+      <c r="X60" s="123" t="s">
         <v>102</v>
       </c>
-      <c r="Y60" s="217"/>
-      <c r="Z60" s="218"/>
-      <c r="AA60" s="216" t="s">
+      <c r="Y60" s="124"/>
+      <c r="Z60" s="125"/>
+      <c r="AA60" s="123" t="s">
         <v>103</v>
       </c>
-      <c r="AB60" s="217"/>
-      <c r="AC60" s="218"/>
-      <c r="AD60" s="216" t="s">
+      <c r="AB60" s="124"/>
+      <c r="AC60" s="125"/>
+      <c r="AD60" s="123" t="s">
         <v>104</v>
       </c>
-      <c r="AE60" s="217"/>
-      <c r="AF60" s="218"/>
-      <c r="AG60" s="216" t="s">
+      <c r="AE60" s="124"/>
+      <c r="AF60" s="125"/>
+      <c r="AG60" s="123" t="s">
         <v>105</v>
       </c>
-      <c r="AH60" s="217"/>
-      <c r="AI60" s="217"/>
-      <c r="AJ60" s="218"/>
+      <c r="AH60" s="124"/>
+      <c r="AI60" s="124"/>
+      <c r="AJ60" s="125"/>
       <c r="AK60" s="94"/>
     </row>
     <row r="61" spans="1:37" ht="12.75" customHeight="1" thickBot="1">
       <c r="A61" s="93"/>
-      <c r="B61" s="219"/>
-      <c r="C61" s="220"/>
-      <c r="D61" s="221"/>
-      <c r="E61" s="222"/>
-      <c r="F61" s="220"/>
-      <c r="G61" s="221"/>
-      <c r="H61" s="222"/>
-      <c r="I61" s="220"/>
-      <c r="J61" s="221"/>
-      <c r="K61" s="222"/>
-      <c r="L61" s="220"/>
-      <c r="M61" s="221"/>
-      <c r="N61" s="222"/>
-      <c r="O61" s="220"/>
-      <c r="P61" s="221"/>
-      <c r="Q61" s="221"/>
-      <c r="R61" s="221"/>
-      <c r="S61" s="222"/>
-      <c r="T61" s="219"/>
-      <c r="U61" s="220"/>
-      <c r="V61" s="221"/>
-      <c r="W61" s="222"/>
-      <c r="X61" s="220"/>
-      <c r="Y61" s="221"/>
-      <c r="Z61" s="222"/>
-      <c r="AA61" s="220"/>
-      <c r="AB61" s="221"/>
-      <c r="AC61" s="222"/>
-      <c r="AD61" s="220"/>
-      <c r="AE61" s="221"/>
-      <c r="AF61" s="222"/>
-      <c r="AG61" s="220"/>
-      <c r="AH61" s="221"/>
-      <c r="AI61" s="221"/>
-      <c r="AJ61" s="222"/>
+      <c r="B61" s="130"/>
+      <c r="C61" s="126"/>
+      <c r="D61" s="127"/>
+      <c r="E61" s="128"/>
+      <c r="F61" s="126"/>
+      <c r="G61" s="127"/>
+      <c r="H61" s="128"/>
+      <c r="I61" s="126"/>
+      <c r="J61" s="127"/>
+      <c r="K61" s="128"/>
+      <c r="L61" s="126"/>
+      <c r="M61" s="127"/>
+      <c r="N61" s="128"/>
+      <c r="O61" s="126"/>
+      <c r="P61" s="127"/>
+      <c r="Q61" s="127"/>
+      <c r="R61" s="127"/>
+      <c r="S61" s="128"/>
+      <c r="T61" s="130"/>
+      <c r="U61" s="126"/>
+      <c r="V61" s="127"/>
+      <c r="W61" s="128"/>
+      <c r="X61" s="126"/>
+      <c r="Y61" s="127"/>
+      <c r="Z61" s="128"/>
+      <c r="AA61" s="126"/>
+      <c r="AB61" s="127"/>
+      <c r="AC61" s="128"/>
+      <c r="AD61" s="126"/>
+      <c r="AE61" s="127"/>
+      <c r="AF61" s="128"/>
+      <c r="AG61" s="126"/>
+      <c r="AH61" s="127"/>
+      <c r="AI61" s="127"/>
+      <c r="AJ61" s="128"/>
       <c r="AK61" s="94"/>
     </row>
     <row r="62" spans="1:37" ht="12.5" customHeight="1">
       <c r="A62" s="93"/>
-      <c r="B62" s="193">
+      <c r="B62" s="121">
         <v>135</v>
       </c>
-      <c r="C62" s="195"/>
-      <c r="D62" s="196"/>
-      <c r="E62" s="197"/>
-      <c r="F62" s="195"/>
-      <c r="G62" s="196"/>
-      <c r="H62" s="197"/>
-      <c r="I62" s="195"/>
-      <c r="J62" s="196"/>
-      <c r="K62" s="197"/>
-      <c r="L62" s="195"/>
-      <c r="M62" s="196"/>
-      <c r="N62" s="197"/>
-      <c r="O62" s="195"/>
-      <c r="P62" s="196"/>
-      <c r="Q62" s="196"/>
-      <c r="R62" s="196"/>
-      <c r="S62" s="197"/>
-      <c r="T62" s="193"/>
-      <c r="U62" s="195"/>
-      <c r="V62" s="196"/>
-      <c r="W62" s="197"/>
-      <c r="X62" s="201"/>
-      <c r="Y62" s="202"/>
-      <c r="Z62" s="203"/>
-      <c r="AA62" s="195"/>
-      <c r="AB62" s="196"/>
-      <c r="AC62" s="197"/>
-      <c r="AD62" s="195"/>
-      <c r="AE62" s="196"/>
-      <c r="AF62" s="197"/>
-      <c r="AG62" s="207"/>
-      <c r="AH62" s="208"/>
-      <c r="AI62" s="211"/>
-      <c r="AJ62" s="212"/>
+      <c r="C62" s="109" t="s">
+        <v>106</v>
+      </c>
+      <c r="D62" s="110"/>
+      <c r="E62" s="111"/>
+      <c r="F62" s="109" t="s">
+        <v>107</v>
+      </c>
+      <c r="G62" s="110"/>
+      <c r="H62" s="111"/>
+      <c r="I62" s="109" t="s">
+        <v>108</v>
+      </c>
+      <c r="J62" s="110"/>
+      <c r="K62" s="111"/>
+      <c r="L62" s="109" t="s">
+        <v>109</v>
+      </c>
+      <c r="M62" s="110"/>
+      <c r="N62" s="111"/>
+      <c r="O62" s="109" t="s">
+        <v>110</v>
+      </c>
+      <c r="P62" s="110"/>
+      <c r="Q62" s="110"/>
+      <c r="R62" s="110"/>
+      <c r="S62" s="111"/>
+      <c r="T62" s="121" t="s">
+        <v>111</v>
+      </c>
+      <c r="U62" s="109" t="s">
+        <v>112</v>
+      </c>
+      <c r="V62" s="110"/>
+      <c r="W62" s="111"/>
+      <c r="X62" s="115" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y62" s="116"/>
+      <c r="Z62" s="117"/>
+      <c r="AA62" s="212" t="s">
+        <v>115</v>
+      </c>
+      <c r="AB62" s="213"/>
+      <c r="AC62" s="214"/>
+      <c r="AD62" s="212" t="s">
+        <v>117</v>
+      </c>
+      <c r="AE62" s="213"/>
+      <c r="AF62" s="214"/>
+      <c r="AG62" s="105"/>
+      <c r="AH62" s="107"/>
+      <c r="AI62" s="210"/>
+      <c r="AJ62" s="107"/>
       <c r="AK62" s="94"/>
     </row>
     <row r="63" spans="1:37" ht="12.5" customHeight="1" thickBot="1">
       <c r="A63" s="93"/>
-      <c r="B63" s="194"/>
-      <c r="C63" s="198"/>
-      <c r="D63" s="199"/>
-      <c r="E63" s="200"/>
-      <c r="F63" s="198"/>
-      <c r="G63" s="199"/>
-      <c r="H63" s="200"/>
-      <c r="I63" s="198"/>
-      <c r="J63" s="199"/>
-      <c r="K63" s="200"/>
-      <c r="L63" s="198"/>
-      <c r="M63" s="199"/>
-      <c r="N63" s="200"/>
-      <c r="O63" s="198"/>
-      <c r="P63" s="199"/>
-      <c r="Q63" s="199"/>
-      <c r="R63" s="199"/>
-      <c r="S63" s="200"/>
-      <c r="T63" s="194"/>
-      <c r="U63" s="198"/>
-      <c r="V63" s="199"/>
-      <c r="W63" s="200"/>
-      <c r="X63" s="204"/>
-      <c r="Y63" s="205"/>
-      <c r="Z63" s="206"/>
-      <c r="AA63" s="198"/>
-      <c r="AB63" s="199"/>
-      <c r="AC63" s="200"/>
-      <c r="AD63" s="198"/>
-      <c r="AE63" s="199"/>
-      <c r="AF63" s="200"/>
-      <c r="AG63" s="209"/>
-      <c r="AH63" s="210"/>
-      <c r="AI63" s="213"/>
-      <c r="AJ63" s="214"/>
+      <c r="B63" s="122"/>
+      <c r="C63" s="112"/>
+      <c r="D63" s="113"/>
+      <c r="E63" s="114"/>
+      <c r="F63" s="112"/>
+      <c r="G63" s="113"/>
+      <c r="H63" s="114"/>
+      <c r="I63" s="112"/>
+      <c r="J63" s="113"/>
+      <c r="K63" s="114"/>
+      <c r="L63" s="112"/>
+      <c r="M63" s="113"/>
+      <c r="N63" s="114"/>
+      <c r="O63" s="112"/>
+      <c r="P63" s="113"/>
+      <c r="Q63" s="113"/>
+      <c r="R63" s="113"/>
+      <c r="S63" s="114"/>
+      <c r="T63" s="122"/>
+      <c r="U63" s="112"/>
+      <c r="V63" s="113"/>
+      <c r="W63" s="114"/>
+      <c r="X63" s="118"/>
+      <c r="Y63" s="119"/>
+      <c r="Z63" s="120"/>
+      <c r="AA63" s="215"/>
+      <c r="AB63" s="216"/>
+      <c r="AC63" s="217"/>
+      <c r="AD63" s="215"/>
+      <c r="AE63" s="216"/>
+      <c r="AF63" s="217"/>
+      <c r="AG63" s="106"/>
+      <c r="AH63" s="108"/>
+      <c r="AI63" s="211"/>
+      <c r="AJ63" s="108"/>
       <c r="AK63" s="94"/>
     </row>
     <row r="64" spans="1:37" ht="12.5" customHeight="1">
       <c r="A64" s="93"/>
-      <c r="B64" s="192">
+      <c r="B64" s="121">
         <v>134</v>
       </c>
-      <c r="C64" s="195"/>
-      <c r="D64" s="196"/>
-      <c r="E64" s="197"/>
-      <c r="F64" s="195"/>
-      <c r="G64" s="196"/>
-      <c r="H64" s="197"/>
-      <c r="I64" s="195"/>
-      <c r="J64" s="196"/>
-      <c r="K64" s="197"/>
-      <c r="L64" s="195"/>
-      <c r="M64" s="196"/>
-      <c r="N64" s="197"/>
-      <c r="O64" s="195"/>
-      <c r="P64" s="196"/>
-      <c r="Q64" s="196"/>
-      <c r="R64" s="196"/>
-      <c r="S64" s="197"/>
-      <c r="T64" s="193"/>
-      <c r="U64" s="195"/>
-      <c r="V64" s="196"/>
-      <c r="W64" s="197"/>
-      <c r="X64" s="201"/>
-      <c r="Y64" s="202"/>
-      <c r="Z64" s="203"/>
-      <c r="AA64" s="195"/>
-      <c r="AB64" s="196"/>
-      <c r="AC64" s="197"/>
-      <c r="AD64" s="195"/>
-      <c r="AE64" s="196"/>
-      <c r="AF64" s="197"/>
-      <c r="AG64" s="207"/>
-      <c r="AH64" s="208"/>
-      <c r="AI64" s="211"/>
-      <c r="AJ64" s="212"/>
+      <c r="C64" s="109" t="s">
+        <v>126</v>
+      </c>
+      <c r="D64" s="110"/>
+      <c r="E64" s="111"/>
+      <c r="F64" s="109" t="s">
+        <v>127</v>
+      </c>
+      <c r="G64" s="110"/>
+      <c r="H64" s="111"/>
+      <c r="I64" s="109" t="s">
+        <v>128</v>
+      </c>
+      <c r="J64" s="110"/>
+      <c r="K64" s="111"/>
+      <c r="L64" s="109" t="s">
+        <v>129</v>
+      </c>
+      <c r="M64" s="110"/>
+      <c r="N64" s="111"/>
+      <c r="O64" s="109" t="s">
+        <v>122</v>
+      </c>
+      <c r="P64" s="110"/>
+      <c r="Q64" s="110"/>
+      <c r="R64" s="110"/>
+      <c r="S64" s="111"/>
+      <c r="T64" s="121" t="s">
+        <v>111</v>
+      </c>
+      <c r="U64" s="109" t="s">
+        <v>112</v>
+      </c>
+      <c r="V64" s="110"/>
+      <c r="W64" s="111"/>
+      <c r="X64" s="115" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y64" s="116"/>
+      <c r="Z64" s="117"/>
+      <c r="AA64" s="212" t="s">
+        <v>116</v>
+      </c>
+      <c r="AB64" s="213"/>
+      <c r="AC64" s="214"/>
+      <c r="AD64" s="212" t="s">
+        <v>115</v>
+      </c>
+      <c r="AE64" s="213"/>
+      <c r="AF64" s="214"/>
+      <c r="AG64" s="105"/>
+      <c r="AH64" s="107"/>
+      <c r="AI64" s="210"/>
+      <c r="AJ64" s="107"/>
       <c r="AK64" s="94"/>
     </row>
     <row r="65" spans="1:37" ht="12.5" customHeight="1" thickBot="1">
       <c r="A65" s="93"/>
-      <c r="B65" s="191"/>
-      <c r="C65" s="198"/>
-      <c r="D65" s="199"/>
-      <c r="E65" s="200"/>
-      <c r="F65" s="198"/>
-      <c r="G65" s="199"/>
-      <c r="H65" s="200"/>
-      <c r="I65" s="198"/>
-      <c r="J65" s="199"/>
-      <c r="K65" s="200"/>
-      <c r="L65" s="198"/>
-      <c r="M65" s="199"/>
-      <c r="N65" s="200"/>
-      <c r="O65" s="198"/>
-      <c r="P65" s="199"/>
-      <c r="Q65" s="199"/>
-      <c r="R65" s="199"/>
-      <c r="S65" s="200"/>
-      <c r="T65" s="194"/>
-      <c r="U65" s="198"/>
-      <c r="V65" s="199"/>
-      <c r="W65" s="200"/>
-      <c r="X65" s="204"/>
-      <c r="Y65" s="205"/>
-      <c r="Z65" s="206"/>
-      <c r="AA65" s="198"/>
-      <c r="AB65" s="199"/>
-      <c r="AC65" s="200"/>
-      <c r="AD65" s="198"/>
-      <c r="AE65" s="199"/>
-      <c r="AF65" s="200"/>
-      <c r="AG65" s="209"/>
-      <c r="AH65" s="210"/>
-      <c r="AI65" s="213"/>
-      <c r="AJ65" s="214"/>
+      <c r="B65" s="122"/>
+      <c r="C65" s="112"/>
+      <c r="D65" s="113"/>
+      <c r="E65" s="114"/>
+      <c r="F65" s="112"/>
+      <c r="G65" s="113"/>
+      <c r="H65" s="114"/>
+      <c r="I65" s="112"/>
+      <c r="J65" s="113"/>
+      <c r="K65" s="114"/>
+      <c r="L65" s="112"/>
+      <c r="M65" s="113"/>
+      <c r="N65" s="114"/>
+      <c r="O65" s="112"/>
+      <c r="P65" s="113"/>
+      <c r="Q65" s="113"/>
+      <c r="R65" s="113"/>
+      <c r="S65" s="114"/>
+      <c r="T65" s="122"/>
+      <c r="U65" s="112"/>
+      <c r="V65" s="113"/>
+      <c r="W65" s="114"/>
+      <c r="X65" s="118"/>
+      <c r="Y65" s="119"/>
+      <c r="Z65" s="120"/>
+      <c r="AA65" s="215"/>
+      <c r="AB65" s="216"/>
+      <c r="AC65" s="217"/>
+      <c r="AD65" s="215"/>
+      <c r="AE65" s="216"/>
+      <c r="AF65" s="217"/>
+      <c r="AG65" s="106"/>
+      <c r="AH65" s="108"/>
+      <c r="AI65" s="211"/>
+      <c r="AJ65" s="108"/>
       <c r="AK65" s="94"/>
     </row>
     <row r="66" spans="1:37" ht="12.5" customHeight="1">
       <c r="A66" s="93"/>
-      <c r="B66" s="191">
+      <c r="B66" s="121">
         <v>133</v>
       </c>
-      <c r="C66" s="195"/>
-      <c r="D66" s="196"/>
-      <c r="E66" s="197"/>
-      <c r="F66" s="195"/>
-      <c r="G66" s="196"/>
-      <c r="H66" s="197"/>
-      <c r="I66" s="195"/>
-      <c r="J66" s="196"/>
-      <c r="K66" s="197"/>
-      <c r="L66" s="195"/>
-      <c r="M66" s="196"/>
-      <c r="N66" s="197"/>
-      <c r="O66" s="195"/>
-      <c r="P66" s="196"/>
-      <c r="Q66" s="196"/>
-      <c r="R66" s="196"/>
-      <c r="S66" s="197"/>
-      <c r="T66" s="193"/>
-      <c r="U66" s="195"/>
-      <c r="V66" s="196"/>
-      <c r="W66" s="197"/>
-      <c r="X66" s="201"/>
-      <c r="Y66" s="202"/>
-      <c r="Z66" s="203"/>
-      <c r="AA66" s="195"/>
-      <c r="AB66" s="196"/>
-      <c r="AC66" s="197"/>
-      <c r="AD66" s="195"/>
-      <c r="AE66" s="196"/>
-      <c r="AF66" s="197"/>
-      <c r="AG66" s="207"/>
-      <c r="AH66" s="208"/>
-      <c r="AI66" s="211"/>
-      <c r="AJ66" s="212"/>
+      <c r="C66" s="109" t="s">
+        <v>133</v>
+      </c>
+      <c r="D66" s="110"/>
+      <c r="E66" s="111"/>
+      <c r="F66" s="109" t="s">
+        <v>132</v>
+      </c>
+      <c r="G66" s="110"/>
+      <c r="H66" s="111"/>
+      <c r="I66" s="109" t="s">
+        <v>131</v>
+      </c>
+      <c r="J66" s="110"/>
+      <c r="K66" s="111"/>
+      <c r="L66" s="109" t="s">
+        <v>130</v>
+      </c>
+      <c r="M66" s="110"/>
+      <c r="N66" s="111"/>
+      <c r="O66" s="109" t="s">
+        <v>123</v>
+      </c>
+      <c r="P66" s="110"/>
+      <c r="Q66" s="110"/>
+      <c r="R66" s="110"/>
+      <c r="S66" s="111"/>
+      <c r="T66" s="121" t="s">
+        <v>111</v>
+      </c>
+      <c r="U66" s="109" t="s">
+        <v>112</v>
+      </c>
+      <c r="V66" s="110"/>
+      <c r="W66" s="111"/>
+      <c r="X66" s="115" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y66" s="116"/>
+      <c r="Z66" s="117"/>
+      <c r="AA66" s="212" t="s">
+        <v>119</v>
+      </c>
+      <c r="AB66" s="213"/>
+      <c r="AC66" s="214"/>
+      <c r="AD66" s="212" t="s">
+        <v>115</v>
+      </c>
+      <c r="AE66" s="213"/>
+      <c r="AF66" s="214"/>
+      <c r="AG66" s="105"/>
+      <c r="AH66" s="107"/>
+      <c r="AI66" s="210"/>
+      <c r="AJ66" s="107"/>
       <c r="AK66" s="94"/>
     </row>
     <row r="67" spans="1:37" ht="12.5" customHeight="1" thickBot="1">
       <c r="A67" s="93"/>
-      <c r="B67" s="191"/>
-      <c r="C67" s="198"/>
-      <c r="D67" s="199"/>
-      <c r="E67" s="200"/>
-      <c r="F67" s="198"/>
-      <c r="G67" s="199"/>
-      <c r="H67" s="200"/>
-      <c r="I67" s="198"/>
-      <c r="J67" s="199"/>
-      <c r="K67" s="200"/>
-      <c r="L67" s="198"/>
-      <c r="M67" s="199"/>
-      <c r="N67" s="200"/>
-      <c r="O67" s="198"/>
-      <c r="P67" s="199"/>
-      <c r="Q67" s="199"/>
-      <c r="R67" s="199"/>
-      <c r="S67" s="200"/>
-      <c r="T67" s="194"/>
-      <c r="U67" s="198"/>
-      <c r="V67" s="199"/>
-      <c r="W67" s="200"/>
-      <c r="X67" s="204"/>
-      <c r="Y67" s="205"/>
-      <c r="Z67" s="206"/>
-      <c r="AA67" s="198"/>
-      <c r="AB67" s="199"/>
-      <c r="AC67" s="200"/>
-      <c r="AD67" s="198"/>
-      <c r="AE67" s="199"/>
-      <c r="AF67" s="200"/>
-      <c r="AG67" s="209"/>
-      <c r="AH67" s="210"/>
-      <c r="AI67" s="213"/>
-      <c r="AJ67" s="214"/>
+      <c r="B67" s="122"/>
+      <c r="C67" s="112"/>
+      <c r="D67" s="113"/>
+      <c r="E67" s="114"/>
+      <c r="F67" s="112"/>
+      <c r="G67" s="113"/>
+      <c r="H67" s="114"/>
+      <c r="I67" s="112"/>
+      <c r="J67" s="113"/>
+      <c r="K67" s="114"/>
+      <c r="L67" s="112"/>
+      <c r="M67" s="113"/>
+      <c r="N67" s="114"/>
+      <c r="O67" s="112"/>
+      <c r="P67" s="113"/>
+      <c r="Q67" s="113"/>
+      <c r="R67" s="113"/>
+      <c r="S67" s="114"/>
+      <c r="T67" s="122"/>
+      <c r="U67" s="112"/>
+      <c r="V67" s="113"/>
+      <c r="W67" s="114"/>
+      <c r="X67" s="118"/>
+      <c r="Y67" s="119"/>
+      <c r="Z67" s="120"/>
+      <c r="AA67" s="215"/>
+      <c r="AB67" s="216"/>
+      <c r="AC67" s="217"/>
+      <c r="AD67" s="215"/>
+      <c r="AE67" s="216"/>
+      <c r="AF67" s="217"/>
+      <c r="AG67" s="106"/>
+      <c r="AH67" s="108"/>
+      <c r="AI67" s="211"/>
+      <c r="AJ67" s="108"/>
       <c r="AK67" s="94"/>
     </row>
     <row r="68" spans="1:37" ht="12.5" customHeight="1">
       <c r="A68" s="93"/>
-      <c r="B68" s="191">
+      <c r="B68" s="121">
         <v>111</v>
       </c>
-      <c r="C68" s="195"/>
-      <c r="D68" s="196"/>
-      <c r="E68" s="197"/>
-      <c r="F68" s="195"/>
-      <c r="G68" s="196"/>
-      <c r="H68" s="197"/>
-      <c r="I68" s="195"/>
-      <c r="J68" s="196"/>
-      <c r="K68" s="197"/>
-      <c r="L68" s="195"/>
-      <c r="M68" s="196"/>
-      <c r="N68" s="197"/>
-      <c r="O68" s="195"/>
-      <c r="P68" s="196"/>
-      <c r="Q68" s="196"/>
-      <c r="R68" s="196"/>
-      <c r="S68" s="197"/>
-      <c r="T68" s="193"/>
-      <c r="U68" s="195"/>
-      <c r="V68" s="196"/>
-      <c r="W68" s="197"/>
-      <c r="X68" s="201"/>
-      <c r="Y68" s="202"/>
-      <c r="Z68" s="203"/>
-      <c r="AA68" s="195"/>
-      <c r="AB68" s="196"/>
-      <c r="AC68" s="197"/>
-      <c r="AD68" s="195"/>
-      <c r="AE68" s="196"/>
-      <c r="AF68" s="197"/>
-      <c r="AG68" s="207"/>
-      <c r="AH68" s="208"/>
-      <c r="AI68" s="211"/>
-      <c r="AJ68" s="212"/>
+      <c r="C68" s="109" t="s">
+        <v>134</v>
+      </c>
+      <c r="D68" s="110"/>
+      <c r="E68" s="111"/>
+      <c r="F68" s="109" t="s">
+        <v>135</v>
+      </c>
+      <c r="G68" s="110"/>
+      <c r="H68" s="111"/>
+      <c r="I68" s="109" t="s">
+        <v>136</v>
+      </c>
+      <c r="J68" s="110"/>
+      <c r="K68" s="111"/>
+      <c r="L68" s="109" t="s">
+        <v>137</v>
+      </c>
+      <c r="M68" s="110"/>
+      <c r="N68" s="111"/>
+      <c r="O68" s="109" t="s">
+        <v>124</v>
+      </c>
+      <c r="P68" s="110"/>
+      <c r="Q68" s="110"/>
+      <c r="R68" s="110"/>
+      <c r="S68" s="111"/>
+      <c r="T68" s="121" t="s">
+        <v>111</v>
+      </c>
+      <c r="U68" s="109" t="s">
+        <v>112</v>
+      </c>
+      <c r="V68" s="110"/>
+      <c r="W68" s="111"/>
+      <c r="X68" s="115" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y68" s="116"/>
+      <c r="Z68" s="117"/>
+      <c r="AA68" s="212" t="s">
+        <v>118</v>
+      </c>
+      <c r="AB68" s="213"/>
+      <c r="AC68" s="214"/>
+      <c r="AD68" s="212"/>
+      <c r="AE68" s="213"/>
+      <c r="AF68" s="214"/>
+      <c r="AG68" s="105"/>
+      <c r="AH68" s="107"/>
+      <c r="AI68" s="210"/>
+      <c r="AJ68" s="107"/>
       <c r="AK68" s="94"/>
     </row>
     <row r="69" spans="1:37" ht="12.5" customHeight="1" thickBot="1">
       <c r="A69" s="93"/>
-      <c r="B69" s="191"/>
-      <c r="C69" s="198"/>
-      <c r="D69" s="199"/>
-      <c r="E69" s="200"/>
-      <c r="F69" s="198"/>
-      <c r="G69" s="199"/>
-      <c r="H69" s="200"/>
-      <c r="I69" s="198"/>
-      <c r="J69" s="199"/>
-      <c r="K69" s="200"/>
-      <c r="L69" s="198"/>
-      <c r="M69" s="199"/>
-      <c r="N69" s="200"/>
-      <c r="O69" s="198"/>
-      <c r="P69" s="199"/>
-      <c r="Q69" s="199"/>
-      <c r="R69" s="199"/>
-      <c r="S69" s="200"/>
-      <c r="T69" s="194"/>
-      <c r="U69" s="198"/>
-      <c r="V69" s="199"/>
-      <c r="W69" s="200"/>
-      <c r="X69" s="204"/>
-      <c r="Y69" s="205"/>
-      <c r="Z69" s="206"/>
-      <c r="AA69" s="198"/>
-      <c r="AB69" s="199"/>
-      <c r="AC69" s="200"/>
-      <c r="AD69" s="198"/>
-      <c r="AE69" s="199"/>
-      <c r="AF69" s="200"/>
-      <c r="AG69" s="209"/>
-      <c r="AH69" s="210"/>
-      <c r="AI69" s="213"/>
-      <c r="AJ69" s="214"/>
+      <c r="B69" s="122"/>
+      <c r="C69" s="112"/>
+      <c r="D69" s="113"/>
+      <c r="E69" s="114"/>
+      <c r="F69" s="112"/>
+      <c r="G69" s="113"/>
+      <c r="H69" s="114"/>
+      <c r="I69" s="112"/>
+      <c r="J69" s="113"/>
+      <c r="K69" s="114"/>
+      <c r="L69" s="112"/>
+      <c r="M69" s="113"/>
+      <c r="N69" s="114"/>
+      <c r="O69" s="112"/>
+      <c r="P69" s="113"/>
+      <c r="Q69" s="113"/>
+      <c r="R69" s="113"/>
+      <c r="S69" s="114"/>
+      <c r="T69" s="122"/>
+      <c r="U69" s="112"/>
+      <c r="V69" s="113"/>
+      <c r="W69" s="114"/>
+      <c r="X69" s="118"/>
+      <c r="Y69" s="119"/>
+      <c r="Z69" s="120"/>
+      <c r="AA69" s="215"/>
+      <c r="AB69" s="216"/>
+      <c r="AC69" s="217"/>
+      <c r="AD69" s="215"/>
+      <c r="AE69" s="216"/>
+      <c r="AF69" s="217"/>
+      <c r="AG69" s="106"/>
+      <c r="AH69" s="108"/>
+      <c r="AI69" s="211"/>
+      <c r="AJ69" s="108"/>
       <c r="AK69" s="94"/>
     </row>
     <row r="70" spans="1:37" ht="12.5" customHeight="1">
       <c r="A70" s="93"/>
-      <c r="B70" s="191">
+      <c r="B70" s="209">
         <v>105</v>
       </c>
-      <c r="C70" s="195"/>
-      <c r="D70" s="196"/>
-      <c r="E70" s="197"/>
-      <c r="F70" s="195"/>
-      <c r="G70" s="196"/>
-      <c r="H70" s="197"/>
-      <c r="I70" s="195"/>
-      <c r="J70" s="196"/>
-      <c r="K70" s="197"/>
-      <c r="L70" s="195"/>
-      <c r="M70" s="196"/>
-      <c r="N70" s="197"/>
-      <c r="O70" s="195"/>
-      <c r="P70" s="196"/>
-      <c r="Q70" s="196"/>
-      <c r="R70" s="196"/>
-      <c r="S70" s="197"/>
-      <c r="T70" s="193"/>
-      <c r="U70" s="195"/>
-      <c r="V70" s="196"/>
-      <c r="W70" s="197"/>
-      <c r="X70" s="201"/>
-      <c r="Y70" s="202"/>
-      <c r="Z70" s="203"/>
-      <c r="AA70" s="195"/>
-      <c r="AB70" s="196"/>
-      <c r="AC70" s="197"/>
-      <c r="AD70" s="195"/>
-      <c r="AE70" s="196"/>
-      <c r="AF70" s="197"/>
-      <c r="AG70" s="207"/>
-      <c r="AH70" s="208"/>
-      <c r="AI70" s="211"/>
-      <c r="AJ70" s="212"/>
+      <c r="C70" s="109" t="s">
+        <v>126</v>
+      </c>
+      <c r="D70" s="110"/>
+      <c r="E70" s="111"/>
+      <c r="F70" s="109" t="s">
+        <v>139</v>
+      </c>
+      <c r="G70" s="110"/>
+      <c r="H70" s="111"/>
+      <c r="I70" s="109" t="s">
+        <v>128</v>
+      </c>
+      <c r="J70" s="110"/>
+      <c r="K70" s="111"/>
+      <c r="L70" s="109" t="s">
+        <v>138</v>
+      </c>
+      <c r="M70" s="110"/>
+      <c r="N70" s="111"/>
+      <c r="O70" s="109" t="s">
+        <v>125</v>
+      </c>
+      <c r="P70" s="110"/>
+      <c r="Q70" s="110"/>
+      <c r="R70" s="110"/>
+      <c r="S70" s="111"/>
+      <c r="T70" s="121" t="s">
+        <v>111</v>
+      </c>
+      <c r="U70" s="109" t="s">
+        <v>112</v>
+      </c>
+      <c r="V70" s="110"/>
+      <c r="W70" s="111"/>
+      <c r="X70" s="115" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y70" s="116"/>
+      <c r="Z70" s="117"/>
+      <c r="AA70" s="212" t="s">
+        <v>120</v>
+      </c>
+      <c r="AB70" s="213"/>
+      <c r="AC70" s="214"/>
+      <c r="AD70" s="212" t="s">
+        <v>121</v>
+      </c>
+      <c r="AE70" s="213"/>
+      <c r="AF70" s="214"/>
+      <c r="AG70" s="105"/>
+      <c r="AH70" s="107"/>
+      <c r="AI70" s="210"/>
+      <c r="AJ70" s="107"/>
       <c r="AK70" s="94"/>
     </row>
     <row r="71" spans="1:37" ht="12.5" customHeight="1" thickBot="1">
       <c r="A71" s="93"/>
-      <c r="B71" s="191"/>
-      <c r="C71" s="198"/>
-      <c r="D71" s="199"/>
-      <c r="E71" s="200"/>
-      <c r="F71" s="198"/>
-      <c r="G71" s="199"/>
-      <c r="H71" s="200"/>
-      <c r="I71" s="198"/>
-      <c r="J71" s="199"/>
-      <c r="K71" s="200"/>
-      <c r="L71" s="198"/>
-      <c r="M71" s="199"/>
-      <c r="N71" s="200"/>
-      <c r="O71" s="198"/>
-      <c r="P71" s="199"/>
-      <c r="Q71" s="199"/>
-      <c r="R71" s="199"/>
-      <c r="S71" s="200"/>
-      <c r="T71" s="194"/>
-      <c r="U71" s="198"/>
-      <c r="V71" s="199"/>
-      <c r="W71" s="200"/>
-      <c r="X71" s="204"/>
-      <c r="Y71" s="205"/>
-      <c r="Z71" s="206"/>
-      <c r="AA71" s="198"/>
-      <c r="AB71" s="199"/>
-      <c r="AC71" s="200"/>
-      <c r="AD71" s="198"/>
-      <c r="AE71" s="199"/>
-      <c r="AF71" s="200"/>
-      <c r="AG71" s="209"/>
-      <c r="AH71" s="210"/>
-      <c r="AI71" s="213"/>
-      <c r="AJ71" s="214"/>
+      <c r="B71" s="122"/>
+      <c r="C71" s="112"/>
+      <c r="D71" s="113"/>
+      <c r="E71" s="114"/>
+      <c r="F71" s="112"/>
+      <c r="G71" s="113"/>
+      <c r="H71" s="114"/>
+      <c r="I71" s="112"/>
+      <c r="J71" s="113"/>
+      <c r="K71" s="114"/>
+      <c r="L71" s="112"/>
+      <c r="M71" s="113"/>
+      <c r="N71" s="114"/>
+      <c r="O71" s="112"/>
+      <c r="P71" s="113"/>
+      <c r="Q71" s="113"/>
+      <c r="R71" s="113"/>
+      <c r="S71" s="114"/>
+      <c r="T71" s="122"/>
+      <c r="U71" s="112"/>
+      <c r="V71" s="113"/>
+      <c r="W71" s="114"/>
+      <c r="X71" s="118"/>
+      <c r="Y71" s="119"/>
+      <c r="Z71" s="120"/>
+      <c r="AA71" s="215"/>
+      <c r="AB71" s="216"/>
+      <c r="AC71" s="217"/>
+      <c r="AD71" s="215"/>
+      <c r="AE71" s="216"/>
+      <c r="AF71" s="217"/>
+      <c r="AG71" s="106"/>
+      <c r="AH71" s="108"/>
+      <c r="AI71" s="211"/>
+      <c r="AJ71" s="108"/>
       <c r="AK71" s="94"/>
     </row>
-    <row r="72" spans="1:37" ht="12.5" customHeight="1">
+    <row r="72" spans="1:37" s="208" customFormat="1" ht="12.5" customHeight="1">
       <c r="A72" s="93"/>
-      <c r="B72" s="191"/>
-      <c r="C72" s="195"/>
-      <c r="D72" s="196"/>
-      <c r="E72" s="197"/>
-      <c r="F72" s="195"/>
-      <c r="G72" s="196"/>
-      <c r="H72" s="197"/>
-      <c r="I72" s="195"/>
-      <c r="J72" s="196"/>
-      <c r="K72" s="197"/>
-      <c r="L72" s="195"/>
-      <c r="M72" s="196"/>
-      <c r="N72" s="197"/>
-      <c r="O72" s="195"/>
-      <c r="P72" s="196"/>
-      <c r="Q72" s="196"/>
-      <c r="R72" s="196"/>
-      <c r="S72" s="197"/>
-      <c r="T72" s="193"/>
-      <c r="U72" s="195"/>
-      <c r="V72" s="196"/>
-      <c r="W72" s="197"/>
-      <c r="X72" s="201"/>
-      <c r="Y72" s="202"/>
-      <c r="Z72" s="203"/>
-      <c r="AA72" s="195"/>
-      <c r="AB72" s="196"/>
-      <c r="AC72" s="197"/>
-      <c r="AD72" s="195"/>
-      <c r="AE72" s="196"/>
-      <c r="AF72" s="197"/>
-      <c r="AG72" s="207"/>
-      <c r="AH72" s="208"/>
-      <c r="AI72" s="211"/>
-      <c r="AJ72" s="212"/>
+      <c r="B72" s="206"/>
+      <c r="C72" s="206"/>
+      <c r="D72" s="206"/>
+      <c r="E72" s="206"/>
+      <c r="F72" s="206"/>
+      <c r="G72" s="206"/>
+      <c r="H72" s="206"/>
+      <c r="I72" s="206"/>
+      <c r="J72" s="206"/>
+      <c r="K72" s="206"/>
+      <c r="L72" s="206"/>
+      <c r="M72" s="206"/>
+      <c r="N72" s="206"/>
+      <c r="O72" s="206"/>
+      <c r="P72" s="206"/>
+      <c r="Q72" s="206"/>
+      <c r="R72" s="206"/>
+      <c r="S72" s="206"/>
+      <c r="T72" s="206"/>
+      <c r="U72" s="206"/>
+      <c r="V72" s="206"/>
+      <c r="W72" s="206"/>
+      <c r="X72" s="207"/>
+      <c r="Y72" s="207"/>
+      <c r="Z72" s="207"/>
+      <c r="AA72" s="206"/>
+      <c r="AB72" s="206"/>
+      <c r="AC72" s="206"/>
+      <c r="AD72" s="206"/>
+      <c r="AE72" s="206"/>
+      <c r="AF72" s="206"/>
+      <c r="AG72" s="206"/>
+      <c r="AH72" s="206"/>
+      <c r="AI72" s="206"/>
+      <c r="AJ72" s="206"/>
       <c r="AK72" s="94"/>
     </row>
-    <row r="73" spans="1:37" ht="12.5" customHeight="1" thickBot="1">
+    <row r="73" spans="1:37" s="208" customFormat="1" ht="12.5" customHeight="1">
       <c r="A73" s="93"/>
-      <c r="B73" s="191"/>
-      <c r="C73" s="198"/>
-      <c r="D73" s="199"/>
-      <c r="E73" s="200"/>
-      <c r="F73" s="198"/>
-      <c r="G73" s="199"/>
-      <c r="H73" s="200"/>
-      <c r="I73" s="198"/>
-      <c r="J73" s="199"/>
-      <c r="K73" s="200"/>
-      <c r="L73" s="198"/>
-      <c r="M73" s="199"/>
-      <c r="N73" s="200"/>
-      <c r="O73" s="198"/>
-      <c r="P73" s="199"/>
-      <c r="Q73" s="199"/>
-      <c r="R73" s="199"/>
-      <c r="S73" s="200"/>
-      <c r="T73" s="194"/>
-      <c r="U73" s="198"/>
-      <c r="V73" s="199"/>
-      <c r="W73" s="200"/>
-      <c r="X73" s="204"/>
-      <c r="Y73" s="205"/>
-      <c r="Z73" s="206"/>
-      <c r="AA73" s="198"/>
-      <c r="AB73" s="199"/>
-      <c r="AC73" s="200"/>
-      <c r="AD73" s="198"/>
-      <c r="AE73" s="199"/>
-      <c r="AF73" s="200"/>
-      <c r="AG73" s="209"/>
-      <c r="AH73" s="210"/>
-      <c r="AI73" s="213"/>
-      <c r="AJ73" s="214"/>
+      <c r="B73" s="206"/>
+      <c r="C73" s="206"/>
+      <c r="D73" s="206"/>
+      <c r="E73" s="206"/>
+      <c r="F73" s="206"/>
+      <c r="G73" s="206"/>
+      <c r="H73" s="206"/>
+      <c r="I73" s="206"/>
+      <c r="J73" s="206"/>
+      <c r="K73" s="206"/>
+      <c r="L73" s="206"/>
+      <c r="M73" s="206"/>
+      <c r="N73" s="206"/>
+      <c r="O73" s="206"/>
+      <c r="P73" s="206"/>
+      <c r="Q73" s="206"/>
+      <c r="R73" s="206"/>
+      <c r="S73" s="206"/>
+      <c r="T73" s="206"/>
+      <c r="U73" s="206"/>
+      <c r="V73" s="206"/>
+      <c r="W73" s="206"/>
+      <c r="X73" s="207"/>
+      <c r="Y73" s="207"/>
+      <c r="Z73" s="207"/>
+      <c r="AA73" s="206"/>
+      <c r="AB73" s="206"/>
+      <c r="AC73" s="206"/>
+      <c r="AD73" s="206"/>
+      <c r="AE73" s="206"/>
+      <c r="AF73" s="206"/>
+      <c r="AG73" s="206"/>
+      <c r="AH73" s="206"/>
+      <c r="AI73" s="206"/>
+      <c r="AJ73" s="206"/>
       <c r="AK73" s="94"/>
     </row>
-    <row r="74" spans="1:37" ht="12.5" customHeight="1">
+    <row r="74" spans="1:37" s="208" customFormat="1" ht="12.5" customHeight="1">
       <c r="A74" s="93"/>
-      <c r="B74" s="191"/>
-      <c r="C74" s="195"/>
-      <c r="D74" s="196"/>
-      <c r="E74" s="197"/>
-      <c r="F74" s="195"/>
-      <c r="G74" s="196"/>
-      <c r="H74" s="197"/>
-      <c r="I74" s="195"/>
-      <c r="J74" s="196"/>
-      <c r="K74" s="197"/>
-      <c r="L74" s="195"/>
-      <c r="M74" s="196"/>
-      <c r="N74" s="197"/>
-      <c r="O74" s="195"/>
-      <c r="P74" s="196"/>
-      <c r="Q74" s="196"/>
-      <c r="R74" s="196"/>
-      <c r="S74" s="197"/>
-      <c r="T74" s="193"/>
-      <c r="U74" s="195"/>
-      <c r="V74" s="196"/>
-      <c r="W74" s="197"/>
-      <c r="X74" s="201"/>
-      <c r="Y74" s="202"/>
-      <c r="Z74" s="203"/>
-      <c r="AA74" s="195"/>
-      <c r="AB74" s="196"/>
-      <c r="AC74" s="197"/>
-      <c r="AD74" s="195"/>
-      <c r="AE74" s="196"/>
-      <c r="AF74" s="197"/>
-      <c r="AG74" s="207"/>
-      <c r="AH74" s="208"/>
-      <c r="AI74" s="211"/>
-      <c r="AJ74" s="212"/>
+      <c r="B74" s="206"/>
+      <c r="C74" s="206"/>
+      <c r="D74" s="206"/>
+      <c r="E74" s="206"/>
+      <c r="F74" s="206"/>
+      <c r="G74" s="206"/>
+      <c r="H74" s="206"/>
+      <c r="I74" s="206"/>
+      <c r="J74" s="206"/>
+      <c r="K74" s="206"/>
+      <c r="L74" s="206"/>
+      <c r="M74" s="206"/>
+      <c r="N74" s="206"/>
+      <c r="O74" s="206"/>
+      <c r="P74" s="206"/>
+      <c r="Q74" s="206"/>
+      <c r="R74" s="206"/>
+      <c r="S74" s="206"/>
+      <c r="T74" s="206"/>
+      <c r="U74" s="206"/>
+      <c r="V74" s="206"/>
+      <c r="W74" s="206"/>
+      <c r="X74" s="207"/>
+      <c r="Y74" s="207"/>
+      <c r="Z74" s="207"/>
+      <c r="AA74" s="206"/>
+      <c r="AB74" s="206"/>
+      <c r="AC74" s="206"/>
+      <c r="AD74" s="206"/>
+      <c r="AE74" s="206"/>
+      <c r="AF74" s="206"/>
+      <c r="AG74" s="206"/>
+      <c r="AH74" s="206"/>
+      <c r="AI74" s="206"/>
+      <c r="AJ74" s="206"/>
       <c r="AK74" s="94"/>
     </row>
-    <row r="75" spans="1:37" ht="12.5" customHeight="1" thickBot="1">
+    <row r="75" spans="1:37" s="208" customFormat="1" ht="12.5" customHeight="1">
       <c r="A75" s="93"/>
-      <c r="B75" s="191"/>
-      <c r="C75" s="198"/>
-      <c r="D75" s="199"/>
-      <c r="E75" s="200"/>
-      <c r="F75" s="198"/>
-      <c r="G75" s="199"/>
-      <c r="H75" s="200"/>
-      <c r="I75" s="198"/>
-      <c r="J75" s="199"/>
-      <c r="K75" s="200"/>
-      <c r="L75" s="198"/>
-      <c r="M75" s="199"/>
-      <c r="N75" s="200"/>
-      <c r="O75" s="198"/>
-      <c r="P75" s="199"/>
-      <c r="Q75" s="199"/>
-      <c r="R75" s="199"/>
-      <c r="S75" s="200"/>
-      <c r="T75" s="194"/>
-      <c r="U75" s="198"/>
-      <c r="V75" s="199"/>
-      <c r="W75" s="200"/>
-      <c r="X75" s="204"/>
-      <c r="Y75" s="205"/>
-      <c r="Z75" s="206"/>
-      <c r="AA75" s="198"/>
-      <c r="AB75" s="199"/>
-      <c r="AC75" s="200"/>
-      <c r="AD75" s="198"/>
-      <c r="AE75" s="199"/>
-      <c r="AF75" s="200"/>
-      <c r="AG75" s="209"/>
-      <c r="AH75" s="210"/>
-      <c r="AI75" s="213"/>
-      <c r="AJ75" s="214"/>
+      <c r="B75" s="206"/>
+      <c r="C75" s="206"/>
+      <c r="D75" s="206"/>
+      <c r="E75" s="206"/>
+      <c r="F75" s="206"/>
+      <c r="G75" s="206"/>
+      <c r="H75" s="206"/>
+      <c r="I75" s="206"/>
+      <c r="J75" s="206"/>
+      <c r="K75" s="206"/>
+      <c r="L75" s="206"/>
+      <c r="M75" s="206"/>
+      <c r="N75" s="206"/>
+      <c r="O75" s="206"/>
+      <c r="P75" s="206"/>
+      <c r="Q75" s="206"/>
+      <c r="R75" s="206"/>
+      <c r="S75" s="206"/>
+      <c r="T75" s="206"/>
+      <c r="U75" s="206"/>
+      <c r="V75" s="206"/>
+      <c r="W75" s="206"/>
+      <c r="X75" s="207"/>
+      <c r="Y75" s="207"/>
+      <c r="Z75" s="207"/>
+      <c r="AA75" s="206"/>
+      <c r="AB75" s="206"/>
+      <c r="AC75" s="206"/>
+      <c r="AD75" s="206"/>
+      <c r="AE75" s="206"/>
+      <c r="AF75" s="206"/>
+      <c r="AG75" s="206"/>
+      <c r="AH75" s="206"/>
+      <c r="AI75" s="206"/>
+      <c r="AJ75" s="206"/>
       <c r="AK75" s="94"/>
     </row>
-    <row r="76" spans="1:37" ht="12.5" customHeight="1">
+    <row r="76" spans="1:37" s="208" customFormat="1" ht="12.5" customHeight="1">
       <c r="A76" s="93"/>
-      <c r="B76" s="191"/>
-      <c r="C76" s="195"/>
-      <c r="D76" s="196"/>
-      <c r="E76" s="197"/>
-      <c r="F76" s="195"/>
-      <c r="G76" s="196"/>
-      <c r="H76" s="197"/>
-      <c r="I76" s="195"/>
-      <c r="J76" s="196"/>
-      <c r="K76" s="197"/>
-      <c r="L76" s="195"/>
-      <c r="M76" s="196"/>
-      <c r="N76" s="197"/>
-      <c r="O76" s="195"/>
-      <c r="P76" s="196"/>
-      <c r="Q76" s="196"/>
-      <c r="R76" s="196"/>
-      <c r="S76" s="197"/>
-      <c r="T76" s="193"/>
-      <c r="U76" s="195"/>
-      <c r="V76" s="196"/>
-      <c r="W76" s="197"/>
-      <c r="X76" s="201"/>
-      <c r="Y76" s="202"/>
-      <c r="Z76" s="203"/>
-      <c r="AA76" s="195"/>
-      <c r="AB76" s="196"/>
-      <c r="AC76" s="197"/>
-      <c r="AD76" s="195"/>
-      <c r="AE76" s="196"/>
-      <c r="AF76" s="197"/>
-      <c r="AG76" s="207"/>
-      <c r="AH76" s="208"/>
-      <c r="AI76" s="211"/>
-      <c r="AJ76" s="212"/>
+      <c r="B76" s="206"/>
+      <c r="C76" s="206"/>
+      <c r="D76" s="206"/>
+      <c r="E76" s="206"/>
+      <c r="F76" s="206"/>
+      <c r="G76" s="206"/>
+      <c r="H76" s="206"/>
+      <c r="I76" s="206"/>
+      <c r="J76" s="206"/>
+      <c r="K76" s="206"/>
+      <c r="L76" s="206"/>
+      <c r="M76" s="206"/>
+      <c r="N76" s="206"/>
+      <c r="O76" s="206"/>
+      <c r="P76" s="206"/>
+      <c r="Q76" s="206"/>
+      <c r="R76" s="206"/>
+      <c r="S76" s="206"/>
+      <c r="T76" s="206"/>
+      <c r="U76" s="206"/>
+      <c r="V76" s="206"/>
+      <c r="W76" s="206"/>
+      <c r="X76" s="207"/>
+      <c r="Y76" s="207"/>
+      <c r="Z76" s="207"/>
+      <c r="AA76" s="206"/>
+      <c r="AB76" s="206"/>
+      <c r="AC76" s="206"/>
+      <c r="AD76" s="206"/>
+      <c r="AE76" s="206"/>
+      <c r="AF76" s="206"/>
+      <c r="AG76" s="206"/>
+      <c r="AH76" s="206"/>
+      <c r="AI76" s="206"/>
+      <c r="AJ76" s="206"/>
       <c r="AK76" s="94"/>
     </row>
-    <row r="77" spans="1:37" ht="12.5" customHeight="1" thickBot="1">
+    <row r="77" spans="1:37" s="208" customFormat="1" ht="12.5" customHeight="1">
       <c r="A77" s="93"/>
-      <c r="B77" s="191"/>
-      <c r="C77" s="198"/>
-      <c r="D77" s="199"/>
-      <c r="E77" s="200"/>
-      <c r="F77" s="198"/>
-      <c r="G77" s="199"/>
-      <c r="H77" s="200"/>
-      <c r="I77" s="198"/>
-      <c r="J77" s="199"/>
-      <c r="K77" s="200"/>
-      <c r="L77" s="198"/>
-      <c r="M77" s="199"/>
-      <c r="N77" s="200"/>
-      <c r="O77" s="198"/>
-      <c r="P77" s="199"/>
-      <c r="Q77" s="199"/>
-      <c r="R77" s="199"/>
-      <c r="S77" s="200"/>
-      <c r="T77" s="194"/>
-      <c r="U77" s="198"/>
-      <c r="V77" s="199"/>
-      <c r="W77" s="200"/>
-      <c r="X77" s="204"/>
-      <c r="Y77" s="205"/>
-      <c r="Z77" s="206"/>
-      <c r="AA77" s="198"/>
-      <c r="AB77" s="199"/>
-      <c r="AC77" s="200"/>
-      <c r="AD77" s="198"/>
-      <c r="AE77" s="199"/>
-      <c r="AF77" s="200"/>
-      <c r="AG77" s="209"/>
-      <c r="AH77" s="210"/>
-      <c r="AI77" s="213"/>
-      <c r="AJ77" s="214"/>
+      <c r="B77" s="206"/>
+      <c r="C77" s="206"/>
+      <c r="D77" s="206"/>
+      <c r="E77" s="206"/>
+      <c r="F77" s="206"/>
+      <c r="G77" s="206"/>
+      <c r="H77" s="206"/>
+      <c r="I77" s="206"/>
+      <c r="J77" s="206"/>
+      <c r="K77" s="206"/>
+      <c r="L77" s="206"/>
+      <c r="M77" s="206"/>
+      <c r="N77" s="206"/>
+      <c r="O77" s="206"/>
+      <c r="P77" s="206"/>
+      <c r="Q77" s="206"/>
+      <c r="R77" s="206"/>
+      <c r="S77" s="206"/>
+      <c r="T77" s="206"/>
+      <c r="U77" s="206"/>
+      <c r="V77" s="206"/>
+      <c r="W77" s="206"/>
+      <c r="X77" s="207"/>
+      <c r="Y77" s="207"/>
+      <c r="Z77" s="207"/>
+      <c r="AA77" s="206"/>
+      <c r="AB77" s="206"/>
+      <c r="AC77" s="206"/>
+      <c r="AD77" s="206"/>
+      <c r="AE77" s="206"/>
+      <c r="AF77" s="206"/>
+      <c r="AG77" s="206"/>
+      <c r="AH77" s="206"/>
+      <c r="AI77" s="206"/>
+      <c r="AJ77" s="206"/>
       <c r="AK77" s="94"/>
     </row>
     <row r="78" spans="1:37" ht="12.75" customHeight="1">
       <c r="A78" s="93"/>
-      <c r="B78" s="170"/>
-      <c r="C78" s="170"/>
-      <c r="D78" s="170"/>
-      <c r="E78" s="170"/>
-      <c r="F78" s="170"/>
-      <c r="G78" s="170"/>
-      <c r="H78" s="170"/>
-      <c r="I78" s="175"/>
-      <c r="J78" s="170"/>
-      <c r="K78" s="170"/>
-      <c r="L78" s="170"/>
-      <c r="M78" s="170"/>
-      <c r="N78" s="170"/>
-      <c r="O78" s="170"/>
-      <c r="P78" s="170"/>
-      <c r="Q78" s="170"/>
-      <c r="R78" s="170"/>
-      <c r="S78" s="170"/>
-      <c r="T78" s="170"/>
-      <c r="U78" s="170"/>
-      <c r="V78" s="170"/>
-      <c r="W78" s="170"/>
-      <c r="X78" s="170"/>
-      <c r="Y78" s="170"/>
-      <c r="Z78" s="170"/>
-      <c r="AA78" s="170"/>
-      <c r="AB78" s="170"/>
-      <c r="AC78" s="170"/>
-      <c r="AD78" s="170"/>
-      <c r="AE78" s="170"/>
-      <c r="AF78" s="170"/>
-      <c r="AG78" s="170"/>
-      <c r="AH78" s="170"/>
-      <c r="AI78" s="170"/>
-      <c r="AJ78" s="171"/>
+      <c r="B78" s="223"/>
+      <c r="C78" s="223"/>
+      <c r="D78" s="223"/>
+      <c r="E78" s="223"/>
+      <c r="F78" s="223"/>
+      <c r="G78" s="223"/>
+      <c r="H78" s="223"/>
+      <c r="I78" s="228"/>
+      <c r="J78" s="223"/>
+      <c r="K78" s="223"/>
+      <c r="L78" s="223"/>
+      <c r="M78" s="223"/>
+      <c r="N78" s="223"/>
+      <c r="O78" s="223"/>
+      <c r="P78" s="223"/>
+      <c r="Q78" s="223"/>
+      <c r="R78" s="223"/>
+      <c r="S78" s="223"/>
+      <c r="T78" s="223"/>
+      <c r="U78" s="223"/>
+      <c r="V78" s="223"/>
+      <c r="W78" s="223"/>
+      <c r="X78" s="223"/>
+      <c r="Y78" s="223"/>
+      <c r="Z78" s="223"/>
+      <c r="AA78" s="223"/>
+      <c r="AB78" s="223"/>
+      <c r="AC78" s="223"/>
+      <c r="AD78" s="223"/>
+      <c r="AE78" s="223"/>
+      <c r="AF78" s="223"/>
+      <c r="AG78" s="223"/>
+      <c r="AH78" s="223"/>
+      <c r="AI78" s="223"/>
+      <c r="AJ78" s="224"/>
       <c r="AK78" s="94"/>
     </row>
     <row r="79" spans="1:37" ht="12.75" customHeight="1">
       <c r="A79" s="93"/>
-      <c r="B79" s="170"/>
-      <c r="C79" s="170"/>
-      <c r="D79" s="170"/>
-      <c r="E79" s="170"/>
-      <c r="F79" s="170"/>
-      <c r="G79" s="175"/>
-      <c r="H79" s="170"/>
-      <c r="I79" s="176"/>
-      <c r="J79" s="170"/>
-      <c r="K79" s="170"/>
-      <c r="L79" s="170"/>
-      <c r="M79" s="170"/>
-      <c r="N79" s="170"/>
-      <c r="O79" s="170"/>
-      <c r="P79" s="170"/>
-      <c r="Q79" s="170"/>
-      <c r="R79" s="170"/>
-      <c r="S79" s="170"/>
-      <c r="T79" s="170"/>
-      <c r="U79" s="170"/>
-      <c r="V79" s="170"/>
-      <c r="W79" s="170"/>
-      <c r="X79" s="170"/>
-      <c r="Y79" s="170"/>
-      <c r="Z79" s="170"/>
-      <c r="AA79" s="170"/>
-      <c r="AB79" s="170"/>
-      <c r="AC79" s="170"/>
-      <c r="AD79" s="170"/>
-      <c r="AE79" s="170"/>
-      <c r="AF79" s="170"/>
-      <c r="AG79" s="170"/>
-      <c r="AH79" s="170"/>
-      <c r="AI79" s="170"/>
-      <c r="AJ79" s="170"/>
+      <c r="B79" s="223"/>
+      <c r="C79" s="223"/>
+      <c r="D79" s="223"/>
+      <c r="E79" s="223"/>
+      <c r="F79" s="223"/>
+      <c r="G79" s="228"/>
+      <c r="H79" s="223"/>
+      <c r="I79" s="229"/>
+      <c r="J79" s="223"/>
+      <c r="K79" s="223"/>
+      <c r="L79" s="223"/>
+      <c r="M79" s="223"/>
+      <c r="N79" s="223"/>
+      <c r="O79" s="223"/>
+      <c r="P79" s="223"/>
+      <c r="Q79" s="223"/>
+      <c r="R79" s="223"/>
+      <c r="S79" s="223"/>
+      <c r="T79" s="223"/>
+      <c r="U79" s="223"/>
+      <c r="V79" s="223"/>
+      <c r="W79" s="223"/>
+      <c r="X79" s="223"/>
+      <c r="Y79" s="223"/>
+      <c r="Z79" s="223"/>
+      <c r="AA79" s="223"/>
+      <c r="AB79" s="223"/>
+      <c r="AC79" s="223"/>
+      <c r="AD79" s="223"/>
+      <c r="AE79" s="223"/>
+      <c r="AF79" s="223"/>
+      <c r="AG79" s="223"/>
+      <c r="AH79" s="223"/>
+      <c r="AI79" s="223"/>
+      <c r="AJ79" s="223"/>
       <c r="AK79" s="94"/>
     </row>
     <row r="80" spans="1:37" ht="12.75" customHeight="1">
-      <c r="A80" s="186"/>
-      <c r="B80" s="177"/>
-      <c r="C80" s="177"/>
-      <c r="D80" s="177"/>
-      <c r="E80" s="177"/>
-      <c r="F80" s="177"/>
-      <c r="G80" s="178"/>
-      <c r="H80" s="178"/>
-      <c r="I80" s="177"/>
-      <c r="J80" s="177"/>
-      <c r="K80" s="177"/>
-      <c r="L80" s="177"/>
-      <c r="M80" s="177"/>
-      <c r="N80" s="177"/>
-      <c r="O80" s="177"/>
-      <c r="P80" s="177"/>
-      <c r="Q80" s="177"/>
-      <c r="R80" s="177"/>
-      <c r="S80" s="177"/>
-      <c r="T80" s="168"/>
-      <c r="U80" s="168"/>
-      <c r="V80" s="168"/>
-      <c r="W80" s="168"/>
-      <c r="X80" s="168"/>
-      <c r="Y80" s="168"/>
-      <c r="Z80" s="168"/>
-      <c r="AA80" s="168"/>
-      <c r="AB80" s="168"/>
-      <c r="AC80" s="168"/>
-      <c r="AD80" s="168"/>
-      <c r="AE80" s="168"/>
-      <c r="AF80" s="168"/>
-      <c r="AG80" s="168"/>
-      <c r="AH80" s="168"/>
-      <c r="AI80" s="168"/>
-      <c r="AJ80" s="168"/>
-      <c r="AK80" s="187"/>
+      <c r="A80" s="100"/>
+      <c r="B80" s="230"/>
+      <c r="C80" s="230"/>
+      <c r="D80" s="230"/>
+      <c r="E80" s="230"/>
+      <c r="F80" s="230"/>
+      <c r="G80" s="231"/>
+      <c r="H80" s="231"/>
+      <c r="I80" s="230"/>
+      <c r="J80" s="230"/>
+      <c r="K80" s="230"/>
+      <c r="L80" s="230"/>
+      <c r="M80" s="230"/>
+      <c r="N80" s="230"/>
+      <c r="O80" s="230"/>
+      <c r="P80" s="230"/>
+      <c r="Q80" s="230"/>
+      <c r="R80" s="230"/>
+      <c r="S80" s="230"/>
+      <c r="T80" s="232"/>
+      <c r="U80" s="232"/>
+      <c r="V80" s="232"/>
+      <c r="W80" s="232"/>
+      <c r="X80" s="232"/>
+      <c r="Y80" s="232"/>
+      <c r="Z80" s="232"/>
+      <c r="AA80" s="232"/>
+      <c r="AB80" s="232"/>
+      <c r="AC80" s="232"/>
+      <c r="AD80" s="232"/>
+      <c r="AE80" s="232"/>
+      <c r="AF80" s="232"/>
+      <c r="AG80" s="232"/>
+      <c r="AH80" s="232"/>
+      <c r="AI80" s="232"/>
+      <c r="AJ80" s="232"/>
+      <c r="AK80" s="101"/>
     </row>
     <row r="81" spans="1:37" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A81" s="188"/>
-      <c r="B81" s="189"/>
-      <c r="C81" s="189"/>
-      <c r="D81" s="189"/>
-      <c r="E81" s="189"/>
-      <c r="F81" s="189"/>
-      <c r="G81" s="189"/>
-      <c r="H81" s="189"/>
-      <c r="I81" s="189"/>
-      <c r="J81" s="189"/>
-      <c r="K81" s="189"/>
-      <c r="L81" s="189"/>
-      <c r="M81" s="189"/>
-      <c r="N81" s="189"/>
-      <c r="O81" s="189"/>
-      <c r="P81" s="189"/>
-      <c r="Q81" s="189"/>
-      <c r="R81" s="189"/>
-      <c r="S81" s="189"/>
-      <c r="T81" s="189"/>
-      <c r="U81" s="189"/>
-      <c r="V81" s="189"/>
-      <c r="W81" s="189"/>
-      <c r="X81" s="189"/>
-      <c r="Y81" s="189"/>
-      <c r="Z81" s="189"/>
-      <c r="AA81" s="189"/>
-      <c r="AB81" s="189"/>
-      <c r="AC81" s="189"/>
-      <c r="AD81" s="189"/>
-      <c r="AE81" s="189"/>
-      <c r="AF81" s="189"/>
-      <c r="AG81" s="189"/>
-      <c r="AH81" s="189"/>
-      <c r="AI81" s="189"/>
-      <c r="AJ81" s="189"/>
-      <c r="AK81" s="190"/>
+      <c r="A81" s="102"/>
+      <c r="B81" s="103"/>
+      <c r="C81" s="103"/>
+      <c r="D81" s="103"/>
+      <c r="E81" s="103"/>
+      <c r="F81" s="103"/>
+      <c r="G81" s="103"/>
+      <c r="H81" s="103"/>
+      <c r="I81" s="103"/>
+      <c r="J81" s="103"/>
+      <c r="K81" s="103"/>
+      <c r="L81" s="103"/>
+      <c r="M81" s="103"/>
+      <c r="N81" s="103"/>
+      <c r="O81" s="103"/>
+      <c r="P81" s="103"/>
+      <c r="Q81" s="103"/>
+      <c r="R81" s="103"/>
+      <c r="S81" s="103"/>
+      <c r="T81" s="103"/>
+      <c r="U81" s="103"/>
+      <c r="V81" s="103"/>
+      <c r="W81" s="103"/>
+      <c r="X81" s="103"/>
+      <c r="Y81" s="103"/>
+      <c r="Z81" s="103"/>
+      <c r="AA81" s="103"/>
+      <c r="AB81" s="103"/>
+      <c r="AC81" s="103"/>
+      <c r="AD81" s="103"/>
+      <c r="AE81" s="103"/>
+      <c r="AF81" s="103"/>
+      <c r="AG81" s="103"/>
+      <c r="AH81" s="103"/>
+      <c r="AI81" s="103"/>
+      <c r="AJ81" s="103"/>
+      <c r="AK81" s="104"/>
     </row>
   </sheetData>
   <mergeCells count="163">
-    <mergeCell ref="AG68:AH69"/>
-    <mergeCell ref="AI68:AJ69"/>
-    <mergeCell ref="AG70:AH71"/>
-    <mergeCell ref="AI70:AJ71"/>
-    <mergeCell ref="AG72:AH73"/>
-    <mergeCell ref="AI72:AJ73"/>
-    <mergeCell ref="AG62:AH63"/>
-    <mergeCell ref="AI62:AJ63"/>
-    <mergeCell ref="AG64:AH65"/>
-    <mergeCell ref="AI64:AJ65"/>
-    <mergeCell ref="AG66:AH67"/>
-    <mergeCell ref="AI66:AJ67"/>
-    <mergeCell ref="U76:W77"/>
-    <mergeCell ref="X76:Z77"/>
-    <mergeCell ref="AA76:AC77"/>
-    <mergeCell ref="AD76:AF77"/>
-    <mergeCell ref="AG76:AH77"/>
-    <mergeCell ref="AI76:AJ77"/>
-    <mergeCell ref="F76:H77"/>
-    <mergeCell ref="I76:K77"/>
-    <mergeCell ref="L76:N77"/>
-    <mergeCell ref="O76:S77"/>
-    <mergeCell ref="T76:T77"/>
-    <mergeCell ref="U74:W75"/>
-    <mergeCell ref="X74:Z75"/>
-    <mergeCell ref="AA74:AC75"/>
-    <mergeCell ref="AD74:AF75"/>
-    <mergeCell ref="AG74:AH75"/>
-    <mergeCell ref="AI74:AJ75"/>
-    <mergeCell ref="F74:H75"/>
-    <mergeCell ref="I74:K75"/>
-    <mergeCell ref="L74:N75"/>
-    <mergeCell ref="O74:S75"/>
-    <mergeCell ref="T74:T75"/>
-    <mergeCell ref="U72:W73"/>
-    <mergeCell ref="X72:Z73"/>
-    <mergeCell ref="AA72:AC73"/>
-    <mergeCell ref="AD72:AF73"/>
-    <mergeCell ref="F72:H73"/>
-    <mergeCell ref="I72:K73"/>
-    <mergeCell ref="L72:N73"/>
-    <mergeCell ref="O72:S73"/>
-    <mergeCell ref="T72:T73"/>
-    <mergeCell ref="U62:W63"/>
-    <mergeCell ref="X62:Z63"/>
-    <mergeCell ref="U64:W65"/>
-    <mergeCell ref="X64:Z65"/>
-    <mergeCell ref="U66:W67"/>
-    <mergeCell ref="X66:Z67"/>
-    <mergeCell ref="F70:H71"/>
-    <mergeCell ref="I70:K71"/>
-    <mergeCell ref="L70:N71"/>
-    <mergeCell ref="O70:S71"/>
-    <mergeCell ref="T70:T71"/>
-    <mergeCell ref="AA70:AC71"/>
-    <mergeCell ref="AD70:AF71"/>
-    <mergeCell ref="U68:W69"/>
-    <mergeCell ref="X68:Z69"/>
-    <mergeCell ref="U70:W71"/>
-    <mergeCell ref="X70:Z71"/>
-    <mergeCell ref="AA68:AC69"/>
-    <mergeCell ref="AD68:AF69"/>
-    <mergeCell ref="F68:H69"/>
-    <mergeCell ref="I68:K69"/>
-    <mergeCell ref="L68:N69"/>
-    <mergeCell ref="O68:S69"/>
-    <mergeCell ref="T68:T69"/>
-    <mergeCell ref="F66:H67"/>
-    <mergeCell ref="I66:K67"/>
-    <mergeCell ref="L66:N67"/>
-    <mergeCell ref="O66:S67"/>
-    <mergeCell ref="T66:T67"/>
-    <mergeCell ref="AA66:AC67"/>
-    <mergeCell ref="AD66:AF67"/>
-    <mergeCell ref="AA64:AC65"/>
-    <mergeCell ref="AD64:AF65"/>
-    <mergeCell ref="F64:H65"/>
-    <mergeCell ref="I64:K65"/>
-    <mergeCell ref="L64:N65"/>
-    <mergeCell ref="O64:S65"/>
-    <mergeCell ref="T64:T65"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="B76:B77"/>
-    <mergeCell ref="C62:E63"/>
-    <mergeCell ref="C64:E65"/>
-    <mergeCell ref="C66:E67"/>
-    <mergeCell ref="C68:E69"/>
-    <mergeCell ref="C70:E71"/>
-    <mergeCell ref="C72:E73"/>
-    <mergeCell ref="C74:E75"/>
-    <mergeCell ref="C76:E77"/>
+    <mergeCell ref="AE3:AG3"/>
+    <mergeCell ref="AJ3:AK3"/>
+    <mergeCell ref="A1:AK1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="I2:AD2"/>
+    <mergeCell ref="AE2:AG2"/>
+    <mergeCell ref="AJ2:AK2"/>
+    <mergeCell ref="G8:I9"/>
+    <mergeCell ref="G10:I11"/>
+    <mergeCell ref="V8:AD9"/>
+    <mergeCell ref="V10:AD11"/>
+    <mergeCell ref="J8:R9"/>
+    <mergeCell ref="J10:R11"/>
+    <mergeCell ref="S8:U9"/>
+    <mergeCell ref="S10:U11"/>
+    <mergeCell ref="G53:I54"/>
+    <mergeCell ref="J53:R54"/>
+    <mergeCell ref="S53:U54"/>
+    <mergeCell ref="V53:AD54"/>
+    <mergeCell ref="G55:I56"/>
+    <mergeCell ref="S55:U56"/>
+    <mergeCell ref="V55:AD56"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="I3:AD3"/>
+    <mergeCell ref="G12:I13"/>
+    <mergeCell ref="G14:I15"/>
+    <mergeCell ref="G16:I17"/>
+    <mergeCell ref="S16:U17"/>
+    <mergeCell ref="V12:AD13"/>
+    <mergeCell ref="V14:AD15"/>
+    <mergeCell ref="V16:AD17"/>
+    <mergeCell ref="J12:R13"/>
+    <mergeCell ref="J14:R15"/>
+    <mergeCell ref="S12:U13"/>
+    <mergeCell ref="S14:U15"/>
+    <mergeCell ref="G47:I48"/>
+    <mergeCell ref="J47:R48"/>
+    <mergeCell ref="S47:U48"/>
+    <mergeCell ref="V47:AD48"/>
+    <mergeCell ref="G49:I50"/>
+    <mergeCell ref="J49:R50"/>
+    <mergeCell ref="S49:U50"/>
+    <mergeCell ref="V49:AD50"/>
+    <mergeCell ref="G51:I52"/>
+    <mergeCell ref="J51:R52"/>
+    <mergeCell ref="S51:U52"/>
+    <mergeCell ref="V51:AD52"/>
     <mergeCell ref="AG60:AJ61"/>
     <mergeCell ref="B62:B63"/>
     <mergeCell ref="B64:B65"/>
@@ -27174,54 +28107,99 @@
     <mergeCell ref="B60:B61"/>
     <mergeCell ref="C60:E61"/>
     <mergeCell ref="F60:H61"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="B76:B77"/>
+    <mergeCell ref="C62:E63"/>
+    <mergeCell ref="C64:E65"/>
+    <mergeCell ref="C66:E67"/>
+    <mergeCell ref="C68:E69"/>
+    <mergeCell ref="C70:E71"/>
+    <mergeCell ref="C72:E73"/>
+    <mergeCell ref="C74:E75"/>
+    <mergeCell ref="C76:E77"/>
     <mergeCell ref="B70:B71"/>
-    <mergeCell ref="G47:I48"/>
-    <mergeCell ref="J47:R48"/>
-    <mergeCell ref="S47:U48"/>
-    <mergeCell ref="V47:AD48"/>
-    <mergeCell ref="G49:I50"/>
-    <mergeCell ref="J49:R50"/>
-    <mergeCell ref="S49:U50"/>
-    <mergeCell ref="V49:AD50"/>
-    <mergeCell ref="G51:I52"/>
-    <mergeCell ref="J51:R52"/>
-    <mergeCell ref="S51:U52"/>
-    <mergeCell ref="V51:AD52"/>
-    <mergeCell ref="G53:I54"/>
-    <mergeCell ref="J53:R54"/>
-    <mergeCell ref="S53:U54"/>
-    <mergeCell ref="V53:AD54"/>
-    <mergeCell ref="G55:I56"/>
-    <mergeCell ref="S55:U56"/>
-    <mergeCell ref="V55:AD56"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="I3:AD3"/>
-    <mergeCell ref="AE3:AG3"/>
-    <mergeCell ref="AJ3:AK3"/>
-    <mergeCell ref="A1:AK1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="I2:AD2"/>
-    <mergeCell ref="AE2:AG2"/>
-    <mergeCell ref="AJ2:AK2"/>
-    <mergeCell ref="G8:I9"/>
-    <mergeCell ref="G10:I11"/>
-    <mergeCell ref="G12:I13"/>
-    <mergeCell ref="G14:I15"/>
-    <mergeCell ref="G16:I17"/>
-    <mergeCell ref="S16:U17"/>
-    <mergeCell ref="V8:AD9"/>
-    <mergeCell ref="V10:AD11"/>
-    <mergeCell ref="V12:AD13"/>
-    <mergeCell ref="V14:AD15"/>
-    <mergeCell ref="V16:AD17"/>
-    <mergeCell ref="J8:R9"/>
-    <mergeCell ref="J10:R11"/>
-    <mergeCell ref="J12:R13"/>
-    <mergeCell ref="J14:R15"/>
-    <mergeCell ref="S8:U9"/>
-    <mergeCell ref="S10:U11"/>
-    <mergeCell ref="S12:U13"/>
-    <mergeCell ref="S14:U15"/>
+    <mergeCell ref="AA66:AC67"/>
+    <mergeCell ref="AD66:AF67"/>
+    <mergeCell ref="AA64:AC65"/>
+    <mergeCell ref="AD64:AF65"/>
+    <mergeCell ref="F64:H65"/>
+    <mergeCell ref="I64:K65"/>
+    <mergeCell ref="L64:N65"/>
+    <mergeCell ref="O64:S65"/>
+    <mergeCell ref="T64:T65"/>
+    <mergeCell ref="AA70:AC71"/>
+    <mergeCell ref="AD70:AF71"/>
+    <mergeCell ref="U68:W69"/>
+    <mergeCell ref="X68:Z69"/>
+    <mergeCell ref="U70:W71"/>
+    <mergeCell ref="X70:Z71"/>
+    <mergeCell ref="AA68:AC69"/>
+    <mergeCell ref="AD68:AF69"/>
+    <mergeCell ref="F68:H69"/>
+    <mergeCell ref="I68:K69"/>
+    <mergeCell ref="L68:N69"/>
+    <mergeCell ref="O68:S69"/>
+    <mergeCell ref="T68:T69"/>
+    <mergeCell ref="U62:W63"/>
+    <mergeCell ref="X62:Z63"/>
+    <mergeCell ref="U64:W65"/>
+    <mergeCell ref="X64:Z65"/>
+    <mergeCell ref="U66:W67"/>
+    <mergeCell ref="X66:Z67"/>
+    <mergeCell ref="F70:H71"/>
+    <mergeCell ref="I70:K71"/>
+    <mergeCell ref="L70:N71"/>
+    <mergeCell ref="O70:S71"/>
+    <mergeCell ref="T70:T71"/>
+    <mergeCell ref="F66:H67"/>
+    <mergeCell ref="I66:K67"/>
+    <mergeCell ref="L66:N67"/>
+    <mergeCell ref="O66:S67"/>
+    <mergeCell ref="T66:T67"/>
+    <mergeCell ref="U72:W73"/>
+    <mergeCell ref="X72:Z73"/>
+    <mergeCell ref="AA72:AC73"/>
+    <mergeCell ref="AD72:AF73"/>
+    <mergeCell ref="F72:H73"/>
+    <mergeCell ref="I72:K73"/>
+    <mergeCell ref="L72:N73"/>
+    <mergeCell ref="O72:S73"/>
+    <mergeCell ref="T72:T73"/>
+    <mergeCell ref="U74:W75"/>
+    <mergeCell ref="X74:Z75"/>
+    <mergeCell ref="AA74:AC75"/>
+    <mergeCell ref="AD74:AF75"/>
+    <mergeCell ref="AG74:AH75"/>
+    <mergeCell ref="AI74:AJ75"/>
+    <mergeCell ref="F74:H75"/>
+    <mergeCell ref="I74:K75"/>
+    <mergeCell ref="L74:N75"/>
+    <mergeCell ref="O74:S75"/>
+    <mergeCell ref="T74:T75"/>
+    <mergeCell ref="U76:W77"/>
+    <mergeCell ref="X76:Z77"/>
+    <mergeCell ref="AA76:AC77"/>
+    <mergeCell ref="AD76:AF77"/>
+    <mergeCell ref="AG76:AH77"/>
+    <mergeCell ref="AI76:AJ77"/>
+    <mergeCell ref="F76:H77"/>
+    <mergeCell ref="I76:K77"/>
+    <mergeCell ref="L76:N77"/>
+    <mergeCell ref="O76:S77"/>
+    <mergeCell ref="T76:T77"/>
+    <mergeCell ref="AG68:AH69"/>
+    <mergeCell ref="AI68:AJ69"/>
+    <mergeCell ref="AG70:AH71"/>
+    <mergeCell ref="AI70:AJ71"/>
+    <mergeCell ref="AG72:AH73"/>
+    <mergeCell ref="AI72:AJ73"/>
+    <mergeCell ref="AG62:AH63"/>
+    <mergeCell ref="AI62:AJ63"/>
+    <mergeCell ref="AG64:AH65"/>
+    <mergeCell ref="AI64:AJ65"/>
+    <mergeCell ref="AG66:AH67"/>
+    <mergeCell ref="AI66:AJ67"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <printOptions horizontalCentered="1"/>

--- a/基本設計書.xlsx
+++ b/基本設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\7_Programing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6195F815-F6C7-4319-A9E8-8443F1602795}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A3B0E56-9E82-45E1-B31F-E106443D009F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="774" firstSheet="5" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="774" firstSheet="7" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IO関連図　原本・見本" sheetId="27" r:id="rId1"/>
@@ -21,6 +21,8 @@
     <sheet name="IO関連図（アカウント更新・削除）" sheetId="32" r:id="rId6"/>
     <sheet name="画面レイアウト（アカウント登録）" sheetId="15" r:id="rId7"/>
     <sheet name="画面レイアウト（アカウント検索・一覧）" sheetId="33" r:id="rId8"/>
+    <sheet name="画面レイアウト（アカウント更新）" sheetId="34" r:id="rId9"/>
+    <sheet name="画面レイアウト（アカウント削除）" sheetId="35" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'IO関連図　原本・見本'!$A$1:$AG$42</definedName>
@@ -29,6 +31,8 @@
     <definedName name="_xlnm.Print_Area" localSheetId="3">'IO関連図（アカウント登録）'!$A$1:$AG$42</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'画面レイアウト　原本・見本'!$A$1:$AG$42</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'画面レイアウト（アカウント検索・一覧）'!$A$1:$AK$81</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'画面レイアウト（アカウント更新）'!$A$1:$W$114</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">'画面レイアウト（アカウント削除）'!$A$1:$W$114</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'画面レイアウト（アカウント登録）'!$A$1:$W$114</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">表紙!$A$1:$AF$43</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'IO関連図　原本・見本'!$1:$2</definedName>
@@ -37,6 +41,8 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'IO関連図（アカウント登録）'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'画面レイアウト　原本・見本'!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'画面レイアウト（アカウント検索・一覧）'!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'画面レイアウト（アカウント更新）'!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'画面レイアウト（アカウント削除）'!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'画面レイアウト（アカウント登録）'!$1:$3</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
@@ -44,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="150">
   <si>
     <t>システム名</t>
     <rPh sb="4" eb="5">
@@ -1012,6 +1018,154 @@
     <t>ひなた</t>
     <phoneticPr fontId="4"/>
   </si>
+  <si>
+    <t>アカウント更新画面・更新確認画面・更新完了画面</t>
+    <rPh sb="5" eb="7">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>アカウント更新確認画面</t>
+    <rPh sb="5" eb="7">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>アカウント更新完了画面</t>
+    <rPh sb="5" eb="7">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>更新完了しました</t>
+    <rPh sb="0" eb="2">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>アカウント削除画面・削除確認画面・削除完了画面</t>
+    <rPh sb="5" eb="7">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>アカウント削除確認画面</t>
+    <rPh sb="5" eb="7">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>本当に削除してもよろしいですか？</t>
+    <rPh sb="0" eb="2">
+      <t>ホントウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>サクジョ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>アカウント削除確認画面</t>
+    <rPh sb="5" eb="9">
+      <t>サクジョカクニン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>アカウント削除完了画面</t>
+    <rPh sb="5" eb="7">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>削除完了しました</t>
+    <rPh sb="0" eb="2">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
 </sst>
 </file>
 
@@ -1021,7 +1175,7 @@
     <numFmt numFmtId="176" formatCode="m&quot;月&quot;d&quot;日&quot;;@"/>
     <numFmt numFmtId="177" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -1152,6 +1306,19 @@
     <font>
       <b/>
       <sz val="12"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="128"/>
@@ -1661,7 +1828,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="233">
+  <cellXfs count="235">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
@@ -2123,6 +2290,12 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="176" fontId="22" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -3207,6 +3380,293 @@
               <a:ea typeface="ＭＳ Ｐゴシック"/>
             </a:rPr>
             <a:t>一覧表</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>88900</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>215900</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>279400</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="Text Box 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{561C6F1B-D98D-42B5-A46F-DC63EB4EF2E6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1231900" y="15684500"/>
+          <a:ext cx="1047750" cy="298450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="C0C0C0" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="22"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="22860" rIns="36576" bIns="0" anchor="t" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>前に戻る</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>82550</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="Text Box 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6FBF645C-40AB-4296-8E20-B73EAD15A73B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4324350" y="15697200"/>
+          <a:ext cx="1047750" cy="311150"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="C0C0C0" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="22"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="22860" rIns="36576" bIns="0" anchor="t" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>削除する</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>200798</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>108122</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="22" name="Text Box 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AEA1CC72-767B-4FAD-B89D-CF15E6F08168}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="2772548" y="7391400"/>
+          <a:ext cx="1050324" cy="241300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="C0C0C0" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="22"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="22860" rIns="36576" bIns="0" anchor="t" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>確認する</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>226884</xdr:colOff>
+      <xdr:row>109</xdr:row>
+      <xdr:rowOff>42905</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>145878</xdr:colOff>
+      <xdr:row>110</xdr:row>
+      <xdr:rowOff>154459</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="24" name="Text Box 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1F1288BA-2930-4A0A-A51C-5012541F5DC6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="2512884" y="23918905"/>
+          <a:ext cx="1633494" cy="340154"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="C0C0C0" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="22"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="22860" rIns="36576" bIns="0" anchor="t" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>TOP</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>ページに戻る</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -8527,7 +8987,7 @@
       <xdr:col>4</xdr:col>
       <xdr:colOff>88900</xdr:colOff>
       <xdr:row>71</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:rowOff>203200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
@@ -8550,8 +9010,8 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="1231900" y="13843000"/>
-          <a:ext cx="1047750" cy="241300"/>
+          <a:off x="1231900" y="15671800"/>
+          <a:ext cx="1047750" cy="311150"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -10954,6 +11414,1467 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>273050</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>209550</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="正方形/長方形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A5CBDA6-D781-4998-B22B-4B6A325AF74D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2863850" y="3416300"/>
+          <a:ext cx="2552700" cy="196850"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>tanakataro@gmail.com</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>12700</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>279400</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>209550</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="正方形/長方形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CDA72866-6272-4567-8746-841C54C6BE62}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2870200" y="3873500"/>
+          <a:ext cx="2552700" cy="196850"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>273050</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>203200</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="正方形/長方形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A07AB0BC-4326-4AC1-954C-90AAABFE98E9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2863850" y="2495550"/>
+          <a:ext cx="2552700" cy="196850"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>タナカ</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>273050</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>203200</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="正方形/長方形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8ED100D7-BF05-4014-B8A1-8FE43D1B2800}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2863850" y="6153150"/>
+          <a:ext cx="2552700" cy="196850"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>1234-56</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>12700</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>279400</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>196850</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="正方形/長方形 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A718D248-9D8E-4ADA-AD2E-19B7A33D927B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2870200" y="5689600"/>
+          <a:ext cx="2552700" cy="196850"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>横浜市</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>222250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>273050</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="正方形/長方形 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3EBEAA32-17C5-4C3E-8305-2CCA083E69C9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2863850" y="4768850"/>
+          <a:ext cx="2552700" cy="196850"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>9876543</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>215900</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="8" name="グループ化 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A482F58-2352-4EFC-971C-883E1EC886EA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="2857500" y="6604000"/>
+          <a:ext cx="1149350" cy="215900"/>
+          <a:chOff x="2857500" y="6604000"/>
+          <a:chExt cx="1149350" cy="215900"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="9" name="正方形/長方形 8">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{56833A84-C67E-9ED1-7DEF-A345A797401D}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="2857500" y="6604000"/>
+            <a:ext cx="1149350" cy="215900"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="12700">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="10" name="グループ化 9">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{25A0201B-6967-2F70-4138-503492D93FDA}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="3810000" y="6654800"/>
+            <a:ext cx="120650" cy="107950"/>
+            <a:chOff x="3200400" y="7112000"/>
+            <a:chExt cx="184150" cy="127000"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="11" name="直線コネクタ 10">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3BC65D18-39F8-B68E-E34B-6B9BC1B184BA}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr/>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3200400" y="7112000"/>
+              <a:ext cx="82550" cy="127000"/>
+            </a:xfrm>
+            <a:prstGeom prst="line">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="12700"/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="1">
+              <a:schemeClr val="dk1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="dk1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="dk1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="12" name="直線コネクタ 11">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B9A2432-8047-85BF-E9C4-DD680AF049F8}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr/>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm flipV="1">
+              <a:off x="3282950" y="7112000"/>
+              <a:ext cx="101600" cy="127000"/>
+            </a:xfrm>
+            <a:prstGeom prst="line">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="12700"/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="1">
+              <a:schemeClr val="dk1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="dk1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="dk1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+      </xdr:grpSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>12700</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>215900</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="13" name="グループ化 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5E7DEF20-7695-45CA-A8C5-72CC160D8ECD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="2863850" y="5232400"/>
+          <a:ext cx="1149350" cy="215900"/>
+          <a:chOff x="2863850" y="5232400"/>
+          <a:chExt cx="1149350" cy="215900"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="14" name="正方形/長方形 13">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{697883A2-DC3C-85FF-8FC3-9DEAFB39A46D}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="2863850" y="5232400"/>
+            <a:ext cx="1149350" cy="215900"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="12700">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="15" name="グループ化 14">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00265363-5D90-2EB1-1BD3-664E80573534}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="3816350" y="5283200"/>
+            <a:ext cx="120650" cy="107950"/>
+            <a:chOff x="3200400" y="7112000"/>
+            <a:chExt cx="184150" cy="127000"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="16" name="直線コネクタ 15">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{42B5A7B5-209A-0E87-6715-C6D297C41BC5}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr/>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3200400" y="7112000"/>
+              <a:ext cx="82550" cy="127000"/>
+            </a:xfrm>
+            <a:prstGeom prst="line">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="12700"/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="1">
+              <a:schemeClr val="dk1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="dk1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="dk1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="17" name="直線コネクタ 16">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E5F4075-343D-6087-6B88-13A25D415B49}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr/>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm flipV="1">
+              <a:off x="3282950" y="7112000"/>
+              <a:ext cx="101600" cy="127000"/>
+            </a:xfrm>
+            <a:prstGeom prst="line">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="12700"/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="1">
+              <a:schemeClr val="dk1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="dk1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="dk1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+      </xdr:grpSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>12700</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>279400</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="正方形/長方形 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{445C694B-0C3D-418F-A227-3E8F34031571}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2870200" y="2038350"/>
+          <a:ext cx="2552700" cy="171450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>太郎</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>273050</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="正方形/長方形 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{84B93520-9FD5-4FD1-9D4C-CFC6CF8F8069}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2863850" y="2952750"/>
+          <a:ext cx="2552700" cy="171450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1200" b="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>タロウ</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP" sz="1200" b="0">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>88900</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>215900</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>279400</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="Text Box 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1397F3BA-3C12-45BE-984E-7F0BD6D87DF4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1231900" y="15684500"/>
+          <a:ext cx="1047750" cy="298450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="C0C0C0" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="22"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="22860" rIns="36576" bIns="0" anchor="t" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>前に戻る</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>82550</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="Text Box 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F940F459-950B-40A3-B83C-284A13721D83}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4324350" y="15697200"/>
+          <a:ext cx="1047750" cy="311150"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="C0C0C0" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="22"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="22860" rIns="36576" bIns="0" anchor="t" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>登録する</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>200798</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>108122</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="22" name="Text Box 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{40F9EEBC-0CDB-4FFA-A3B3-B3232935801E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="2772548" y="7391400"/>
+          <a:ext cx="1050324" cy="241300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="C0C0C0" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="22"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="22860" rIns="36576" bIns="0" anchor="t" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>確認する</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>25400</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="23" name="正方形/長方形 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{98750817-9733-4DBB-AF8F-3454B5866DB6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2882900" y="1593850"/>
+          <a:ext cx="2552700" cy="171450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1200" b="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>田中</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP" sz="1200">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP" sz="800">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>226884</xdr:colOff>
+      <xdr:row>109</xdr:row>
+      <xdr:rowOff>42905</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>145878</xdr:colOff>
+      <xdr:row>110</xdr:row>
+      <xdr:rowOff>154459</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="24" name="Text Box 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{435388FE-E1C8-4B8C-B881-C1758887C482}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="2512884" y="23918905"/>
+          <a:ext cx="1633494" cy="340154"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="C0C0C0" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="22"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="22860" rIns="36576" bIns="0" anchor="t" upright="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>TOP</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="ＭＳ Ｐゴシック"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
+            </a:rPr>
+            <a:t>ページに戻る</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>120650</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>177800</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>203200</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="25" name="楕円 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{29852E10-A73D-4796-AB9C-713CD7E2187C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2971800" y="4438650"/>
+          <a:ext cx="63500" cy="82550"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
@@ -12921,6 +14842,3120 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92893647-1EFA-4980-8F2F-7B330C3593AB}">
+  <sheetPr>
+    <tabColor theme="8" tint="0.39997558519241921"/>
+  </sheetPr>
+  <dimension ref="A1:FK114"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" customHeight="1"/>
+  <cols>
+    <col min="1" max="4" width="4.08984375" style="36" customWidth="1"/>
+    <col min="5" max="6" width="4.08984375" style="35" customWidth="1"/>
+    <col min="7" max="10" width="4.08984375" style="36" customWidth="1"/>
+    <col min="11" max="13" width="4.08984375" style="81" customWidth="1"/>
+    <col min="14" max="23" width="4.08984375" style="36" customWidth="1"/>
+    <col min="24" max="27" width="4" style="36" customWidth="1"/>
+    <col min="28" max="16384" width="9" style="36"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:167" ht="12.75" customHeight="1">
+      <c r="A1" s="166" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="166"/>
+      <c r="C1" s="166"/>
+      <c r="D1" s="166"/>
+      <c r="E1" s="166"/>
+      <c r="F1" s="166"/>
+      <c r="G1" s="166"/>
+      <c r="H1" s="166"/>
+      <c r="I1" s="166"/>
+      <c r="J1" s="166"/>
+      <c r="K1" s="166"/>
+      <c r="L1" s="166"/>
+      <c r="M1" s="166"/>
+      <c r="N1" s="166"/>
+      <c r="O1" s="166"/>
+      <c r="P1" s="166"/>
+      <c r="Q1" s="166"/>
+      <c r="R1" s="166"/>
+      <c r="S1" s="166"/>
+      <c r="T1" s="166"/>
+      <c r="U1" s="166"/>
+      <c r="V1" s="166"/>
+      <c r="W1" s="166"/>
+    </row>
+    <row r="2" spans="1:167" ht="13" customHeight="1">
+      <c r="A2" s="157" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="155"/>
+      <c r="C2" s="155"/>
+      <c r="D2" s="155"/>
+      <c r="E2" s="155"/>
+      <c r="F2" s="156"/>
+      <c r="G2" s="155" t="s">
+        <v>53</v>
+      </c>
+      <c r="H2" s="155"/>
+      <c r="I2" s="155"/>
+      <c r="J2" s="155"/>
+      <c r="K2" s="155"/>
+      <c r="L2" s="155"/>
+      <c r="M2" s="155"/>
+      <c r="N2" s="155"/>
+      <c r="O2" s="155"/>
+      <c r="P2" s="155"/>
+      <c r="Q2" s="155"/>
+      <c r="R2" s="155"/>
+      <c r="S2" s="156"/>
+      <c r="T2" s="157" t="s">
+        <v>1</v>
+      </c>
+      <c r="U2" s="156"/>
+      <c r="V2" s="157" t="s">
+        <v>2</v>
+      </c>
+      <c r="W2" s="156"/>
+    </row>
+    <row r="3" spans="1:167" s="15" customFormat="1" ht="12.75" customHeight="1">
+      <c r="A3" s="59" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" s="60"/>
+      <c r="C3" s="60"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="157" t="s">
+        <v>144</v>
+      </c>
+      <c r="H3" s="155"/>
+      <c r="I3" s="155"/>
+      <c r="J3" s="155"/>
+      <c r="K3" s="155"/>
+      <c r="L3" s="155"/>
+      <c r="M3" s="155"/>
+      <c r="N3" s="155"/>
+      <c r="O3" s="155"/>
+      <c r="P3" s="155"/>
+      <c r="Q3" s="155"/>
+      <c r="R3" s="155"/>
+      <c r="S3" s="155"/>
+      <c r="T3" s="202"/>
+      <c r="U3" s="202"/>
+      <c r="V3" s="202"/>
+      <c r="W3" s="202"/>
+      <c r="X3" s="13"/>
+      <c r="Y3" s="14"/>
+      <c r="Z3" s="14"/>
+      <c r="AA3" s="14"/>
+      <c r="AB3" s="14"/>
+      <c r="AC3" s="14"/>
+      <c r="AD3" s="14"/>
+      <c r="AE3" s="14"/>
+      <c r="AF3" s="14"/>
+      <c r="AG3" s="14"/>
+      <c r="AH3" s="14"/>
+      <c r="AI3" s="14"/>
+      <c r="AJ3" s="14"/>
+      <c r="AK3" s="14"/>
+      <c r="AL3" s="14"/>
+      <c r="AM3" s="14"/>
+      <c r="AN3" s="14"/>
+      <c r="AO3" s="14"/>
+      <c r="AP3" s="14"/>
+      <c r="AQ3" s="14"/>
+      <c r="AR3" s="14"/>
+      <c r="AS3" s="14"/>
+      <c r="AT3" s="14"/>
+      <c r="AU3" s="14"/>
+      <c r="AV3" s="14"/>
+      <c r="AW3" s="14"/>
+      <c r="AX3" s="14"/>
+      <c r="AY3" s="14"/>
+      <c r="AZ3" s="14"/>
+      <c r="BA3" s="14"/>
+      <c r="BB3" s="14"/>
+      <c r="BC3" s="14"/>
+      <c r="BD3" s="14"/>
+      <c r="BE3" s="14"/>
+      <c r="BF3" s="14"/>
+      <c r="BG3" s="14"/>
+      <c r="BH3" s="14"/>
+      <c r="BI3" s="14"/>
+      <c r="BJ3" s="14"/>
+      <c r="BK3" s="14"/>
+      <c r="BL3" s="14"/>
+      <c r="BM3" s="14"/>
+      <c r="BN3" s="14"/>
+      <c r="BO3" s="14"/>
+      <c r="BP3" s="14"/>
+      <c r="BQ3" s="14"/>
+      <c r="BR3" s="14"/>
+      <c r="BS3" s="14"/>
+      <c r="BT3" s="14"/>
+      <c r="BU3" s="14"/>
+      <c r="BV3" s="14"/>
+      <c r="BW3" s="14"/>
+      <c r="BX3" s="14"/>
+      <c r="BY3" s="14"/>
+      <c r="BZ3" s="14"/>
+      <c r="CA3" s="14"/>
+      <c r="CB3" s="14"/>
+      <c r="CC3" s="14"/>
+      <c r="CD3" s="14"/>
+      <c r="CE3" s="14"/>
+      <c r="CF3" s="14"/>
+      <c r="CG3" s="14"/>
+      <c r="CH3" s="14"/>
+      <c r="CI3" s="14"/>
+      <c r="CJ3" s="14"/>
+      <c r="CK3" s="14"/>
+      <c r="CL3" s="14"/>
+      <c r="CM3" s="14"/>
+      <c r="CN3" s="14"/>
+      <c r="CO3" s="14"/>
+      <c r="CP3" s="14"/>
+      <c r="CQ3" s="14"/>
+      <c r="CR3" s="14"/>
+      <c r="CS3" s="14"/>
+      <c r="CT3" s="14"/>
+      <c r="CU3" s="14"/>
+      <c r="CV3" s="14"/>
+      <c r="CW3" s="14"/>
+      <c r="CX3" s="14"/>
+      <c r="CY3" s="14"/>
+      <c r="CZ3" s="14"/>
+      <c r="DA3" s="14"/>
+      <c r="DB3" s="14"/>
+      <c r="DC3" s="14"/>
+      <c r="DD3" s="14"/>
+      <c r="DE3" s="14"/>
+      <c r="DF3" s="14"/>
+      <c r="DG3" s="14"/>
+      <c r="DH3" s="14"/>
+      <c r="DI3" s="14"/>
+      <c r="DJ3" s="14"/>
+      <c r="DK3" s="14"/>
+      <c r="DL3" s="14"/>
+      <c r="DM3" s="14"/>
+      <c r="DN3" s="14"/>
+      <c r="DO3" s="14"/>
+      <c r="DP3" s="14"/>
+      <c r="DQ3" s="14"/>
+      <c r="DR3" s="14"/>
+      <c r="DS3" s="14"/>
+      <c r="DT3" s="14"/>
+      <c r="DU3" s="14"/>
+      <c r="DV3" s="14"/>
+      <c r="DW3" s="14"/>
+      <c r="DX3" s="14"/>
+      <c r="DY3" s="14"/>
+      <c r="DZ3" s="14"/>
+      <c r="EA3" s="14"/>
+      <c r="EB3" s="14"/>
+      <c r="EC3" s="14"/>
+      <c r="ED3" s="14"/>
+      <c r="EE3" s="14"/>
+      <c r="EF3" s="14"/>
+      <c r="EG3" s="14"/>
+      <c r="EH3" s="14"/>
+      <c r="EI3" s="14"/>
+      <c r="EJ3" s="14"/>
+      <c r="EK3" s="14"/>
+      <c r="EL3" s="14"/>
+      <c r="EM3" s="14"/>
+      <c r="EN3" s="14"/>
+      <c r="EO3" s="14"/>
+      <c r="EP3" s="14"/>
+      <c r="EQ3" s="14"/>
+      <c r="ER3" s="14"/>
+      <c r="ES3" s="14"/>
+      <c r="ET3" s="14"/>
+      <c r="EU3" s="14"/>
+      <c r="EV3" s="14"/>
+      <c r="EW3" s="14"/>
+      <c r="EX3" s="14"/>
+      <c r="EY3" s="14"/>
+      <c r="EZ3" s="14"/>
+      <c r="FA3" s="14"/>
+      <c r="FB3" s="14"/>
+      <c r="FC3" s="14"/>
+      <c r="FD3" s="14"/>
+      <c r="FE3" s="14"/>
+      <c r="FF3" s="14"/>
+      <c r="FG3" s="14"/>
+      <c r="FH3" s="14"/>
+      <c r="FI3" s="14"/>
+      <c r="FJ3" s="14"/>
+      <c r="FK3" s="14"/>
+    </row>
+    <row r="4" spans="1:167" ht="12.75" customHeight="1">
+      <c r="A4" s="64"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="65"/>
+      <c r="K4" s="77"/>
+      <c r="L4" s="77"/>
+      <c r="M4" s="77"/>
+      <c r="N4" s="65"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
+      <c r="U4" s="65"/>
+      <c r="V4" s="65"/>
+      <c r="W4" s="65"/>
+    </row>
+    <row r="5" spans="1:167" ht="12.75" customHeight="1">
+      <c r="A5" s="66"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="67"/>
+      <c r="K5" s="78"/>
+      <c r="L5" s="78"/>
+      <c r="M5" s="78"/>
+      <c r="N5" s="67"/>
+      <c r="O5" s="67"/>
+      <c r="P5" s="67"/>
+      <c r="Q5" s="67"/>
+      <c r="R5" s="67"/>
+      <c r="S5" s="67"/>
+      <c r="T5" s="67"/>
+      <c r="U5" s="67"/>
+      <c r="V5" s="67"/>
+      <c r="W5" s="67"/>
+    </row>
+    <row r="6" spans="1:167" ht="12.75" customHeight="1">
+      <c r="A6" s="16"/>
+      <c r="B6" s="73" t="s">
+        <v>145</v>
+      </c>
+      <c r="C6" s="38"/>
+      <c r="D6" s="38"/>
+      <c r="E6" s="38"/>
+      <c r="F6" s="38"/>
+      <c r="G6" s="38"/>
+      <c r="H6" s="38"/>
+      <c r="I6" s="38"/>
+      <c r="J6" s="38"/>
+      <c r="K6" s="73"/>
+      <c r="L6" s="73"/>
+      <c r="M6" s="73"/>
+      <c r="N6" s="38"/>
+      <c r="O6" s="38"/>
+      <c r="P6" s="38"/>
+      <c r="Q6" s="38"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="38"/>
+      <c r="T6" s="38"/>
+      <c r="U6" s="38"/>
+      <c r="V6" s="38"/>
+      <c r="W6" s="38"/>
+    </row>
+    <row r="7" spans="1:167" ht="12.75" customHeight="1" thickBot="1">
+      <c r="A7" s="13"/>
+      <c r="B7" s="38"/>
+      <c r="C7" s="38"/>
+      <c r="D7" s="38"/>
+      <c r="E7" s="38"/>
+      <c r="F7" s="38"/>
+      <c r="G7" s="38"/>
+      <c r="H7" s="38"/>
+      <c r="I7" s="38"/>
+      <c r="J7" s="42"/>
+      <c r="K7" s="73"/>
+      <c r="L7" s="73"/>
+      <c r="M7" s="73"/>
+      <c r="N7" s="38"/>
+      <c r="O7" s="38"/>
+      <c r="P7" s="38"/>
+      <c r="Q7" s="38"/>
+      <c r="R7" s="38"/>
+      <c r="S7" s="38"/>
+      <c r="T7" s="38"/>
+      <c r="U7" s="42"/>
+      <c r="V7" s="42"/>
+      <c r="W7" s="38"/>
+    </row>
+    <row r="8" spans="1:167" ht="18" customHeight="1">
+      <c r="A8" s="13"/>
+      <c r="B8" s="38"/>
+      <c r="C8" s="82"/>
+      <c r="D8" s="83"/>
+      <c r="E8" s="83"/>
+      <c r="F8" s="83"/>
+      <c r="G8" s="83"/>
+      <c r="H8" s="83"/>
+      <c r="I8" s="83"/>
+      <c r="J8" s="83"/>
+      <c r="K8" s="85"/>
+      <c r="L8" s="85"/>
+      <c r="M8" s="85"/>
+      <c r="N8" s="83"/>
+      <c r="O8" s="83"/>
+      <c r="P8" s="83"/>
+      <c r="Q8" s="83"/>
+      <c r="R8" s="83"/>
+      <c r="S8" s="83"/>
+      <c r="T8" s="83"/>
+      <c r="U8" s="87"/>
+      <c r="V8" s="38"/>
+      <c r="W8" s="38"/>
+    </row>
+    <row r="9" spans="1:167" ht="18" customHeight="1">
+      <c r="A9" s="13"/>
+      <c r="B9" s="38"/>
+      <c r="C9" s="88"/>
+      <c r="D9" s="38"/>
+      <c r="E9" s="38"/>
+      <c r="F9" s="38"/>
+      <c r="G9" s="38"/>
+      <c r="H9" s="38"/>
+      <c r="I9" s="42"/>
+      <c r="J9" s="42"/>
+      <c r="K9" s="73"/>
+      <c r="L9" s="73"/>
+      <c r="M9" s="76"/>
+      <c r="N9" s="38"/>
+      <c r="O9" s="38"/>
+      <c r="P9" s="38"/>
+      <c r="Q9" s="38"/>
+      <c r="R9" s="38"/>
+      <c r="S9" s="38"/>
+      <c r="T9" s="38"/>
+      <c r="U9" s="89"/>
+      <c r="V9" s="38"/>
+      <c r="W9" s="38"/>
+    </row>
+    <row r="10" spans="1:167" ht="18" customHeight="1">
+      <c r="A10" s="13"/>
+      <c r="B10" s="38"/>
+      <c r="C10" s="88"/>
+      <c r="D10" s="38"/>
+      <c r="E10" s="73" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" s="44"/>
+      <c r="G10" s="38"/>
+      <c r="H10" s="38"/>
+      <c r="I10" s="38"/>
+      <c r="J10" s="38"/>
+      <c r="K10" s="73" t="s">
+        <v>71</v>
+      </c>
+      <c r="L10" s="73"/>
+      <c r="M10" s="73"/>
+      <c r="N10" s="38"/>
+      <c r="O10" s="38"/>
+      <c r="P10" s="38"/>
+      <c r="Q10" s="38"/>
+      <c r="R10" s="38"/>
+      <c r="S10" s="38"/>
+      <c r="T10" s="38"/>
+      <c r="U10" s="89"/>
+      <c r="V10" s="38"/>
+      <c r="W10" s="38"/>
+    </row>
+    <row r="11" spans="1:167" ht="18" customHeight="1">
+      <c r="A11" s="13"/>
+      <c r="B11" s="38"/>
+      <c r="C11" s="88"/>
+      <c r="D11" s="38"/>
+      <c r="E11" s="73"/>
+      <c r="F11" s="74"/>
+      <c r="G11" s="73"/>
+      <c r="H11" s="38"/>
+      <c r="I11" s="38"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="73"/>
+      <c r="L11" s="73"/>
+      <c r="M11" s="73"/>
+      <c r="N11" s="38"/>
+      <c r="O11" s="38"/>
+      <c r="P11" s="38"/>
+      <c r="Q11" s="38"/>
+      <c r="R11" s="38"/>
+      <c r="S11" s="38"/>
+      <c r="T11" s="38"/>
+      <c r="U11" s="89"/>
+      <c r="V11" s="38"/>
+      <c r="W11" s="38"/>
+    </row>
+    <row r="12" spans="1:167" ht="18" customHeight="1">
+      <c r="A12" s="13"/>
+      <c r="B12" s="38"/>
+      <c r="C12" s="88"/>
+      <c r="D12" s="38"/>
+      <c r="E12" s="73" t="s">
+        <v>56</v>
+      </c>
+      <c r="F12" s="73"/>
+      <c r="G12" s="73"/>
+      <c r="H12" s="38"/>
+      <c r="I12" s="38"/>
+      <c r="J12" s="38"/>
+      <c r="K12" s="73" t="s">
+        <v>72</v>
+      </c>
+      <c r="L12" s="73"/>
+      <c r="M12" s="73"/>
+      <c r="N12" s="38"/>
+      <c r="O12" s="63"/>
+      <c r="P12" s="63"/>
+      <c r="Q12" s="38"/>
+      <c r="R12" s="63"/>
+      <c r="S12" s="38"/>
+      <c r="T12" s="63"/>
+      <c r="U12" s="90"/>
+      <c r="V12" s="38"/>
+      <c r="W12" s="63"/>
+    </row>
+    <row r="13" spans="1:167" ht="18" customHeight="1">
+      <c r="A13" s="13"/>
+      <c r="B13" s="62"/>
+      <c r="C13" s="91"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="75"/>
+      <c r="F13" s="73"/>
+      <c r="G13" s="73"/>
+      <c r="H13" s="44"/>
+      <c r="I13" s="44"/>
+      <c r="J13" s="44"/>
+      <c r="K13" s="73"/>
+      <c r="L13" s="73"/>
+      <c r="M13" s="73"/>
+      <c r="N13" s="38"/>
+      <c r="O13" s="38"/>
+      <c r="P13" s="38"/>
+      <c r="Q13" s="38"/>
+      <c r="R13" s="38"/>
+      <c r="S13" s="44"/>
+      <c r="T13" s="44"/>
+      <c r="U13" s="92"/>
+      <c r="V13" s="44"/>
+      <c r="W13" s="44"/>
+    </row>
+    <row r="14" spans="1:167" ht="18" customHeight="1">
+      <c r="A14" s="13"/>
+      <c r="B14" s="38"/>
+      <c r="C14" s="88"/>
+      <c r="D14" s="38"/>
+      <c r="E14" s="73" t="s">
+        <v>57</v>
+      </c>
+      <c r="F14" s="73"/>
+      <c r="G14" s="73"/>
+      <c r="H14" s="44"/>
+      <c r="I14" s="38"/>
+      <c r="J14" s="38"/>
+      <c r="K14" s="73" t="s">
+        <v>73</v>
+      </c>
+      <c r="L14" s="73"/>
+      <c r="M14" s="73"/>
+      <c r="N14" s="38"/>
+      <c r="O14" s="38"/>
+      <c r="P14" s="38"/>
+      <c r="Q14" s="38"/>
+      <c r="R14" s="38"/>
+      <c r="S14" s="44"/>
+      <c r="T14" s="38"/>
+      <c r="U14" s="89"/>
+      <c r="V14" s="44"/>
+      <c r="W14" s="38"/>
+    </row>
+    <row r="15" spans="1:167" ht="18" customHeight="1">
+      <c r="A15" s="13"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="88"/>
+      <c r="D15" s="38"/>
+      <c r="E15" s="73"/>
+      <c r="F15" s="73"/>
+      <c r="G15" s="73"/>
+      <c r="H15" s="44"/>
+      <c r="I15" s="38"/>
+      <c r="J15" s="38"/>
+      <c r="K15" s="73"/>
+      <c r="L15" s="73"/>
+      <c r="M15" s="73"/>
+      <c r="N15" s="38"/>
+      <c r="O15" s="38"/>
+      <c r="P15" s="38"/>
+      <c r="Q15" s="38"/>
+      <c r="R15" s="38"/>
+      <c r="S15" s="44"/>
+      <c r="T15" s="38"/>
+      <c r="U15" s="89"/>
+      <c r="V15" s="44"/>
+      <c r="W15" s="38"/>
+    </row>
+    <row r="16" spans="1:167" ht="18" customHeight="1">
+      <c r="A16" s="13"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="88"/>
+      <c r="D16" s="38"/>
+      <c r="E16" s="73" t="s">
+        <v>58</v>
+      </c>
+      <c r="F16" s="73"/>
+      <c r="G16" s="73"/>
+      <c r="H16" s="44"/>
+      <c r="I16" s="38"/>
+      <c r="J16" s="38"/>
+      <c r="K16" s="73" t="s">
+        <v>74</v>
+      </c>
+      <c r="L16" s="73"/>
+      <c r="M16" s="73"/>
+      <c r="N16" s="38"/>
+      <c r="O16" s="38"/>
+      <c r="P16" s="38"/>
+      <c r="Q16" s="38"/>
+      <c r="R16" s="38"/>
+      <c r="S16" s="44"/>
+      <c r="T16" s="38"/>
+      <c r="U16" s="89"/>
+      <c r="V16" s="44"/>
+      <c r="W16" s="38"/>
+    </row>
+    <row r="17" spans="1:23" ht="18" customHeight="1">
+      <c r="A17" s="13"/>
+      <c r="B17" s="38"/>
+      <c r="C17" s="88"/>
+      <c r="D17" s="38"/>
+      <c r="E17" s="73"/>
+      <c r="F17" s="73"/>
+      <c r="G17" s="73"/>
+      <c r="H17" s="44"/>
+      <c r="I17" s="38"/>
+      <c r="J17" s="38"/>
+      <c r="K17" s="73"/>
+      <c r="L17" s="73"/>
+      <c r="M17" s="73"/>
+      <c r="N17" s="38"/>
+      <c r="O17" s="38"/>
+      <c r="P17" s="38"/>
+      <c r="Q17" s="38"/>
+      <c r="R17" s="38"/>
+      <c r="S17" s="44"/>
+      <c r="T17" s="38"/>
+      <c r="U17" s="89"/>
+      <c r="V17" s="44"/>
+      <c r="W17" s="38"/>
+    </row>
+    <row r="18" spans="1:23" ht="18" customHeight="1">
+      <c r="A18" s="13"/>
+      <c r="B18" s="38"/>
+      <c r="C18" s="88"/>
+      <c r="D18" s="38"/>
+      <c r="E18" s="73" t="s">
+        <v>59</v>
+      </c>
+      <c r="F18" s="73"/>
+      <c r="G18" s="73"/>
+      <c r="H18" s="44"/>
+      <c r="I18" s="38"/>
+      <c r="J18" s="38"/>
+      <c r="K18" s="73" t="s">
+        <v>75</v>
+      </c>
+      <c r="L18" s="73"/>
+      <c r="M18" s="73"/>
+      <c r="N18" s="38"/>
+      <c r="O18" s="38"/>
+      <c r="P18" s="38"/>
+      <c r="Q18" s="38"/>
+      <c r="R18" s="38"/>
+      <c r="S18" s="44"/>
+      <c r="T18" s="38"/>
+      <c r="U18" s="89"/>
+      <c r="V18" s="44"/>
+      <c r="W18" s="38"/>
+    </row>
+    <row r="19" spans="1:23" ht="18" customHeight="1">
+      <c r="A19" s="13"/>
+      <c r="B19" s="38"/>
+      <c r="C19" s="88"/>
+      <c r="D19" s="38"/>
+      <c r="E19" s="73"/>
+      <c r="F19" s="73"/>
+      <c r="G19" s="73"/>
+      <c r="H19" s="44"/>
+      <c r="I19" s="38"/>
+      <c r="J19" s="38"/>
+      <c r="K19" s="73"/>
+      <c r="L19" s="73"/>
+      <c r="M19" s="73"/>
+      <c r="N19" s="38"/>
+      <c r="O19" s="38"/>
+      <c r="P19" s="38"/>
+      <c r="Q19" s="38"/>
+      <c r="R19" s="38"/>
+      <c r="S19" s="44"/>
+      <c r="T19" s="38"/>
+      <c r="U19" s="89"/>
+      <c r="V19" s="44"/>
+      <c r="W19" s="38"/>
+    </row>
+    <row r="20" spans="1:23" ht="18" customHeight="1">
+      <c r="A20" s="13"/>
+      <c r="B20" s="38"/>
+      <c r="C20" s="88"/>
+      <c r="D20" s="38"/>
+      <c r="E20" s="73" t="s">
+        <v>60</v>
+      </c>
+      <c r="F20" s="73"/>
+      <c r="G20" s="73"/>
+      <c r="H20" s="44"/>
+      <c r="I20" s="38"/>
+      <c r="J20" s="38"/>
+      <c r="K20" s="73" t="s">
+        <v>76</v>
+      </c>
+      <c r="L20" s="73"/>
+      <c r="M20" s="73"/>
+      <c r="N20" s="38"/>
+      <c r="O20" s="38"/>
+      <c r="P20" s="38"/>
+      <c r="Q20" s="38"/>
+      <c r="R20" s="38"/>
+      <c r="S20" s="44"/>
+      <c r="T20" s="38"/>
+      <c r="U20" s="89"/>
+      <c r="V20" s="44"/>
+      <c r="W20" s="38"/>
+    </row>
+    <row r="21" spans="1:23" ht="18" customHeight="1">
+      <c r="A21" s="13"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="88"/>
+      <c r="D21" s="38"/>
+      <c r="E21" s="73"/>
+      <c r="F21" s="73"/>
+      <c r="G21" s="73"/>
+      <c r="H21" s="44"/>
+      <c r="I21" s="38"/>
+      <c r="J21" s="38"/>
+      <c r="K21" s="73"/>
+      <c r="L21" s="73"/>
+      <c r="M21" s="73"/>
+      <c r="N21" s="38"/>
+      <c r="O21" s="38"/>
+      <c r="P21" s="38"/>
+      <c r="Q21" s="38"/>
+      <c r="R21" s="38"/>
+      <c r="S21" s="44"/>
+      <c r="T21" s="38"/>
+      <c r="U21" s="89"/>
+      <c r="V21" s="44"/>
+      <c r="W21" s="38"/>
+    </row>
+    <row r="22" spans="1:23" ht="18" customHeight="1">
+      <c r="A22" s="13"/>
+      <c r="B22" s="38"/>
+      <c r="C22" s="88"/>
+      <c r="D22" s="38"/>
+      <c r="E22" s="73" t="s">
+        <v>61</v>
+      </c>
+      <c r="F22" s="73"/>
+      <c r="G22" s="73"/>
+      <c r="H22" s="44"/>
+      <c r="I22" s="38"/>
+      <c r="J22" s="38"/>
+      <c r="K22" s="76" t="s">
+        <v>68</v>
+      </c>
+      <c r="L22" s="76"/>
+      <c r="M22" s="73"/>
+      <c r="N22" s="38"/>
+      <c r="O22" s="76"/>
+      <c r="P22" s="76"/>
+      <c r="Q22" s="38"/>
+      <c r="R22" s="38"/>
+      <c r="S22" s="44"/>
+      <c r="T22" s="38"/>
+      <c r="U22" s="89"/>
+      <c r="V22" s="44"/>
+      <c r="W22" s="38"/>
+    </row>
+    <row r="23" spans="1:23" ht="18" customHeight="1">
+      <c r="A23" s="13"/>
+      <c r="B23" s="38"/>
+      <c r="C23" s="88"/>
+      <c r="D23" s="38"/>
+      <c r="E23" s="73"/>
+      <c r="F23" s="73"/>
+      <c r="G23" s="74"/>
+      <c r="H23" s="44"/>
+      <c r="I23" s="38"/>
+      <c r="J23" s="38"/>
+      <c r="K23" s="73"/>
+      <c r="L23" s="73"/>
+      <c r="M23" s="73"/>
+      <c r="N23" s="38"/>
+      <c r="O23" s="38"/>
+      <c r="P23" s="38"/>
+      <c r="Q23" s="38"/>
+      <c r="R23" s="38"/>
+      <c r="S23" s="44"/>
+      <c r="T23" s="38"/>
+      <c r="U23" s="89"/>
+      <c r="V23" s="44"/>
+      <c r="W23" s="38"/>
+    </row>
+    <row r="24" spans="1:23" ht="18" customHeight="1">
+      <c r="A24" s="13"/>
+      <c r="B24" s="38"/>
+      <c r="C24" s="88"/>
+      <c r="D24" s="38"/>
+      <c r="E24" s="73" t="s">
+        <v>62</v>
+      </c>
+      <c r="F24" s="73"/>
+      <c r="G24" s="74"/>
+      <c r="H24" s="44"/>
+      <c r="I24" s="38"/>
+      <c r="J24" s="38"/>
+      <c r="K24" s="203">
+        <v>9876543</v>
+      </c>
+      <c r="L24" s="203"/>
+      <c r="M24" s="203"/>
+      <c r="N24" s="203"/>
+      <c r="O24" s="38"/>
+      <c r="P24" s="38"/>
+      <c r="Q24" s="38"/>
+      <c r="R24" s="38"/>
+      <c r="S24" s="44"/>
+      <c r="T24" s="38"/>
+      <c r="U24" s="89"/>
+      <c r="V24" s="44"/>
+      <c r="W24" s="38"/>
+    </row>
+    <row r="25" spans="1:23" ht="18" customHeight="1">
+      <c r="A25" s="13"/>
+      <c r="B25" s="38"/>
+      <c r="C25" s="88"/>
+      <c r="D25" s="38"/>
+      <c r="E25" s="75"/>
+      <c r="F25" s="73"/>
+      <c r="G25" s="74"/>
+      <c r="H25" s="44"/>
+      <c r="I25" s="38"/>
+      <c r="J25" s="38"/>
+      <c r="K25" s="73"/>
+      <c r="L25" s="73"/>
+      <c r="M25" s="73"/>
+      <c r="N25" s="38"/>
+      <c r="O25" s="38"/>
+      <c r="P25" s="38"/>
+      <c r="Q25" s="38"/>
+      <c r="R25" s="38"/>
+      <c r="S25" s="44"/>
+      <c r="T25" s="38"/>
+      <c r="U25" s="89"/>
+      <c r="V25" s="44"/>
+      <c r="W25" s="38"/>
+    </row>
+    <row r="26" spans="1:23" ht="18" customHeight="1">
+      <c r="A26" s="13"/>
+      <c r="B26" s="38"/>
+      <c r="C26" s="88"/>
+      <c r="D26" s="38"/>
+      <c r="E26" s="73" t="s">
+        <v>63</v>
+      </c>
+      <c r="F26" s="73"/>
+      <c r="G26" s="74"/>
+      <c r="H26" s="44"/>
+      <c r="I26" s="38"/>
+      <c r="J26" s="38"/>
+      <c r="K26" s="73" t="s">
+        <v>77</v>
+      </c>
+      <c r="L26" s="73"/>
+      <c r="M26" s="73"/>
+      <c r="N26" s="38"/>
+      <c r="O26" s="38"/>
+      <c r="P26" s="38"/>
+      <c r="Q26" s="38"/>
+      <c r="R26" s="38"/>
+      <c r="S26" s="44"/>
+      <c r="T26" s="38"/>
+      <c r="U26" s="89"/>
+      <c r="V26" s="44"/>
+      <c r="W26" s="38"/>
+    </row>
+    <row r="27" spans="1:23" ht="18" customHeight="1">
+      <c r="A27" s="13"/>
+      <c r="B27" s="38"/>
+      <c r="C27" s="88"/>
+      <c r="D27" s="38"/>
+      <c r="E27" s="73"/>
+      <c r="F27" s="73"/>
+      <c r="G27" s="74"/>
+      <c r="H27" s="44"/>
+      <c r="I27" s="38"/>
+      <c r="J27" s="38"/>
+      <c r="K27" s="73"/>
+      <c r="L27" s="73"/>
+      <c r="M27" s="73"/>
+      <c r="N27" s="38"/>
+      <c r="O27" s="38"/>
+      <c r="P27" s="38"/>
+      <c r="Q27" s="38"/>
+      <c r="R27" s="38"/>
+      <c r="S27" s="44"/>
+      <c r="T27" s="38"/>
+      <c r="U27" s="89"/>
+      <c r="V27" s="44"/>
+      <c r="W27" s="38"/>
+    </row>
+    <row r="28" spans="1:23" ht="18" customHeight="1">
+      <c r="A28" s="13"/>
+      <c r="B28" s="38"/>
+      <c r="C28" s="88"/>
+      <c r="D28" s="38"/>
+      <c r="E28" s="75" t="s">
+        <v>64</v>
+      </c>
+      <c r="F28" s="73"/>
+      <c r="G28" s="74"/>
+      <c r="H28" s="44"/>
+      <c r="I28" s="38"/>
+      <c r="J28" s="38"/>
+      <c r="K28" s="73" t="s">
+        <v>78</v>
+      </c>
+      <c r="L28" s="73"/>
+      <c r="M28" s="73"/>
+      <c r="N28" s="38"/>
+      <c r="O28" s="38"/>
+      <c r="P28" s="38"/>
+      <c r="Q28" s="38"/>
+      <c r="R28" s="38"/>
+      <c r="S28" s="44"/>
+      <c r="T28" s="38"/>
+      <c r="U28" s="89"/>
+      <c r="V28" s="44"/>
+      <c r="W28" s="38"/>
+    </row>
+    <row r="29" spans="1:23" ht="18" customHeight="1">
+      <c r="A29" s="13"/>
+      <c r="B29" s="38"/>
+      <c r="C29" s="88"/>
+      <c r="D29" s="38"/>
+      <c r="E29" s="75"/>
+      <c r="F29" s="73"/>
+      <c r="G29" s="74"/>
+      <c r="H29" s="44"/>
+      <c r="I29" s="38"/>
+      <c r="J29" s="38"/>
+      <c r="K29" s="73"/>
+      <c r="L29" s="73"/>
+      <c r="M29" s="73"/>
+      <c r="N29" s="38"/>
+      <c r="O29" s="38"/>
+      <c r="P29" s="38"/>
+      <c r="Q29" s="38"/>
+      <c r="R29" s="38"/>
+      <c r="S29" s="44"/>
+      <c r="T29" s="38"/>
+      <c r="U29" s="89"/>
+      <c r="V29" s="44"/>
+      <c r="W29" s="38"/>
+    </row>
+    <row r="30" spans="1:23" ht="18" customHeight="1">
+      <c r="A30" s="13"/>
+      <c r="B30" s="38"/>
+      <c r="C30" s="88"/>
+      <c r="D30" s="38"/>
+      <c r="E30" s="75" t="s">
+        <v>65</v>
+      </c>
+      <c r="F30" s="73"/>
+      <c r="G30" s="74"/>
+      <c r="H30" s="44"/>
+      <c r="I30" s="38"/>
+      <c r="J30" s="38"/>
+      <c r="K30" s="204" t="s">
+        <v>79</v>
+      </c>
+      <c r="L30" s="204"/>
+      <c r="M30" s="204"/>
+      <c r="N30" s="38"/>
+      <c r="O30" s="38"/>
+      <c r="P30" s="38"/>
+      <c r="Q30" s="38"/>
+      <c r="R30" s="38"/>
+      <c r="S30" s="44"/>
+      <c r="T30" s="38"/>
+      <c r="U30" s="89"/>
+      <c r="V30" s="44"/>
+      <c r="W30" s="38"/>
+    </row>
+    <row r="31" spans="1:23" ht="18" customHeight="1">
+      <c r="A31" s="13"/>
+      <c r="B31" s="38"/>
+      <c r="C31" s="88"/>
+      <c r="D31" s="38"/>
+      <c r="E31" s="75"/>
+      <c r="F31" s="73"/>
+      <c r="G31" s="74"/>
+      <c r="H31" s="44"/>
+      <c r="I31" s="38"/>
+      <c r="J31" s="38"/>
+      <c r="K31" s="73"/>
+      <c r="L31" s="73"/>
+      <c r="M31" s="73"/>
+      <c r="N31" s="38"/>
+      <c r="O31" s="38"/>
+      <c r="P31" s="38"/>
+      <c r="Q31" s="38"/>
+      <c r="R31" s="38"/>
+      <c r="S31" s="44"/>
+      <c r="T31" s="38"/>
+      <c r="U31" s="89"/>
+      <c r="V31" s="44"/>
+      <c r="W31" s="38"/>
+    </row>
+    <row r="32" spans="1:23" ht="18" customHeight="1">
+      <c r="A32" s="13"/>
+      <c r="B32" s="38"/>
+      <c r="C32" s="88"/>
+      <c r="D32" s="38"/>
+      <c r="E32" s="73" t="s">
+        <v>66</v>
+      </c>
+      <c r="F32" s="73"/>
+      <c r="G32" s="74"/>
+      <c r="H32" s="44"/>
+      <c r="I32" s="38"/>
+      <c r="J32" s="38"/>
+      <c r="K32" s="73" t="s">
+        <v>80</v>
+      </c>
+      <c r="L32" s="73"/>
+      <c r="M32" s="73"/>
+      <c r="N32" s="38"/>
+      <c r="O32" s="38"/>
+      <c r="P32" s="38"/>
+      <c r="Q32" s="38"/>
+      <c r="R32" s="38"/>
+      <c r="S32" s="44"/>
+      <c r="T32" s="38"/>
+      <c r="U32" s="89"/>
+      <c r="V32" s="44"/>
+      <c r="W32" s="38"/>
+    </row>
+    <row r="33" spans="1:23" ht="18" customHeight="1">
+      <c r="A33" s="13"/>
+      <c r="B33" s="38"/>
+      <c r="C33" s="88"/>
+      <c r="D33" s="38"/>
+      <c r="E33" s="38"/>
+      <c r="F33" s="38"/>
+      <c r="G33" s="44"/>
+      <c r="H33" s="44"/>
+      <c r="I33" s="38"/>
+      <c r="J33" s="38"/>
+      <c r="K33" s="73"/>
+      <c r="L33" s="73"/>
+      <c r="M33" s="73"/>
+      <c r="N33" s="38"/>
+      <c r="O33" s="38"/>
+      <c r="P33" s="38"/>
+      <c r="Q33" s="38"/>
+      <c r="R33" s="38"/>
+      <c r="S33" s="44"/>
+      <c r="T33" s="38"/>
+      <c r="U33" s="89"/>
+      <c r="V33" s="44"/>
+      <c r="W33" s="38"/>
+    </row>
+    <row r="34" spans="1:23" ht="18" customHeight="1">
+      <c r="A34" s="13"/>
+      <c r="B34" s="38"/>
+      <c r="C34" s="88"/>
+      <c r="D34" s="38"/>
+      <c r="F34" s="38"/>
+      <c r="G34" s="44"/>
+      <c r="H34" s="44"/>
+      <c r="I34" s="38"/>
+      <c r="J34" s="38"/>
+      <c r="K34" s="73"/>
+      <c r="L34" s="73"/>
+      <c r="M34" s="73"/>
+      <c r="N34" s="38"/>
+      <c r="O34" s="38"/>
+      <c r="P34" s="38"/>
+      <c r="Q34" s="38"/>
+      <c r="R34" s="38"/>
+      <c r="S34" s="44"/>
+      <c r="T34" s="38"/>
+      <c r="U34" s="89"/>
+      <c r="V34" s="44"/>
+      <c r="W34" s="38"/>
+    </row>
+    <row r="35" spans="1:23" ht="18" customHeight="1">
+      <c r="A35" s="13"/>
+      <c r="B35" s="38"/>
+      <c r="C35" s="88"/>
+      <c r="D35" s="38"/>
+      <c r="E35" s="38"/>
+      <c r="F35" s="38"/>
+      <c r="G35" s="44"/>
+      <c r="H35" s="44"/>
+      <c r="I35" s="38"/>
+      <c r="J35" s="38"/>
+      <c r="K35" s="73"/>
+      <c r="L35" s="73"/>
+      <c r="M35" s="73"/>
+      <c r="N35" s="38"/>
+      <c r="O35" s="38"/>
+      <c r="P35" s="38"/>
+      <c r="Q35" s="38"/>
+      <c r="R35" s="38"/>
+      <c r="S35" s="44"/>
+      <c r="T35" s="38"/>
+      <c r="U35" s="89"/>
+      <c r="V35" s="44"/>
+      <c r="W35" s="38"/>
+    </row>
+    <row r="36" spans="1:23" ht="18" customHeight="1">
+      <c r="A36" s="13"/>
+      <c r="B36" s="13"/>
+      <c r="C36" s="93"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="13"/>
+      <c r="H36" s="13"/>
+      <c r="I36" s="13"/>
+      <c r="J36" s="13"/>
+      <c r="K36" s="13"/>
+      <c r="L36" s="13"/>
+      <c r="M36" s="13"/>
+      <c r="N36" s="13"/>
+      <c r="O36" s="13"/>
+      <c r="P36" s="13"/>
+      <c r="Q36" s="13"/>
+      <c r="R36" s="13"/>
+      <c r="S36" s="13"/>
+      <c r="T36" s="13"/>
+      <c r="U36" s="94"/>
+      <c r="V36" s="13"/>
+      <c r="W36" s="13"/>
+    </row>
+    <row r="37" spans="1:23" ht="18" customHeight="1" thickBot="1">
+      <c r="A37" s="13"/>
+      <c r="B37" s="13"/>
+      <c r="C37" s="95"/>
+      <c r="D37" s="96"/>
+      <c r="E37" s="96"/>
+      <c r="F37" s="96"/>
+      <c r="G37" s="96"/>
+      <c r="H37" s="96"/>
+      <c r="I37" s="96"/>
+      <c r="J37" s="96"/>
+      <c r="K37" s="96"/>
+      <c r="L37" s="96"/>
+      <c r="M37" s="96"/>
+      <c r="N37" s="96"/>
+      <c r="O37" s="96"/>
+      <c r="P37" s="96"/>
+      <c r="Q37" s="96"/>
+      <c r="R37" s="96"/>
+      <c r="S37" s="96"/>
+      <c r="T37" s="96"/>
+      <c r="U37" s="97"/>
+      <c r="V37" s="13"/>
+      <c r="W37" s="13"/>
+    </row>
+    <row r="38" spans="1:23" ht="18" customHeight="1">
+      <c r="A38" s="13"/>
+      <c r="B38" s="13"/>
+      <c r="C38" s="13"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="13"/>
+      <c r="H38" s="13"/>
+      <c r="I38" s="13"/>
+      <c r="J38" s="13"/>
+      <c r="K38" s="13"/>
+      <c r="L38" s="13"/>
+      <c r="M38" s="13"/>
+      <c r="N38" s="13"/>
+      <c r="O38" s="13"/>
+      <c r="P38" s="13"/>
+      <c r="Q38" s="13"/>
+      <c r="R38" s="13"/>
+      <c r="S38" s="13"/>
+      <c r="T38" s="13"/>
+      <c r="U38" s="13"/>
+      <c r="V38" s="13"/>
+      <c r="W38" s="13"/>
+    </row>
+    <row r="39" spans="1:23" ht="18" customHeight="1">
+      <c r="A39" s="66"/>
+      <c r="B39" s="68"/>
+      <c r="C39" s="68"/>
+      <c r="D39" s="68"/>
+      <c r="E39" s="69"/>
+      <c r="F39" s="69"/>
+      <c r="G39" s="68"/>
+      <c r="H39" s="68"/>
+      <c r="I39" s="68"/>
+      <c r="J39" s="68"/>
+      <c r="K39" s="79"/>
+      <c r="L39" s="79"/>
+      <c r="M39" s="79"/>
+      <c r="N39" s="68"/>
+      <c r="O39" s="68"/>
+      <c r="P39" s="68"/>
+      <c r="Q39" s="68"/>
+      <c r="R39" s="68"/>
+      <c r="S39" s="70"/>
+      <c r="T39" s="70"/>
+      <c r="U39" s="70"/>
+      <c r="V39" s="70"/>
+      <c r="W39" s="70"/>
+    </row>
+    <row r="40" spans="1:23" ht="18" customHeight="1">
+      <c r="A40" s="71"/>
+      <c r="B40" s="72"/>
+      <c r="C40" s="72"/>
+      <c r="D40" s="72"/>
+      <c r="E40" s="72"/>
+      <c r="F40" s="72"/>
+      <c r="G40" s="72"/>
+      <c r="H40" s="72"/>
+      <c r="I40" s="72"/>
+      <c r="J40" s="72"/>
+      <c r="K40" s="80"/>
+      <c r="L40" s="80"/>
+      <c r="M40" s="80"/>
+      <c r="N40" s="72"/>
+      <c r="O40" s="72"/>
+      <c r="P40" s="72"/>
+      <c r="Q40" s="72"/>
+      <c r="R40" s="72"/>
+      <c r="S40" s="72"/>
+      <c r="T40" s="72"/>
+      <c r="U40" s="72"/>
+      <c r="V40" s="72"/>
+      <c r="W40" s="72"/>
+    </row>
+    <row r="41" spans="1:23" ht="12.5" customHeight="1">
+      <c r="A41" s="64"/>
+      <c r="B41" s="65"/>
+      <c r="C41" s="65"/>
+      <c r="D41" s="65"/>
+      <c r="E41" s="65"/>
+      <c r="F41" s="65"/>
+      <c r="G41" s="65"/>
+      <c r="H41" s="65"/>
+      <c r="I41" s="65"/>
+      <c r="J41" s="65"/>
+      <c r="K41" s="77"/>
+      <c r="L41" s="77"/>
+      <c r="M41" s="77"/>
+      <c r="N41" s="65"/>
+      <c r="O41" s="65"/>
+      <c r="P41" s="65"/>
+      <c r="Q41" s="65"/>
+      <c r="R41" s="65"/>
+      <c r="S41" s="65"/>
+      <c r="T41" s="65"/>
+      <c r="U41" s="65"/>
+      <c r="V41" s="65"/>
+      <c r="W41" s="65"/>
+    </row>
+    <row r="42" spans="1:23" ht="12.5" customHeight="1">
+      <c r="A42" s="66"/>
+      <c r="B42" s="67"/>
+      <c r="C42" s="67"/>
+      <c r="D42" s="67"/>
+      <c r="E42" s="67"/>
+      <c r="F42" s="67"/>
+      <c r="G42" s="67"/>
+      <c r="H42" s="67"/>
+      <c r="I42" s="67"/>
+      <c r="J42" s="67"/>
+      <c r="K42" s="78"/>
+      <c r="L42" s="78"/>
+      <c r="M42" s="78"/>
+      <c r="N42" s="67"/>
+      <c r="O42" s="67"/>
+      <c r="P42" s="67"/>
+      <c r="Q42" s="67"/>
+      <c r="R42" s="67"/>
+      <c r="S42" s="67"/>
+      <c r="T42" s="67"/>
+      <c r="U42" s="67"/>
+      <c r="V42" s="67"/>
+      <c r="W42" s="67"/>
+    </row>
+    <row r="43" spans="1:23" ht="12.5" customHeight="1">
+      <c r="A43" s="16"/>
+      <c r="B43" s="73" t="s">
+        <v>147</v>
+      </c>
+      <c r="C43" s="38"/>
+      <c r="D43" s="38"/>
+      <c r="E43" s="38"/>
+      <c r="F43" s="38"/>
+      <c r="G43" s="38"/>
+      <c r="H43" s="38"/>
+      <c r="I43" s="38"/>
+      <c r="J43" s="38"/>
+      <c r="K43" s="73"/>
+      <c r="L43" s="73"/>
+      <c r="M43" s="73"/>
+      <c r="N43" s="38"/>
+      <c r="O43" s="38"/>
+      <c r="P43" s="38"/>
+      <c r="Q43" s="38"/>
+      <c r="R43" s="38"/>
+      <c r="S43" s="38"/>
+      <c r="T43" s="38"/>
+      <c r="U43" s="38"/>
+      <c r="V43" s="38"/>
+      <c r="W43" s="38"/>
+    </row>
+    <row r="44" spans="1:23" ht="12.5" customHeight="1">
+      <c r="A44" s="13"/>
+      <c r="B44" s="38"/>
+      <c r="C44" s="38"/>
+      <c r="D44" s="38"/>
+      <c r="E44" s="38"/>
+      <c r="F44" s="38"/>
+      <c r="G44" s="38"/>
+      <c r="H44" s="38"/>
+      <c r="I44" s="38"/>
+      <c r="J44" s="42"/>
+      <c r="K44" s="73"/>
+      <c r="L44" s="73"/>
+      <c r="M44" s="73"/>
+      <c r="N44" s="38"/>
+      <c r="O44" s="38"/>
+      <c r="P44" s="38"/>
+      <c r="Q44" s="38"/>
+      <c r="R44" s="38"/>
+      <c r="S44" s="38"/>
+      <c r="T44" s="38"/>
+      <c r="U44" s="42"/>
+      <c r="V44" s="42"/>
+      <c r="W44" s="38"/>
+    </row>
+    <row r="45" spans="1:23" ht="18" customHeight="1">
+      <c r="A45" s="13"/>
+      <c r="B45" s="38"/>
+      <c r="C45" s="38"/>
+      <c r="D45" s="38"/>
+      <c r="E45" s="38"/>
+      <c r="F45" s="38"/>
+      <c r="G45" s="38"/>
+      <c r="H45" s="38"/>
+      <c r="I45" s="38"/>
+      <c r="J45" s="38"/>
+      <c r="K45" s="73"/>
+      <c r="L45" s="73"/>
+      <c r="M45" s="73"/>
+      <c r="N45" s="38"/>
+      <c r="O45" s="38"/>
+      <c r="P45" s="38"/>
+      <c r="Q45" s="38"/>
+      <c r="R45" s="38"/>
+      <c r="S45" s="38"/>
+      <c r="T45" s="38"/>
+      <c r="U45" s="38"/>
+      <c r="V45" s="38"/>
+      <c r="W45" s="38"/>
+    </row>
+    <row r="46" spans="1:23" ht="18" customHeight="1">
+      <c r="A46" s="13"/>
+      <c r="B46" s="38"/>
+      <c r="C46" s="38"/>
+      <c r="D46" s="38"/>
+      <c r="E46" s="38"/>
+      <c r="F46" s="38"/>
+      <c r="G46" s="38"/>
+      <c r="H46" s="38"/>
+      <c r="I46" s="42"/>
+      <c r="J46" s="42"/>
+      <c r="K46" s="73"/>
+      <c r="L46" s="73"/>
+      <c r="M46" s="76"/>
+      <c r="N46" s="38"/>
+      <c r="O46" s="38"/>
+      <c r="P46" s="38"/>
+      <c r="Q46" s="38"/>
+      <c r="R46" s="38"/>
+      <c r="S46" s="38"/>
+      <c r="T46" s="38"/>
+      <c r="U46" s="38"/>
+      <c r="V46" s="38"/>
+      <c r="W46" s="38"/>
+    </row>
+    <row r="47" spans="1:23" ht="18" customHeight="1">
+      <c r="A47" s="13"/>
+      <c r="B47" s="38"/>
+      <c r="C47" s="38"/>
+      <c r="D47" s="38"/>
+      <c r="E47" s="73"/>
+      <c r="F47" s="44"/>
+      <c r="G47" s="38"/>
+      <c r="H47" s="38"/>
+      <c r="I47" s="38"/>
+      <c r="J47" s="38"/>
+      <c r="K47" s="73"/>
+      <c r="L47" s="73"/>
+      <c r="M47" s="73"/>
+      <c r="N47" s="38"/>
+      <c r="O47" s="38"/>
+      <c r="P47" s="38"/>
+      <c r="Q47" s="38"/>
+      <c r="R47" s="38"/>
+      <c r="S47" s="38"/>
+      <c r="T47" s="38"/>
+      <c r="U47" s="38"/>
+      <c r="V47" s="38"/>
+      <c r="W47" s="38"/>
+    </row>
+    <row r="48" spans="1:23" ht="18" customHeight="1">
+      <c r="A48" s="13"/>
+      <c r="B48" s="38"/>
+      <c r="C48" s="38"/>
+      <c r="D48" s="38"/>
+      <c r="E48" s="73"/>
+      <c r="F48" s="74"/>
+      <c r="G48" s="73"/>
+      <c r="H48" s="38"/>
+      <c r="I48" s="38"/>
+      <c r="J48" s="38"/>
+      <c r="K48" s="73"/>
+      <c r="L48" s="73"/>
+      <c r="M48" s="73"/>
+      <c r="N48" s="38"/>
+      <c r="O48" s="38"/>
+      <c r="P48" s="38"/>
+      <c r="Q48" s="38"/>
+      <c r="R48" s="38"/>
+      <c r="S48" s="38"/>
+      <c r="T48" s="38"/>
+      <c r="U48" s="38"/>
+      <c r="V48" s="38"/>
+      <c r="W48" s="38"/>
+    </row>
+    <row r="49" spans="1:23" ht="18" customHeight="1">
+      <c r="A49" s="13"/>
+      <c r="B49" s="38"/>
+      <c r="C49" s="38"/>
+      <c r="D49" s="38"/>
+      <c r="E49" s="73"/>
+      <c r="F49" s="73"/>
+      <c r="G49" s="73"/>
+      <c r="H49" s="38"/>
+      <c r="I49" s="38"/>
+      <c r="J49" s="38"/>
+      <c r="K49" s="73"/>
+      <c r="L49" s="73"/>
+      <c r="M49" s="73"/>
+      <c r="N49" s="38"/>
+      <c r="O49" s="63"/>
+      <c r="P49" s="63"/>
+      <c r="Q49" s="38"/>
+      <c r="R49" s="63"/>
+      <c r="S49" s="38"/>
+      <c r="T49" s="63"/>
+      <c r="U49" s="63"/>
+      <c r="V49" s="38"/>
+      <c r="W49" s="63"/>
+    </row>
+    <row r="50" spans="1:23" ht="18" customHeight="1">
+      <c r="A50" s="13"/>
+      <c r="B50" s="62"/>
+      <c r="C50" s="62"/>
+      <c r="D50" s="38"/>
+      <c r="E50" s="75"/>
+      <c r="F50" s="73"/>
+      <c r="G50" s="73"/>
+      <c r="H50" s="44"/>
+      <c r="I50" s="44"/>
+      <c r="J50" s="44"/>
+      <c r="K50" s="73"/>
+      <c r="L50" s="73"/>
+      <c r="M50" s="73"/>
+      <c r="N50" s="38"/>
+      <c r="O50" s="38"/>
+      <c r="P50" s="38"/>
+      <c r="Q50" s="38"/>
+      <c r="R50" s="38"/>
+      <c r="S50" s="44"/>
+      <c r="T50" s="44"/>
+      <c r="U50" s="44"/>
+      <c r="V50" s="44"/>
+      <c r="W50" s="44"/>
+    </row>
+    <row r="51" spans="1:23" ht="18" customHeight="1">
+      <c r="A51" s="13"/>
+      <c r="B51" s="38"/>
+      <c r="C51" s="38"/>
+      <c r="D51" s="38"/>
+      <c r="E51" s="73"/>
+      <c r="F51" s="73"/>
+      <c r="G51" s="73"/>
+      <c r="H51" s="44"/>
+      <c r="I51" s="38"/>
+      <c r="J51" s="38"/>
+      <c r="K51" s="73"/>
+      <c r="L51" s="73"/>
+      <c r="M51" s="73"/>
+      <c r="N51" s="38"/>
+      <c r="O51" s="38"/>
+      <c r="P51" s="38"/>
+      <c r="Q51" s="38"/>
+      <c r="R51" s="38"/>
+      <c r="S51" s="44"/>
+      <c r="T51" s="38"/>
+      <c r="U51" s="38"/>
+      <c r="V51" s="44"/>
+      <c r="W51" s="38"/>
+    </row>
+    <row r="52" spans="1:23" ht="18" customHeight="1">
+      <c r="A52" s="13"/>
+      <c r="B52" s="38"/>
+      <c r="C52" s="38"/>
+      <c r="D52" s="38"/>
+      <c r="E52" s="73"/>
+      <c r="F52" s="73"/>
+      <c r="G52" s="73"/>
+      <c r="H52" s="44"/>
+      <c r="I52" s="38"/>
+      <c r="J52" s="38"/>
+      <c r="K52" s="73"/>
+      <c r="L52" s="73"/>
+      <c r="M52" s="73"/>
+      <c r="N52" s="38"/>
+      <c r="O52" s="38"/>
+      <c r="P52" s="38"/>
+      <c r="Q52" s="38"/>
+      <c r="R52" s="38"/>
+      <c r="S52" s="44"/>
+      <c r="T52" s="38"/>
+      <c r="U52" s="38"/>
+      <c r="V52" s="44"/>
+      <c r="W52" s="38"/>
+    </row>
+    <row r="53" spans="1:23" ht="18" customHeight="1">
+      <c r="A53" s="13"/>
+      <c r="B53" s="38"/>
+      <c r="C53" s="38"/>
+      <c r="D53" s="38"/>
+      <c r="E53" s="73"/>
+      <c r="F53" s="73"/>
+      <c r="G53" s="73"/>
+      <c r="H53" s="44"/>
+      <c r="I53" s="38"/>
+      <c r="J53" s="38"/>
+      <c r="K53" s="73"/>
+      <c r="L53" s="73"/>
+      <c r="M53" s="73"/>
+      <c r="N53" s="38"/>
+      <c r="O53" s="38"/>
+      <c r="P53" s="38"/>
+      <c r="Q53" s="38"/>
+      <c r="R53" s="38"/>
+      <c r="S53" s="44"/>
+      <c r="T53" s="38"/>
+      <c r="U53" s="38"/>
+      <c r="V53" s="44"/>
+      <c r="W53" s="38"/>
+    </row>
+    <row r="54" spans="1:23" ht="18" customHeight="1">
+      <c r="A54" s="13"/>
+      <c r="B54" s="38"/>
+      <c r="C54" s="38"/>
+      <c r="D54" s="38"/>
+      <c r="E54" s="73"/>
+      <c r="F54" s="73"/>
+      <c r="G54" s="73"/>
+      <c r="H54" s="44"/>
+      <c r="I54" s="38"/>
+      <c r="J54" s="38"/>
+      <c r="K54" s="73"/>
+      <c r="L54" s="73"/>
+      <c r="M54" s="73"/>
+      <c r="N54" s="38"/>
+      <c r="O54" s="38"/>
+      <c r="P54" s="38"/>
+      <c r="Q54" s="38"/>
+      <c r="R54" s="38"/>
+      <c r="S54" s="44"/>
+      <c r="T54" s="38"/>
+      <c r="U54" s="38"/>
+      <c r="V54" s="44"/>
+      <c r="W54" s="38"/>
+    </row>
+    <row r="55" spans="1:23" ht="18" customHeight="1">
+      <c r="A55" s="13"/>
+      <c r="B55" s="38"/>
+      <c r="C55" s="38"/>
+      <c r="D55" s="38"/>
+      <c r="E55" s="73"/>
+      <c r="F55" s="234" t="s">
+        <v>146</v>
+      </c>
+      <c r="G55" s="234"/>
+      <c r="H55" s="234"/>
+      <c r="I55" s="234"/>
+      <c r="J55" s="234"/>
+      <c r="K55" s="234"/>
+      <c r="L55" s="234"/>
+      <c r="M55" s="234"/>
+      <c r="N55" s="234"/>
+      <c r="O55" s="234"/>
+      <c r="P55" s="234"/>
+      <c r="Q55" s="234"/>
+      <c r="R55" s="234"/>
+      <c r="S55" s="44"/>
+      <c r="T55" s="38"/>
+      <c r="U55" s="38"/>
+      <c r="V55" s="44"/>
+      <c r="W55" s="38"/>
+    </row>
+    <row r="56" spans="1:23" ht="18" customHeight="1">
+      <c r="A56" s="13"/>
+      <c r="B56" s="38"/>
+      <c r="C56" s="38"/>
+      <c r="D56" s="38"/>
+      <c r="E56" s="73"/>
+      <c r="F56" s="234"/>
+      <c r="G56" s="234"/>
+      <c r="H56" s="234"/>
+      <c r="I56" s="234"/>
+      <c r="J56" s="234"/>
+      <c r="K56" s="234"/>
+      <c r="L56" s="234"/>
+      <c r="M56" s="234"/>
+      <c r="N56" s="234"/>
+      <c r="O56" s="234"/>
+      <c r="P56" s="234"/>
+      <c r="Q56" s="234"/>
+      <c r="R56" s="234"/>
+      <c r="S56" s="44"/>
+      <c r="T56" s="38"/>
+      <c r="U56" s="38"/>
+      <c r="V56" s="44"/>
+      <c r="W56" s="38"/>
+    </row>
+    <row r="57" spans="1:23" ht="18" customHeight="1">
+      <c r="A57" s="13"/>
+      <c r="B57" s="38"/>
+      <c r="C57" s="38"/>
+      <c r="D57" s="38"/>
+      <c r="E57" s="73"/>
+      <c r="F57" s="234"/>
+      <c r="G57" s="234"/>
+      <c r="H57" s="234"/>
+      <c r="I57" s="234"/>
+      <c r="J57" s="234"/>
+      <c r="K57" s="234"/>
+      <c r="L57" s="234"/>
+      <c r="M57" s="234"/>
+      <c r="N57" s="234"/>
+      <c r="O57" s="234"/>
+      <c r="P57" s="234"/>
+      <c r="Q57" s="234"/>
+      <c r="R57" s="234"/>
+      <c r="S57" s="44"/>
+      <c r="T57" s="38"/>
+      <c r="U57" s="38"/>
+      <c r="V57" s="44"/>
+      <c r="W57" s="38"/>
+    </row>
+    <row r="58" spans="1:23" ht="18" customHeight="1">
+      <c r="A58" s="13"/>
+      <c r="B58" s="38"/>
+      <c r="C58" s="38"/>
+      <c r="D58" s="38"/>
+      <c r="E58" s="73"/>
+      <c r="F58" s="73"/>
+      <c r="G58" s="73"/>
+      <c r="H58" s="44"/>
+      <c r="I58" s="38"/>
+      <c r="J58" s="38"/>
+      <c r="K58" s="73"/>
+      <c r="L58" s="73"/>
+      <c r="M58" s="73"/>
+      <c r="N58" s="38"/>
+      <c r="O58" s="38"/>
+      <c r="P58" s="38"/>
+      <c r="Q58" s="38"/>
+      <c r="R58" s="38"/>
+      <c r="S58" s="44"/>
+      <c r="T58" s="38"/>
+      <c r="U58" s="38"/>
+      <c r="V58" s="44"/>
+      <c r="W58" s="38"/>
+    </row>
+    <row r="59" spans="1:23" ht="18" customHeight="1">
+      <c r="A59" s="13"/>
+      <c r="B59" s="38"/>
+      <c r="C59" s="38"/>
+      <c r="D59" s="38"/>
+      <c r="E59" s="73"/>
+      <c r="F59" s="73"/>
+      <c r="G59" s="73"/>
+      <c r="H59" s="44"/>
+      <c r="I59" s="38"/>
+      <c r="J59" s="38"/>
+      <c r="K59" s="76"/>
+      <c r="L59" s="76"/>
+      <c r="M59" s="73"/>
+      <c r="N59" s="38"/>
+      <c r="O59" s="76"/>
+      <c r="P59" s="76"/>
+      <c r="Q59" s="38"/>
+      <c r="R59" s="38"/>
+      <c r="S59" s="44"/>
+      <c r="T59" s="38"/>
+      <c r="U59" s="38"/>
+      <c r="V59" s="44"/>
+      <c r="W59" s="38"/>
+    </row>
+    <row r="60" spans="1:23" ht="18" customHeight="1">
+      <c r="A60" s="13"/>
+      <c r="B60" s="38"/>
+      <c r="C60" s="38"/>
+      <c r="D60" s="38"/>
+      <c r="E60" s="73"/>
+      <c r="F60" s="73"/>
+      <c r="G60" s="74"/>
+      <c r="H60" s="44"/>
+      <c r="I60" s="38"/>
+      <c r="J60" s="38"/>
+      <c r="K60" s="73"/>
+      <c r="L60" s="73"/>
+      <c r="M60" s="73"/>
+      <c r="N60" s="38"/>
+      <c r="O60" s="38"/>
+      <c r="P60" s="38"/>
+      <c r="Q60" s="38"/>
+      <c r="R60" s="38"/>
+      <c r="S60" s="44"/>
+      <c r="T60" s="38"/>
+      <c r="U60" s="38"/>
+      <c r="V60" s="44"/>
+      <c r="W60" s="38"/>
+    </row>
+    <row r="61" spans="1:23" ht="18" customHeight="1">
+      <c r="A61" s="13"/>
+      <c r="B61" s="38"/>
+      <c r="C61" s="38"/>
+      <c r="D61" s="38"/>
+      <c r="E61" s="73"/>
+      <c r="F61" s="73"/>
+      <c r="G61" s="74"/>
+      <c r="H61" s="44"/>
+      <c r="I61" s="38"/>
+      <c r="J61" s="38"/>
+      <c r="K61" s="203"/>
+      <c r="L61" s="203"/>
+      <c r="M61" s="203"/>
+      <c r="N61" s="203"/>
+      <c r="O61" s="38"/>
+      <c r="P61" s="38"/>
+      <c r="Q61" s="38"/>
+      <c r="R61" s="38"/>
+      <c r="S61" s="44"/>
+      <c r="T61" s="38"/>
+      <c r="U61" s="38"/>
+      <c r="V61" s="44"/>
+      <c r="W61" s="38"/>
+    </row>
+    <row r="62" spans="1:23" ht="18" customHeight="1">
+      <c r="A62" s="13"/>
+      <c r="B62" s="38"/>
+      <c r="C62" s="38"/>
+      <c r="D62" s="38"/>
+      <c r="E62" s="75"/>
+      <c r="F62" s="73"/>
+      <c r="G62" s="74"/>
+      <c r="H62" s="44"/>
+      <c r="I62" s="38"/>
+      <c r="J62" s="38"/>
+      <c r="K62" s="73"/>
+      <c r="L62" s="73"/>
+      <c r="M62" s="73"/>
+      <c r="N62" s="38"/>
+      <c r="O62" s="38"/>
+      <c r="P62" s="38"/>
+      <c r="Q62" s="38"/>
+      <c r="R62" s="38"/>
+      <c r="S62" s="44"/>
+      <c r="T62" s="38"/>
+      <c r="U62" s="38"/>
+      <c r="V62" s="44"/>
+      <c r="W62" s="38"/>
+    </row>
+    <row r="63" spans="1:23" ht="18" customHeight="1">
+      <c r="A63" s="13"/>
+      <c r="B63" s="38"/>
+      <c r="C63" s="38"/>
+      <c r="D63" s="38"/>
+      <c r="E63" s="73"/>
+      <c r="F63" s="73"/>
+      <c r="G63" s="74"/>
+      <c r="H63" s="44"/>
+      <c r="I63" s="38"/>
+      <c r="J63" s="38"/>
+      <c r="K63" s="73"/>
+      <c r="L63" s="73"/>
+      <c r="M63" s="73"/>
+      <c r="N63" s="38"/>
+      <c r="O63" s="38"/>
+      <c r="P63" s="38"/>
+      <c r="Q63" s="38"/>
+      <c r="R63" s="38"/>
+      <c r="S63" s="44"/>
+      <c r="T63" s="38"/>
+      <c r="U63" s="38"/>
+      <c r="V63" s="44"/>
+      <c r="W63" s="38"/>
+    </row>
+    <row r="64" spans="1:23" ht="18" customHeight="1">
+      <c r="A64" s="13"/>
+      <c r="B64" s="38"/>
+      <c r="C64" s="38"/>
+      <c r="D64" s="38"/>
+      <c r="E64" s="73"/>
+      <c r="F64" s="73"/>
+      <c r="G64" s="74"/>
+      <c r="H64" s="44"/>
+      <c r="I64" s="38"/>
+      <c r="J64" s="38"/>
+      <c r="K64" s="73"/>
+      <c r="L64" s="73"/>
+      <c r="M64" s="73"/>
+      <c r="N64" s="38"/>
+      <c r="O64" s="38"/>
+      <c r="P64" s="38"/>
+      <c r="Q64" s="38"/>
+      <c r="R64" s="38"/>
+      <c r="S64" s="44"/>
+      <c r="T64" s="38"/>
+      <c r="U64" s="38"/>
+      <c r="V64" s="44"/>
+      <c r="W64" s="38"/>
+    </row>
+    <row r="65" spans="1:23" ht="18" customHeight="1">
+      <c r="A65" s="13"/>
+      <c r="B65" s="38"/>
+      <c r="C65" s="38"/>
+      <c r="D65" s="38"/>
+      <c r="E65" s="75"/>
+      <c r="F65" s="73"/>
+      <c r="G65" s="74"/>
+      <c r="H65" s="44"/>
+      <c r="I65" s="38"/>
+      <c r="J65" s="38"/>
+      <c r="K65" s="73"/>
+      <c r="L65" s="73"/>
+      <c r="M65" s="73"/>
+      <c r="N65" s="38"/>
+      <c r="O65" s="38"/>
+      <c r="P65" s="38"/>
+      <c r="Q65" s="38"/>
+      <c r="R65" s="38"/>
+      <c r="S65" s="44"/>
+      <c r="T65" s="38"/>
+      <c r="U65" s="38"/>
+      <c r="V65" s="44"/>
+      <c r="W65" s="38"/>
+    </row>
+    <row r="66" spans="1:23" ht="18" customHeight="1">
+      <c r="A66" s="13"/>
+      <c r="B66" s="38"/>
+      <c r="C66" s="38"/>
+      <c r="D66" s="38"/>
+      <c r="E66" s="75"/>
+      <c r="F66" s="73"/>
+      <c r="G66" s="74"/>
+      <c r="H66" s="44"/>
+      <c r="I66" s="38"/>
+      <c r="J66" s="38"/>
+      <c r="K66" s="73"/>
+      <c r="L66" s="73"/>
+      <c r="M66" s="73"/>
+      <c r="N66" s="38"/>
+      <c r="O66" s="38"/>
+      <c r="P66" s="38"/>
+      <c r="Q66" s="38"/>
+      <c r="R66" s="38"/>
+      <c r="S66" s="44"/>
+      <c r="T66" s="38"/>
+      <c r="U66" s="38"/>
+      <c r="V66" s="44"/>
+      <c r="W66" s="38"/>
+    </row>
+    <row r="67" spans="1:23" ht="18" customHeight="1">
+      <c r="A67" s="13"/>
+      <c r="B67" s="38"/>
+      <c r="C67" s="38"/>
+      <c r="D67" s="38"/>
+      <c r="E67" s="75"/>
+      <c r="F67" s="73"/>
+      <c r="G67" s="74"/>
+      <c r="H67" s="44"/>
+      <c r="I67" s="38"/>
+      <c r="J67" s="38"/>
+      <c r="K67" s="204"/>
+      <c r="L67" s="204"/>
+      <c r="M67" s="204"/>
+      <c r="N67" s="38"/>
+      <c r="O67" s="38"/>
+      <c r="P67" s="38"/>
+      <c r="Q67" s="38"/>
+      <c r="R67" s="38"/>
+      <c r="S67" s="44"/>
+      <c r="T67" s="38"/>
+      <c r="U67" s="38"/>
+      <c r="V67" s="44"/>
+      <c r="W67" s="38"/>
+    </row>
+    <row r="68" spans="1:23" ht="18" customHeight="1">
+      <c r="A68" s="13"/>
+      <c r="B68" s="38"/>
+      <c r="C68" s="38"/>
+      <c r="D68" s="38"/>
+      <c r="E68" s="75"/>
+      <c r="F68" s="73"/>
+      <c r="G68" s="74"/>
+      <c r="H68" s="44"/>
+      <c r="I68" s="38"/>
+      <c r="J68" s="38"/>
+      <c r="K68" s="73"/>
+      <c r="L68" s="73"/>
+      <c r="M68" s="73"/>
+      <c r="N68" s="38"/>
+      <c r="O68" s="38"/>
+      <c r="P68" s="38"/>
+      <c r="Q68" s="38"/>
+      <c r="R68" s="38"/>
+      <c r="S68" s="44"/>
+      <c r="T68" s="38"/>
+      <c r="U68" s="38"/>
+      <c r="V68" s="44"/>
+      <c r="W68" s="38"/>
+    </row>
+    <row r="69" spans="1:23" ht="18" customHeight="1">
+      <c r="A69" s="13"/>
+      <c r="B69" s="38"/>
+      <c r="C69" s="38"/>
+      <c r="D69" s="38"/>
+      <c r="E69" s="73"/>
+      <c r="F69" s="73"/>
+      <c r="G69" s="74"/>
+      <c r="H69" s="44"/>
+      <c r="I69" s="38"/>
+      <c r="J69" s="38"/>
+      <c r="K69" s="73"/>
+      <c r="L69" s="73"/>
+      <c r="M69" s="73"/>
+      <c r="N69" s="38"/>
+      <c r="O69" s="38"/>
+      <c r="P69" s="38"/>
+      <c r="Q69" s="38"/>
+      <c r="R69" s="38"/>
+      <c r="S69" s="44"/>
+      <c r="T69" s="38"/>
+      <c r="U69" s="38"/>
+      <c r="V69" s="44"/>
+      <c r="W69" s="38"/>
+    </row>
+    <row r="70" spans="1:23" ht="18" customHeight="1">
+      <c r="A70" s="13"/>
+      <c r="B70" s="38"/>
+      <c r="C70" s="38"/>
+      <c r="D70" s="38"/>
+      <c r="E70" s="38"/>
+      <c r="F70" s="38"/>
+      <c r="G70" s="44"/>
+      <c r="H70" s="44"/>
+      <c r="I70" s="38"/>
+      <c r="J70" s="38"/>
+      <c r="K70" s="73"/>
+      <c r="L70" s="73"/>
+      <c r="M70" s="73"/>
+      <c r="N70" s="38"/>
+      <c r="O70" s="38"/>
+      <c r="P70" s="38"/>
+      <c r="Q70" s="38"/>
+      <c r="R70" s="38"/>
+      <c r="S70" s="44"/>
+      <c r="T70" s="38"/>
+      <c r="U70" s="38"/>
+      <c r="V70" s="44"/>
+      <c r="W70" s="38"/>
+    </row>
+    <row r="71" spans="1:23" ht="18" customHeight="1">
+      <c r="A71" s="13"/>
+      <c r="B71" s="38"/>
+      <c r="C71" s="38"/>
+      <c r="D71" s="38"/>
+      <c r="F71" s="38"/>
+      <c r="G71" s="44"/>
+      <c r="H71" s="44"/>
+      <c r="I71" s="38"/>
+      <c r="J71" s="38"/>
+      <c r="K71" s="73"/>
+      <c r="L71" s="73"/>
+      <c r="M71" s="73"/>
+      <c r="N71" s="38"/>
+      <c r="O71" s="38"/>
+      <c r="P71" s="38"/>
+      <c r="Q71" s="38"/>
+      <c r="R71" s="38"/>
+      <c r="S71" s="44"/>
+      <c r="T71" s="38"/>
+      <c r="U71" s="38"/>
+      <c r="V71" s="44"/>
+      <c r="W71" s="38"/>
+    </row>
+    <row r="72" spans="1:23" ht="18" customHeight="1">
+      <c r="A72" s="13"/>
+      <c r="B72" s="38"/>
+      <c r="C72" s="38"/>
+      <c r="D72" s="38"/>
+      <c r="E72" s="38"/>
+      <c r="F72" s="38"/>
+      <c r="G72" s="44"/>
+      <c r="H72" s="44"/>
+      <c r="I72" s="38"/>
+      <c r="J72" s="38"/>
+      <c r="K72" s="73"/>
+      <c r="L72" s="73"/>
+      <c r="M72" s="73"/>
+      <c r="N72" s="38"/>
+      <c r="O72" s="38"/>
+      <c r="P72" s="38"/>
+      <c r="Q72" s="38"/>
+      <c r="R72" s="38"/>
+      <c r="S72" s="44"/>
+      <c r="T72" s="38"/>
+      <c r="U72" s="38"/>
+      <c r="V72" s="44"/>
+      <c r="W72" s="38"/>
+    </row>
+    <row r="73" spans="1:23" ht="18" customHeight="1">
+      <c r="A73" s="13"/>
+      <c r="B73" s="13"/>
+      <c r="C73" s="13"/>
+      <c r="D73" s="13"/>
+      <c r="E73" s="13"/>
+      <c r="F73" s="13"/>
+      <c r="G73" s="13"/>
+      <c r="H73" s="13"/>
+      <c r="I73" s="13"/>
+      <c r="J73" s="13"/>
+      <c r="K73" s="13"/>
+      <c r="L73" s="13"/>
+      <c r="M73" s="13"/>
+      <c r="N73" s="13"/>
+      <c r="O73" s="13"/>
+      <c r="P73" s="13"/>
+      <c r="Q73" s="13"/>
+      <c r="R73" s="13"/>
+      <c r="S73" s="13"/>
+      <c r="T73" s="13"/>
+      <c r="U73" s="13"/>
+      <c r="V73" s="13"/>
+      <c r="W73" s="13"/>
+    </row>
+    <row r="74" spans="1:23" ht="18" customHeight="1">
+      <c r="A74" s="13"/>
+      <c r="B74" s="13"/>
+      <c r="C74" s="13"/>
+      <c r="D74" s="13"/>
+      <c r="E74" s="13"/>
+      <c r="F74" s="13"/>
+      <c r="G74" s="13"/>
+      <c r="H74" s="13"/>
+      <c r="I74" s="13"/>
+      <c r="J74" s="13"/>
+      <c r="K74" s="13"/>
+      <c r="L74" s="13"/>
+      <c r="M74" s="13"/>
+      <c r="N74" s="13"/>
+      <c r="O74" s="13"/>
+      <c r="P74" s="13"/>
+      <c r="Q74" s="13"/>
+      <c r="R74" s="13"/>
+      <c r="S74" s="13"/>
+      <c r="T74" s="13"/>
+      <c r="U74" s="13"/>
+      <c r="V74" s="13"/>
+      <c r="W74" s="13"/>
+    </row>
+    <row r="75" spans="1:23" ht="18" customHeight="1">
+      <c r="A75" s="13"/>
+      <c r="B75" s="13"/>
+      <c r="C75" s="13"/>
+      <c r="D75" s="13"/>
+      <c r="E75" s="13"/>
+      <c r="F75" s="13"/>
+      <c r="G75" s="13"/>
+      <c r="H75" s="13"/>
+      <c r="I75" s="13"/>
+      <c r="J75" s="13"/>
+      <c r="K75" s="13"/>
+      <c r="L75" s="13"/>
+      <c r="M75" s="13"/>
+      <c r="N75" s="13"/>
+      <c r="O75" s="13"/>
+      <c r="P75" s="13"/>
+      <c r="Q75" s="13"/>
+      <c r="R75" s="13"/>
+      <c r="S75" s="13"/>
+      <c r="T75" s="13"/>
+      <c r="U75" s="13"/>
+      <c r="V75" s="13"/>
+      <c r="W75" s="13"/>
+    </row>
+    <row r="76" spans="1:23" ht="18" customHeight="1">
+      <c r="A76" s="66"/>
+      <c r="B76" s="68"/>
+      <c r="C76" s="68"/>
+      <c r="D76" s="68"/>
+      <c r="E76" s="69"/>
+      <c r="F76" s="69"/>
+      <c r="G76" s="68"/>
+      <c r="H76" s="68"/>
+      <c r="I76" s="68"/>
+      <c r="J76" s="68"/>
+      <c r="K76" s="79"/>
+      <c r="L76" s="79"/>
+      <c r="M76" s="79"/>
+      <c r="N76" s="68"/>
+      <c r="O76" s="68"/>
+      <c r="P76" s="68"/>
+      <c r="Q76" s="68"/>
+      <c r="R76" s="68"/>
+      <c r="S76" s="70"/>
+      <c r="T76" s="70"/>
+      <c r="U76" s="70"/>
+      <c r="V76" s="70"/>
+      <c r="W76" s="70"/>
+    </row>
+    <row r="77" spans="1:23" ht="18" customHeight="1">
+      <c r="A77" s="71"/>
+      <c r="B77" s="72"/>
+      <c r="C77" s="72"/>
+      <c r="D77" s="72"/>
+      <c r="E77" s="72"/>
+      <c r="F77" s="72"/>
+      <c r="G77" s="72"/>
+      <c r="H77" s="72"/>
+      <c r="I77" s="72"/>
+      <c r="J77" s="72"/>
+      <c r="K77" s="80"/>
+      <c r="L77" s="80"/>
+      <c r="M77" s="80"/>
+      <c r="N77" s="72"/>
+      <c r="O77" s="72"/>
+      <c r="P77" s="72"/>
+      <c r="Q77" s="72"/>
+      <c r="R77" s="72"/>
+      <c r="S77" s="72"/>
+      <c r="T77" s="72"/>
+      <c r="U77" s="72"/>
+      <c r="V77" s="72"/>
+      <c r="W77" s="72"/>
+    </row>
+    <row r="78" spans="1:23" ht="12.75" customHeight="1">
+      <c r="A78" s="64"/>
+      <c r="B78" s="65"/>
+      <c r="C78" s="65"/>
+      <c r="D78" s="65"/>
+      <c r="E78" s="65"/>
+      <c r="F78" s="65"/>
+      <c r="G78" s="65"/>
+      <c r="H78" s="65"/>
+      <c r="I78" s="65"/>
+      <c r="J78" s="65"/>
+      <c r="K78" s="77"/>
+      <c r="L78" s="77"/>
+      <c r="M78" s="77"/>
+      <c r="N78" s="65"/>
+      <c r="O78" s="65"/>
+      <c r="P78" s="65"/>
+      <c r="Q78" s="65"/>
+      <c r="R78" s="65"/>
+      <c r="S78" s="65"/>
+      <c r="T78" s="65"/>
+      <c r="U78" s="65"/>
+      <c r="V78" s="65"/>
+      <c r="W78" s="65"/>
+    </row>
+    <row r="79" spans="1:23" ht="12.75" customHeight="1">
+      <c r="A79" s="66"/>
+      <c r="B79" s="67"/>
+      <c r="C79" s="67"/>
+      <c r="D79" s="67"/>
+      <c r="E79" s="67"/>
+      <c r="F79" s="67"/>
+      <c r="G79" s="67"/>
+      <c r="H79" s="67"/>
+      <c r="I79" s="67"/>
+      <c r="J79" s="67"/>
+      <c r="K79" s="78"/>
+      <c r="L79" s="78"/>
+      <c r="M79" s="78"/>
+      <c r="N79" s="67"/>
+      <c r="O79" s="67"/>
+      <c r="P79" s="67"/>
+      <c r="Q79" s="67"/>
+      <c r="R79" s="67"/>
+      <c r="S79" s="67"/>
+      <c r="T79" s="67"/>
+      <c r="U79" s="67"/>
+      <c r="V79" s="67"/>
+      <c r="W79" s="67"/>
+    </row>
+    <row r="80" spans="1:23" ht="12.75" customHeight="1">
+      <c r="A80" s="16"/>
+      <c r="B80" s="73" t="s">
+        <v>148</v>
+      </c>
+      <c r="C80" s="38"/>
+      <c r="D80" s="38"/>
+      <c r="E80" s="38"/>
+      <c r="F80" s="38"/>
+      <c r="G80" s="38"/>
+      <c r="H80" s="38"/>
+      <c r="I80" s="38"/>
+      <c r="J80" s="38"/>
+      <c r="K80" s="73"/>
+      <c r="L80" s="73"/>
+      <c r="M80" s="73"/>
+      <c r="N80" s="38"/>
+      <c r="O80" s="38"/>
+      <c r="P80" s="38"/>
+      <c r="Q80" s="38"/>
+      <c r="R80" s="38"/>
+      <c r="S80" s="38"/>
+      <c r="T80" s="38"/>
+      <c r="U80" s="38"/>
+      <c r="V80" s="38"/>
+      <c r="W80" s="38"/>
+    </row>
+    <row r="81" spans="1:23" ht="12.75" customHeight="1">
+      <c r="A81" s="13"/>
+      <c r="B81" s="38"/>
+      <c r="C81" s="38"/>
+      <c r="D81" s="38"/>
+      <c r="E81" s="38"/>
+      <c r="F81" s="38"/>
+      <c r="G81" s="38"/>
+      <c r="H81" s="38"/>
+      <c r="I81" s="38"/>
+      <c r="J81" s="42"/>
+      <c r="K81" s="73"/>
+      <c r="L81" s="73"/>
+      <c r="M81" s="73"/>
+      <c r="N81" s="38"/>
+      <c r="O81" s="38"/>
+      <c r="P81" s="38"/>
+      <c r="Q81" s="38"/>
+      <c r="R81" s="38"/>
+      <c r="S81" s="38"/>
+      <c r="T81" s="38"/>
+      <c r="U81" s="42"/>
+      <c r="V81" s="42"/>
+      <c r="W81" s="38"/>
+    </row>
+    <row r="82" spans="1:23" ht="18" customHeight="1">
+      <c r="A82" s="13"/>
+      <c r="B82" s="38"/>
+      <c r="C82" s="38"/>
+      <c r="D82" s="38"/>
+      <c r="E82" s="38"/>
+      <c r="F82" s="38"/>
+      <c r="G82" s="38"/>
+      <c r="H82" s="38"/>
+      <c r="I82" s="38"/>
+      <c r="J82" s="38"/>
+      <c r="K82" s="73"/>
+      <c r="L82" s="73"/>
+      <c r="M82" s="73"/>
+      <c r="N82" s="38"/>
+      <c r="O82" s="38"/>
+      <c r="P82" s="38"/>
+      <c r="Q82" s="38"/>
+      <c r="R82" s="38"/>
+      <c r="S82" s="38"/>
+      <c r="T82" s="38"/>
+      <c r="U82" s="38"/>
+      <c r="V82" s="38"/>
+      <c r="W82" s="38"/>
+    </row>
+    <row r="83" spans="1:23" ht="18" customHeight="1">
+      <c r="A83" s="13"/>
+      <c r="B83" s="38"/>
+      <c r="C83" s="38"/>
+      <c r="D83" s="38"/>
+      <c r="E83" s="38"/>
+      <c r="F83" s="38"/>
+      <c r="G83" s="38"/>
+      <c r="H83" s="38"/>
+      <c r="I83" s="42"/>
+      <c r="J83" s="42"/>
+      <c r="K83" s="73"/>
+      <c r="L83" s="73"/>
+      <c r="M83" s="76"/>
+      <c r="N83" s="38"/>
+      <c r="O83" s="38"/>
+      <c r="P83" s="38"/>
+      <c r="Q83" s="38"/>
+      <c r="R83" s="38"/>
+      <c r="S83" s="38"/>
+      <c r="T83" s="38"/>
+      <c r="U83" s="38"/>
+      <c r="V83" s="38"/>
+      <c r="W83" s="38"/>
+    </row>
+    <row r="84" spans="1:23" ht="18" customHeight="1">
+      <c r="A84" s="13"/>
+      <c r="B84" s="38"/>
+      <c r="C84" s="38"/>
+      <c r="D84" s="38"/>
+      <c r="E84" s="73"/>
+      <c r="F84" s="44"/>
+      <c r="G84" s="38"/>
+      <c r="H84" s="38"/>
+      <c r="I84" s="38"/>
+      <c r="J84" s="38"/>
+      <c r="K84" s="73"/>
+      <c r="L84" s="73"/>
+      <c r="M84" s="73"/>
+      <c r="N84" s="38"/>
+      <c r="O84" s="38"/>
+      <c r="P84" s="38"/>
+      <c r="Q84" s="38"/>
+      <c r="R84" s="38"/>
+      <c r="S84" s="38"/>
+      <c r="T84" s="38"/>
+      <c r="U84" s="38"/>
+      <c r="V84" s="38"/>
+      <c r="W84" s="38"/>
+    </row>
+    <row r="85" spans="1:23" ht="18" customHeight="1">
+      <c r="A85" s="13"/>
+      <c r="B85" s="38"/>
+      <c r="C85" s="38"/>
+      <c r="D85" s="38"/>
+      <c r="E85" s="73"/>
+      <c r="F85" s="74"/>
+      <c r="G85" s="73"/>
+      <c r="H85" s="38"/>
+      <c r="I85" s="38"/>
+      <c r="J85" s="38"/>
+      <c r="K85" s="73"/>
+      <c r="L85" s="73"/>
+      <c r="M85" s="73"/>
+      <c r="N85" s="38"/>
+      <c r="O85" s="38"/>
+      <c r="P85" s="38"/>
+      <c r="Q85" s="38"/>
+      <c r="R85" s="38"/>
+      <c r="S85" s="38"/>
+      <c r="T85" s="38"/>
+      <c r="U85" s="38"/>
+      <c r="V85" s="38"/>
+      <c r="W85" s="38"/>
+    </row>
+    <row r="86" spans="1:23" ht="18" customHeight="1">
+      <c r="A86" s="13"/>
+      <c r="B86" s="38"/>
+      <c r="C86" s="38"/>
+      <c r="D86" s="38"/>
+      <c r="E86" s="73"/>
+      <c r="F86" s="73"/>
+      <c r="G86" s="73"/>
+      <c r="H86" s="38"/>
+      <c r="I86" s="38"/>
+      <c r="J86" s="38"/>
+      <c r="K86" s="73"/>
+      <c r="L86" s="73"/>
+      <c r="M86" s="73"/>
+      <c r="N86" s="38"/>
+      <c r="O86" s="63"/>
+      <c r="P86" s="63"/>
+      <c r="Q86" s="38"/>
+      <c r="R86" s="63"/>
+      <c r="S86" s="38"/>
+      <c r="T86" s="63"/>
+      <c r="U86" s="63"/>
+      <c r="V86" s="38"/>
+      <c r="W86" s="63"/>
+    </row>
+    <row r="87" spans="1:23" ht="18" customHeight="1">
+      <c r="A87" s="13"/>
+      <c r="B87" s="62"/>
+      <c r="C87" s="62"/>
+      <c r="D87" s="38"/>
+      <c r="E87" s="75"/>
+      <c r="F87" s="73"/>
+      <c r="G87" s="73"/>
+      <c r="H87" s="44"/>
+      <c r="I87" s="44"/>
+      <c r="J87" s="44"/>
+      <c r="K87" s="73"/>
+      <c r="L87" s="73"/>
+      <c r="M87" s="73"/>
+      <c r="N87" s="38"/>
+      <c r="O87" s="38"/>
+      <c r="P87" s="38"/>
+      <c r="Q87" s="38"/>
+      <c r="R87" s="38"/>
+      <c r="S87" s="44"/>
+      <c r="T87" s="44"/>
+      <c r="U87" s="44"/>
+      <c r="V87" s="44"/>
+      <c r="W87" s="44"/>
+    </row>
+    <row r="88" spans="1:23" ht="18" customHeight="1">
+      <c r="A88" s="13"/>
+      <c r="B88" s="38"/>
+      <c r="C88" s="38"/>
+      <c r="D88" s="38"/>
+      <c r="E88" s="73"/>
+      <c r="F88" s="73"/>
+      <c r="G88" s="73"/>
+      <c r="H88" s="44"/>
+      <c r="I88" s="38"/>
+      <c r="J88" s="38"/>
+      <c r="K88" s="73"/>
+      <c r="L88" s="73"/>
+      <c r="M88" s="73"/>
+      <c r="N88" s="38"/>
+      <c r="O88" s="38"/>
+      <c r="P88" s="38"/>
+      <c r="Q88" s="38"/>
+      <c r="R88" s="38"/>
+      <c r="S88" s="44"/>
+      <c r="T88" s="38"/>
+      <c r="U88" s="38"/>
+      <c r="V88" s="44"/>
+      <c r="W88" s="38"/>
+    </row>
+    <row r="89" spans="1:23" ht="18" customHeight="1">
+      <c r="A89" s="13"/>
+      <c r="B89" s="38"/>
+      <c r="C89" s="38"/>
+      <c r="D89" s="38"/>
+      <c r="E89" s="73"/>
+      <c r="F89" s="73"/>
+      <c r="G89" s="73"/>
+      <c r="H89" s="44"/>
+      <c r="I89" s="38"/>
+      <c r="J89" s="38"/>
+      <c r="K89" s="73"/>
+      <c r="L89" s="73"/>
+      <c r="M89" s="73"/>
+      <c r="N89" s="38"/>
+      <c r="O89" s="38"/>
+      <c r="P89" s="38"/>
+      <c r="Q89" s="38"/>
+      <c r="R89" s="38"/>
+      <c r="S89" s="44"/>
+      <c r="T89" s="38"/>
+      <c r="U89" s="38"/>
+      <c r="V89" s="44"/>
+      <c r="W89" s="38"/>
+    </row>
+    <row r="90" spans="1:23" ht="18" customHeight="1">
+      <c r="A90" s="13"/>
+      <c r="B90" s="38"/>
+      <c r="C90" s="38"/>
+      <c r="D90" s="38"/>
+      <c r="E90" s="73"/>
+      <c r="F90" s="73"/>
+      <c r="G90" s="73"/>
+      <c r="H90" s="44"/>
+      <c r="I90" s="38"/>
+      <c r="J90" s="38"/>
+      <c r="K90" s="73"/>
+      <c r="L90" s="73"/>
+      <c r="M90" s="73"/>
+      <c r="N90" s="38"/>
+      <c r="O90" s="38"/>
+      <c r="P90" s="38"/>
+      <c r="Q90" s="38"/>
+      <c r="R90" s="38"/>
+      <c r="S90" s="44"/>
+      <c r="T90" s="38"/>
+      <c r="U90" s="38"/>
+      <c r="V90" s="44"/>
+      <c r="W90" s="38"/>
+    </row>
+    <row r="91" spans="1:23" ht="18" customHeight="1">
+      <c r="A91" s="13"/>
+      <c r="B91" s="38"/>
+      <c r="C91" s="38"/>
+      <c r="D91" s="38"/>
+      <c r="E91" s="73"/>
+      <c r="F91" s="73"/>
+      <c r="G91" s="73"/>
+      <c r="H91" s="44"/>
+      <c r="I91" s="38"/>
+      <c r="J91" s="38"/>
+      <c r="K91" s="73"/>
+      <c r="L91" s="73"/>
+      <c r="M91" s="73"/>
+      <c r="N91" s="38"/>
+      <c r="O91" s="38"/>
+      <c r="P91" s="38"/>
+      <c r="Q91" s="38"/>
+      <c r="R91" s="38"/>
+      <c r="S91" s="44"/>
+      <c r="T91" s="38"/>
+      <c r="U91" s="38"/>
+      <c r="V91" s="44"/>
+      <c r="W91" s="38"/>
+    </row>
+    <row r="92" spans="1:23" ht="18" customHeight="1">
+      <c r="A92" s="13"/>
+      <c r="B92" s="38"/>
+      <c r="C92" s="38"/>
+      <c r="D92" s="38"/>
+      <c r="E92" s="73"/>
+      <c r="F92" s="73"/>
+      <c r="G92" s="73"/>
+      <c r="H92" s="205" t="s">
+        <v>149</v>
+      </c>
+      <c r="I92" s="205"/>
+      <c r="J92" s="205"/>
+      <c r="K92" s="205"/>
+      <c r="L92" s="205"/>
+      <c r="M92" s="205"/>
+      <c r="N92" s="205"/>
+      <c r="O92" s="205"/>
+      <c r="P92" s="205"/>
+      <c r="Q92" s="38"/>
+      <c r="R92" s="38"/>
+      <c r="S92" s="44"/>
+      <c r="T92" s="38"/>
+      <c r="U92" s="38"/>
+      <c r="V92" s="44"/>
+      <c r="W92" s="38"/>
+    </row>
+    <row r="93" spans="1:23" ht="18" customHeight="1">
+      <c r="A93" s="13"/>
+      <c r="B93" s="38"/>
+      <c r="C93" s="38"/>
+      <c r="D93" s="38"/>
+      <c r="E93" s="73"/>
+      <c r="F93" s="73"/>
+      <c r="G93" s="73"/>
+      <c r="H93" s="205"/>
+      <c r="I93" s="205"/>
+      <c r="J93" s="205"/>
+      <c r="K93" s="205"/>
+      <c r="L93" s="205"/>
+      <c r="M93" s="205"/>
+      <c r="N93" s="205"/>
+      <c r="O93" s="205"/>
+      <c r="P93" s="205"/>
+      <c r="Q93" s="38"/>
+      <c r="R93" s="38"/>
+      <c r="S93" s="44"/>
+      <c r="T93" s="38"/>
+      <c r="U93" s="38"/>
+      <c r="V93" s="44"/>
+      <c r="W93" s="38"/>
+    </row>
+    <row r="94" spans="1:23" ht="18" customHeight="1">
+      <c r="A94" s="13"/>
+      <c r="B94" s="38"/>
+      <c r="C94" s="38"/>
+      <c r="D94" s="38"/>
+      <c r="E94" s="73"/>
+      <c r="F94" s="73"/>
+      <c r="G94" s="73"/>
+      <c r="H94" s="205"/>
+      <c r="I94" s="205"/>
+      <c r="J94" s="205"/>
+      <c r="K94" s="205"/>
+      <c r="L94" s="205"/>
+      <c r="M94" s="205"/>
+      <c r="N94" s="205"/>
+      <c r="O94" s="205"/>
+      <c r="P94" s="205"/>
+      <c r="Q94" s="38"/>
+      <c r="R94" s="38"/>
+      <c r="S94" s="44"/>
+      <c r="T94" s="38"/>
+      <c r="U94" s="38"/>
+      <c r="V94" s="44"/>
+      <c r="W94" s="38"/>
+    </row>
+    <row r="95" spans="1:23" ht="18" customHeight="1">
+      <c r="A95" s="13"/>
+      <c r="B95" s="38"/>
+      <c r="C95" s="38"/>
+      <c r="D95" s="38"/>
+      <c r="E95" s="73"/>
+      <c r="F95" s="73"/>
+      <c r="G95" s="73"/>
+      <c r="H95" s="44"/>
+      <c r="I95" s="38"/>
+      <c r="J95" s="38"/>
+      <c r="K95" s="73"/>
+      <c r="L95" s="73"/>
+      <c r="M95" s="73"/>
+      <c r="N95" s="38"/>
+      <c r="O95" s="38"/>
+      <c r="P95" s="38"/>
+      <c r="Q95" s="38"/>
+      <c r="R95" s="38"/>
+      <c r="S95" s="44"/>
+      <c r="T95" s="38"/>
+      <c r="U95" s="38"/>
+      <c r="V95" s="44"/>
+      <c r="W95" s="38"/>
+    </row>
+    <row r="96" spans="1:23" ht="18" customHeight="1">
+      <c r="A96" s="13"/>
+      <c r="B96" s="38"/>
+      <c r="C96" s="38"/>
+      <c r="D96" s="38"/>
+      <c r="E96" s="73"/>
+      <c r="F96" s="73"/>
+      <c r="G96" s="73"/>
+      <c r="H96" s="44"/>
+      <c r="I96" s="38"/>
+      <c r="J96" s="38"/>
+      <c r="K96" s="76"/>
+      <c r="L96" s="76"/>
+      <c r="M96" s="73"/>
+      <c r="N96" s="38"/>
+      <c r="O96" s="76"/>
+      <c r="P96" s="76"/>
+      <c r="Q96" s="38"/>
+      <c r="R96" s="38"/>
+      <c r="S96" s="44"/>
+      <c r="T96" s="38"/>
+      <c r="U96" s="38"/>
+      <c r="V96" s="44"/>
+      <c r="W96" s="38"/>
+    </row>
+    <row r="97" spans="1:23" ht="18" customHeight="1">
+      <c r="A97" s="13"/>
+      <c r="B97" s="38"/>
+      <c r="C97" s="38"/>
+      <c r="D97" s="38"/>
+      <c r="E97" s="73"/>
+      <c r="F97" s="73"/>
+      <c r="G97" s="74"/>
+      <c r="H97" s="44"/>
+      <c r="I97" s="38"/>
+      <c r="J97" s="38"/>
+      <c r="K97" s="73"/>
+      <c r="L97" s="73"/>
+      <c r="M97" s="73"/>
+      <c r="N97" s="38"/>
+      <c r="O97" s="38"/>
+      <c r="P97" s="38"/>
+      <c r="Q97" s="38"/>
+      <c r="R97" s="38"/>
+      <c r="S97" s="44"/>
+      <c r="T97" s="38"/>
+      <c r="U97" s="38"/>
+      <c r="V97" s="44"/>
+      <c r="W97" s="38"/>
+    </row>
+    <row r="98" spans="1:23" ht="18" customHeight="1">
+      <c r="A98" s="13"/>
+      <c r="B98" s="38"/>
+      <c r="C98" s="38"/>
+      <c r="D98" s="38"/>
+      <c r="E98" s="73"/>
+      <c r="F98" s="73"/>
+      <c r="G98" s="74"/>
+      <c r="H98" s="44"/>
+      <c r="I98" s="38"/>
+      <c r="J98" s="38"/>
+      <c r="K98" s="203"/>
+      <c r="L98" s="203"/>
+      <c r="M98" s="203"/>
+      <c r="N98" s="203"/>
+      <c r="O98" s="38"/>
+      <c r="P98" s="38"/>
+      <c r="Q98" s="38"/>
+      <c r="R98" s="38"/>
+      <c r="S98" s="44"/>
+      <c r="T98" s="38"/>
+      <c r="U98" s="38"/>
+      <c r="V98" s="44"/>
+      <c r="W98" s="38"/>
+    </row>
+    <row r="99" spans="1:23" ht="18" customHeight="1">
+      <c r="A99" s="13"/>
+      <c r="B99" s="38"/>
+      <c r="C99" s="38"/>
+      <c r="D99" s="38"/>
+      <c r="E99" s="75"/>
+      <c r="F99" s="73"/>
+      <c r="G99" s="74"/>
+      <c r="H99" s="44"/>
+      <c r="I99" s="38"/>
+      <c r="J99" s="38"/>
+      <c r="K99" s="73"/>
+      <c r="L99" s="73"/>
+      <c r="M99" s="73"/>
+      <c r="N99" s="38"/>
+      <c r="O99" s="38"/>
+      <c r="P99" s="38"/>
+      <c r="Q99" s="38"/>
+      <c r="R99" s="38"/>
+      <c r="S99" s="44"/>
+      <c r="T99" s="38"/>
+      <c r="U99" s="38"/>
+      <c r="V99" s="44"/>
+      <c r="W99" s="38"/>
+    </row>
+    <row r="100" spans="1:23" ht="18" customHeight="1">
+      <c r="A100" s="13"/>
+      <c r="B100" s="38"/>
+      <c r="C100" s="38"/>
+      <c r="D100" s="38"/>
+      <c r="E100" s="73"/>
+      <c r="F100" s="73"/>
+      <c r="G100" s="74"/>
+      <c r="H100" s="44"/>
+      <c r="I100" s="38"/>
+      <c r="J100" s="38"/>
+      <c r="K100" s="73"/>
+      <c r="L100" s="73"/>
+      <c r="M100" s="73"/>
+      <c r="N100" s="38"/>
+      <c r="O100" s="38"/>
+      <c r="P100" s="38"/>
+      <c r="Q100" s="38"/>
+      <c r="R100" s="38"/>
+      <c r="S100" s="44"/>
+      <c r="T100" s="38"/>
+      <c r="U100" s="38"/>
+      <c r="V100" s="44"/>
+      <c r="W100" s="38"/>
+    </row>
+    <row r="101" spans="1:23" ht="18" customHeight="1">
+      <c r="A101" s="13"/>
+      <c r="B101" s="38"/>
+      <c r="C101" s="38"/>
+      <c r="D101" s="38"/>
+      <c r="E101" s="73"/>
+      <c r="F101" s="73"/>
+      <c r="G101" s="74"/>
+      <c r="H101" s="44"/>
+      <c r="I101" s="38"/>
+      <c r="J101" s="38"/>
+      <c r="K101" s="73"/>
+      <c r="L101" s="73"/>
+      <c r="M101" s="73"/>
+      <c r="N101" s="38"/>
+      <c r="O101" s="38"/>
+      <c r="P101" s="38"/>
+      <c r="Q101" s="38"/>
+      <c r="R101" s="38"/>
+      <c r="S101" s="44"/>
+      <c r="T101" s="38"/>
+      <c r="U101" s="38"/>
+      <c r="V101" s="44"/>
+      <c r="W101" s="38"/>
+    </row>
+    <row r="102" spans="1:23" ht="18" customHeight="1">
+      <c r="A102" s="13"/>
+      <c r="B102" s="38"/>
+      <c r="C102" s="38"/>
+      <c r="D102" s="38"/>
+      <c r="E102" s="75"/>
+      <c r="F102" s="73"/>
+      <c r="G102" s="74"/>
+      <c r="H102" s="44"/>
+      <c r="I102" s="38"/>
+      <c r="J102" s="38"/>
+      <c r="K102" s="73"/>
+      <c r="L102" s="73"/>
+      <c r="M102" s="73"/>
+      <c r="N102" s="38"/>
+      <c r="O102" s="38"/>
+      <c r="P102" s="38"/>
+      <c r="Q102" s="38"/>
+      <c r="R102" s="38"/>
+      <c r="S102" s="44"/>
+      <c r="T102" s="38"/>
+      <c r="U102" s="38"/>
+      <c r="V102" s="44"/>
+      <c r="W102" s="38"/>
+    </row>
+    <row r="103" spans="1:23" ht="18" customHeight="1">
+      <c r="A103" s="13"/>
+      <c r="B103" s="38"/>
+      <c r="C103" s="38"/>
+      <c r="D103" s="38"/>
+      <c r="E103" s="75"/>
+      <c r="F103" s="73"/>
+      <c r="G103" s="74"/>
+      <c r="H103" s="44"/>
+      <c r="I103" s="38"/>
+      <c r="J103" s="38"/>
+      <c r="K103" s="73"/>
+      <c r="L103" s="73"/>
+      <c r="M103" s="73"/>
+      <c r="N103" s="38"/>
+      <c r="O103" s="38"/>
+      <c r="P103" s="38"/>
+      <c r="Q103" s="38"/>
+      <c r="R103" s="38"/>
+      <c r="S103" s="44"/>
+      <c r="T103" s="38"/>
+      <c r="U103" s="38"/>
+      <c r="V103" s="44"/>
+      <c r="W103" s="38"/>
+    </row>
+    <row r="104" spans="1:23" ht="18" customHeight="1">
+      <c r="A104" s="13"/>
+      <c r="B104" s="38"/>
+      <c r="C104" s="38"/>
+      <c r="D104" s="38"/>
+      <c r="E104" s="75"/>
+      <c r="F104" s="73"/>
+      <c r="G104" s="74"/>
+      <c r="H104" s="44"/>
+      <c r="I104" s="38"/>
+      <c r="J104" s="38"/>
+      <c r="K104" s="204"/>
+      <c r="L104" s="204"/>
+      <c r="M104" s="204"/>
+      <c r="N104" s="38"/>
+      <c r="O104" s="38"/>
+      <c r="P104" s="38"/>
+      <c r="Q104" s="38"/>
+      <c r="R104" s="38"/>
+      <c r="S104" s="44"/>
+      <c r="T104" s="38"/>
+      <c r="U104" s="38"/>
+      <c r="V104" s="44"/>
+      <c r="W104" s="38"/>
+    </row>
+    <row r="105" spans="1:23" ht="18" customHeight="1">
+      <c r="A105" s="13"/>
+      <c r="B105" s="38"/>
+      <c r="C105" s="38"/>
+      <c r="D105" s="38"/>
+      <c r="E105" s="75"/>
+      <c r="F105" s="73"/>
+      <c r="G105" s="74"/>
+      <c r="H105" s="44"/>
+      <c r="I105" s="38"/>
+      <c r="J105" s="38"/>
+      <c r="K105" s="73"/>
+      <c r="L105" s="73"/>
+      <c r="M105" s="73"/>
+      <c r="N105" s="38"/>
+      <c r="O105" s="38"/>
+      <c r="P105" s="38"/>
+      <c r="Q105" s="38"/>
+      <c r="R105" s="38"/>
+      <c r="S105" s="44"/>
+      <c r="T105" s="38"/>
+      <c r="U105" s="38"/>
+      <c r="V105" s="44"/>
+      <c r="W105" s="38"/>
+    </row>
+    <row r="106" spans="1:23" ht="18" customHeight="1">
+      <c r="A106" s="13"/>
+      <c r="B106" s="38"/>
+      <c r="C106" s="38"/>
+      <c r="D106" s="38"/>
+      <c r="E106" s="73"/>
+      <c r="F106" s="73"/>
+      <c r="G106" s="74"/>
+      <c r="H106" s="44"/>
+      <c r="I106" s="38"/>
+      <c r="J106" s="38"/>
+      <c r="K106" s="73"/>
+      <c r="L106" s="73"/>
+      <c r="M106" s="73"/>
+      <c r="N106" s="38"/>
+      <c r="O106" s="38"/>
+      <c r="P106" s="38"/>
+      <c r="Q106" s="38"/>
+      <c r="R106" s="38"/>
+      <c r="S106" s="44"/>
+      <c r="T106" s="38"/>
+      <c r="U106" s="38"/>
+      <c r="V106" s="44"/>
+      <c r="W106" s="38"/>
+    </row>
+    <row r="107" spans="1:23" ht="18" customHeight="1">
+      <c r="A107" s="13"/>
+      <c r="B107" s="38"/>
+      <c r="C107" s="38"/>
+      <c r="D107" s="38"/>
+      <c r="E107" s="38"/>
+      <c r="F107" s="38"/>
+      <c r="G107" s="44"/>
+      <c r="H107" s="44"/>
+      <c r="I107" s="38"/>
+      <c r="J107" s="38"/>
+      <c r="K107" s="73"/>
+      <c r="L107" s="73"/>
+      <c r="M107" s="73"/>
+      <c r="N107" s="38"/>
+      <c r="O107" s="38"/>
+      <c r="P107" s="38"/>
+      <c r="Q107" s="38"/>
+      <c r="R107" s="38"/>
+      <c r="S107" s="44"/>
+      <c r="T107" s="38"/>
+      <c r="U107" s="38"/>
+      <c r="V107" s="44"/>
+      <c r="W107" s="38"/>
+    </row>
+    <row r="108" spans="1:23" ht="18" customHeight="1">
+      <c r="A108" s="13"/>
+      <c r="B108" s="38"/>
+      <c r="C108" s="38"/>
+      <c r="D108" s="38"/>
+      <c r="F108" s="38"/>
+      <c r="G108" s="44"/>
+      <c r="H108" s="44"/>
+      <c r="I108" s="38"/>
+      <c r="J108" s="38"/>
+      <c r="K108" s="73"/>
+      <c r="L108" s="73"/>
+      <c r="M108" s="73"/>
+      <c r="N108" s="38"/>
+      <c r="O108" s="38"/>
+      <c r="P108" s="38"/>
+      <c r="Q108" s="38"/>
+      <c r="R108" s="38"/>
+      <c r="S108" s="44"/>
+      <c r="T108" s="38"/>
+      <c r="U108" s="38"/>
+      <c r="V108" s="44"/>
+      <c r="W108" s="38"/>
+    </row>
+    <row r="109" spans="1:23" ht="18" customHeight="1">
+      <c r="A109" s="13"/>
+      <c r="B109" s="38"/>
+      <c r="C109" s="38"/>
+      <c r="D109" s="38"/>
+      <c r="E109" s="38"/>
+      <c r="F109" s="38"/>
+      <c r="G109" s="44"/>
+      <c r="H109" s="44"/>
+      <c r="I109" s="38"/>
+      <c r="J109" s="38"/>
+      <c r="K109" s="73"/>
+      <c r="L109" s="73"/>
+      <c r="M109" s="73"/>
+      <c r="N109" s="38"/>
+      <c r="O109" s="38"/>
+      <c r="P109" s="38"/>
+      <c r="Q109" s="38"/>
+      <c r="R109" s="38"/>
+      <c r="S109" s="44"/>
+      <c r="T109" s="38"/>
+      <c r="U109" s="38"/>
+      <c r="V109" s="44"/>
+      <c r="W109" s="38"/>
+    </row>
+    <row r="110" spans="1:23" ht="18" customHeight="1">
+      <c r="A110" s="13"/>
+      <c r="B110" s="13"/>
+      <c r="C110" s="13"/>
+      <c r="D110" s="13"/>
+      <c r="E110" s="13"/>
+      <c r="F110" s="13"/>
+      <c r="G110" s="13"/>
+      <c r="H110" s="13"/>
+      <c r="I110" s="13"/>
+      <c r="J110" s="13"/>
+      <c r="K110" s="13"/>
+      <c r="L110" s="13"/>
+      <c r="M110" s="13"/>
+      <c r="N110" s="13"/>
+      <c r="O110" s="13"/>
+      <c r="P110" s="13"/>
+      <c r="Q110" s="13"/>
+      <c r="R110" s="13"/>
+      <c r="S110" s="13"/>
+      <c r="T110" s="13"/>
+      <c r="U110" s="13"/>
+      <c r="V110" s="13"/>
+      <c r="W110" s="13"/>
+    </row>
+    <row r="111" spans="1:23" ht="18" customHeight="1">
+      <c r="A111" s="13"/>
+      <c r="B111" s="13"/>
+      <c r="C111" s="13"/>
+      <c r="D111" s="13"/>
+      <c r="E111" s="13"/>
+      <c r="F111" s="13"/>
+      <c r="G111" s="13"/>
+      <c r="H111" s="13"/>
+      <c r="I111" s="13"/>
+      <c r="J111" s="13"/>
+      <c r="K111" s="13"/>
+      <c r="L111" s="13"/>
+      <c r="M111" s="13"/>
+      <c r="N111" s="13"/>
+      <c r="O111" s="13"/>
+      <c r="P111" s="13"/>
+      <c r="Q111" s="13"/>
+      <c r="R111" s="13"/>
+      <c r="S111" s="13"/>
+      <c r="T111" s="13"/>
+      <c r="U111" s="13"/>
+      <c r="V111" s="13"/>
+      <c r="W111" s="13"/>
+    </row>
+    <row r="112" spans="1:23" ht="18" customHeight="1">
+      <c r="A112" s="13"/>
+      <c r="B112" s="13"/>
+      <c r="C112" s="13"/>
+      <c r="D112" s="13"/>
+      <c r="E112" s="13"/>
+      <c r="F112" s="13"/>
+      <c r="G112" s="13"/>
+      <c r="H112" s="13"/>
+      <c r="I112" s="13"/>
+      <c r="J112" s="13"/>
+      <c r="K112" s="13"/>
+      <c r="L112" s="13"/>
+      <c r="M112" s="13"/>
+      <c r="N112" s="13"/>
+      <c r="O112" s="13"/>
+      <c r="P112" s="13"/>
+      <c r="Q112" s="13"/>
+      <c r="R112" s="13"/>
+      <c r="S112" s="13"/>
+      <c r="T112" s="13"/>
+      <c r="U112" s="13"/>
+      <c r="V112" s="13"/>
+      <c r="W112" s="13"/>
+    </row>
+    <row r="113" spans="1:23" ht="18" customHeight="1">
+      <c r="A113" s="66"/>
+      <c r="B113" s="68"/>
+      <c r="C113" s="68"/>
+      <c r="D113" s="68"/>
+      <c r="E113" s="69"/>
+      <c r="F113" s="69"/>
+      <c r="G113" s="68"/>
+      <c r="H113" s="68"/>
+      <c r="I113" s="68"/>
+      <c r="J113" s="68"/>
+      <c r="K113" s="79"/>
+      <c r="L113" s="79"/>
+      <c r="M113" s="79"/>
+      <c r="N113" s="68"/>
+      <c r="O113" s="68"/>
+      <c r="P113" s="68"/>
+      <c r="Q113" s="68"/>
+      <c r="R113" s="68"/>
+      <c r="S113" s="70"/>
+      <c r="T113" s="70"/>
+      <c r="U113" s="70"/>
+      <c r="V113" s="70"/>
+      <c r="W113" s="70"/>
+    </row>
+    <row r="114" spans="1:23" ht="18" customHeight="1">
+      <c r="A114" s="71"/>
+      <c r="B114" s="72"/>
+      <c r="C114" s="72"/>
+      <c r="D114" s="72"/>
+      <c r="E114" s="72"/>
+      <c r="F114" s="72"/>
+      <c r="G114" s="72"/>
+      <c r="H114" s="72"/>
+      <c r="I114" s="72"/>
+      <c r="J114" s="72"/>
+      <c r="K114" s="80"/>
+      <c r="L114" s="80"/>
+      <c r="M114" s="80"/>
+      <c r="N114" s="72"/>
+      <c r="O114" s="72"/>
+      <c r="P114" s="72"/>
+      <c r="Q114" s="72"/>
+      <c r="R114" s="72"/>
+      <c r="S114" s="72"/>
+      <c r="T114" s="72"/>
+      <c r="U114" s="72"/>
+      <c r="V114" s="72"/>
+      <c r="W114" s="72"/>
+    </row>
+  </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="K61:N61"/>
+    <mergeCell ref="K67:M67"/>
+    <mergeCell ref="H92:P94"/>
+    <mergeCell ref="K98:N98"/>
+    <mergeCell ref="K104:M104"/>
+    <mergeCell ref="K24:N24"/>
+    <mergeCell ref="K30:M30"/>
+    <mergeCell ref="F55:R57"/>
+    <mergeCell ref="A1:W1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="G2:S2"/>
+    <mergeCell ref="T2:U2"/>
+    <mergeCell ref="V2:W2"/>
+    <mergeCell ref="G3:S3"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="V3:W3"/>
+  </mergeCells>
+  <phoneticPr fontId="4"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.59055118110236227" bottom="0.39370078740157483" header="0.51181102362204722" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <headerFooter alignWithMargins="0">
+    <oddFooter>&amp;LCopyright© 2005 System Integrator Corp.&amp;C&amp;P</oddFooter>
+  </headerFooter>
+  <rowBreaks count="2" manualBreakCount="2">
+    <brk id="40" max="22" man="1"/>
+    <brk id="77" max="22" man="1"/>
+  </rowBreaks>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C1E6855-304D-4E72-A746-EC9944D8D8EE}">
   <sheetPr>
@@ -28213,4 +33248,3149 @@
   </rowBreaks>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAB4FED4-0FD5-4957-BA75-6AEFCE0B8106}">
+  <sheetPr>
+    <tabColor theme="8" tint="0.39997558519241921"/>
+  </sheetPr>
+  <dimension ref="A1:FK114"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" customHeight="1"/>
+  <cols>
+    <col min="1" max="4" width="4.08984375" style="36" customWidth="1"/>
+    <col min="5" max="6" width="4.08984375" style="35" customWidth="1"/>
+    <col min="7" max="10" width="4.08984375" style="36" customWidth="1"/>
+    <col min="11" max="13" width="4.08984375" style="81" customWidth="1"/>
+    <col min="14" max="23" width="4.08984375" style="36" customWidth="1"/>
+    <col min="24" max="27" width="4" style="36" customWidth="1"/>
+    <col min="28" max="16384" width="9" style="36"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:167" ht="12.75" customHeight="1">
+      <c r="A1" s="166" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="166"/>
+      <c r="C1" s="166"/>
+      <c r="D1" s="166"/>
+      <c r="E1" s="166"/>
+      <c r="F1" s="166"/>
+      <c r="G1" s="166"/>
+      <c r="H1" s="166"/>
+      <c r="I1" s="166"/>
+      <c r="J1" s="166"/>
+      <c r="K1" s="166"/>
+      <c r="L1" s="166"/>
+      <c r="M1" s="166"/>
+      <c r="N1" s="166"/>
+      <c r="O1" s="166"/>
+      <c r="P1" s="166"/>
+      <c r="Q1" s="166"/>
+      <c r="R1" s="166"/>
+      <c r="S1" s="166"/>
+      <c r="T1" s="166"/>
+      <c r="U1" s="166"/>
+      <c r="V1" s="166"/>
+      <c r="W1" s="166"/>
+    </row>
+    <row r="2" spans="1:167" ht="13" customHeight="1">
+      <c r="A2" s="157" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="155"/>
+      <c r="C2" s="155"/>
+      <c r="D2" s="155"/>
+      <c r="E2" s="155"/>
+      <c r="F2" s="156"/>
+      <c r="G2" s="155" t="s">
+        <v>53</v>
+      </c>
+      <c r="H2" s="155"/>
+      <c r="I2" s="155"/>
+      <c r="J2" s="155"/>
+      <c r="K2" s="155"/>
+      <c r="L2" s="155"/>
+      <c r="M2" s="155"/>
+      <c r="N2" s="155"/>
+      <c r="O2" s="155"/>
+      <c r="P2" s="155"/>
+      <c r="Q2" s="155"/>
+      <c r="R2" s="155"/>
+      <c r="S2" s="156"/>
+      <c r="T2" s="157" t="s">
+        <v>1</v>
+      </c>
+      <c r="U2" s="156"/>
+      <c r="V2" s="157" t="s">
+        <v>2</v>
+      </c>
+      <c r="W2" s="156"/>
+    </row>
+    <row r="3" spans="1:167" s="15" customFormat="1" ht="12.75" customHeight="1">
+      <c r="A3" s="59" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" s="60"/>
+      <c r="C3" s="60"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="157" t="s">
+        <v>140</v>
+      </c>
+      <c r="H3" s="155"/>
+      <c r="I3" s="155"/>
+      <c r="J3" s="155"/>
+      <c r="K3" s="155"/>
+      <c r="L3" s="155"/>
+      <c r="M3" s="155"/>
+      <c r="N3" s="155"/>
+      <c r="O3" s="155"/>
+      <c r="P3" s="155"/>
+      <c r="Q3" s="155"/>
+      <c r="R3" s="155"/>
+      <c r="S3" s="155"/>
+      <c r="T3" s="202"/>
+      <c r="U3" s="202"/>
+      <c r="V3" s="202"/>
+      <c r="W3" s="202"/>
+      <c r="X3" s="13"/>
+      <c r="Y3" s="14"/>
+      <c r="Z3" s="14"/>
+      <c r="AA3" s="14"/>
+      <c r="AB3" s="14"/>
+      <c r="AC3" s="14"/>
+      <c r="AD3" s="14"/>
+      <c r="AE3" s="14"/>
+      <c r="AF3" s="14"/>
+      <c r="AG3" s="14"/>
+      <c r="AH3" s="14"/>
+      <c r="AI3" s="14"/>
+      <c r="AJ3" s="14"/>
+      <c r="AK3" s="14"/>
+      <c r="AL3" s="14"/>
+      <c r="AM3" s="14"/>
+      <c r="AN3" s="14"/>
+      <c r="AO3" s="14"/>
+      <c r="AP3" s="14"/>
+      <c r="AQ3" s="14"/>
+      <c r="AR3" s="14"/>
+      <c r="AS3" s="14"/>
+      <c r="AT3" s="14"/>
+      <c r="AU3" s="14"/>
+      <c r="AV3" s="14"/>
+      <c r="AW3" s="14"/>
+      <c r="AX3" s="14"/>
+      <c r="AY3" s="14"/>
+      <c r="AZ3" s="14"/>
+      <c r="BA3" s="14"/>
+      <c r="BB3" s="14"/>
+      <c r="BC3" s="14"/>
+      <c r="BD3" s="14"/>
+      <c r="BE3" s="14"/>
+      <c r="BF3" s="14"/>
+      <c r="BG3" s="14"/>
+      <c r="BH3" s="14"/>
+      <c r="BI3" s="14"/>
+      <c r="BJ3" s="14"/>
+      <c r="BK3" s="14"/>
+      <c r="BL3" s="14"/>
+      <c r="BM3" s="14"/>
+      <c r="BN3" s="14"/>
+      <c r="BO3" s="14"/>
+      <c r="BP3" s="14"/>
+      <c r="BQ3" s="14"/>
+      <c r="BR3" s="14"/>
+      <c r="BS3" s="14"/>
+      <c r="BT3" s="14"/>
+      <c r="BU3" s="14"/>
+      <c r="BV3" s="14"/>
+      <c r="BW3" s="14"/>
+      <c r="BX3" s="14"/>
+      <c r="BY3" s="14"/>
+      <c r="BZ3" s="14"/>
+      <c r="CA3" s="14"/>
+      <c r="CB3" s="14"/>
+      <c r="CC3" s="14"/>
+      <c r="CD3" s="14"/>
+      <c r="CE3" s="14"/>
+      <c r="CF3" s="14"/>
+      <c r="CG3" s="14"/>
+      <c r="CH3" s="14"/>
+      <c r="CI3" s="14"/>
+      <c r="CJ3" s="14"/>
+      <c r="CK3" s="14"/>
+      <c r="CL3" s="14"/>
+      <c r="CM3" s="14"/>
+      <c r="CN3" s="14"/>
+      <c r="CO3" s="14"/>
+      <c r="CP3" s="14"/>
+      <c r="CQ3" s="14"/>
+      <c r="CR3" s="14"/>
+      <c r="CS3" s="14"/>
+      <c r="CT3" s="14"/>
+      <c r="CU3" s="14"/>
+      <c r="CV3" s="14"/>
+      <c r="CW3" s="14"/>
+      <c r="CX3" s="14"/>
+      <c r="CY3" s="14"/>
+      <c r="CZ3" s="14"/>
+      <c r="DA3" s="14"/>
+      <c r="DB3" s="14"/>
+      <c r="DC3" s="14"/>
+      <c r="DD3" s="14"/>
+      <c r="DE3" s="14"/>
+      <c r="DF3" s="14"/>
+      <c r="DG3" s="14"/>
+      <c r="DH3" s="14"/>
+      <c r="DI3" s="14"/>
+      <c r="DJ3" s="14"/>
+      <c r="DK3" s="14"/>
+      <c r="DL3" s="14"/>
+      <c r="DM3" s="14"/>
+      <c r="DN3" s="14"/>
+      <c r="DO3" s="14"/>
+      <c r="DP3" s="14"/>
+      <c r="DQ3" s="14"/>
+      <c r="DR3" s="14"/>
+      <c r="DS3" s="14"/>
+      <c r="DT3" s="14"/>
+      <c r="DU3" s="14"/>
+      <c r="DV3" s="14"/>
+      <c r="DW3" s="14"/>
+      <c r="DX3" s="14"/>
+      <c r="DY3" s="14"/>
+      <c r="DZ3" s="14"/>
+      <c r="EA3" s="14"/>
+      <c r="EB3" s="14"/>
+      <c r="EC3" s="14"/>
+      <c r="ED3" s="14"/>
+      <c r="EE3" s="14"/>
+      <c r="EF3" s="14"/>
+      <c r="EG3" s="14"/>
+      <c r="EH3" s="14"/>
+      <c r="EI3" s="14"/>
+      <c r="EJ3" s="14"/>
+      <c r="EK3" s="14"/>
+      <c r="EL3" s="14"/>
+      <c r="EM3" s="14"/>
+      <c r="EN3" s="14"/>
+      <c r="EO3" s="14"/>
+      <c r="EP3" s="14"/>
+      <c r="EQ3" s="14"/>
+      <c r="ER3" s="14"/>
+      <c r="ES3" s="14"/>
+      <c r="ET3" s="14"/>
+      <c r="EU3" s="14"/>
+      <c r="EV3" s="14"/>
+      <c r="EW3" s="14"/>
+      <c r="EX3" s="14"/>
+      <c r="EY3" s="14"/>
+      <c r="EZ3" s="14"/>
+      <c r="FA3" s="14"/>
+      <c r="FB3" s="14"/>
+      <c r="FC3" s="14"/>
+      <c r="FD3" s="14"/>
+      <c r="FE3" s="14"/>
+      <c r="FF3" s="14"/>
+      <c r="FG3" s="14"/>
+      <c r="FH3" s="14"/>
+      <c r="FI3" s="14"/>
+      <c r="FJ3" s="14"/>
+      <c r="FK3" s="14"/>
+    </row>
+    <row r="4" spans="1:167" ht="12.75" customHeight="1">
+      <c r="A4" s="64"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="65"/>
+      <c r="K4" s="77"/>
+      <c r="L4" s="77"/>
+      <c r="M4" s="77"/>
+      <c r="N4" s="65"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
+      <c r="U4" s="65"/>
+      <c r="V4" s="65"/>
+      <c r="W4" s="65"/>
+    </row>
+    <row r="5" spans="1:167" ht="12.75" customHeight="1">
+      <c r="A5" s="66"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="67"/>
+      <c r="K5" s="78"/>
+      <c r="L5" s="78"/>
+      <c r="M5" s="78"/>
+      <c r="N5" s="67"/>
+      <c r="O5" s="67"/>
+      <c r="P5" s="67"/>
+      <c r="Q5" s="67"/>
+      <c r="R5" s="67"/>
+      <c r="S5" s="67"/>
+      <c r="T5" s="67"/>
+      <c r="U5" s="67"/>
+      <c r="V5" s="67"/>
+      <c r="W5" s="67"/>
+    </row>
+    <row r="6" spans="1:167" ht="12.75" customHeight="1">
+      <c r="A6" s="16"/>
+      <c r="B6" s="73" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="38"/>
+      <c r="D6" s="38"/>
+      <c r="E6" s="38"/>
+      <c r="F6" s="38"/>
+      <c r="G6" s="38"/>
+      <c r="H6" s="38"/>
+      <c r="I6" s="38"/>
+      <c r="J6" s="38"/>
+      <c r="K6" s="73"/>
+      <c r="L6" s="73"/>
+      <c r="M6" s="73"/>
+      <c r="N6" s="38"/>
+      <c r="O6" s="38"/>
+      <c r="P6" s="38"/>
+      <c r="Q6" s="38"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="38"/>
+      <c r="T6" s="38"/>
+      <c r="U6" s="38"/>
+      <c r="V6" s="38"/>
+      <c r="W6" s="38"/>
+    </row>
+    <row r="7" spans="1:167" ht="12.75" customHeight="1">
+      <c r="A7" s="13"/>
+      <c r="B7" s="38"/>
+      <c r="C7" s="38"/>
+      <c r="D7" s="38"/>
+      <c r="E7" s="38"/>
+      <c r="F7" s="38"/>
+      <c r="G7" s="38"/>
+      <c r="H7" s="38"/>
+      <c r="I7" s="38"/>
+      <c r="J7" s="42"/>
+      <c r="K7" s="73"/>
+      <c r="L7" s="73"/>
+      <c r="M7" s="73"/>
+      <c r="N7" s="38"/>
+      <c r="O7" s="38"/>
+      <c r="P7" s="38"/>
+      <c r="Q7" s="38"/>
+      <c r="R7" s="38"/>
+      <c r="S7" s="38"/>
+      <c r="T7" s="38"/>
+      <c r="U7" s="42"/>
+      <c r="V7" s="42"/>
+      <c r="W7" s="38"/>
+    </row>
+    <row r="8" spans="1:167" ht="18" customHeight="1" thickBot="1">
+      <c r="A8" s="13"/>
+      <c r="B8" s="38"/>
+      <c r="C8" s="38"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="38"/>
+      <c r="I8" s="38"/>
+      <c r="J8" s="38"/>
+      <c r="K8" s="73"/>
+      <c r="L8" s="73"/>
+      <c r="M8" s="73"/>
+      <c r="N8" s="38"/>
+      <c r="O8" s="38"/>
+      <c r="P8" s="38"/>
+      <c r="Q8" s="38"/>
+      <c r="R8" s="38"/>
+      <c r="S8" s="38"/>
+      <c r="T8" s="38"/>
+      <c r="U8" s="38"/>
+      <c r="V8" s="38"/>
+      <c r="W8" s="38"/>
+    </row>
+    <row r="9" spans="1:167" ht="18" customHeight="1">
+      <c r="A9" s="13"/>
+      <c r="B9" s="38"/>
+      <c r="C9" s="82"/>
+      <c r="D9" s="83"/>
+      <c r="E9" s="83"/>
+      <c r="F9" s="83"/>
+      <c r="G9" s="83"/>
+      <c r="H9" s="83"/>
+      <c r="I9" s="84"/>
+      <c r="J9" s="84"/>
+      <c r="K9" s="85"/>
+      <c r="L9" s="85"/>
+      <c r="M9" s="86"/>
+      <c r="N9" s="83"/>
+      <c r="O9" s="83"/>
+      <c r="P9" s="83"/>
+      <c r="Q9" s="83"/>
+      <c r="R9" s="83"/>
+      <c r="S9" s="83"/>
+      <c r="T9" s="83"/>
+      <c r="U9" s="87"/>
+      <c r="V9" s="38"/>
+      <c r="W9" s="38"/>
+    </row>
+    <row r="10" spans="1:167" ht="18" customHeight="1">
+      <c r="A10" s="13"/>
+      <c r="B10" s="38"/>
+      <c r="C10" s="88"/>
+      <c r="D10" s="38"/>
+      <c r="E10" s="73" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" s="44"/>
+      <c r="G10" s="38"/>
+      <c r="H10" s="38"/>
+      <c r="I10" s="38"/>
+      <c r="J10" s="38"/>
+      <c r="K10" s="73"/>
+      <c r="L10" s="73"/>
+      <c r="M10" s="73"/>
+      <c r="N10" s="38"/>
+      <c r="O10" s="38"/>
+      <c r="P10" s="38"/>
+      <c r="Q10" s="38"/>
+      <c r="R10" s="38"/>
+      <c r="S10" s="38"/>
+      <c r="T10" s="38"/>
+      <c r="U10" s="89"/>
+      <c r="V10" s="38"/>
+      <c r="W10" s="38"/>
+    </row>
+    <row r="11" spans="1:167" ht="18" customHeight="1">
+      <c r="A11" s="13"/>
+      <c r="B11" s="38"/>
+      <c r="C11" s="88"/>
+      <c r="D11" s="38"/>
+      <c r="E11" s="73"/>
+      <c r="F11" s="74"/>
+      <c r="G11" s="73"/>
+      <c r="H11" s="38"/>
+      <c r="I11" s="38"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="73"/>
+      <c r="L11" s="73"/>
+      <c r="M11" s="73"/>
+      <c r="N11" s="38"/>
+      <c r="O11" s="38"/>
+      <c r="P11" s="38"/>
+      <c r="Q11" s="38"/>
+      <c r="R11" s="38"/>
+      <c r="S11" s="38"/>
+      <c r="T11" s="38"/>
+      <c r="U11" s="89"/>
+      <c r="V11" s="38"/>
+      <c r="W11" s="38"/>
+    </row>
+    <row r="12" spans="1:167" ht="18" customHeight="1">
+      <c r="A12" s="13"/>
+      <c r="B12" s="38"/>
+      <c r="C12" s="88"/>
+      <c r="D12" s="38"/>
+      <c r="E12" s="73" t="s">
+        <v>56</v>
+      </c>
+      <c r="F12" s="73"/>
+      <c r="G12" s="73"/>
+      <c r="H12" s="38"/>
+      <c r="I12" s="38"/>
+      <c r="J12" s="38"/>
+      <c r="K12" s="73"/>
+      <c r="L12" s="73"/>
+      <c r="M12" s="73"/>
+      <c r="N12" s="38"/>
+      <c r="O12" s="63"/>
+      <c r="P12" s="63"/>
+      <c r="Q12" s="38"/>
+      <c r="R12" s="63"/>
+      <c r="S12" s="38"/>
+      <c r="T12" s="63"/>
+      <c r="U12" s="90"/>
+      <c r="V12" s="38"/>
+      <c r="W12" s="63"/>
+    </row>
+    <row r="13" spans="1:167" ht="18" customHeight="1">
+      <c r="A13" s="13"/>
+      <c r="B13" s="62"/>
+      <c r="C13" s="91"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="75"/>
+      <c r="F13" s="73"/>
+      <c r="G13" s="73"/>
+      <c r="H13" s="44"/>
+      <c r="I13" s="44"/>
+      <c r="J13" s="44"/>
+      <c r="K13" s="73"/>
+      <c r="L13" s="73"/>
+      <c r="M13" s="73"/>
+      <c r="N13" s="38"/>
+      <c r="O13" s="38"/>
+      <c r="P13" s="38"/>
+      <c r="Q13" s="38"/>
+      <c r="R13" s="38"/>
+      <c r="S13" s="44"/>
+      <c r="T13" s="44"/>
+      <c r="U13" s="92"/>
+      <c r="V13" s="44"/>
+      <c r="W13" s="44"/>
+    </row>
+    <row r="14" spans="1:167" ht="18" customHeight="1">
+      <c r="A14" s="13"/>
+      <c r="B14" s="38"/>
+      <c r="C14" s="88"/>
+      <c r="D14" s="38"/>
+      <c r="E14" s="73" t="s">
+        <v>57</v>
+      </c>
+      <c r="F14" s="73"/>
+      <c r="G14" s="73"/>
+      <c r="H14" s="44"/>
+      <c r="I14" s="38"/>
+      <c r="J14" s="38"/>
+      <c r="K14" s="73"/>
+      <c r="L14" s="73"/>
+      <c r="M14" s="73"/>
+      <c r="N14" s="38"/>
+      <c r="O14" s="38"/>
+      <c r="P14" s="38"/>
+      <c r="Q14" s="38"/>
+      <c r="R14" s="38"/>
+      <c r="S14" s="44"/>
+      <c r="T14" s="38"/>
+      <c r="U14" s="89"/>
+      <c r="V14" s="44"/>
+      <c r="W14" s="38"/>
+    </row>
+    <row r="15" spans="1:167" ht="18" customHeight="1">
+      <c r="A15" s="13"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="88"/>
+      <c r="D15" s="38"/>
+      <c r="E15" s="73"/>
+      <c r="F15" s="73"/>
+      <c r="G15" s="73"/>
+      <c r="H15" s="44"/>
+      <c r="I15" s="38"/>
+      <c r="J15" s="38"/>
+      <c r="K15" s="73"/>
+      <c r="L15" s="73"/>
+      <c r="M15" s="73"/>
+      <c r="N15" s="38"/>
+      <c r="O15" s="38"/>
+      <c r="P15" s="38"/>
+      <c r="Q15" s="38"/>
+      <c r="R15" s="38"/>
+      <c r="S15" s="44"/>
+      <c r="T15" s="38"/>
+      <c r="U15" s="89"/>
+      <c r="V15" s="44"/>
+      <c r="W15" s="38"/>
+    </row>
+    <row r="16" spans="1:167" ht="18" customHeight="1">
+      <c r="A16" s="13"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="88"/>
+      <c r="D16" s="38"/>
+      <c r="E16" s="73" t="s">
+        <v>58</v>
+      </c>
+      <c r="F16" s="73"/>
+      <c r="G16" s="73"/>
+      <c r="H16" s="44"/>
+      <c r="I16" s="38"/>
+      <c r="J16" s="38"/>
+      <c r="K16" s="73"/>
+      <c r="L16" s="73"/>
+      <c r="M16" s="73"/>
+      <c r="N16" s="38"/>
+      <c r="O16" s="38"/>
+      <c r="P16" s="38"/>
+      <c r="Q16" s="38"/>
+      <c r="R16" s="38"/>
+      <c r="S16" s="44"/>
+      <c r="T16" s="38"/>
+      <c r="U16" s="89"/>
+      <c r="V16" s="44"/>
+      <c r="W16" s="38"/>
+    </row>
+    <row r="17" spans="1:23" ht="18" customHeight="1">
+      <c r="A17" s="13"/>
+      <c r="B17" s="38"/>
+      <c r="C17" s="88"/>
+      <c r="D17" s="38"/>
+      <c r="E17" s="73"/>
+      <c r="F17" s="73"/>
+      <c r="G17" s="73"/>
+      <c r="H17" s="44"/>
+      <c r="I17" s="38"/>
+      <c r="J17" s="38"/>
+      <c r="K17" s="73"/>
+      <c r="L17" s="73"/>
+      <c r="M17" s="73"/>
+      <c r="N17" s="38"/>
+      <c r="O17" s="38"/>
+      <c r="P17" s="38"/>
+      <c r="Q17" s="38"/>
+      <c r="R17" s="38"/>
+      <c r="S17" s="44"/>
+      <c r="T17" s="38"/>
+      <c r="U17" s="89"/>
+      <c r="V17" s="44"/>
+      <c r="W17" s="38"/>
+    </row>
+    <row r="18" spans="1:23" ht="18" customHeight="1">
+      <c r="A18" s="13"/>
+      <c r="B18" s="38"/>
+      <c r="C18" s="88"/>
+      <c r="D18" s="38"/>
+      <c r="E18" s="73" t="s">
+        <v>59</v>
+      </c>
+      <c r="F18" s="73"/>
+      <c r="G18" s="73"/>
+      <c r="H18" s="44"/>
+      <c r="I18" s="38"/>
+      <c r="J18" s="38"/>
+      <c r="K18" s="73"/>
+      <c r="L18" s="73"/>
+      <c r="M18" s="73"/>
+      <c r="N18" s="38"/>
+      <c r="O18" s="38"/>
+      <c r="P18" s="38"/>
+      <c r="Q18" s="38"/>
+      <c r="R18" s="38"/>
+      <c r="S18" s="44"/>
+      <c r="T18" s="38"/>
+      <c r="U18" s="89"/>
+      <c r="V18" s="44"/>
+      <c r="W18" s="38"/>
+    </row>
+    <row r="19" spans="1:23" ht="18" customHeight="1">
+      <c r="A19" s="13"/>
+      <c r="B19" s="38"/>
+      <c r="C19" s="88"/>
+      <c r="D19" s="38"/>
+      <c r="E19" s="73"/>
+      <c r="F19" s="73"/>
+      <c r="G19" s="73"/>
+      <c r="H19" s="44"/>
+      <c r="I19" s="38"/>
+      <c r="J19" s="38"/>
+      <c r="K19" s="73"/>
+      <c r="L19" s="73"/>
+      <c r="M19" s="73"/>
+      <c r="N19" s="38"/>
+      <c r="O19" s="38"/>
+      <c r="P19" s="38"/>
+      <c r="Q19" s="38"/>
+      <c r="R19" s="38"/>
+      <c r="S19" s="44"/>
+      <c r="T19" s="38"/>
+      <c r="U19" s="89"/>
+      <c r="V19" s="44"/>
+      <c r="W19" s="38"/>
+    </row>
+    <row r="20" spans="1:23" ht="18" customHeight="1">
+      <c r="A20" s="13"/>
+      <c r="B20" s="38"/>
+      <c r="C20" s="88"/>
+      <c r="D20" s="38"/>
+      <c r="E20" s="73" t="s">
+        <v>60</v>
+      </c>
+      <c r="F20" s="73"/>
+      <c r="G20" s="73"/>
+      <c r="H20" s="44"/>
+      <c r="I20" s="38"/>
+      <c r="J20" s="38"/>
+      <c r="K20" s="73"/>
+      <c r="L20" s="73"/>
+      <c r="M20" s="73"/>
+      <c r="N20" s="38"/>
+      <c r="O20" s="38"/>
+      <c r="P20" s="38"/>
+      <c r="Q20" s="38"/>
+      <c r="R20" s="38"/>
+      <c r="S20" s="44"/>
+      <c r="T20" s="38"/>
+      <c r="U20" s="89"/>
+      <c r="V20" s="44"/>
+      <c r="W20" s="38"/>
+    </row>
+    <row r="21" spans="1:23" ht="18" customHeight="1">
+      <c r="A21" s="13"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="88"/>
+      <c r="D21" s="38"/>
+      <c r="E21" s="73"/>
+      <c r="F21" s="73"/>
+      <c r="G21" s="73"/>
+      <c r="H21" s="44"/>
+      <c r="I21" s="38"/>
+      <c r="J21" s="38"/>
+      <c r="K21" s="73"/>
+      <c r="L21" s="73"/>
+      <c r="M21" s="73"/>
+      <c r="N21" s="38"/>
+      <c r="O21" s="38"/>
+      <c r="P21" s="38"/>
+      <c r="Q21" s="38"/>
+      <c r="R21" s="38"/>
+      <c r="S21" s="44"/>
+      <c r="T21" s="38"/>
+      <c r="U21" s="89"/>
+      <c r="V21" s="44"/>
+      <c r="W21" s="38"/>
+    </row>
+    <row r="22" spans="1:23" ht="18" customHeight="1">
+      <c r="A22" s="13"/>
+      <c r="B22" s="38"/>
+      <c r="C22" s="88"/>
+      <c r="D22" s="38"/>
+      <c r="E22" s="73" t="s">
+        <v>61</v>
+      </c>
+      <c r="F22" s="73"/>
+      <c r="G22" s="73"/>
+      <c r="H22" s="44"/>
+      <c r="I22" s="38"/>
+      <c r="J22" s="38"/>
+      <c r="K22" s="76" t="s">
+        <v>67</v>
+      </c>
+      <c r="L22" s="76" t="s">
+        <v>68</v>
+      </c>
+      <c r="M22" s="73"/>
+      <c r="N22" s="38"/>
+      <c r="O22" s="76" t="s">
+        <v>67</v>
+      </c>
+      <c r="P22" s="76" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q22" s="38"/>
+      <c r="R22" s="38"/>
+      <c r="S22" s="44"/>
+      <c r="T22" s="38"/>
+      <c r="U22" s="89"/>
+      <c r="V22" s="44"/>
+      <c r="W22" s="38"/>
+    </row>
+    <row r="23" spans="1:23" ht="18" customHeight="1">
+      <c r="A23" s="13"/>
+      <c r="B23" s="38"/>
+      <c r="C23" s="88"/>
+      <c r="D23" s="38"/>
+      <c r="E23" s="73"/>
+      <c r="F23" s="73"/>
+      <c r="G23" s="74"/>
+      <c r="H23" s="44"/>
+      <c r="I23" s="38"/>
+      <c r="J23" s="38"/>
+      <c r="K23" s="73"/>
+      <c r="L23" s="73"/>
+      <c r="M23" s="73"/>
+      <c r="N23" s="38"/>
+      <c r="O23" s="38"/>
+      <c r="P23" s="38"/>
+      <c r="Q23" s="38"/>
+      <c r="R23" s="38"/>
+      <c r="S23" s="44"/>
+      <c r="T23" s="38"/>
+      <c r="U23" s="89"/>
+      <c r="V23" s="44"/>
+      <c r="W23" s="38"/>
+    </row>
+    <row r="24" spans="1:23" ht="18" customHeight="1">
+      <c r="A24" s="13"/>
+      <c r="B24" s="38"/>
+      <c r="C24" s="88"/>
+      <c r="D24" s="38"/>
+      <c r="E24" s="73" t="s">
+        <v>62</v>
+      </c>
+      <c r="F24" s="73"/>
+      <c r="G24" s="74"/>
+      <c r="H24" s="44"/>
+      <c r="I24" s="38"/>
+      <c r="J24" s="38"/>
+      <c r="K24" s="73"/>
+      <c r="L24" s="73"/>
+      <c r="M24" s="73"/>
+      <c r="N24" s="38"/>
+      <c r="O24" s="38"/>
+      <c r="P24" s="38"/>
+      <c r="Q24" s="38"/>
+      <c r="R24" s="38"/>
+      <c r="S24" s="44"/>
+      <c r="T24" s="38"/>
+      <c r="U24" s="89"/>
+      <c r="V24" s="44"/>
+      <c r="W24" s="38"/>
+    </row>
+    <row r="25" spans="1:23" ht="18" customHeight="1">
+      <c r="A25" s="13"/>
+      <c r="B25" s="38"/>
+      <c r="C25" s="88"/>
+      <c r="D25" s="38"/>
+      <c r="E25" s="75"/>
+      <c r="F25" s="73"/>
+      <c r="G25" s="74"/>
+      <c r="H25" s="44"/>
+      <c r="I25" s="38"/>
+      <c r="J25" s="38"/>
+      <c r="K25" s="73"/>
+      <c r="L25" s="73"/>
+      <c r="M25" s="73"/>
+      <c r="N25" s="38"/>
+      <c r="O25" s="38"/>
+      <c r="P25" s="38"/>
+      <c r="Q25" s="38"/>
+      <c r="R25" s="38"/>
+      <c r="S25" s="44"/>
+      <c r="T25" s="38"/>
+      <c r="U25" s="89"/>
+      <c r="V25" s="44"/>
+      <c r="W25" s="38"/>
+    </row>
+    <row r="26" spans="1:23" ht="18" customHeight="1">
+      <c r="A26" s="13"/>
+      <c r="B26" s="38"/>
+      <c r="C26" s="88"/>
+      <c r="D26" s="38"/>
+      <c r="E26" s="73" t="s">
+        <v>63</v>
+      </c>
+      <c r="F26" s="73"/>
+      <c r="G26" s="74"/>
+      <c r="H26" s="44"/>
+      <c r="I26" s="38"/>
+      <c r="J26" s="38"/>
+      <c r="K26" s="233" t="s">
+        <v>77</v>
+      </c>
+      <c r="L26" s="73"/>
+      <c r="M26" s="73"/>
+      <c r="N26" s="38"/>
+      <c r="O26" s="38"/>
+      <c r="P26" s="38"/>
+      <c r="Q26" s="38"/>
+      <c r="R26" s="38"/>
+      <c r="S26" s="44"/>
+      <c r="T26" s="38"/>
+      <c r="U26" s="89"/>
+      <c r="V26" s="44"/>
+      <c r="W26" s="38"/>
+    </row>
+    <row r="27" spans="1:23" ht="18" customHeight="1">
+      <c r="A27" s="13"/>
+      <c r="B27" s="38"/>
+      <c r="C27" s="88"/>
+      <c r="D27" s="38"/>
+      <c r="E27" s="73"/>
+      <c r="F27" s="73"/>
+      <c r="G27" s="74"/>
+      <c r="H27" s="44"/>
+      <c r="I27" s="38"/>
+      <c r="J27" s="38"/>
+      <c r="K27" s="73"/>
+      <c r="L27" s="73"/>
+      <c r="M27" s="73"/>
+      <c r="N27" s="38"/>
+      <c r="O27" s="38"/>
+      <c r="P27" s="38"/>
+      <c r="Q27" s="38"/>
+      <c r="R27" s="38"/>
+      <c r="S27" s="44"/>
+      <c r="T27" s="38"/>
+      <c r="U27" s="89"/>
+      <c r="V27" s="44"/>
+      <c r="W27" s="38"/>
+    </row>
+    <row r="28" spans="1:23" ht="18" customHeight="1">
+      <c r="A28" s="13"/>
+      <c r="B28" s="38"/>
+      <c r="C28" s="88"/>
+      <c r="D28" s="38"/>
+      <c r="E28" s="75" t="s">
+        <v>64</v>
+      </c>
+      <c r="F28" s="73"/>
+      <c r="G28" s="74"/>
+      <c r="H28" s="44"/>
+      <c r="I28" s="38"/>
+      <c r="J28" s="38"/>
+      <c r="K28" s="73"/>
+      <c r="L28" s="73"/>
+      <c r="M28" s="73"/>
+      <c r="N28" s="38"/>
+      <c r="O28" s="38"/>
+      <c r="P28" s="38"/>
+      <c r="Q28" s="38"/>
+      <c r="R28" s="38"/>
+      <c r="S28" s="44"/>
+      <c r="T28" s="38"/>
+      <c r="U28" s="89"/>
+      <c r="V28" s="44"/>
+      <c r="W28" s="38"/>
+    </row>
+    <row r="29" spans="1:23" ht="18" customHeight="1">
+      <c r="A29" s="13"/>
+      <c r="B29" s="38"/>
+      <c r="C29" s="88"/>
+      <c r="D29" s="38"/>
+      <c r="E29" s="75"/>
+      <c r="F29" s="73"/>
+      <c r="G29" s="74"/>
+      <c r="H29" s="44"/>
+      <c r="I29" s="38"/>
+      <c r="J29" s="38"/>
+      <c r="K29" s="73"/>
+      <c r="L29" s="73"/>
+      <c r="M29" s="73"/>
+      <c r="N29" s="38"/>
+      <c r="O29" s="38"/>
+      <c r="P29" s="38"/>
+      <c r="Q29" s="38"/>
+      <c r="R29" s="38"/>
+      <c r="S29" s="44"/>
+      <c r="T29" s="38"/>
+      <c r="U29" s="89"/>
+      <c r="V29" s="44"/>
+      <c r="W29" s="38"/>
+    </row>
+    <row r="30" spans="1:23" ht="18" customHeight="1">
+      <c r="A30" s="13"/>
+      <c r="B30" s="38"/>
+      <c r="C30" s="88"/>
+      <c r="D30" s="38"/>
+      <c r="E30" s="75" t="s">
+        <v>65</v>
+      </c>
+      <c r="F30" s="73"/>
+      <c r="G30" s="74"/>
+      <c r="H30" s="44"/>
+      <c r="I30" s="38"/>
+      <c r="J30" s="38"/>
+      <c r="K30" s="73"/>
+      <c r="L30" s="73"/>
+      <c r="M30" s="73"/>
+      <c r="N30" s="38"/>
+      <c r="O30" s="38"/>
+      <c r="P30" s="38"/>
+      <c r="Q30" s="38"/>
+      <c r="R30" s="38"/>
+      <c r="S30" s="44"/>
+      <c r="T30" s="38"/>
+      <c r="U30" s="89"/>
+      <c r="V30" s="44"/>
+      <c r="W30" s="38"/>
+    </row>
+    <row r="31" spans="1:23" ht="18" customHeight="1">
+      <c r="A31" s="13"/>
+      <c r="B31" s="38"/>
+      <c r="C31" s="88"/>
+      <c r="D31" s="38"/>
+      <c r="E31" s="75"/>
+      <c r="F31" s="73"/>
+      <c r="G31" s="74"/>
+      <c r="H31" s="44"/>
+      <c r="I31" s="38"/>
+      <c r="J31" s="38"/>
+      <c r="K31" s="73"/>
+      <c r="L31" s="73"/>
+      <c r="M31" s="73"/>
+      <c r="N31" s="38"/>
+      <c r="O31" s="38"/>
+      <c r="P31" s="38"/>
+      <c r="Q31" s="38"/>
+      <c r="R31" s="38"/>
+      <c r="S31" s="44"/>
+      <c r="T31" s="38"/>
+      <c r="U31" s="89"/>
+      <c r="V31" s="44"/>
+      <c r="W31" s="38"/>
+    </row>
+    <row r="32" spans="1:23" ht="18" customHeight="1">
+      <c r="A32" s="13"/>
+      <c r="B32" s="38"/>
+      <c r="C32" s="88"/>
+      <c r="D32" s="38"/>
+      <c r="E32" s="73" t="s">
+        <v>66</v>
+      </c>
+      <c r="F32" s="73"/>
+      <c r="G32" s="74"/>
+      <c r="H32" s="44"/>
+      <c r="I32" s="38"/>
+      <c r="J32" s="38"/>
+      <c r="K32" s="233" t="s">
+        <v>80</v>
+      </c>
+      <c r="L32" s="73"/>
+      <c r="M32" s="73"/>
+      <c r="N32" s="38"/>
+      <c r="O32" s="38"/>
+      <c r="P32" s="38"/>
+      <c r="Q32" s="38"/>
+      <c r="R32" s="38"/>
+      <c r="S32" s="44"/>
+      <c r="T32" s="38"/>
+      <c r="U32" s="89"/>
+      <c r="V32" s="44"/>
+      <c r="W32" s="38"/>
+    </row>
+    <row r="33" spans="1:23" ht="18" customHeight="1">
+      <c r="A33" s="13"/>
+      <c r="B33" s="38"/>
+      <c r="C33" s="88"/>
+      <c r="D33" s="38"/>
+      <c r="E33" s="38"/>
+      <c r="F33" s="38"/>
+      <c r="G33" s="44"/>
+      <c r="H33" s="44"/>
+      <c r="I33" s="38"/>
+      <c r="J33" s="38"/>
+      <c r="K33" s="73"/>
+      <c r="L33" s="73"/>
+      <c r="M33" s="73"/>
+      <c r="N33" s="38"/>
+      <c r="O33" s="38"/>
+      <c r="P33" s="38"/>
+      <c r="Q33" s="38"/>
+      <c r="R33" s="38"/>
+      <c r="S33" s="44"/>
+      <c r="T33" s="38"/>
+      <c r="U33" s="89"/>
+      <c r="V33" s="44"/>
+      <c r="W33" s="38"/>
+    </row>
+    <row r="34" spans="1:23" ht="18" customHeight="1">
+      <c r="A34" s="13"/>
+      <c r="B34" s="38"/>
+      <c r="C34" s="88"/>
+      <c r="D34" s="38"/>
+      <c r="F34" s="38"/>
+      <c r="G34" s="44"/>
+      <c r="H34" s="44"/>
+      <c r="I34" s="38"/>
+      <c r="J34" s="38"/>
+      <c r="K34" s="73"/>
+      <c r="L34" s="73"/>
+      <c r="M34" s="73"/>
+      <c r="N34" s="38"/>
+      <c r="O34" s="38"/>
+      <c r="P34" s="38"/>
+      <c r="Q34" s="38"/>
+      <c r="R34" s="38"/>
+      <c r="S34" s="44"/>
+      <c r="T34" s="38"/>
+      <c r="U34" s="89"/>
+      <c r="V34" s="44"/>
+      <c r="W34" s="38"/>
+    </row>
+    <row r="35" spans="1:23" ht="18" customHeight="1">
+      <c r="A35" s="13"/>
+      <c r="B35" s="38"/>
+      <c r="C35" s="88"/>
+      <c r="D35" s="38"/>
+      <c r="E35" s="38"/>
+      <c r="F35" s="38"/>
+      <c r="G35" s="44"/>
+      <c r="H35" s="44"/>
+      <c r="I35" s="38"/>
+      <c r="J35" s="38"/>
+      <c r="K35" s="73"/>
+      <c r="L35" s="73"/>
+      <c r="M35" s="73"/>
+      <c r="N35" s="38"/>
+      <c r="O35" s="38"/>
+      <c r="P35" s="38"/>
+      <c r="Q35" s="38"/>
+      <c r="R35" s="38"/>
+      <c r="S35" s="44"/>
+      <c r="T35" s="38"/>
+      <c r="U35" s="89"/>
+      <c r="V35" s="44"/>
+      <c r="W35" s="38"/>
+    </row>
+    <row r="36" spans="1:23" ht="18" customHeight="1">
+      <c r="A36" s="13"/>
+      <c r="B36" s="13"/>
+      <c r="C36" s="93"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="13"/>
+      <c r="H36" s="13"/>
+      <c r="I36" s="13"/>
+      <c r="J36" s="13"/>
+      <c r="K36" s="13"/>
+      <c r="L36" s="13"/>
+      <c r="M36" s="13"/>
+      <c r="N36" s="13"/>
+      <c r="O36" s="13"/>
+      <c r="P36" s="13"/>
+      <c r="Q36" s="13"/>
+      <c r="R36" s="13"/>
+      <c r="S36" s="13"/>
+      <c r="T36" s="13"/>
+      <c r="U36" s="94"/>
+      <c r="V36" s="13"/>
+      <c r="W36" s="13"/>
+    </row>
+    <row r="37" spans="1:23" ht="18" customHeight="1" thickBot="1">
+      <c r="A37" s="13"/>
+      <c r="B37" s="13"/>
+      <c r="C37" s="95"/>
+      <c r="D37" s="96"/>
+      <c r="E37" s="96"/>
+      <c r="F37" s="96"/>
+      <c r="G37" s="96"/>
+      <c r="H37" s="96"/>
+      <c r="I37" s="96"/>
+      <c r="J37" s="96"/>
+      <c r="K37" s="96"/>
+      <c r="L37" s="96"/>
+      <c r="M37" s="96"/>
+      <c r="N37" s="96"/>
+      <c r="O37" s="96"/>
+      <c r="P37" s="96"/>
+      <c r="Q37" s="96"/>
+      <c r="R37" s="96"/>
+      <c r="S37" s="96"/>
+      <c r="T37" s="96"/>
+      <c r="U37" s="97"/>
+      <c r="V37" s="13"/>
+      <c r="W37" s="13"/>
+    </row>
+    <row r="38" spans="1:23" ht="18" customHeight="1">
+      <c r="A38" s="13"/>
+      <c r="B38" s="13"/>
+      <c r="C38" s="13"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="13"/>
+      <c r="H38" s="13"/>
+      <c r="I38" s="13"/>
+      <c r="J38" s="13"/>
+      <c r="K38" s="13"/>
+      <c r="L38" s="13"/>
+      <c r="M38" s="13"/>
+      <c r="N38" s="13"/>
+      <c r="O38" s="13"/>
+      <c r="P38" s="13"/>
+      <c r="Q38" s="13"/>
+      <c r="R38" s="13"/>
+      <c r="S38" s="13"/>
+      <c r="T38" s="13"/>
+      <c r="U38" s="13"/>
+      <c r="V38" s="13"/>
+      <c r="W38" s="13"/>
+    </row>
+    <row r="39" spans="1:23" ht="18" customHeight="1">
+      <c r="A39" s="66"/>
+      <c r="B39" s="68"/>
+      <c r="C39" s="68"/>
+      <c r="D39" s="68"/>
+      <c r="E39" s="69"/>
+      <c r="F39" s="69"/>
+      <c r="G39" s="68"/>
+      <c r="H39" s="68"/>
+      <c r="I39" s="68"/>
+      <c r="J39" s="68"/>
+      <c r="K39" s="79"/>
+      <c r="L39" s="79"/>
+      <c r="M39" s="79"/>
+      <c r="N39" s="68"/>
+      <c r="O39" s="68"/>
+      <c r="P39" s="68"/>
+      <c r="Q39" s="68"/>
+      <c r="R39" s="68"/>
+      <c r="S39" s="70"/>
+      <c r="T39" s="70"/>
+      <c r="U39" s="70"/>
+      <c r="V39" s="70"/>
+      <c r="W39" s="70"/>
+    </row>
+    <row r="40" spans="1:23" ht="18" customHeight="1">
+      <c r="A40" s="71"/>
+      <c r="B40" s="72"/>
+      <c r="C40" s="72"/>
+      <c r="D40" s="72"/>
+      <c r="E40" s="72"/>
+      <c r="F40" s="72"/>
+      <c r="G40" s="72"/>
+      <c r="H40" s="72"/>
+      <c r="I40" s="72"/>
+      <c r="J40" s="72"/>
+      <c r="K40" s="80"/>
+      <c r="L40" s="80"/>
+      <c r="M40" s="80"/>
+      <c r="N40" s="72"/>
+      <c r="O40" s="72"/>
+      <c r="P40" s="72"/>
+      <c r="Q40" s="72"/>
+      <c r="R40" s="72"/>
+      <c r="S40" s="72"/>
+      <c r="T40" s="72"/>
+      <c r="U40" s="72"/>
+      <c r="V40" s="72"/>
+      <c r="W40" s="72"/>
+    </row>
+    <row r="41" spans="1:23" ht="12.5" customHeight="1">
+      <c r="A41" s="64"/>
+      <c r="B41" s="65"/>
+      <c r="C41" s="65"/>
+      <c r="D41" s="65"/>
+      <c r="E41" s="65"/>
+      <c r="F41" s="65"/>
+      <c r="G41" s="65"/>
+      <c r="H41" s="65"/>
+      <c r="I41" s="65"/>
+      <c r="J41" s="65"/>
+      <c r="K41" s="77"/>
+      <c r="L41" s="77"/>
+      <c r="M41" s="77"/>
+      <c r="N41" s="65"/>
+      <c r="O41" s="65"/>
+      <c r="P41" s="65"/>
+      <c r="Q41" s="65"/>
+      <c r="R41" s="65"/>
+      <c r="S41" s="65"/>
+      <c r="T41" s="65"/>
+      <c r="U41" s="65"/>
+      <c r="V41" s="65"/>
+      <c r="W41" s="65"/>
+    </row>
+    <row r="42" spans="1:23" ht="12.5" customHeight="1">
+      <c r="A42" s="66"/>
+      <c r="B42" s="67"/>
+      <c r="C42" s="67"/>
+      <c r="D42" s="67"/>
+      <c r="E42" s="67"/>
+      <c r="F42" s="67"/>
+      <c r="G42" s="67"/>
+      <c r="H42" s="67"/>
+      <c r="I42" s="67"/>
+      <c r="J42" s="67"/>
+      <c r="K42" s="78"/>
+      <c r="L42" s="78"/>
+      <c r="M42" s="78"/>
+      <c r="N42" s="67"/>
+      <c r="O42" s="67"/>
+      <c r="P42" s="67"/>
+      <c r="Q42" s="67"/>
+      <c r="R42" s="67"/>
+      <c r="S42" s="67"/>
+      <c r="T42" s="67"/>
+      <c r="U42" s="67"/>
+      <c r="V42" s="67"/>
+      <c r="W42" s="67"/>
+    </row>
+    <row r="43" spans="1:23" ht="12.5" customHeight="1">
+      <c r="A43" s="16"/>
+      <c r="B43" s="73" t="s">
+        <v>141</v>
+      </c>
+      <c r="C43" s="38"/>
+      <c r="D43" s="38"/>
+      <c r="E43" s="38"/>
+      <c r="F43" s="38"/>
+      <c r="G43" s="38"/>
+      <c r="H43" s="38"/>
+      <c r="I43" s="38"/>
+      <c r="J43" s="38"/>
+      <c r="K43" s="73"/>
+      <c r="L43" s="73"/>
+      <c r="M43" s="73"/>
+      <c r="N43" s="38"/>
+      <c r="O43" s="38"/>
+      <c r="P43" s="38"/>
+      <c r="Q43" s="38"/>
+      <c r="R43" s="38"/>
+      <c r="S43" s="38"/>
+      <c r="T43" s="38"/>
+      <c r="U43" s="38"/>
+      <c r="V43" s="38"/>
+      <c r="W43" s="38"/>
+    </row>
+    <row r="44" spans="1:23" ht="12.5" customHeight="1" thickBot="1">
+      <c r="A44" s="13"/>
+      <c r="B44" s="38"/>
+      <c r="C44" s="38"/>
+      <c r="D44" s="38"/>
+      <c r="E44" s="38"/>
+      <c r="F44" s="38"/>
+      <c r="G44" s="38"/>
+      <c r="H44" s="38"/>
+      <c r="I44" s="38"/>
+      <c r="J44" s="42"/>
+      <c r="K44" s="73"/>
+      <c r="L44" s="73"/>
+      <c r="M44" s="73"/>
+      <c r="N44" s="38"/>
+      <c r="O44" s="38"/>
+      <c r="P44" s="38"/>
+      <c r="Q44" s="38"/>
+      <c r="R44" s="38"/>
+      <c r="S44" s="38"/>
+      <c r="T44" s="38"/>
+      <c r="U44" s="42"/>
+      <c r="V44" s="42"/>
+      <c r="W44" s="38"/>
+    </row>
+    <row r="45" spans="1:23" ht="18" customHeight="1">
+      <c r="A45" s="13"/>
+      <c r="B45" s="38"/>
+      <c r="C45" s="82"/>
+      <c r="D45" s="83"/>
+      <c r="E45" s="83"/>
+      <c r="F45" s="83"/>
+      <c r="G45" s="83"/>
+      <c r="H45" s="83"/>
+      <c r="I45" s="83"/>
+      <c r="J45" s="83"/>
+      <c r="K45" s="85"/>
+      <c r="L45" s="85"/>
+      <c r="M45" s="85"/>
+      <c r="N45" s="83"/>
+      <c r="O45" s="83"/>
+      <c r="P45" s="83"/>
+      <c r="Q45" s="83"/>
+      <c r="R45" s="83"/>
+      <c r="S45" s="83"/>
+      <c r="T45" s="83"/>
+      <c r="U45" s="87"/>
+      <c r="V45" s="38"/>
+      <c r="W45" s="38"/>
+    </row>
+    <row r="46" spans="1:23" ht="18" customHeight="1">
+      <c r="A46" s="13"/>
+      <c r="B46" s="38"/>
+      <c r="C46" s="88"/>
+      <c r="D46" s="38"/>
+      <c r="E46" s="38"/>
+      <c r="F46" s="38"/>
+      <c r="G46" s="38"/>
+      <c r="H46" s="38"/>
+      <c r="I46" s="42"/>
+      <c r="J46" s="42"/>
+      <c r="K46" s="73"/>
+      <c r="L46" s="73"/>
+      <c r="M46" s="76"/>
+      <c r="N46" s="38"/>
+      <c r="O46" s="38"/>
+      <c r="P46" s="38"/>
+      <c r="Q46" s="38"/>
+      <c r="R46" s="38"/>
+      <c r="S46" s="38"/>
+      <c r="T46" s="38"/>
+      <c r="U46" s="89"/>
+      <c r="V46" s="38"/>
+      <c r="W46" s="38"/>
+    </row>
+    <row r="47" spans="1:23" ht="18" customHeight="1">
+      <c r="A47" s="13"/>
+      <c r="B47" s="38"/>
+      <c r="C47" s="88"/>
+      <c r="D47" s="38"/>
+      <c r="E47" s="73" t="s">
+        <v>55</v>
+      </c>
+      <c r="F47" s="44"/>
+      <c r="G47" s="38"/>
+      <c r="H47" s="38"/>
+      <c r="I47" s="38"/>
+      <c r="J47" s="38"/>
+      <c r="K47" s="73" t="s">
+        <v>71</v>
+      </c>
+      <c r="L47" s="73"/>
+      <c r="M47" s="73"/>
+      <c r="N47" s="38"/>
+      <c r="O47" s="38"/>
+      <c r="P47" s="38"/>
+      <c r="Q47" s="38"/>
+      <c r="R47" s="38"/>
+      <c r="S47" s="38"/>
+      <c r="T47" s="38"/>
+      <c r="U47" s="89"/>
+      <c r="V47" s="38"/>
+      <c r="W47" s="38"/>
+    </row>
+    <row r="48" spans="1:23" ht="18" customHeight="1">
+      <c r="A48" s="13"/>
+      <c r="B48" s="38"/>
+      <c r="C48" s="88"/>
+      <c r="D48" s="38"/>
+      <c r="E48" s="73"/>
+      <c r="F48" s="74"/>
+      <c r="G48" s="73"/>
+      <c r="H48" s="38"/>
+      <c r="I48" s="38"/>
+      <c r="J48" s="38"/>
+      <c r="K48" s="73"/>
+      <c r="L48" s="73"/>
+      <c r="M48" s="73"/>
+      <c r="N48" s="38"/>
+      <c r="O48" s="38"/>
+      <c r="P48" s="38"/>
+      <c r="Q48" s="38"/>
+      <c r="R48" s="38"/>
+      <c r="S48" s="38"/>
+      <c r="T48" s="38"/>
+      <c r="U48" s="89"/>
+      <c r="V48" s="38"/>
+      <c r="W48" s="38"/>
+    </row>
+    <row r="49" spans="1:23" ht="18" customHeight="1">
+      <c r="A49" s="13"/>
+      <c r="B49" s="38"/>
+      <c r="C49" s="88"/>
+      <c r="D49" s="38"/>
+      <c r="E49" s="73" t="s">
+        <v>56</v>
+      </c>
+      <c r="F49" s="73"/>
+      <c r="G49" s="73"/>
+      <c r="H49" s="38"/>
+      <c r="I49" s="38"/>
+      <c r="J49" s="38"/>
+      <c r="K49" s="73" t="s">
+        <v>72</v>
+      </c>
+      <c r="L49" s="73"/>
+      <c r="M49" s="73"/>
+      <c r="N49" s="38"/>
+      <c r="O49" s="63"/>
+      <c r="P49" s="63"/>
+      <c r="Q49" s="38"/>
+      <c r="R49" s="63"/>
+      <c r="S49" s="38"/>
+      <c r="T49" s="63"/>
+      <c r="U49" s="90"/>
+      <c r="V49" s="38"/>
+      <c r="W49" s="63"/>
+    </row>
+    <row r="50" spans="1:23" ht="18" customHeight="1">
+      <c r="A50" s="13"/>
+      <c r="B50" s="62"/>
+      <c r="C50" s="91"/>
+      <c r="D50" s="38"/>
+      <c r="E50" s="75"/>
+      <c r="F50" s="73"/>
+      <c r="G50" s="73"/>
+      <c r="H50" s="44"/>
+      <c r="I50" s="44"/>
+      <c r="J50" s="44"/>
+      <c r="K50" s="73"/>
+      <c r="L50" s="73"/>
+      <c r="M50" s="73"/>
+      <c r="N50" s="38"/>
+      <c r="O50" s="38"/>
+      <c r="P50" s="38"/>
+      <c r="Q50" s="38"/>
+      <c r="R50" s="38"/>
+      <c r="S50" s="44"/>
+      <c r="T50" s="44"/>
+      <c r="U50" s="92"/>
+      <c r="V50" s="44"/>
+      <c r="W50" s="44"/>
+    </row>
+    <row r="51" spans="1:23" ht="18" customHeight="1">
+      <c r="A51" s="13"/>
+      <c r="B51" s="38"/>
+      <c r="C51" s="88"/>
+      <c r="D51" s="38"/>
+      <c r="E51" s="73" t="s">
+        <v>57</v>
+      </c>
+      <c r="F51" s="73"/>
+      <c r="G51" s="73"/>
+      <c r="H51" s="44"/>
+      <c r="I51" s="38"/>
+      <c r="J51" s="38"/>
+      <c r="K51" s="73" t="s">
+        <v>73</v>
+      </c>
+      <c r="L51" s="73"/>
+      <c r="M51" s="73"/>
+      <c r="N51" s="38"/>
+      <c r="O51" s="38"/>
+      <c r="P51" s="38"/>
+      <c r="Q51" s="38"/>
+      <c r="R51" s="38"/>
+      <c r="S51" s="44"/>
+      <c r="T51" s="38"/>
+      <c r="U51" s="89"/>
+      <c r="V51" s="44"/>
+      <c r="W51" s="38"/>
+    </row>
+    <row r="52" spans="1:23" ht="18" customHeight="1">
+      <c r="A52" s="13"/>
+      <c r="B52" s="38"/>
+      <c r="C52" s="88"/>
+      <c r="D52" s="38"/>
+      <c r="E52" s="73"/>
+      <c r="F52" s="73"/>
+      <c r="G52" s="73"/>
+      <c r="H52" s="44"/>
+      <c r="I52" s="38"/>
+      <c r="J52" s="38"/>
+      <c r="K52" s="73"/>
+      <c r="L52" s="73"/>
+      <c r="M52" s="73"/>
+      <c r="N52" s="38"/>
+      <c r="O52" s="38"/>
+      <c r="P52" s="38"/>
+      <c r="Q52" s="38"/>
+      <c r="R52" s="38"/>
+      <c r="S52" s="44"/>
+      <c r="T52" s="38"/>
+      <c r="U52" s="89"/>
+      <c r="V52" s="44"/>
+      <c r="W52" s="38"/>
+    </row>
+    <row r="53" spans="1:23" ht="18" customHeight="1">
+      <c r="A53" s="13"/>
+      <c r="B53" s="38"/>
+      <c r="C53" s="88"/>
+      <c r="D53" s="38"/>
+      <c r="E53" s="73" t="s">
+        <v>58</v>
+      </c>
+      <c r="F53" s="73"/>
+      <c r="G53" s="73"/>
+      <c r="H53" s="44"/>
+      <c r="I53" s="38"/>
+      <c r="J53" s="38"/>
+      <c r="K53" s="73" t="s">
+        <v>74</v>
+      </c>
+      <c r="L53" s="73"/>
+      <c r="M53" s="73"/>
+      <c r="N53" s="38"/>
+      <c r="O53" s="38"/>
+      <c r="P53" s="38"/>
+      <c r="Q53" s="38"/>
+      <c r="R53" s="38"/>
+      <c r="S53" s="44"/>
+      <c r="T53" s="38"/>
+      <c r="U53" s="89"/>
+      <c r="V53" s="44"/>
+      <c r="W53" s="38"/>
+    </row>
+    <row r="54" spans="1:23" ht="18" customHeight="1">
+      <c r="A54" s="13"/>
+      <c r="B54" s="38"/>
+      <c r="C54" s="88"/>
+      <c r="D54" s="38"/>
+      <c r="E54" s="73"/>
+      <c r="F54" s="73"/>
+      <c r="G54" s="73"/>
+      <c r="H54" s="44"/>
+      <c r="I54" s="38"/>
+      <c r="J54" s="38"/>
+      <c r="K54" s="73"/>
+      <c r="L54" s="73"/>
+      <c r="M54" s="73"/>
+      <c r="N54" s="38"/>
+      <c r="O54" s="38"/>
+      <c r="P54" s="38"/>
+      <c r="Q54" s="38"/>
+      <c r="R54" s="38"/>
+      <c r="S54" s="44"/>
+      <c r="T54" s="38"/>
+      <c r="U54" s="89"/>
+      <c r="V54" s="44"/>
+      <c r="W54" s="38"/>
+    </row>
+    <row r="55" spans="1:23" ht="18" customHeight="1">
+      <c r="A55" s="13"/>
+      <c r="B55" s="38"/>
+      <c r="C55" s="88"/>
+      <c r="D55" s="38"/>
+      <c r="E55" s="73" t="s">
+        <v>59</v>
+      </c>
+      <c r="F55" s="73"/>
+      <c r="G55" s="73"/>
+      <c r="H55" s="44"/>
+      <c r="I55" s="38"/>
+      <c r="J55" s="38"/>
+      <c r="K55" s="73" t="s">
+        <v>75</v>
+      </c>
+      <c r="L55" s="73"/>
+      <c r="M55" s="73"/>
+      <c r="N55" s="38"/>
+      <c r="O55" s="38"/>
+      <c r="P55" s="38"/>
+      <c r="Q55" s="38"/>
+      <c r="R55" s="38"/>
+      <c r="S55" s="44"/>
+      <c r="T55" s="38"/>
+      <c r="U55" s="89"/>
+      <c r="V55" s="44"/>
+      <c r="W55" s="38"/>
+    </row>
+    <row r="56" spans="1:23" ht="18" customHeight="1">
+      <c r="A56" s="13"/>
+      <c r="B56" s="38"/>
+      <c r="C56" s="88"/>
+      <c r="D56" s="38"/>
+      <c r="E56" s="73"/>
+      <c r="F56" s="73"/>
+      <c r="G56" s="73"/>
+      <c r="H56" s="44"/>
+      <c r="I56" s="38"/>
+      <c r="J56" s="38"/>
+      <c r="K56" s="73"/>
+      <c r="L56" s="73"/>
+      <c r="M56" s="73"/>
+      <c r="N56" s="38"/>
+      <c r="O56" s="38"/>
+      <c r="P56" s="38"/>
+      <c r="Q56" s="38"/>
+      <c r="R56" s="38"/>
+      <c r="S56" s="44"/>
+      <c r="T56" s="38"/>
+      <c r="U56" s="89"/>
+      <c r="V56" s="44"/>
+      <c r="W56" s="38"/>
+    </row>
+    <row r="57" spans="1:23" ht="18" customHeight="1">
+      <c r="A57" s="13"/>
+      <c r="B57" s="38"/>
+      <c r="C57" s="88"/>
+      <c r="D57" s="38"/>
+      <c r="E57" s="73" t="s">
+        <v>60</v>
+      </c>
+      <c r="F57" s="73"/>
+      <c r="G57" s="73"/>
+      <c r="H57" s="44"/>
+      <c r="I57" s="38"/>
+      <c r="J57" s="38"/>
+      <c r="K57" s="73" t="s">
+        <v>76</v>
+      </c>
+      <c r="L57" s="73"/>
+      <c r="M57" s="73"/>
+      <c r="N57" s="38"/>
+      <c r="O57" s="38"/>
+      <c r="P57" s="38"/>
+      <c r="Q57" s="38"/>
+      <c r="R57" s="38"/>
+      <c r="S57" s="44"/>
+      <c r="T57" s="38"/>
+      <c r="U57" s="89"/>
+      <c r="V57" s="44"/>
+      <c r="W57" s="38"/>
+    </row>
+    <row r="58" spans="1:23" ht="18" customHeight="1">
+      <c r="A58" s="13"/>
+      <c r="B58" s="38"/>
+      <c r="C58" s="88"/>
+      <c r="D58" s="38"/>
+      <c r="E58" s="73"/>
+      <c r="F58" s="73"/>
+      <c r="G58" s="73"/>
+      <c r="H58" s="44"/>
+      <c r="I58" s="38"/>
+      <c r="J58" s="38"/>
+      <c r="K58" s="73"/>
+      <c r="L58" s="73"/>
+      <c r="M58" s="73"/>
+      <c r="N58" s="38"/>
+      <c r="O58" s="38"/>
+      <c r="P58" s="38"/>
+      <c r="Q58" s="38"/>
+      <c r="R58" s="38"/>
+      <c r="S58" s="44"/>
+      <c r="T58" s="38"/>
+      <c r="U58" s="89"/>
+      <c r="V58" s="44"/>
+      <c r="W58" s="38"/>
+    </row>
+    <row r="59" spans="1:23" ht="18" customHeight="1">
+      <c r="A59" s="13"/>
+      <c r="B59" s="38"/>
+      <c r="C59" s="88"/>
+      <c r="D59" s="38"/>
+      <c r="E59" s="73" t="s">
+        <v>61</v>
+      </c>
+      <c r="F59" s="73"/>
+      <c r="G59" s="73"/>
+      <c r="H59" s="44"/>
+      <c r="I59" s="38"/>
+      <c r="J59" s="38"/>
+      <c r="K59" s="76" t="s">
+        <v>68</v>
+      </c>
+      <c r="L59" s="76"/>
+      <c r="M59" s="73"/>
+      <c r="N59" s="38"/>
+      <c r="O59" s="76"/>
+      <c r="P59" s="76"/>
+      <c r="Q59" s="38"/>
+      <c r="R59" s="38"/>
+      <c r="S59" s="44"/>
+      <c r="T59" s="38"/>
+      <c r="U59" s="89"/>
+      <c r="V59" s="44"/>
+      <c r="W59" s="38"/>
+    </row>
+    <row r="60" spans="1:23" ht="18" customHeight="1">
+      <c r="A60" s="13"/>
+      <c r="B60" s="38"/>
+      <c r="C60" s="88"/>
+      <c r="D60" s="38"/>
+      <c r="E60" s="73"/>
+      <c r="F60" s="73"/>
+      <c r="G60" s="74"/>
+      <c r="H60" s="44"/>
+      <c r="I60" s="38"/>
+      <c r="J60" s="38"/>
+      <c r="K60" s="73"/>
+      <c r="L60" s="73"/>
+      <c r="M60" s="73"/>
+      <c r="N60" s="38"/>
+      <c r="O60" s="38"/>
+      <c r="P60" s="38"/>
+      <c r="Q60" s="38"/>
+      <c r="R60" s="38"/>
+      <c r="S60" s="44"/>
+      <c r="T60" s="38"/>
+      <c r="U60" s="89"/>
+      <c r="V60" s="44"/>
+      <c r="W60" s="38"/>
+    </row>
+    <row r="61" spans="1:23" ht="18" customHeight="1">
+      <c r="A61" s="13"/>
+      <c r="B61" s="38"/>
+      <c r="C61" s="88"/>
+      <c r="D61" s="38"/>
+      <c r="E61" s="73" t="s">
+        <v>62</v>
+      </c>
+      <c r="F61" s="73"/>
+      <c r="G61" s="74"/>
+      <c r="H61" s="44"/>
+      <c r="I61" s="38"/>
+      <c r="J61" s="38"/>
+      <c r="K61" s="203">
+        <v>9876543</v>
+      </c>
+      <c r="L61" s="203"/>
+      <c r="M61" s="203"/>
+      <c r="N61" s="203"/>
+      <c r="O61" s="38"/>
+      <c r="P61" s="38"/>
+      <c r="Q61" s="38"/>
+      <c r="R61" s="38"/>
+      <c r="S61" s="44"/>
+      <c r="T61" s="38"/>
+      <c r="U61" s="89"/>
+      <c r="V61" s="44"/>
+      <c r="W61" s="38"/>
+    </row>
+    <row r="62" spans="1:23" ht="18" customHeight="1">
+      <c r="A62" s="13"/>
+      <c r="B62" s="38"/>
+      <c r="C62" s="88"/>
+      <c r="D62" s="38"/>
+      <c r="E62" s="75"/>
+      <c r="F62" s="73"/>
+      <c r="G62" s="74"/>
+      <c r="H62" s="44"/>
+      <c r="I62" s="38"/>
+      <c r="J62" s="38"/>
+      <c r="K62" s="73"/>
+      <c r="L62" s="73"/>
+      <c r="M62" s="73"/>
+      <c r="N62" s="38"/>
+      <c r="O62" s="38"/>
+      <c r="P62" s="38"/>
+      <c r="Q62" s="38"/>
+      <c r="R62" s="38"/>
+      <c r="S62" s="44"/>
+      <c r="T62" s="38"/>
+      <c r="U62" s="89"/>
+      <c r="V62" s="44"/>
+      <c r="W62" s="38"/>
+    </row>
+    <row r="63" spans="1:23" ht="18" customHeight="1">
+      <c r="A63" s="13"/>
+      <c r="B63" s="38"/>
+      <c r="C63" s="88"/>
+      <c r="D63" s="38"/>
+      <c r="E63" s="73" t="s">
+        <v>63</v>
+      </c>
+      <c r="F63" s="73"/>
+      <c r="G63" s="74"/>
+      <c r="H63" s="44"/>
+      <c r="I63" s="38"/>
+      <c r="J63" s="38"/>
+      <c r="K63" s="73" t="s">
+        <v>77</v>
+      </c>
+      <c r="L63" s="73"/>
+      <c r="M63" s="73"/>
+      <c r="N63" s="38"/>
+      <c r="O63" s="38"/>
+      <c r="P63" s="38"/>
+      <c r="Q63" s="38"/>
+      <c r="R63" s="38"/>
+      <c r="S63" s="44"/>
+      <c r="T63" s="38"/>
+      <c r="U63" s="89"/>
+      <c r="V63" s="44"/>
+      <c r="W63" s="38"/>
+    </row>
+    <row r="64" spans="1:23" ht="18" customHeight="1">
+      <c r="A64" s="13"/>
+      <c r="B64" s="38"/>
+      <c r="C64" s="88"/>
+      <c r="D64" s="38"/>
+      <c r="E64" s="73"/>
+      <c r="F64" s="73"/>
+      <c r="G64" s="74"/>
+      <c r="H64" s="44"/>
+      <c r="I64" s="38"/>
+      <c r="J64" s="38"/>
+      <c r="K64" s="73"/>
+      <c r="L64" s="73"/>
+      <c r="M64" s="73"/>
+      <c r="N64" s="38"/>
+      <c r="O64" s="38"/>
+      <c r="P64" s="38"/>
+      <c r="Q64" s="38"/>
+      <c r="R64" s="38"/>
+      <c r="S64" s="44"/>
+      <c r="T64" s="38"/>
+      <c r="U64" s="89"/>
+      <c r="V64" s="44"/>
+      <c r="W64" s="38"/>
+    </row>
+    <row r="65" spans="1:23" ht="18" customHeight="1">
+      <c r="A65" s="13"/>
+      <c r="B65" s="38"/>
+      <c r="C65" s="88"/>
+      <c r="D65" s="38"/>
+      <c r="E65" s="75" t="s">
+        <v>64</v>
+      </c>
+      <c r="F65" s="73"/>
+      <c r="G65" s="74"/>
+      <c r="H65" s="44"/>
+      <c r="I65" s="38"/>
+      <c r="J65" s="38"/>
+      <c r="K65" s="73" t="s">
+        <v>78</v>
+      </c>
+      <c r="L65" s="73"/>
+      <c r="M65" s="73"/>
+      <c r="N65" s="38"/>
+      <c r="O65" s="38"/>
+      <c r="P65" s="38"/>
+      <c r="Q65" s="38"/>
+      <c r="R65" s="38"/>
+      <c r="S65" s="44"/>
+      <c r="T65" s="38"/>
+      <c r="U65" s="89"/>
+      <c r="V65" s="44"/>
+      <c r="W65" s="38"/>
+    </row>
+    <row r="66" spans="1:23" ht="18" customHeight="1">
+      <c r="A66" s="13"/>
+      <c r="B66" s="38"/>
+      <c r="C66" s="88"/>
+      <c r="D66" s="38"/>
+      <c r="E66" s="75"/>
+      <c r="F66" s="73"/>
+      <c r="G66" s="74"/>
+      <c r="H66" s="44"/>
+      <c r="I66" s="38"/>
+      <c r="J66" s="38"/>
+      <c r="K66" s="73"/>
+      <c r="L66" s="73"/>
+      <c r="M66" s="73"/>
+      <c r="N66" s="38"/>
+      <c r="O66" s="38"/>
+      <c r="P66" s="38"/>
+      <c r="Q66" s="38"/>
+      <c r="R66" s="38"/>
+      <c r="S66" s="44"/>
+      <c r="T66" s="38"/>
+      <c r="U66" s="89"/>
+      <c r="V66" s="44"/>
+      <c r="W66" s="38"/>
+    </row>
+    <row r="67" spans="1:23" ht="18" customHeight="1">
+      <c r="A67" s="13"/>
+      <c r="B67" s="38"/>
+      <c r="C67" s="88"/>
+      <c r="D67" s="38"/>
+      <c r="E67" s="75" t="s">
+        <v>65</v>
+      </c>
+      <c r="F67" s="73"/>
+      <c r="G67" s="74"/>
+      <c r="H67" s="44"/>
+      <c r="I67" s="38"/>
+      <c r="J67" s="38"/>
+      <c r="K67" s="204" t="s">
+        <v>79</v>
+      </c>
+      <c r="L67" s="204"/>
+      <c r="M67" s="204"/>
+      <c r="N67" s="38"/>
+      <c r="O67" s="38"/>
+      <c r="P67" s="38"/>
+      <c r="Q67" s="38"/>
+      <c r="R67" s="38"/>
+      <c r="S67" s="44"/>
+      <c r="T67" s="38"/>
+      <c r="U67" s="89"/>
+      <c r="V67" s="44"/>
+      <c r="W67" s="38"/>
+    </row>
+    <row r="68" spans="1:23" ht="18" customHeight="1">
+      <c r="A68" s="13"/>
+      <c r="B68" s="38"/>
+      <c r="C68" s="88"/>
+      <c r="D68" s="38"/>
+      <c r="E68" s="75"/>
+      <c r="F68" s="73"/>
+      <c r="G68" s="74"/>
+      <c r="H68" s="44"/>
+      <c r="I68" s="38"/>
+      <c r="J68" s="38"/>
+      <c r="K68" s="73"/>
+      <c r="L68" s="73"/>
+      <c r="M68" s="73"/>
+      <c r="N68" s="38"/>
+      <c r="O68" s="38"/>
+      <c r="P68" s="38"/>
+      <c r="Q68" s="38"/>
+      <c r="R68" s="38"/>
+      <c r="S68" s="44"/>
+      <c r="T68" s="38"/>
+      <c r="U68" s="89"/>
+      <c r="V68" s="44"/>
+      <c r="W68" s="38"/>
+    </row>
+    <row r="69" spans="1:23" ht="18" customHeight="1">
+      <c r="A69" s="13"/>
+      <c r="B69" s="38"/>
+      <c r="C69" s="88"/>
+      <c r="D69" s="38"/>
+      <c r="E69" s="73" t="s">
+        <v>66</v>
+      </c>
+      <c r="F69" s="73"/>
+      <c r="G69" s="74"/>
+      <c r="H69" s="44"/>
+      <c r="I69" s="38"/>
+      <c r="J69" s="38"/>
+      <c r="K69" s="73" t="s">
+        <v>80</v>
+      </c>
+      <c r="L69" s="73"/>
+      <c r="M69" s="73"/>
+      <c r="N69" s="38"/>
+      <c r="O69" s="38"/>
+      <c r="P69" s="38"/>
+      <c r="Q69" s="38"/>
+      <c r="R69" s="38"/>
+      <c r="S69" s="44"/>
+      <c r="T69" s="38"/>
+      <c r="U69" s="89"/>
+      <c r="V69" s="44"/>
+      <c r="W69" s="38"/>
+    </row>
+    <row r="70" spans="1:23" ht="18" customHeight="1">
+      <c r="A70" s="13"/>
+      <c r="B70" s="38"/>
+      <c r="C70" s="88"/>
+      <c r="D70" s="38"/>
+      <c r="E70" s="38"/>
+      <c r="F70" s="38"/>
+      <c r="G70" s="44"/>
+      <c r="H70" s="44"/>
+      <c r="I70" s="38"/>
+      <c r="J70" s="38"/>
+      <c r="K70" s="73"/>
+      <c r="L70" s="73"/>
+      <c r="M70" s="73"/>
+      <c r="N70" s="38"/>
+      <c r="O70" s="38"/>
+      <c r="P70" s="38"/>
+      <c r="Q70" s="38"/>
+      <c r="R70" s="38"/>
+      <c r="S70" s="44"/>
+      <c r="T70" s="38"/>
+      <c r="U70" s="89"/>
+      <c r="V70" s="44"/>
+      <c r="W70" s="38"/>
+    </row>
+    <row r="71" spans="1:23" ht="18" customHeight="1">
+      <c r="A71" s="13"/>
+      <c r="B71" s="38"/>
+      <c r="C71" s="88"/>
+      <c r="D71" s="38"/>
+      <c r="F71" s="38"/>
+      <c r="G71" s="44"/>
+      <c r="H71" s="44"/>
+      <c r="I71" s="38"/>
+      <c r="J71" s="38"/>
+      <c r="K71" s="73"/>
+      <c r="L71" s="73"/>
+      <c r="M71" s="73"/>
+      <c r="N71" s="38"/>
+      <c r="O71" s="38"/>
+      <c r="P71" s="38"/>
+      <c r="Q71" s="38"/>
+      <c r="R71" s="38"/>
+      <c r="S71" s="44"/>
+      <c r="T71" s="38"/>
+      <c r="U71" s="89"/>
+      <c r="V71" s="44"/>
+      <c r="W71" s="38"/>
+    </row>
+    <row r="72" spans="1:23" ht="18" customHeight="1">
+      <c r="A72" s="13"/>
+      <c r="B72" s="38"/>
+      <c r="C72" s="88"/>
+      <c r="D72" s="38"/>
+      <c r="E72" s="38"/>
+      <c r="F72" s="38"/>
+      <c r="G72" s="44"/>
+      <c r="H72" s="44"/>
+      <c r="I72" s="38"/>
+      <c r="J72" s="38"/>
+      <c r="K72" s="73"/>
+      <c r="L72" s="73"/>
+      <c r="M72" s="73"/>
+      <c r="N72" s="38"/>
+      <c r="O72" s="38"/>
+      <c r="P72" s="38"/>
+      <c r="Q72" s="38"/>
+      <c r="R72" s="38"/>
+      <c r="S72" s="44"/>
+      <c r="T72" s="38"/>
+      <c r="U72" s="89"/>
+      <c r="V72" s="44"/>
+      <c r="W72" s="38"/>
+    </row>
+    <row r="73" spans="1:23" ht="18" customHeight="1">
+      <c r="A73" s="13"/>
+      <c r="B73" s="13"/>
+      <c r="C73" s="93"/>
+      <c r="D73" s="13"/>
+      <c r="E73" s="13"/>
+      <c r="F73" s="13"/>
+      <c r="G73" s="13"/>
+      <c r="H73" s="13"/>
+      <c r="I73" s="13"/>
+      <c r="J73" s="13"/>
+      <c r="K73" s="13"/>
+      <c r="L73" s="13"/>
+      <c r="M73" s="13"/>
+      <c r="N73" s="13"/>
+      <c r="O73" s="13"/>
+      <c r="P73" s="13"/>
+      <c r="Q73" s="13"/>
+      <c r="R73" s="13"/>
+      <c r="S73" s="13"/>
+      <c r="T73" s="13"/>
+      <c r="U73" s="94"/>
+      <c r="V73" s="13"/>
+      <c r="W73" s="13"/>
+    </row>
+    <row r="74" spans="1:23" ht="18" customHeight="1" thickBot="1">
+      <c r="A74" s="13"/>
+      <c r="B74" s="13"/>
+      <c r="C74" s="95"/>
+      <c r="D74" s="96"/>
+      <c r="E74" s="96"/>
+      <c r="F74" s="96"/>
+      <c r="G74" s="96"/>
+      <c r="H74" s="96"/>
+      <c r="I74" s="96"/>
+      <c r="J74" s="96"/>
+      <c r="K74" s="96"/>
+      <c r="L74" s="96"/>
+      <c r="M74" s="96"/>
+      <c r="N74" s="96"/>
+      <c r="O74" s="96"/>
+      <c r="P74" s="96"/>
+      <c r="Q74" s="96"/>
+      <c r="R74" s="96"/>
+      <c r="S74" s="96"/>
+      <c r="T74" s="96"/>
+      <c r="U74" s="97"/>
+      <c r="V74" s="13"/>
+      <c r="W74" s="13"/>
+    </row>
+    <row r="75" spans="1:23" ht="18" customHeight="1">
+      <c r="A75" s="13"/>
+      <c r="B75" s="13"/>
+      <c r="C75" s="13"/>
+      <c r="D75" s="13"/>
+      <c r="E75" s="13"/>
+      <c r="F75" s="13"/>
+      <c r="G75" s="13"/>
+      <c r="H75" s="13"/>
+      <c r="I75" s="13"/>
+      <c r="J75" s="13"/>
+      <c r="K75" s="13"/>
+      <c r="L75" s="13"/>
+      <c r="M75" s="13"/>
+      <c r="N75" s="13"/>
+      <c r="O75" s="13"/>
+      <c r="P75" s="13"/>
+      <c r="Q75" s="13"/>
+      <c r="R75" s="13"/>
+      <c r="S75" s="13"/>
+      <c r="T75" s="13"/>
+      <c r="U75" s="13"/>
+      <c r="V75" s="13"/>
+      <c r="W75" s="13"/>
+    </row>
+    <row r="76" spans="1:23" ht="18" customHeight="1">
+      <c r="A76" s="66"/>
+      <c r="B76" s="68"/>
+      <c r="C76" s="68"/>
+      <c r="D76" s="68"/>
+      <c r="E76" s="69"/>
+      <c r="F76" s="69"/>
+      <c r="G76" s="68"/>
+      <c r="H76" s="68"/>
+      <c r="I76" s="68"/>
+      <c r="J76" s="68"/>
+      <c r="K76" s="79"/>
+      <c r="L76" s="79"/>
+      <c r="M76" s="79"/>
+      <c r="N76" s="68"/>
+      <c r="O76" s="68"/>
+      <c r="P76" s="68"/>
+      <c r="Q76" s="68"/>
+      <c r="R76" s="68"/>
+      <c r="S76" s="70"/>
+      <c r="T76" s="70"/>
+      <c r="U76" s="70"/>
+      <c r="V76" s="70"/>
+      <c r="W76" s="70"/>
+    </row>
+    <row r="77" spans="1:23" ht="18" customHeight="1">
+      <c r="A77" s="71"/>
+      <c r="B77" s="72"/>
+      <c r="C77" s="72"/>
+      <c r="D77" s="72"/>
+      <c r="E77" s="72"/>
+      <c r="F77" s="72"/>
+      <c r="G77" s="72"/>
+      <c r="H77" s="72"/>
+      <c r="I77" s="72"/>
+      <c r="J77" s="72"/>
+      <c r="K77" s="80"/>
+      <c r="L77" s="80"/>
+      <c r="M77" s="80"/>
+      <c r="N77" s="72"/>
+      <c r="O77" s="72"/>
+      <c r="P77" s="72"/>
+      <c r="Q77" s="72"/>
+      <c r="R77" s="72"/>
+      <c r="S77" s="72"/>
+      <c r="T77" s="72"/>
+      <c r="U77" s="72"/>
+      <c r="V77" s="72"/>
+      <c r="W77" s="72"/>
+    </row>
+    <row r="78" spans="1:23" ht="12.75" customHeight="1">
+      <c r="A78" s="64"/>
+      <c r="B78" s="65"/>
+      <c r="C78" s="65"/>
+      <c r="D78" s="65"/>
+      <c r="E78" s="65"/>
+      <c r="F78" s="65"/>
+      <c r="G78" s="65"/>
+      <c r="H78" s="65"/>
+      <c r="I78" s="65"/>
+      <c r="J78" s="65"/>
+      <c r="K78" s="77"/>
+      <c r="L78" s="77"/>
+      <c r="M78" s="77"/>
+      <c r="N78" s="65"/>
+      <c r="O78" s="65"/>
+      <c r="P78" s="65"/>
+      <c r="Q78" s="65"/>
+      <c r="R78" s="65"/>
+      <c r="S78" s="65"/>
+      <c r="T78" s="65"/>
+      <c r="U78" s="65"/>
+      <c r="V78" s="65"/>
+      <c r="W78" s="65"/>
+    </row>
+    <row r="79" spans="1:23" ht="12.75" customHeight="1">
+      <c r="A79" s="66"/>
+      <c r="B79" s="67"/>
+      <c r="C79" s="67"/>
+      <c r="D79" s="67"/>
+      <c r="E79" s="67"/>
+      <c r="F79" s="67"/>
+      <c r="G79" s="67"/>
+      <c r="H79" s="67"/>
+      <c r="I79" s="67"/>
+      <c r="J79" s="67"/>
+      <c r="K79" s="78"/>
+      <c r="L79" s="78"/>
+      <c r="M79" s="78"/>
+      <c r="N79" s="67"/>
+      <c r="O79" s="67"/>
+      <c r="P79" s="67"/>
+      <c r="Q79" s="67"/>
+      <c r="R79" s="67"/>
+      <c r="S79" s="67"/>
+      <c r="T79" s="67"/>
+      <c r="U79" s="67"/>
+      <c r="V79" s="67"/>
+      <c r="W79" s="67"/>
+    </row>
+    <row r="80" spans="1:23" ht="12.75" customHeight="1">
+      <c r="A80" s="16"/>
+      <c r="B80" s="73" t="s">
+        <v>142</v>
+      </c>
+      <c r="C80" s="38"/>
+      <c r="D80" s="38"/>
+      <c r="E80" s="38"/>
+      <c r="F80" s="38"/>
+      <c r="G80" s="38"/>
+      <c r="H80" s="38"/>
+      <c r="I80" s="38"/>
+      <c r="J80" s="38"/>
+      <c r="K80" s="73"/>
+      <c r="L80" s="73"/>
+      <c r="M80" s="73"/>
+      <c r="N80" s="38"/>
+      <c r="O80" s="38"/>
+      <c r="P80" s="38"/>
+      <c r="Q80" s="38"/>
+      <c r="R80" s="38"/>
+      <c r="S80" s="38"/>
+      <c r="T80" s="38"/>
+      <c r="U80" s="38"/>
+      <c r="V80" s="38"/>
+      <c r="W80" s="38"/>
+    </row>
+    <row r="81" spans="1:23" ht="12.75" customHeight="1">
+      <c r="A81" s="13"/>
+      <c r="B81" s="38"/>
+      <c r="C81" s="38"/>
+      <c r="D81" s="38"/>
+      <c r="E81" s="38"/>
+      <c r="F81" s="38"/>
+      <c r="G81" s="38"/>
+      <c r="H81" s="38"/>
+      <c r="I81" s="38"/>
+      <c r="J81" s="42"/>
+      <c r="K81" s="73"/>
+      <c r="L81" s="73"/>
+      <c r="M81" s="73"/>
+      <c r="N81" s="38"/>
+      <c r="O81" s="38"/>
+      <c r="P81" s="38"/>
+      <c r="Q81" s="38"/>
+      <c r="R81" s="38"/>
+      <c r="S81" s="38"/>
+      <c r="T81" s="38"/>
+      <c r="U81" s="42"/>
+      <c r="V81" s="42"/>
+      <c r="W81" s="38"/>
+    </row>
+    <row r="82" spans="1:23" ht="18" customHeight="1">
+      <c r="A82" s="13"/>
+      <c r="B82" s="38"/>
+      <c r="C82" s="38"/>
+      <c r="D82" s="38"/>
+      <c r="E82" s="38"/>
+      <c r="F82" s="38"/>
+      <c r="G82" s="38"/>
+      <c r="H82" s="38"/>
+      <c r="I82" s="38"/>
+      <c r="J82" s="38"/>
+      <c r="K82" s="73"/>
+      <c r="L82" s="73"/>
+      <c r="M82" s="73"/>
+      <c r="N82" s="38"/>
+      <c r="O82" s="38"/>
+      <c r="P82" s="38"/>
+      <c r="Q82" s="38"/>
+      <c r="R82" s="38"/>
+      <c r="S82" s="38"/>
+      <c r="T82" s="38"/>
+      <c r="U82" s="38"/>
+      <c r="V82" s="38"/>
+      <c r="W82" s="38"/>
+    </row>
+    <row r="83" spans="1:23" ht="18" customHeight="1">
+      <c r="A83" s="13"/>
+      <c r="B83" s="38"/>
+      <c r="C83" s="38"/>
+      <c r="D83" s="38"/>
+      <c r="E83" s="38"/>
+      <c r="F83" s="38"/>
+      <c r="G83" s="38"/>
+      <c r="H83" s="38"/>
+      <c r="I83" s="42"/>
+      <c r="J83" s="42"/>
+      <c r="K83" s="73"/>
+      <c r="L83" s="73"/>
+      <c r="M83" s="76"/>
+      <c r="N83" s="38"/>
+      <c r="O83" s="38"/>
+      <c r="P83" s="38"/>
+      <c r="Q83" s="38"/>
+      <c r="R83" s="38"/>
+      <c r="S83" s="38"/>
+      <c r="T83" s="38"/>
+      <c r="U83" s="38"/>
+      <c r="V83" s="38"/>
+      <c r="W83" s="38"/>
+    </row>
+    <row r="84" spans="1:23" ht="18" customHeight="1">
+      <c r="A84" s="13"/>
+      <c r="B84" s="38"/>
+      <c r="C84" s="38"/>
+      <c r="D84" s="38"/>
+      <c r="E84" s="73"/>
+      <c r="F84" s="44"/>
+      <c r="G84" s="38"/>
+      <c r="H84" s="38"/>
+      <c r="I84" s="38"/>
+      <c r="J84" s="38"/>
+      <c r="K84" s="73"/>
+      <c r="L84" s="73"/>
+      <c r="M84" s="73"/>
+      <c r="N84" s="38"/>
+      <c r="O84" s="38"/>
+      <c r="P84" s="38"/>
+      <c r="Q84" s="38"/>
+      <c r="R84" s="38"/>
+      <c r="S84" s="38"/>
+      <c r="T84" s="38"/>
+      <c r="U84" s="38"/>
+      <c r="V84" s="38"/>
+      <c r="W84" s="38"/>
+    </row>
+    <row r="85" spans="1:23" ht="18" customHeight="1">
+      <c r="A85" s="13"/>
+      <c r="B85" s="38"/>
+      <c r="C85" s="38"/>
+      <c r="D85" s="38"/>
+      <c r="E85" s="73"/>
+      <c r="F85" s="74"/>
+      <c r="G85" s="73"/>
+      <c r="H85" s="38"/>
+      <c r="I85" s="38"/>
+      <c r="J85" s="38"/>
+      <c r="K85" s="73"/>
+      <c r="L85" s="73"/>
+      <c r="M85" s="73"/>
+      <c r="N85" s="38"/>
+      <c r="O85" s="38"/>
+      <c r="P85" s="38"/>
+      <c r="Q85" s="38"/>
+      <c r="R85" s="38"/>
+      <c r="S85" s="38"/>
+      <c r="T85" s="38"/>
+      <c r="U85" s="38"/>
+      <c r="V85" s="38"/>
+      <c r="W85" s="38"/>
+    </row>
+    <row r="86" spans="1:23" ht="18" customHeight="1">
+      <c r="A86" s="13"/>
+      <c r="B86" s="38"/>
+      <c r="C86" s="38"/>
+      <c r="D86" s="38"/>
+      <c r="E86" s="73"/>
+      <c r="F86" s="73"/>
+      <c r="G86" s="73"/>
+      <c r="H86" s="38"/>
+      <c r="I86" s="38"/>
+      <c r="J86" s="38"/>
+      <c r="K86" s="73"/>
+      <c r="L86" s="73"/>
+      <c r="M86" s="73"/>
+      <c r="N86" s="38"/>
+      <c r="O86" s="63"/>
+      <c r="P86" s="63"/>
+      <c r="Q86" s="38"/>
+      <c r="R86" s="63"/>
+      <c r="S86" s="38"/>
+      <c r="T86" s="63"/>
+      <c r="U86" s="63"/>
+      <c r="V86" s="38"/>
+      <c r="W86" s="63"/>
+    </row>
+    <row r="87" spans="1:23" ht="18" customHeight="1">
+      <c r="A87" s="13"/>
+      <c r="B87" s="62"/>
+      <c r="C87" s="62"/>
+      <c r="D87" s="38"/>
+      <c r="E87" s="75"/>
+      <c r="F87" s="73"/>
+      <c r="G87" s="73"/>
+      <c r="H87" s="44"/>
+      <c r="I87" s="44"/>
+      <c r="J87" s="44"/>
+      <c r="K87" s="73"/>
+      <c r="L87" s="73"/>
+      <c r="M87" s="73"/>
+      <c r="N87" s="38"/>
+      <c r="O87" s="38"/>
+      <c r="P87" s="38"/>
+      <c r="Q87" s="38"/>
+      <c r="R87" s="38"/>
+      <c r="S87" s="44"/>
+      <c r="T87" s="44"/>
+      <c r="U87" s="44"/>
+      <c r="V87" s="44"/>
+      <c r="W87" s="44"/>
+    </row>
+    <row r="88" spans="1:23" ht="18" customHeight="1">
+      <c r="A88" s="13"/>
+      <c r="B88" s="38"/>
+      <c r="C88" s="38"/>
+      <c r="D88" s="38"/>
+      <c r="E88" s="73"/>
+      <c r="F88" s="73"/>
+      <c r="G88" s="73"/>
+      <c r="H88" s="44"/>
+      <c r="I88" s="38"/>
+      <c r="J88" s="38"/>
+      <c r="K88" s="73"/>
+      <c r="L88" s="73"/>
+      <c r="M88" s="73"/>
+      <c r="N88" s="38"/>
+      <c r="O88" s="38"/>
+      <c r="P88" s="38"/>
+      <c r="Q88" s="38"/>
+      <c r="R88" s="38"/>
+      <c r="S88" s="44"/>
+      <c r="T88" s="38"/>
+      <c r="U88" s="38"/>
+      <c r="V88" s="44"/>
+      <c r="W88" s="38"/>
+    </row>
+    <row r="89" spans="1:23" ht="18" customHeight="1">
+      <c r="A89" s="13"/>
+      <c r="B89" s="38"/>
+      <c r="C89" s="38"/>
+      <c r="D89" s="38"/>
+      <c r="E89" s="73"/>
+      <c r="F89" s="73"/>
+      <c r="G89" s="73"/>
+      <c r="H89" s="44"/>
+      <c r="I89" s="38"/>
+      <c r="J89" s="38"/>
+      <c r="K89" s="73"/>
+      <c r="L89" s="73"/>
+      <c r="M89" s="73"/>
+      <c r="N89" s="38"/>
+      <c r="O89" s="38"/>
+      <c r="P89" s="38"/>
+      <c r="Q89" s="38"/>
+      <c r="R89" s="38"/>
+      <c r="S89" s="44"/>
+      <c r="T89" s="38"/>
+      <c r="U89" s="38"/>
+      <c r="V89" s="44"/>
+      <c r="W89" s="38"/>
+    </row>
+    <row r="90" spans="1:23" ht="18" customHeight="1">
+      <c r="A90" s="13"/>
+      <c r="B90" s="38"/>
+      <c r="C90" s="38"/>
+      <c r="D90" s="38"/>
+      <c r="E90" s="73"/>
+      <c r="F90" s="73"/>
+      <c r="G90" s="73"/>
+      <c r="H90" s="44"/>
+      <c r="I90" s="38"/>
+      <c r="J90" s="38"/>
+      <c r="K90" s="73"/>
+      <c r="L90" s="73"/>
+      <c r="M90" s="73"/>
+      <c r="N90" s="38"/>
+      <c r="O90" s="38"/>
+      <c r="P90" s="38"/>
+      <c r="Q90" s="38"/>
+      <c r="R90" s="38"/>
+      <c r="S90" s="44"/>
+      <c r="T90" s="38"/>
+      <c r="U90" s="38"/>
+      <c r="V90" s="44"/>
+      <c r="W90" s="38"/>
+    </row>
+    <row r="91" spans="1:23" ht="18" customHeight="1">
+      <c r="A91" s="13"/>
+      <c r="B91" s="38"/>
+      <c r="C91" s="38"/>
+      <c r="D91" s="38"/>
+      <c r="E91" s="73"/>
+      <c r="F91" s="73"/>
+      <c r="G91" s="73"/>
+      <c r="H91" s="44"/>
+      <c r="I91" s="38"/>
+      <c r="J91" s="38"/>
+      <c r="K91" s="73"/>
+      <c r="L91" s="73"/>
+      <c r="M91" s="73"/>
+      <c r="N91" s="38"/>
+      <c r="O91" s="38"/>
+      <c r="P91" s="38"/>
+      <c r="Q91" s="38"/>
+      <c r="R91" s="38"/>
+      <c r="S91" s="44"/>
+      <c r="T91" s="38"/>
+      <c r="U91" s="38"/>
+      <c r="V91" s="44"/>
+      <c r="W91" s="38"/>
+    </row>
+    <row r="92" spans="1:23" ht="18" customHeight="1">
+      <c r="A92" s="13"/>
+      <c r="B92" s="38"/>
+      <c r="C92" s="38"/>
+      <c r="D92" s="38"/>
+      <c r="E92" s="73"/>
+      <c r="F92" s="73"/>
+      <c r="G92" s="73"/>
+      <c r="H92" s="205" t="s">
+        <v>143</v>
+      </c>
+      <c r="I92" s="205"/>
+      <c r="J92" s="205"/>
+      <c r="K92" s="205"/>
+      <c r="L92" s="205"/>
+      <c r="M92" s="205"/>
+      <c r="N92" s="205"/>
+      <c r="O92" s="205"/>
+      <c r="P92" s="205"/>
+      <c r="Q92" s="38"/>
+      <c r="R92" s="38"/>
+      <c r="S92" s="44"/>
+      <c r="T92" s="38"/>
+      <c r="U92" s="38"/>
+      <c r="V92" s="44"/>
+      <c r="W92" s="38"/>
+    </row>
+    <row r="93" spans="1:23" ht="18" customHeight="1">
+      <c r="A93" s="13"/>
+      <c r="B93" s="38"/>
+      <c r="C93" s="38"/>
+      <c r="D93" s="38"/>
+      <c r="E93" s="73"/>
+      <c r="F93" s="73"/>
+      <c r="G93" s="73"/>
+      <c r="H93" s="205"/>
+      <c r="I93" s="205"/>
+      <c r="J93" s="205"/>
+      <c r="K93" s="205"/>
+      <c r="L93" s="205"/>
+      <c r="M93" s="205"/>
+      <c r="N93" s="205"/>
+      <c r="O93" s="205"/>
+      <c r="P93" s="205"/>
+      <c r="Q93" s="38"/>
+      <c r="R93" s="38"/>
+      <c r="S93" s="44"/>
+      <c r="T93" s="38"/>
+      <c r="U93" s="38"/>
+      <c r="V93" s="44"/>
+      <c r="W93" s="38"/>
+    </row>
+    <row r="94" spans="1:23" ht="18" customHeight="1">
+      <c r="A94" s="13"/>
+      <c r="B94" s="38"/>
+      <c r="C94" s="38"/>
+      <c r="D94" s="38"/>
+      <c r="E94" s="73"/>
+      <c r="F94" s="73"/>
+      <c r="G94" s="73"/>
+      <c r="H94" s="205"/>
+      <c r="I94" s="205"/>
+      <c r="J94" s="205"/>
+      <c r="K94" s="205"/>
+      <c r="L94" s="205"/>
+      <c r="M94" s="205"/>
+      <c r="N94" s="205"/>
+      <c r="O94" s="205"/>
+      <c r="P94" s="205"/>
+      <c r="Q94" s="38"/>
+      <c r="R94" s="38"/>
+      <c r="S94" s="44"/>
+      <c r="T94" s="38"/>
+      <c r="U94" s="38"/>
+      <c r="V94" s="44"/>
+      <c r="W94" s="38"/>
+    </row>
+    <row r="95" spans="1:23" ht="18" customHeight="1">
+      <c r="A95" s="13"/>
+      <c r="B95" s="38"/>
+      <c r="C95" s="38"/>
+      <c r="D95" s="38"/>
+      <c r="E95" s="73"/>
+      <c r="F95" s="73"/>
+      <c r="G95" s="73"/>
+      <c r="H95" s="44"/>
+      <c r="I95" s="38"/>
+      <c r="J95" s="38"/>
+      <c r="K95" s="73"/>
+      <c r="L95" s="73"/>
+      <c r="M95" s="73"/>
+      <c r="N95" s="38"/>
+      <c r="O95" s="38"/>
+      <c r="P95" s="38"/>
+      <c r="Q95" s="38"/>
+      <c r="R95" s="38"/>
+      <c r="S95" s="44"/>
+      <c r="T95" s="38"/>
+      <c r="U95" s="38"/>
+      <c r="V95" s="44"/>
+      <c r="W95" s="38"/>
+    </row>
+    <row r="96" spans="1:23" ht="18" customHeight="1">
+      <c r="A96" s="13"/>
+      <c r="B96" s="38"/>
+      <c r="C96" s="38"/>
+      <c r="D96" s="38"/>
+      <c r="E96" s="73"/>
+      <c r="F96" s="73"/>
+      <c r="G96" s="73"/>
+      <c r="H96" s="44"/>
+      <c r="I96" s="38"/>
+      <c r="J96" s="38"/>
+      <c r="K96" s="76"/>
+      <c r="L96" s="76"/>
+      <c r="M96" s="73"/>
+      <c r="N96" s="38"/>
+      <c r="O96" s="76"/>
+      <c r="P96" s="76"/>
+      <c r="Q96" s="38"/>
+      <c r="R96" s="38"/>
+      <c r="S96" s="44"/>
+      <c r="T96" s="38"/>
+      <c r="U96" s="38"/>
+      <c r="V96" s="44"/>
+      <c r="W96" s="38"/>
+    </row>
+    <row r="97" spans="1:23" ht="18" customHeight="1">
+      <c r="A97" s="13"/>
+      <c r="B97" s="38"/>
+      <c r="C97" s="38"/>
+      <c r="D97" s="38"/>
+      <c r="E97" s="73"/>
+      <c r="F97" s="73"/>
+      <c r="G97" s="74"/>
+      <c r="H97" s="44"/>
+      <c r="I97" s="38"/>
+      <c r="J97" s="38"/>
+      <c r="K97" s="73"/>
+      <c r="L97" s="73"/>
+      <c r="M97" s="73"/>
+      <c r="N97" s="38"/>
+      <c r="O97" s="38"/>
+      <c r="P97" s="38"/>
+      <c r="Q97" s="38"/>
+      <c r="R97" s="38"/>
+      <c r="S97" s="44"/>
+      <c r="T97" s="38"/>
+      <c r="U97" s="38"/>
+      <c r="V97" s="44"/>
+      <c r="W97" s="38"/>
+    </row>
+    <row r="98" spans="1:23" ht="18" customHeight="1">
+      <c r="A98" s="13"/>
+      <c r="B98" s="38"/>
+      <c r="C98" s="38"/>
+      <c r="D98" s="38"/>
+      <c r="E98" s="73"/>
+      <c r="F98" s="73"/>
+      <c r="G98" s="74"/>
+      <c r="H98" s="44"/>
+      <c r="I98" s="38"/>
+      <c r="J98" s="38"/>
+      <c r="K98" s="203"/>
+      <c r="L98" s="203"/>
+      <c r="M98" s="203"/>
+      <c r="N98" s="203"/>
+      <c r="O98" s="38"/>
+      <c r="P98" s="38"/>
+      <c r="Q98" s="38"/>
+      <c r="R98" s="38"/>
+      <c r="S98" s="44"/>
+      <c r="T98" s="38"/>
+      <c r="U98" s="38"/>
+      <c r="V98" s="44"/>
+      <c r="W98" s="38"/>
+    </row>
+    <row r="99" spans="1:23" ht="18" customHeight="1">
+      <c r="A99" s="13"/>
+      <c r="B99" s="38"/>
+      <c r="C99" s="38"/>
+      <c r="D99" s="38"/>
+      <c r="E99" s="75"/>
+      <c r="F99" s="73"/>
+      <c r="G99" s="74"/>
+      <c r="H99" s="44"/>
+      <c r="I99" s="38"/>
+      <c r="J99" s="38"/>
+      <c r="K99" s="73"/>
+      <c r="L99" s="73"/>
+      <c r="M99" s="73"/>
+      <c r="N99" s="38"/>
+      <c r="O99" s="38"/>
+      <c r="P99" s="38"/>
+      <c r="Q99" s="38"/>
+      <c r="R99" s="38"/>
+      <c r="S99" s="44"/>
+      <c r="T99" s="38"/>
+      <c r="U99" s="38"/>
+      <c r="V99" s="44"/>
+      <c r="W99" s="38"/>
+    </row>
+    <row r="100" spans="1:23" ht="18" customHeight="1">
+      <c r="A100" s="13"/>
+      <c r="B100" s="38"/>
+      <c r="C100" s="38"/>
+      <c r="D100" s="38"/>
+      <c r="E100" s="73"/>
+      <c r="F100" s="73"/>
+      <c r="G100" s="74"/>
+      <c r="H100" s="44"/>
+      <c r="I100" s="38"/>
+      <c r="J100" s="38"/>
+      <c r="K100" s="73"/>
+      <c r="L100" s="73"/>
+      <c r="M100" s="73"/>
+      <c r="N100" s="38"/>
+      <c r="O100" s="38"/>
+      <c r="P100" s="38"/>
+      <c r="Q100" s="38"/>
+      <c r="R100" s="38"/>
+      <c r="S100" s="44"/>
+      <c r="T100" s="38"/>
+      <c r="U100" s="38"/>
+      <c r="V100" s="44"/>
+      <c r="W100" s="38"/>
+    </row>
+    <row r="101" spans="1:23" ht="18" customHeight="1">
+      <c r="A101" s="13"/>
+      <c r="B101" s="38"/>
+      <c r="C101" s="38"/>
+      <c r="D101" s="38"/>
+      <c r="E101" s="73"/>
+      <c r="F101" s="73"/>
+      <c r="G101" s="74"/>
+      <c r="H101" s="44"/>
+      <c r="I101" s="38"/>
+      <c r="J101" s="38"/>
+      <c r="K101" s="73"/>
+      <c r="L101" s="73"/>
+      <c r="M101" s="73"/>
+      <c r="N101" s="38"/>
+      <c r="O101" s="38"/>
+      <c r="P101" s="38"/>
+      <c r="Q101" s="38"/>
+      <c r="R101" s="38"/>
+      <c r="S101" s="44"/>
+      <c r="T101" s="38"/>
+      <c r="U101" s="38"/>
+      <c r="V101" s="44"/>
+      <c r="W101" s="38"/>
+    </row>
+    <row r="102" spans="1:23" ht="18" customHeight="1">
+      <c r="A102" s="13"/>
+      <c r="B102" s="38"/>
+      <c r="C102" s="38"/>
+      <c r="D102" s="38"/>
+      <c r="E102" s="75"/>
+      <c r="F102" s="73"/>
+      <c r="G102" s="74"/>
+      <c r="H102" s="44"/>
+      <c r="I102" s="38"/>
+      <c r="J102" s="38"/>
+      <c r="K102" s="73"/>
+      <c r="L102" s="73"/>
+      <c r="M102" s="73"/>
+      <c r="N102" s="38"/>
+      <c r="O102" s="38"/>
+      <c r="P102" s="38"/>
+      <c r="Q102" s="38"/>
+      <c r="R102" s="38"/>
+      <c r="S102" s="44"/>
+      <c r="T102" s="38"/>
+      <c r="U102" s="38"/>
+      <c r="V102" s="44"/>
+      <c r="W102" s="38"/>
+    </row>
+    <row r="103" spans="1:23" ht="18" customHeight="1">
+      <c r="A103" s="13"/>
+      <c r="B103" s="38"/>
+      <c r="C103" s="38"/>
+      <c r="D103" s="38"/>
+      <c r="E103" s="75"/>
+      <c r="F103" s="73"/>
+      <c r="G103" s="74"/>
+      <c r="H103" s="44"/>
+      <c r="I103" s="38"/>
+      <c r="J103" s="38"/>
+      <c r="K103" s="73"/>
+      <c r="L103" s="73"/>
+      <c r="M103" s="73"/>
+      <c r="N103" s="38"/>
+      <c r="O103" s="38"/>
+      <c r="P103" s="38"/>
+      <c r="Q103" s="38"/>
+      <c r="R103" s="38"/>
+      <c r="S103" s="44"/>
+      <c r="T103" s="38"/>
+      <c r="U103" s="38"/>
+      <c r="V103" s="44"/>
+      <c r="W103" s="38"/>
+    </row>
+    <row r="104" spans="1:23" ht="18" customHeight="1">
+      <c r="A104" s="13"/>
+      <c r="B104" s="38"/>
+      <c r="C104" s="38"/>
+      <c r="D104" s="38"/>
+      <c r="E104" s="75"/>
+      <c r="F104" s="73"/>
+      <c r="G104" s="74"/>
+      <c r="H104" s="44"/>
+      <c r="I104" s="38"/>
+      <c r="J104" s="38"/>
+      <c r="K104" s="204"/>
+      <c r="L104" s="204"/>
+      <c r="M104" s="204"/>
+      <c r="N104" s="38"/>
+      <c r="O104" s="38"/>
+      <c r="P104" s="38"/>
+      <c r="Q104" s="38"/>
+      <c r="R104" s="38"/>
+      <c r="S104" s="44"/>
+      <c r="T104" s="38"/>
+      <c r="U104" s="38"/>
+      <c r="V104" s="44"/>
+      <c r="W104" s="38"/>
+    </row>
+    <row r="105" spans="1:23" ht="18" customHeight="1">
+      <c r="A105" s="13"/>
+      <c r="B105" s="38"/>
+      <c r="C105" s="38"/>
+      <c r="D105" s="38"/>
+      <c r="E105" s="75"/>
+      <c r="F105" s="73"/>
+      <c r="G105" s="74"/>
+      <c r="H105" s="44"/>
+      <c r="I105" s="38"/>
+      <c r="J105" s="38"/>
+      <c r="K105" s="73"/>
+      <c r="L105" s="73"/>
+      <c r="M105" s="73"/>
+      <c r="N105" s="38"/>
+      <c r="O105" s="38"/>
+      <c r="P105" s="38"/>
+      <c r="Q105" s="38"/>
+      <c r="R105" s="38"/>
+      <c r="S105" s="44"/>
+      <c r="T105" s="38"/>
+      <c r="U105" s="38"/>
+      <c r="V105" s="44"/>
+      <c r="W105" s="38"/>
+    </row>
+    <row r="106" spans="1:23" ht="18" customHeight="1">
+      <c r="A106" s="13"/>
+      <c r="B106" s="38"/>
+      <c r="C106" s="38"/>
+      <c r="D106" s="38"/>
+      <c r="E106" s="73"/>
+      <c r="F106" s="73"/>
+      <c r="G106" s="74"/>
+      <c r="H106" s="44"/>
+      <c r="I106" s="38"/>
+      <c r="J106" s="38"/>
+      <c r="K106" s="73"/>
+      <c r="L106" s="73"/>
+      <c r="M106" s="73"/>
+      <c r="N106" s="38"/>
+      <c r="O106" s="38"/>
+      <c r="P106" s="38"/>
+      <c r="Q106" s="38"/>
+      <c r="R106" s="38"/>
+      <c r="S106" s="44"/>
+      <c r="T106" s="38"/>
+      <c r="U106" s="38"/>
+      <c r="V106" s="44"/>
+      <c r="W106" s="38"/>
+    </row>
+    <row r="107" spans="1:23" ht="18" customHeight="1">
+      <c r="A107" s="13"/>
+      <c r="B107" s="38"/>
+      <c r="C107" s="38"/>
+      <c r="D107" s="38"/>
+      <c r="E107" s="38"/>
+      <c r="F107" s="38"/>
+      <c r="G107" s="44"/>
+      <c r="H107" s="44"/>
+      <c r="I107" s="38"/>
+      <c r="J107" s="38"/>
+      <c r="K107" s="73"/>
+      <c r="L107" s="73"/>
+      <c r="M107" s="73"/>
+      <c r="N107" s="38"/>
+      <c r="O107" s="38"/>
+      <c r="P107" s="38"/>
+      <c r="Q107" s="38"/>
+      <c r="R107" s="38"/>
+      <c r="S107" s="44"/>
+      <c r="T107" s="38"/>
+      <c r="U107" s="38"/>
+      <c r="V107" s="44"/>
+      <c r="W107" s="38"/>
+    </row>
+    <row r="108" spans="1:23" ht="18" customHeight="1">
+      <c r="A108" s="13"/>
+      <c r="B108" s="38"/>
+      <c r="C108" s="38"/>
+      <c r="D108" s="38"/>
+      <c r="F108" s="38"/>
+      <c r="G108" s="44"/>
+      <c r="H108" s="44"/>
+      <c r="I108" s="38"/>
+      <c r="J108" s="38"/>
+      <c r="K108" s="73"/>
+      <c r="L108" s="73"/>
+      <c r="M108" s="73"/>
+      <c r="N108" s="38"/>
+      <c r="O108" s="38"/>
+      <c r="P108" s="38"/>
+      <c r="Q108" s="38"/>
+      <c r="R108" s="38"/>
+      <c r="S108" s="44"/>
+      <c r="T108" s="38"/>
+      <c r="U108" s="38"/>
+      <c r="V108" s="44"/>
+      <c r="W108" s="38"/>
+    </row>
+    <row r="109" spans="1:23" ht="18" customHeight="1">
+      <c r="A109" s="13"/>
+      <c r="B109" s="38"/>
+      <c r="C109" s="38"/>
+      <c r="D109" s="38"/>
+      <c r="E109" s="38"/>
+      <c r="F109" s="38"/>
+      <c r="G109" s="44"/>
+      <c r="H109" s="44"/>
+      <c r="I109" s="38"/>
+      <c r="J109" s="38"/>
+      <c r="K109" s="73"/>
+      <c r="L109" s="73"/>
+      <c r="M109" s="73"/>
+      <c r="N109" s="38"/>
+      <c r="O109" s="38"/>
+      <c r="P109" s="38"/>
+      <c r="Q109" s="38"/>
+      <c r="R109" s="38"/>
+      <c r="S109" s="44"/>
+      <c r="T109" s="38"/>
+      <c r="U109" s="38"/>
+      <c r="V109" s="44"/>
+      <c r="W109" s="38"/>
+    </row>
+    <row r="110" spans="1:23" ht="18" customHeight="1">
+      <c r="A110" s="13"/>
+      <c r="B110" s="13"/>
+      <c r="C110" s="13"/>
+      <c r="D110" s="13"/>
+      <c r="E110" s="13"/>
+      <c r="F110" s="13"/>
+      <c r="G110" s="13"/>
+      <c r="H110" s="13"/>
+      <c r="I110" s="13"/>
+      <c r="J110" s="13"/>
+      <c r="K110" s="13"/>
+      <c r="L110" s="13"/>
+      <c r="M110" s="13"/>
+      <c r="N110" s="13"/>
+      <c r="O110" s="13"/>
+      <c r="P110" s="13"/>
+      <c r="Q110" s="13"/>
+      <c r="R110" s="13"/>
+      <c r="S110" s="13"/>
+      <c r="T110" s="13"/>
+      <c r="U110" s="13"/>
+      <c r="V110" s="13"/>
+      <c r="W110" s="13"/>
+    </row>
+    <row r="111" spans="1:23" ht="18" customHeight="1">
+      <c r="A111" s="13"/>
+      <c r="B111" s="13"/>
+      <c r="C111" s="13"/>
+      <c r="D111" s="13"/>
+      <c r="E111" s="13"/>
+      <c r="F111" s="13"/>
+      <c r="G111" s="13"/>
+      <c r="H111" s="13"/>
+      <c r="I111" s="13"/>
+      <c r="J111" s="13"/>
+      <c r="K111" s="13"/>
+      <c r="L111" s="13"/>
+      <c r="M111" s="13"/>
+      <c r="N111" s="13"/>
+      <c r="O111" s="13"/>
+      <c r="P111" s="13"/>
+      <c r="Q111" s="13"/>
+      <c r="R111" s="13"/>
+      <c r="S111" s="13"/>
+      <c r="T111" s="13"/>
+      <c r="U111" s="13"/>
+      <c r="V111" s="13"/>
+      <c r="W111" s="13"/>
+    </row>
+    <row r="112" spans="1:23" ht="18" customHeight="1">
+      <c r="A112" s="13"/>
+      <c r="B112" s="13"/>
+      <c r="C112" s="13"/>
+      <c r="D112" s="13"/>
+      <c r="E112" s="13"/>
+      <c r="F112" s="13"/>
+      <c r="G112" s="13"/>
+      <c r="H112" s="13"/>
+      <c r="I112" s="13"/>
+      <c r="J112" s="13"/>
+      <c r="K112" s="13"/>
+      <c r="L112" s="13"/>
+      <c r="M112" s="13"/>
+      <c r="N112" s="13"/>
+      <c r="O112" s="13"/>
+      <c r="P112" s="13"/>
+      <c r="Q112" s="13"/>
+      <c r="R112" s="13"/>
+      <c r="S112" s="13"/>
+      <c r="T112" s="13"/>
+      <c r="U112" s="13"/>
+      <c r="V112" s="13"/>
+      <c r="W112" s="13"/>
+    </row>
+    <row r="113" spans="1:23" ht="18" customHeight="1">
+      <c r="A113" s="66"/>
+      <c r="B113" s="68"/>
+      <c r="C113" s="68"/>
+      <c r="D113" s="68"/>
+      <c r="E113" s="69"/>
+      <c r="F113" s="69"/>
+      <c r="G113" s="68"/>
+      <c r="H113" s="68"/>
+      <c r="I113" s="68"/>
+      <c r="J113" s="68"/>
+      <c r="K113" s="79"/>
+      <c r="L113" s="79"/>
+      <c r="M113" s="79"/>
+      <c r="N113" s="68"/>
+      <c r="O113" s="68"/>
+      <c r="P113" s="68"/>
+      <c r="Q113" s="68"/>
+      <c r="R113" s="68"/>
+      <c r="S113" s="70"/>
+      <c r="T113" s="70"/>
+      <c r="U113" s="70"/>
+      <c r="V113" s="70"/>
+      <c r="W113" s="70"/>
+    </row>
+    <row r="114" spans="1:23" ht="18" customHeight="1">
+      <c r="A114" s="71"/>
+      <c r="B114" s="72"/>
+      <c r="C114" s="72"/>
+      <c r="D114" s="72"/>
+      <c r="E114" s="72"/>
+      <c r="F114" s="72"/>
+      <c r="G114" s="72"/>
+      <c r="H114" s="72"/>
+      <c r="I114" s="72"/>
+      <c r="J114" s="72"/>
+      <c r="K114" s="80"/>
+      <c r="L114" s="80"/>
+      <c r="M114" s="80"/>
+      <c r="N114" s="72"/>
+      <c r="O114" s="72"/>
+      <c r="P114" s="72"/>
+      <c r="Q114" s="72"/>
+      <c r="R114" s="72"/>
+      <c r="S114" s="72"/>
+      <c r="T114" s="72"/>
+      <c r="U114" s="72"/>
+      <c r="V114" s="72"/>
+      <c r="W114" s="72"/>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="K61:N61"/>
+    <mergeCell ref="K67:M67"/>
+    <mergeCell ref="H92:P94"/>
+    <mergeCell ref="K98:N98"/>
+    <mergeCell ref="K104:M104"/>
+    <mergeCell ref="A1:W1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="G2:S2"/>
+    <mergeCell ref="T2:U2"/>
+    <mergeCell ref="V2:W2"/>
+    <mergeCell ref="G3:S3"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="V3:W3"/>
+  </mergeCells>
+  <phoneticPr fontId="4"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.59055118110236227" bottom="0.39370078740157483" header="0.51181102362204722" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <headerFooter alignWithMargins="0">
+    <oddFooter>&amp;LCopyright© 2005 System Integrator Corp.&amp;C&amp;P</oddFooter>
+  </headerFooter>
+  <rowBreaks count="2" manualBreakCount="2">
+    <brk id="40" max="22" man="1"/>
+    <brk id="77" max="22" man="1"/>
+  </rowBreaks>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>